--- a/output/Bonus_Plan_SIMPLE.xlsx
+++ b/output/Bonus_Plan_SIMPLE.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NB Bonus Examples" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWR Bonus Examples" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REN Bonus Examples" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent Examples - 100% Flip" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Combined Bonus Examples" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chargeback Process" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manual Tracker Template" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Data" sheetId="10" state="visible" r:id="rId10"/>
@@ -29,7 +29,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -97,8 +97,15 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F4E78"/>
-      <sz val="11"/>
+      <color rgb="00006100"/>
+    </font>
+    <font>
+      <color rgb="009C0006"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
     </font>
   </fonts>
   <fills count="14">
@@ -160,7 +167,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="0000B050"/>
       </patternFill>
     </fill>
     <fill>
@@ -239,7 +246,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -326,14 +333,23 @@
     <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="16" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -342,6 +358,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1038,12 +1057,12 @@
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6. Agent Examples - 100% Flip</t>
+          <t xml:space="preserve">  6. Combined Bonus Examples</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Per-agent month-by-month under the strongest behavior shift.</t>
+          <t>NB + RWR + REN side-by-side with the TOTAL BONUS per agent-month.</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1241,7 @@
       <c r="E5" s="16" t="n">
         <v>4938.26</v>
       </c>
-      <c r="F5" s="34" t="n">
+      <c r="F5" s="45" t="n">
         <v>0.1278963581240991</v>
       </c>
       <c r="G5" s="15" t="n">
@@ -1234,7 +1253,7 @@
       <c r="I5" s="16" t="n">
         <v>6186.16</v>
       </c>
-      <c r="J5" s="34" t="n">
+      <c r="J5" s="45" t="n">
         <v>0.224800043607028</v>
       </c>
       <c r="K5" s="15" t="n">
@@ -1246,7 +1265,7 @@
       <c r="M5" s="16" t="n">
         <v>1734.23</v>
       </c>
-      <c r="N5" s="34" t="n">
+      <c r="N5" s="45" t="n">
         <v>0.2280381328073636</v>
       </c>
     </row>
@@ -1270,7 +1289,7 @@
       <c r="E6" s="16" t="n">
         <v>3258.77</v>
       </c>
-      <c r="F6" s="34" t="n">
+      <c r="F6" s="45" t="n">
         <v>0.1284649347577561</v>
       </c>
       <c r="G6" s="15" t="n">
@@ -1282,7 +1301,7 @@
       <c r="I6" s="16" t="n">
         <v>4268.29</v>
       </c>
-      <c r="J6" s="34" t="n">
+      <c r="J6" s="45" t="n">
         <v>0.1392908657768495</v>
       </c>
       <c r="K6" s="15" t="n">
@@ -1294,7 +1313,7 @@
       <c r="M6" s="16" t="n">
         <v>1422.16</v>
       </c>
-      <c r="N6" s="34" t="n">
+      <c r="N6" s="45" t="n">
         <v>0.1891924970067846</v>
       </c>
     </row>
@@ -1318,7 +1337,7 @@
       <c r="E7" s="16" t="n">
         <v>6523.33</v>
       </c>
-      <c r="F7" s="34" t="n">
+      <c r="F7" s="45" t="n">
         <v>0.140216196720057</v>
       </c>
       <c r="G7" s="15" t="n">
@@ -1330,7 +1349,7 @@
       <c r="I7" s="16" t="n">
         <v>5844.85</v>
       </c>
-      <c r="J7" s="34" t="n">
+      <c r="J7" s="45" t="n">
         <v>0.2316847421078502</v>
       </c>
       <c r="K7" s="15" t="n">
@@ -1342,7 +1361,7 @@
       <c r="M7" s="16" t="n">
         <v>1274.08</v>
       </c>
-      <c r="N7" s="34" t="n">
+      <c r="N7" s="45" t="n">
         <v>0.3266034350166624</v>
       </c>
     </row>
@@ -1366,7 +1385,7 @@
       <c r="E8" s="16" t="n">
         <v>8163.72</v>
       </c>
-      <c r="F8" s="34" t="n">
+      <c r="F8" s="45" t="n">
         <v>0.2158233783016042</v>
       </c>
       <c r="G8" s="15" t="n">
@@ -1378,7 +1397,7 @@
       <c r="I8" s="16" t="n">
         <v>3967.81</v>
       </c>
-      <c r="J8" s="34" t="n">
+      <c r="J8" s="45" t="n">
         <v>0.2582881730509473</v>
       </c>
       <c r="K8" s="15" t="n">
@@ -1390,7 +1409,7 @@
       <c r="M8" s="16" t="n">
         <v>5439.19</v>
       </c>
-      <c r="N8" s="34" t="n">
+      <c r="N8" s="45" t="n">
         <v>0.4973660363625058</v>
       </c>
     </row>
@@ -1401,7 +1420,7 @@
           <t>4-mo TOTAL</t>
         </is>
       </c>
-      <c r="C9" s="42" t="n">
+      <c r="C9" s="46" t="n">
         <v>95</v>
       </c>
       <c r="D9" s="19" t="n">
@@ -1410,10 +1429,10 @@
       <c r="E9" s="19" t="n">
         <v>22884.08</v>
       </c>
-      <c r="F9" s="43" t="n">
+      <c r="F9" s="47" t="n">
         <v>0.1542805350206961</v>
       </c>
-      <c r="G9" s="42" t="n">
+      <c r="G9" s="46" t="n">
         <v>68</v>
       </c>
       <c r="H9" s="19" t="n">
@@ -1422,10 +1441,10 @@
       <c r="I9" s="19" t="n">
         <v>20267.11</v>
       </c>
-      <c r="J9" s="43" t="n">
+      <c r="J9" s="47" t="n">
         <v>0.2052343747231042</v>
       </c>
-      <c r="K9" s="42" t="n">
+      <c r="K9" s="46" t="n">
         <v>34</v>
       </c>
       <c r="L9" s="19" t="n">
@@ -1434,7 +1453,7 @@
       <c r="M9" s="19" t="n">
         <v>9869.66</v>
       </c>
-      <c r="N9" s="43" t="n">
+      <c r="N9" s="47" t="n">
         <v>0.3294390097930538</v>
       </c>
     </row>
@@ -1458,7 +1477,7 @@
       <c r="E11" s="16" t="n">
         <v>4925</v>
       </c>
-      <c r="F11" s="34" t="n">
+      <c r="F11" s="45" t="n">
         <v>0.1223624980931326</v>
       </c>
       <c r="G11" s="15" t="n">
@@ -1470,7 +1489,7 @@
       <c r="I11" s="16" t="n">
         <v>10936.32</v>
       </c>
-      <c r="J11" s="34" t="n">
+      <c r="J11" s="45" t="n">
         <v>0.1665208484518856</v>
       </c>
       <c r="K11" s="15" t="n">
@@ -1482,7 +1501,7 @@
       <c r="M11" s="16" t="n">
         <v>4951.59</v>
       </c>
-      <c r="N11" s="34" t="n">
+      <c r="N11" s="45" t="n">
         <v>0.395163948359479</v>
       </c>
     </row>
@@ -1506,7 +1525,7 @@
       <c r="E12" s="16" t="n">
         <v>5766.72</v>
       </c>
-      <c r="F12" s="34" t="n">
+      <c r="F12" s="45" t="n">
         <v>0.1918537861440041</v>
       </c>
       <c r="G12" s="15" t="n">
@@ -1518,7 +1537,7 @@
       <c r="I12" s="16" t="n">
         <v>13931.43</v>
       </c>
-      <c r="J12" s="34" t="n">
+      <c r="J12" s="45" t="n">
         <v>0.1628557500999478</v>
       </c>
       <c r="K12" s="15" t="n">
@@ -1530,7 +1549,7 @@
       <c r="M12" s="16" t="n">
         <v>1937.6</v>
       </c>
-      <c r="N12" s="34" t="n">
+      <c r="N12" s="45" t="n">
         <v>0.1666081955823376</v>
       </c>
     </row>
@@ -1554,7 +1573,7 @@
       <c r="E13" s="16" t="n">
         <v>10546.59</v>
       </c>
-      <c r="F13" s="34" t="n">
+      <c r="F13" s="45" t="n">
         <v>0.2011368382508596</v>
       </c>
       <c r="G13" s="15" t="n">
@@ -1566,7 +1585,7 @@
       <c r="I13" s="16" t="n">
         <v>19700.38</v>
       </c>
-      <c r="J13" s="34" t="n">
+      <c r="J13" s="45" t="n">
         <v>0.2047253226310126</v>
       </c>
       <c r="K13" s="15" t="n">
@@ -1578,7 +1597,7 @@
       <c r="M13" s="16" t="n">
         <v>3080</v>
       </c>
-      <c r="N13" s="34" t="n">
+      <c r="N13" s="45" t="n">
         <v>0.5165618448637317</v>
       </c>
     </row>
@@ -1602,7 +1621,7 @@
       <c r="E14" s="16" t="n">
         <v>8831.440000000001</v>
       </c>
-      <c r="F14" s="34" t="n">
+      <c r="F14" s="45" t="n">
         <v>0.1777330554736579</v>
       </c>
       <c r="G14" s="15" t="n">
@@ -1614,7 +1633,7 @@
       <c r="I14" s="16" t="n">
         <v>16668.05</v>
       </c>
-      <c r="J14" s="34" t="n">
+      <c r="J14" s="45" t="n">
         <v>0.2597668245969831</v>
       </c>
       <c r="K14" s="15" t="n">
@@ -1626,7 +1645,7 @@
       <c r="M14" s="16" t="n">
         <v>2939.65</v>
       </c>
-      <c r="N14" s="34" t="n">
+      <c r="N14" s="45" t="n">
         <v>0.1501736909323116</v>
       </c>
     </row>
@@ -1637,7 +1656,7 @@
           <t>4-mo TOTAL</t>
         </is>
       </c>
-      <c r="C15" s="42" t="n">
+      <c r="C15" s="46" t="n">
         <v>117</v>
       </c>
       <c r="D15" s="19" t="n">
@@ -1646,10 +1665,10 @@
       <c r="E15" s="19" t="n">
         <v>30069.75</v>
       </c>
-      <c r="F15" s="43" t="n">
+      <c r="F15" s="47" t="n">
         <v>0.1743867416259452</v>
       </c>
-      <c r="G15" s="42" t="n">
+      <c r="G15" s="46" t="n">
         <v>217</v>
       </c>
       <c r="H15" s="19" t="n">
@@ -1658,10 +1677,10 @@
       <c r="I15" s="19" t="n">
         <v>61236.18000000001</v>
       </c>
-      <c r="J15" s="43" t="n">
+      <c r="J15" s="47" t="n">
         <v>0.1965130808087551</v>
       </c>
-      <c r="K15" s="42" t="n">
+      <c r="K15" s="46" t="n">
         <v>29</v>
       </c>
       <c r="L15" s="19" t="n">
@@ -1670,7 +1689,7 @@
       <c r="M15" s="19" t="n">
         <v>12908.84</v>
       </c>
-      <c r="N15" s="43" t="n">
+      <c r="N15" s="47" t="n">
         <v>0.2597474930907196</v>
       </c>
     </row>
@@ -1694,7 +1713,7 @@
       <c r="E17" s="16" t="n">
         <v>7651.14</v>
       </c>
-      <c r="F17" s="34" t="n">
+      <c r="F17" s="45" t="n">
         <v>0.2065698317989147</v>
       </c>
       <c r="G17" s="15" t="n">
@@ -1706,7 +1725,7 @@
       <c r="I17" s="16" t="n">
         <v>11897.57</v>
       </c>
-      <c r="J17" s="34" t="n">
+      <c r="J17" s="45" t="n">
         <v>0.1877343410993381</v>
       </c>
       <c r="K17" s="15" t="n">
@@ -1718,7 +1737,7 @@
       <c r="M17" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="N17" s="34" t="n">
+      <c r="N17" s="45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1742,7 +1761,7 @@
       <c r="E18" s="16" t="n">
         <v>2095.02</v>
       </c>
-      <c r="F18" s="34" t="n">
+      <c r="F18" s="45" t="n">
         <v>0.2735191592140479</v>
       </c>
       <c r="G18" s="15" t="n">
@@ -1754,7 +1773,7 @@
       <c r="I18" s="16" t="n">
         <v>6802.73</v>
       </c>
-      <c r="J18" s="34" t="n">
+      <c r="J18" s="45" t="n">
         <v>0.1360799108634206</v>
       </c>
       <c r="K18" s="15" t="n">
@@ -1766,7 +1785,7 @@
       <c r="M18" s="16" t="n">
         <v>91.75</v>
       </c>
-      <c r="N18" s="34" t="n">
+      <c r="N18" s="45" t="n">
         <v>0.08631232361241768</v>
       </c>
     </row>
@@ -1790,7 +1809,7 @@
       <c r="E19" s="16" t="n">
         <v>5669.41</v>
       </c>
-      <c r="F19" s="34" t="n">
+      <c r="F19" s="45" t="n">
         <v>0.142591870663008</v>
       </c>
       <c r="G19" s="15" t="n">
@@ -1802,7 +1821,7 @@
       <c r="I19" s="16" t="n">
         <v>8620.469999999999</v>
       </c>
-      <c r="J19" s="34" t="n">
+      <c r="J19" s="45" t="n">
         <v>0.1516070882122243</v>
       </c>
       <c r="K19" s="15" t="n">
@@ -1814,7 +1833,7 @@
       <c r="M19" s="16" t="n">
         <v>180.45</v>
       </c>
-      <c r="N19" s="34" t="n">
+      <c r="N19" s="45" t="n">
         <v>0.1745164410058027</v>
       </c>
     </row>
@@ -1838,7 +1857,7 @@
       <c r="E20" s="16" t="n">
         <v>4344.3</v>
       </c>
-      <c r="F20" s="34" t="n">
+      <c r="F20" s="45" t="n">
         <v>0.225229218673448</v>
       </c>
       <c r="G20" s="15" t="n">
@@ -1850,7 +1869,7 @@
       <c r="I20" s="16" t="n">
         <v>7660.7</v>
       </c>
-      <c r="J20" s="34" t="n">
+      <c r="J20" s="45" t="n">
         <v>0.1765292813656495</v>
       </c>
       <c r="K20" s="15" t="n">
@@ -1862,7 +1881,7 @@
       <c r="M20" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="N20" s="34" t="n">
+      <c r="N20" s="45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1873,7 +1892,7 @@
           <t>4-mo TOTAL</t>
         </is>
       </c>
-      <c r="C21" s="42" t="n">
+      <c r="C21" s="46" t="n">
         <v>87</v>
       </c>
       <c r="D21" s="19" t="n">
@@ -1882,10 +1901,10 @@
       <c r="E21" s="19" t="n">
         <v>19759.87</v>
       </c>
-      <c r="F21" s="43" t="n">
+      <c r="F21" s="47" t="n">
         <v>0.1904629117787531</v>
       </c>
-      <c r="G21" s="42" t="n">
+      <c r="G21" s="46" t="n">
         <v>170</v>
       </c>
       <c r="H21" s="19" t="n">
@@ -1894,10 +1913,10 @@
       <c r="I21" s="19" t="n">
         <v>34981.46999999999</v>
       </c>
-      <c r="J21" s="43" t="n">
+      <c r="J21" s="47" t="n">
         <v>0.1637540609113293</v>
       </c>
-      <c r="K21" s="42" t="n">
+      <c r="K21" s="46" t="n">
         <v>2</v>
       </c>
       <c r="L21" s="19" t="n">
@@ -1906,7 +1925,7 @@
       <c r="M21" s="19" t="n">
         <v>272.2</v>
       </c>
-      <c r="N21" s="43" t="n">
+      <c r="N21" s="47" t="n">
         <v>0.1298044825941821</v>
       </c>
     </row>
@@ -1930,7 +1949,7 @@
       <c r="E23" s="16" t="n">
         <v>5657.4</v>
       </c>
-      <c r="F23" s="34" t="n">
+      <c r="F23" s="45" t="n">
         <v>0.1983309406994904</v>
       </c>
       <c r="G23" s="15" t="n">
@@ -1942,7 +1961,7 @@
       <c r="I23" s="16" t="n">
         <v>8795.290000000001</v>
       </c>
-      <c r="J23" s="34" t="n">
+      <c r="J23" s="45" t="n">
         <v>0.2223388159932049</v>
       </c>
       <c r="K23" s="15" t="n">
@@ -1954,7 +1973,7 @@
       <c r="M23" s="16" t="n">
         <v>302.12</v>
       </c>
-      <c r="N23" s="34" t="n">
+      <c r="N23" s="45" t="n">
         <v>0.2063167958479872</v>
       </c>
     </row>
@@ -1978,7 +1997,7 @@
       <c r="E24" s="16" t="n">
         <v>3832.59</v>
       </c>
-      <c r="F24" s="34" t="n">
+      <c r="F24" s="45" t="n">
         <v>0.1722690435415796</v>
       </c>
       <c r="G24" s="15" t="n">
@@ -1990,7 +2009,7 @@
       <c r="I24" s="16" t="n">
         <v>13820.09</v>
       </c>
-      <c r="J24" s="34" t="n">
+      <c r="J24" s="45" t="n">
         <v>0.3163400473133589</v>
       </c>
       <c r="K24" s="15" t="n">
@@ -2002,7 +2021,7 @@
       <c r="M24" s="16" t="n">
         <v>321.01</v>
       </c>
-      <c r="N24" s="34" t="n">
+      <c r="N24" s="45" t="n">
         <v>0.152934730824202</v>
       </c>
     </row>
@@ -2026,7 +2045,7 @@
       <c r="E25" s="16" t="n">
         <v>8642.02</v>
       </c>
-      <c r="F25" s="34" t="n">
+      <c r="F25" s="45" t="n">
         <v>0.2763766030253606</v>
       </c>
       <c r="G25" s="15" t="n">
@@ -2038,7 +2057,7 @@
       <c r="I25" s="16" t="n">
         <v>9060.629999999999</v>
       </c>
-      <c r="J25" s="34" t="n">
+      <c r="J25" s="45" t="n">
         <v>0.3851211602137146</v>
       </c>
       <c r="K25" s="15" t="n">
@@ -2050,7 +2069,7 @@
       <c r="M25" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="N25" s="34" t="n">
+      <c r="N25" s="45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2074,7 +2093,7 @@
       <c r="E26" s="16" t="n">
         <v>6600.51</v>
       </c>
-      <c r="F26" s="34" t="n">
+      <c r="F26" s="45" t="n">
         <v>0.2231330530863509</v>
       </c>
       <c r="G26" s="15" t="n">
@@ -2086,7 +2105,7 @@
       <c r="I26" s="16" t="n">
         <v>7710.62</v>
       </c>
-      <c r="J26" s="34" t="n">
+      <c r="J26" s="45" t="n">
         <v>0.2500788122762931</v>
       </c>
       <c r="K26" s="15" t="n">
@@ -2098,7 +2117,7 @@
       <c r="M26" s="16" t="n">
         <v>885</v>
       </c>
-      <c r="N26" s="34" t="n">
+      <c r="N26" s="45" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2109,7 +2128,7 @@
           <t>4-mo TOTAL</t>
         </is>
       </c>
-      <c r="C27" s="42" t="n">
+      <c r="C27" s="46" t="n">
         <v>92</v>
       </c>
       <c r="D27" s="19" t="n">
@@ -2118,10 +2137,10 @@
       <c r="E27" s="19" t="n">
         <v>24732.52</v>
       </c>
-      <c r="F27" s="43" t="n">
+      <c r="F27" s="47" t="n">
         <v>0.2215722952658418</v>
       </c>
-      <c r="G27" s="42" t="n">
+      <c r="G27" s="46" t="n">
         <v>135</v>
       </c>
       <c r="H27" s="19" t="n">
@@ -2130,10 +2149,10 @@
       <c r="I27" s="19" t="n">
         <v>39386.63</v>
       </c>
-      <c r="J27" s="43" t="n">
+      <c r="J27" s="47" t="n">
         <v>0.2862297260215039</v>
       </c>
-      <c r="K27" s="42" t="n">
+      <c r="K27" s="46" t="n">
         <v>4</v>
       </c>
       <c r="L27" s="19" t="n">
@@ -2142,7 +2161,7 @@
       <c r="M27" s="19" t="n">
         <v>1508.13</v>
       </c>
-      <c r="N27" s="43" t="n">
+      <c r="N27" s="47" t="n">
         <v>0.3390313262220823</v>
       </c>
     </row>
@@ -2166,7 +2185,7 @@
       <c r="E29" s="16" t="n">
         <v>2238.28</v>
       </c>
-      <c r="F29" s="34" t="n">
+      <c r="F29" s="45" t="n">
         <v>0.1443688362283039</v>
       </c>
       <c r="G29" s="15" t="n">
@@ -2178,7 +2197,7 @@
       <c r="I29" s="16" t="n">
         <v>6461.48</v>
       </c>
-      <c r="J29" s="34" t="n">
+      <c r="J29" s="45" t="n">
         <v>0.1953056967536807</v>
       </c>
       <c r="K29" s="15" t="n">
@@ -2190,7 +2209,7 @@
       <c r="M29" s="16" t="n">
         <v>642.04</v>
       </c>
-      <c r="N29" s="34" t="n">
+      <c r="N29" s="45" t="n">
         <v>0.1739945799457994</v>
       </c>
     </row>
@@ -2214,7 +2233,7 @@
       <c r="E30" s="16" t="n">
         <v>3640.91</v>
       </c>
-      <c r="F30" s="34" t="n">
+      <c r="F30" s="45" t="n">
         <v>0.1875380197535315</v>
       </c>
       <c r="G30" s="15" t="n">
@@ -2226,7 +2245,7 @@
       <c r="I30" s="16" t="n">
         <v>5276.12</v>
       </c>
-      <c r="J30" s="34" t="n">
+      <c r="J30" s="45" t="n">
         <v>0.186447458067945</v>
       </c>
       <c r="K30" s="15" t="n">
@@ -2238,7 +2257,7 @@
       <c r="M30" s="16" t="n">
         <v>3293.14</v>
       </c>
-      <c r="N30" s="34" t="n">
+      <c r="N30" s="45" t="n">
         <v>0.442269674993285</v>
       </c>
     </row>
@@ -2262,7 +2281,7 @@
       <c r="E31" s="16" t="n">
         <v>4965.76</v>
       </c>
-      <c r="F31" s="34" t="n">
+      <c r="F31" s="45" t="n">
         <v>0.2782922142225067</v>
       </c>
       <c r="G31" s="15" t="n">
@@ -2274,7 +2293,7 @@
       <c r="I31" s="16" t="n">
         <v>3981.64</v>
       </c>
-      <c r="J31" s="34" t="n">
+      <c r="J31" s="45" t="n">
         <v>0.2006789023655741</v>
       </c>
       <c r="K31" s="15" t="n">
@@ -2286,7 +2305,7 @@
       <c r="M31" s="16" t="n">
         <v>1575.86</v>
       </c>
-      <c r="N31" s="34" t="n">
+      <c r="N31" s="45" t="n">
         <v>0.2792147274048087</v>
       </c>
     </row>
@@ -2310,7 +2329,7 @@
       <c r="E32" s="16" t="n">
         <v>3941.94</v>
       </c>
-      <c r="F32" s="34" t="n">
+      <c r="F32" s="45" t="n">
         <v>0.2795900418469395</v>
       </c>
       <c r="G32" s="15" t="n">
@@ -2322,7 +2341,7 @@
       <c r="I32" s="16" t="n">
         <v>7674.9</v>
       </c>
-      <c r="J32" s="34" t="n">
+      <c r="J32" s="45" t="n">
         <v>0.1928638200349798</v>
       </c>
       <c r="K32" s="15" t="n">
@@ -2334,7 +2353,7 @@
       <c r="M32" s="16" t="n">
         <v>3096.58</v>
       </c>
-      <c r="N32" s="34" t="n">
+      <c r="N32" s="45" t="n">
         <v>0.8561183301078241</v>
       </c>
     </row>
@@ -2345,7 +2364,7 @@
           <t>4-mo TOTAL</t>
         </is>
       </c>
-      <c r="C33" s="42" t="n">
+      <c r="C33" s="46" t="n">
         <v>52</v>
       </c>
       <c r="D33" s="19" t="n">
@@ -2354,10 +2373,10 @@
       <c r="E33" s="19" t="n">
         <v>14786.89</v>
       </c>
-      <c r="F33" s="43" t="n">
+      <c r="F33" s="47" t="n">
         <v>0.2211592017091021</v>
       </c>
-      <c r="G33" s="42" t="n">
+      <c r="G33" s="46" t="n">
         <v>100</v>
       </c>
       <c r="H33" s="19" t="n">
@@ -2366,10 +2385,10 @@
       <c r="I33" s="19" t="n">
         <v>23394.14</v>
       </c>
-      <c r="J33" s="43" t="n">
+      <c r="J33" s="47" t="n">
         <v>0.1933122972294714</v>
       </c>
-      <c r="K33" s="42" t="n">
+      <c r="K33" s="46" t="n">
         <v>18</v>
       </c>
       <c r="L33" s="19" t="n">
@@ -2378,7 +2397,7 @@
       <c r="M33" s="19" t="n">
         <v>8607.619999999999</v>
       </c>
-      <c r="N33" s="43" t="n">
+      <c r="N33" s="47" t="n">
         <v>0.4220062852688398</v>
       </c>
     </row>
@@ -2402,7 +2421,7 @@
       <c r="E35" s="16" t="n">
         <v>6551.7</v>
       </c>
-      <c r="F35" s="34" t="n">
+      <c r="F35" s="45" t="n">
         <v>0.2290380555484667</v>
       </c>
       <c r="G35" s="15" t="n">
@@ -2414,7 +2433,7 @@
       <c r="I35" s="16" t="n">
         <v>8203.879999999999</v>
       </c>
-      <c r="J35" s="34" t="n">
+      <c r="J35" s="45" t="n">
         <v>0.1687591127962584</v>
       </c>
       <c r="K35" s="15" t="n">
@@ -2426,7 +2445,7 @@
       <c r="M35" s="16" t="n">
         <v>1439.3</v>
       </c>
-      <c r="N35" s="34" t="n">
+      <c r="N35" s="45" t="n">
         <v>0.2213316807398534</v>
       </c>
     </row>
@@ -2450,7 +2469,7 @@
       <c r="E36" s="16" t="n">
         <v>6512.87</v>
       </c>
-      <c r="F36" s="34" t="n">
+      <c r="F36" s="45" t="n">
         <v>0.206646582235908</v>
       </c>
       <c r="G36" s="15" t="n">
@@ -2462,7 +2481,7 @@
       <c r="I36" s="16" t="n">
         <v>7155.23</v>
       </c>
-      <c r="J36" s="34" t="n">
+      <c r="J36" s="45" t="n">
         <v>0.1515034032647457</v>
       </c>
       <c r="K36" s="15" t="n">
@@ -2474,7 +2493,7 @@
       <c r="M36" s="16" t="n">
         <v>272.87</v>
       </c>
-      <c r="N36" s="34" t="n">
+      <c r="N36" s="45" t="n">
         <v>0.0882503234152652</v>
       </c>
     </row>
@@ -2498,7 +2517,7 @@
       <c r="E37" s="16" t="n">
         <v>17019.79</v>
       </c>
-      <c r="F37" s="34" t="n">
+      <c r="F37" s="45" t="n">
         <v>0.2482965508528406</v>
       </c>
       <c r="G37" s="15" t="n">
@@ -2510,7 +2529,7 @@
       <c r="I37" s="16" t="n">
         <v>5300.53</v>
       </c>
-      <c r="J37" s="34" t="n">
+      <c r="J37" s="45" t="n">
         <v>0.135029353210384</v>
       </c>
       <c r="K37" s="15" t="n">
@@ -2522,7 +2541,7 @@
       <c r="M37" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="N37" s="34" t="n">
+      <c r="N37" s="45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2546,7 +2565,7 @@
       <c r="E38" s="16" t="n">
         <v>6197.26</v>
       </c>
-      <c r="F38" s="34" t="n">
+      <c r="F38" s="45" t="n">
         <v>0.2082728262918876</v>
       </c>
       <c r="G38" s="15" t="n">
@@ -2558,7 +2577,7 @@
       <c r="I38" s="16" t="n">
         <v>7305.79</v>
       </c>
-      <c r="J38" s="34" t="n">
+      <c r="J38" s="45" t="n">
         <v>0.2070808023832267</v>
       </c>
       <c r="K38" s="15" t="n">
@@ -2570,7 +2589,7 @@
       <c r="M38" s="16" t="n">
         <v>291.12</v>
       </c>
-      <c r="N38" s="34" t="n">
+      <c r="N38" s="45" t="n">
         <v>0.115799522673031</v>
       </c>
     </row>
@@ -2581,7 +2600,7 @@
           <t>4-mo TOTAL</t>
         </is>
       </c>
-      <c r="C39" s="42" t="n">
+      <c r="C39" s="46" t="n">
         <v>102</v>
       </c>
       <c r="D39" s="19" t="n">
@@ -2590,10 +2609,10 @@
       <c r="E39" s="19" t="n">
         <v>36281.62</v>
       </c>
-      <c r="F39" s="43" t="n">
+      <c r="F39" s="47" t="n">
         <v>0.2290160042089596</v>
       </c>
-      <c r="G39" s="42" t="n">
+      <c r="G39" s="46" t="n">
         <v>116</v>
       </c>
       <c r="H39" s="19" t="n">
@@ -2602,10 +2621,10 @@
       <c r="I39" s="19" t="n">
         <v>27965.43</v>
       </c>
-      <c r="J39" s="43" t="n">
+      <c r="J39" s="47" t="n">
         <v>0.1641397901308573</v>
       </c>
-      <c r="K39" s="42" t="n">
+      <c r="K39" s="46" t="n">
         <v>10</v>
       </c>
       <c r="L39" s="19" t="n">
@@ -2614,7 +2633,7 @@
       <c r="M39" s="19" t="n">
         <v>2003.29</v>
       </c>
-      <c r="N39" s="43" t="n">
+      <c r="N39" s="47" t="n">
         <v>0.1654393335155683</v>
       </c>
     </row>
@@ -12224,3446 +12243,2893 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N92"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Agent Examples - 100% FLIP (if rewrites had been renewals)</t>
+          <t>COMBINED BONUS EXAMPLES - NB + RWR + REN per agent-month, three scenarios</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Same premiums, same collected $, but rewrites and renewals are FULLY SWAPPED. Strongest behavior-change test.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>Each row = one agent-month. Shows the NB, RWR, and REN bonus side by side and the TOTAL BONUS for the month. Sorted by total bonus descending. Bonus cells that paid are shaded green; red total = nothing paid (NB minimum not met).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
+          <t>SCENARIO 1: REAL DATA (Jan-Apr 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>NB Premium</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>NB Bonus</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>RWR Premium</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>RWR Bonus</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>REN Premium</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>REN Bonus</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Progress Bar</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL BONUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>Dialinerys Dieguez</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="n">
+        <v>52434.9</v>
+      </c>
+      <c r="D6" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>96228.35000000001</v>
+      </c>
+      <c r="F6" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>5962.5</v>
+      </c>
+      <c r="H6" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="26" t="n">
+        <v>600</v>
+      </c>
+      <c r="J6" s="36" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>Dialinerys Dieguez</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>49689.35</v>
+      </c>
+      <c r="D7" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>64165.43</v>
+      </c>
+      <c r="F7" s="34" t="n">
+        <v>200</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>19575</v>
+      </c>
+      <c r="H7" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="26" t="n">
+        <v>450</v>
+      </c>
+      <c r="J7" s="36" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>Monica Valdes</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="n">
+        <v>68546.22</v>
+      </c>
+      <c r="D8" s="34" t="n">
+        <v>375</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>39254.65</v>
+      </c>
+      <c r="F8" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="26" t="n">
+        <v>375</v>
+      </c>
+      <c r="J8" s="36" t="n">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
           <t>Abel Guaina</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>46523.37</v>
+      </c>
+      <c r="D9" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>25227.6</v>
+      </c>
+      <c r="F9" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <v>3901</v>
+      </c>
+      <c r="H9" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="26" t="n">
+        <v>250</v>
+      </c>
+      <c r="J9" s="36" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>Abel Guaina</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="n">
+        <v>38611.42</v>
+      </c>
+      <c r="D10" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>27518.5</v>
+      </c>
+      <c r="F10" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="16" t="n">
+        <v>7605</v>
+      </c>
+      <c r="H10" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>Abel Guaina</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>25367</v>
+      </c>
+      <c r="D11" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>30643</v>
+      </c>
+      <c r="F11" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>7517</v>
+      </c>
+      <c r="H11" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t>Abel Guaina</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>37825.93</v>
+      </c>
+      <c r="D12" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>15361.95</v>
+      </c>
+      <c r="F12" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <v>10935.99</v>
+      </c>
+      <c r="H12" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>Dialinerys Dieguez</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="n">
+        <v>40249.26</v>
+      </c>
+      <c r="D13" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>65675.38</v>
+      </c>
+      <c r="F13" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <v>12530.47</v>
+      </c>
+      <c r="H13" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>Dialinerys Dieguez</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="n">
+        <v>30057.89</v>
+      </c>
+      <c r="D14" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>85544.60000000001</v>
+      </c>
+      <c r="F14" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="16" t="n">
+        <v>11629.68</v>
+      </c>
+      <c r="H14" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>Melissa Hernandez</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="n">
+        <v>37039</v>
+      </c>
+      <c r="D15" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>63374.5</v>
+      </c>
+      <c r="F15" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t>Melissa Hernandez</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="n">
+        <v>7659.5</v>
+      </c>
+      <c r="D16" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>49990.7</v>
+      </c>
+      <c r="F16" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="16" t="n">
+        <v>1063</v>
+      </c>
+      <c r="H16" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>Melissa Hernandez</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="n">
+        <v>39759.7</v>
+      </c>
+      <c r="D17" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>56860.6</v>
+      </c>
+      <c r="F17" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="16" t="n">
+        <v>1034</v>
+      </c>
+      <c r="H17" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="25" t="inlineStr">
+        <is>
+          <t>Melissa Hernandez</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="n">
+        <v>19288.35</v>
+      </c>
+      <c r="D18" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="16" t="n">
+        <v>43396.2</v>
+      </c>
+      <c r="F18" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t>Flavia Parra</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="n">
+        <v>28525.05</v>
+      </c>
+      <c r="D19" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>39558.05</v>
+      </c>
+      <c r="F19" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="16" t="n">
+        <v>1464.35</v>
+      </c>
+      <c r="H19" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="25" t="inlineStr">
+        <is>
+          <t>Flavia Parra</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="n">
+        <v>22247.7</v>
+      </c>
+      <c r="D20" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>43687.45</v>
+      </c>
+      <c r="F20" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="16" t="n">
+        <v>2099</v>
+      </c>
+      <c r="H20" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>Flavia Parra</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="n">
+        <v>31269</v>
+      </c>
+      <c r="D21" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>23526.7</v>
+      </c>
+      <c r="F21" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="25" t="inlineStr">
+        <is>
+          <t>Flavia Parra</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="n">
+        <v>29581.05</v>
+      </c>
+      <c r="D22" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="16" t="n">
+        <v>30832.76</v>
+      </c>
+      <c r="F22" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="16" t="n">
+        <v>885</v>
+      </c>
+      <c r="H22" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="25" t="inlineStr">
+        <is>
+          <t>Thalia Rojas</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="n">
+        <v>15503.9</v>
+      </c>
+      <c r="D23" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="16" t="n">
+        <v>33083.93</v>
+      </c>
+      <c r="F23" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="16" t="n">
+        <v>3690</v>
+      </c>
+      <c r="H23" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="25" t="inlineStr">
+        <is>
+          <t>Thalia Rojas</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="n">
+        <v>19414.25</v>
+      </c>
+      <c r="D24" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="16" t="n">
+        <v>28298.16</v>
+      </c>
+      <c r="F24" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="16" t="n">
+        <v>7446</v>
+      </c>
+      <c r="H24" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>Thalia Rojas</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="n">
+        <v>17843.69</v>
+      </c>
+      <c r="D25" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="16" t="n">
+        <v>19840.85</v>
+      </c>
+      <c r="F25" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="16" t="n">
+        <v>5643.9</v>
+      </c>
+      <c r="H25" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>Thalia Rojas</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="n">
+        <v>14099</v>
+      </c>
+      <c r="D26" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <v>39794.4</v>
+      </c>
+      <c r="F26" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="16" t="n">
+        <v>3617</v>
+      </c>
+      <c r="H26" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>Monica Valdes</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="n">
+        <v>28605.29</v>
+      </c>
+      <c r="D27" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="16" t="n">
+        <v>48612.96</v>
+      </c>
+      <c r="F27" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="16" t="n">
+        <v>6502.91</v>
+      </c>
+      <c r="H27" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>Monica Valdes</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="n">
+        <v>31516.95</v>
+      </c>
+      <c r="D28" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="16" t="n">
+        <v>47228.18</v>
+      </c>
+      <c r="F28" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="16" t="n">
+        <v>3092</v>
+      </c>
+      <c r="H28" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Monica Valdes</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="n">
+        <v>29755.49</v>
+      </c>
+      <c r="D29" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>35279.9</v>
+      </c>
+      <c r="F29" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="16" t="n">
+        <v>2514</v>
+      </c>
+      <c r="H29" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="38" t="inlineStr">
+        <is>
+          <t>4-MONTH TOTAL (all 6 agents)</t>
+        </is>
+      </c>
+      <c r="B30" s="39" t="n"/>
+      <c r="C30" s="39" t="n"/>
+      <c r="D30" s="39" t="n"/>
+      <c r="E30" s="39" t="n"/>
+      <c r="F30" s="39" t="n"/>
+      <c r="G30" s="39" t="n"/>
+      <c r="H30" s="39" t="n"/>
+      <c r="I30" s="39" t="n"/>
+      <c r="J30" s="40" t="n">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>SCENARIO 2: 50% SWAP (half of RWR -&gt; REN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>NB Count</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>NB Premium</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>NB Collected</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>NB Coll %</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>RWR Count</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>NB Bonus</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>RWR Premium</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>RWR Collected</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>RWR Coll %</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>REN Count</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>RWR Bonus</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
         <is>
           <t>REN Premium</t>
         </is>
       </c>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>REN Collected</t>
-        </is>
-      </c>
-      <c r="M5" s="6" t="inlineStr">
-        <is>
-          <t>REN Coll %</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>REN Bonus</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>Progress Bar</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL BONUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Dialinerys Dieguez</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="n">
+        <v>52434.9</v>
+      </c>
+      <c r="D34" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="E34" s="16" t="n">
+        <v>48114.175</v>
+      </c>
+      <c r="F34" s="34" t="n">
+        <v>100</v>
+      </c>
+      <c r="G34" s="16" t="n">
+        <v>54076.675</v>
+      </c>
+      <c r="H34" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="I34" s="26" t="n">
+        <v>700</v>
+      </c>
+      <c r="J34" s="36" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>Dialinerys Dieguez</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="n">
+        <v>49689.35</v>
+      </c>
+      <c r="D35" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="E35" s="16" t="n">
+        <v>32082.715</v>
+      </c>
+      <c r="F35" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="16" t="n">
+        <v>51657.715</v>
+      </c>
+      <c r="H35" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="I35" s="26" t="n">
+        <v>600</v>
+      </c>
+      <c r="J35" s="36" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>Monica Valdes</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="n">
+        <v>68546.22</v>
+      </c>
+      <c r="D36" s="34" t="n">
+        <v>375</v>
+      </c>
+      <c r="E36" s="16" t="n">
+        <v>19627.325</v>
+      </c>
+      <c r="F36" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="16" t="n">
+        <v>19627.325</v>
+      </c>
+      <c r="H36" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="26" t="n">
+        <v>375</v>
+      </c>
+      <c r="J36" s="36" t="n">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>Dialinerys Dieguez</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
         <is>
           <t>January</t>
         </is>
       </c>
-      <c r="B6" s="15" t="n">
-        <v>25</v>
-      </c>
-      <c r="C6" s="16" t="n">
+      <c r="C37" s="16" t="n">
+        <v>40249.26</v>
+      </c>
+      <c r="D37" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="16" t="n">
+        <v>32837.69</v>
+      </c>
+      <c r="F37" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="16" t="n">
+        <v>45368.16</v>
+      </c>
+      <c r="H37" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="I37" s="26" t="n">
+        <v>350</v>
+      </c>
+      <c r="J37" s="36" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>Dialinerys Dieguez</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="n">
+        <v>30057.89</v>
+      </c>
+      <c r="D38" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="16" t="n">
+        <v>42772.3</v>
+      </c>
+      <c r="F38" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="16" t="n">
+        <v>54401.98</v>
+      </c>
+      <c r="H38" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="I38" s="26" t="n">
+        <v>350</v>
+      </c>
+      <c r="J38" s="36" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="25" t="inlineStr">
+        <is>
+          <t>Abel Guaina</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="n">
+        <v>46523.37</v>
+      </c>
+      <c r="D39" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="E39" s="16" t="n">
+        <v>12613.8</v>
+      </c>
+      <c r="F39" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="16" t="n">
+        <v>16514.8</v>
+      </c>
+      <c r="H39" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="26" t="n">
+        <v>250</v>
+      </c>
+      <c r="J39" s="36" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>Melissa Hernandez</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="n">
+        <v>37039</v>
+      </c>
+      <c r="D40" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="16" t="n">
+        <v>31687.25</v>
+      </c>
+      <c r="F40" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="16" t="n">
+        <v>31687.25</v>
+      </c>
+      <c r="H40" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I40" s="26" t="n">
+        <v>250</v>
+      </c>
+      <c r="J40" s="36" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="25" t="inlineStr">
+        <is>
+          <t>Melissa Hernandez</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="C41" s="16" t="n">
+        <v>7659.5</v>
+      </c>
+      <c r="D41" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="16" t="n">
+        <v>24995.35</v>
+      </c>
+      <c r="F41" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="16" t="n">
+        <v>26058.35</v>
+      </c>
+      <c r="H41" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I41" s="26" t="n">
+        <v>250</v>
+      </c>
+      <c r="J41" s="36" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="25" t="inlineStr">
+        <is>
+          <t>Melissa Hernandez</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="n">
+        <v>39759.7</v>
+      </c>
+      <c r="D42" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="16" t="n">
+        <v>28430.3</v>
+      </c>
+      <c r="F42" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="16" t="n">
+        <v>29464.3</v>
+      </c>
+      <c r="H42" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I42" s="26" t="n">
+        <v>250</v>
+      </c>
+      <c r="J42" s="36" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="25" t="inlineStr">
+        <is>
+          <t>Monica Valdes</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C43" s="16" t="n">
+        <v>28605.29</v>
+      </c>
+      <c r="D43" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="16" t="n">
+        <v>24306.48</v>
+      </c>
+      <c r="F43" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="16" t="n">
+        <v>30809.39</v>
+      </c>
+      <c r="H43" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I43" s="26" t="n">
+        <v>250</v>
+      </c>
+      <c r="J43" s="36" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="25" t="inlineStr">
+        <is>
+          <t>Monica Valdes</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="n">
+        <v>31516.95</v>
+      </c>
+      <c r="D44" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="16" t="n">
+        <v>23614.09</v>
+      </c>
+      <c r="F44" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="16" t="n">
+        <v>26706.09</v>
+      </c>
+      <c r="H44" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I44" s="26" t="n">
+        <v>250</v>
+      </c>
+      <c r="J44" s="36" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="25" t="inlineStr">
+        <is>
+          <t>Abel Guaina</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="n">
         <v>38611.42</v>
       </c>
-      <c r="D6" s="16" t="n">
-        <v>4938.26</v>
-      </c>
-      <c r="E6" s="34" t="n">
-        <v>0.1278963581240991</v>
-      </c>
-      <c r="F6" s="15" t="n">
-        <v>9</v>
-      </c>
-      <c r="G6" s="16" t="n">
+      <c r="D45" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="16" t="n">
+        <v>13759.25</v>
+      </c>
+      <c r="F45" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="16" t="n">
+        <v>21364.25</v>
+      </c>
+      <c r="H45" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="25" t="inlineStr">
+        <is>
+          <t>Abel Guaina</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="C46" s="16" t="n">
+        <v>25367</v>
+      </c>
+      <c r="D46" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="16" t="n">
+        <v>15321.5</v>
+      </c>
+      <c r="F46" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="16" t="n">
+        <v>22838.5</v>
+      </c>
+      <c r="H46" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="25" t="inlineStr">
+        <is>
+          <t>Abel Guaina</t>
+        </is>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="n">
+        <v>37825.93</v>
+      </c>
+      <c r="D47" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="16" t="n">
+        <v>7680.975</v>
+      </c>
+      <c r="F47" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="16" t="n">
+        <v>18616.965</v>
+      </c>
+      <c r="H47" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="25" t="inlineStr">
+        <is>
+          <t>Melissa Hernandez</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C48" s="16" t="n">
+        <v>19288.35</v>
+      </c>
+      <c r="D48" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="16" t="n">
+        <v>21698.1</v>
+      </c>
+      <c r="F48" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="16" t="n">
+        <v>21698.1</v>
+      </c>
+      <c r="H48" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="25" t="inlineStr">
+        <is>
+          <t>Flavia Parra</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C49" s="16" t="n">
+        <v>28525.05</v>
+      </c>
+      <c r="D49" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="16" t="n">
+        <v>19779.025</v>
+      </c>
+      <c r="F49" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="16" t="n">
+        <v>21243.375</v>
+      </c>
+      <c r="H49" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="25" t="inlineStr">
+        <is>
+          <t>Flavia Parra</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="C50" s="16" t="n">
+        <v>22247.7</v>
+      </c>
+      <c r="D50" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="16" t="n">
+        <v>21843.725</v>
+      </c>
+      <c r="F50" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="16" t="n">
+        <v>23942.725</v>
+      </c>
+      <c r="H50" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="25" t="inlineStr">
+        <is>
+          <t>Flavia Parra</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="C51" s="16" t="n">
+        <v>31269</v>
+      </c>
+      <c r="D51" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="16" t="n">
+        <v>11763.35</v>
+      </c>
+      <c r="F51" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="16" t="n">
+        <v>11763.35</v>
+      </c>
+      <c r="H51" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="25" t="inlineStr">
+        <is>
+          <t>Flavia Parra</t>
+        </is>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C52" s="16" t="n">
+        <v>29581.05</v>
+      </c>
+      <c r="D52" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="16" t="n">
+        <v>15416.38</v>
+      </c>
+      <c r="F52" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="16" t="n">
+        <v>16301.38</v>
+      </c>
+      <c r="H52" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="25" t="inlineStr">
+        <is>
+          <t>Thalia Rojas</t>
+        </is>
+      </c>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C53" s="16" t="n">
+        <v>15503.9</v>
+      </c>
+      <c r="D53" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="16" t="n">
+        <v>16541.965</v>
+      </c>
+      <c r="F53" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="16" t="n">
+        <v>20231.965</v>
+      </c>
+      <c r="H53" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="25" t="inlineStr">
+        <is>
+          <t>Thalia Rojas</t>
+        </is>
+      </c>
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="C54" s="16" t="n">
+        <v>19414.25</v>
+      </c>
+      <c r="D54" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="16" t="n">
+        <v>14149.08</v>
+      </c>
+      <c r="F54" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="16" t="n">
+        <v>21595.08</v>
+      </c>
+      <c r="H54" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="25" t="inlineStr">
+        <is>
+          <t>Thalia Rojas</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="C55" s="16" t="n">
+        <v>17843.69</v>
+      </c>
+      <c r="D55" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="16" t="n">
+        <v>9920.424999999999</v>
+      </c>
+      <c r="F55" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="16" t="n">
+        <v>15564.325</v>
+      </c>
+      <c r="H55" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="25" t="inlineStr">
+        <is>
+          <t>Thalia Rojas</t>
+        </is>
+      </c>
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C56" s="16" t="n">
+        <v>14099</v>
+      </c>
+      <c r="D56" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="16" t="n">
+        <v>19897.2</v>
+      </c>
+      <c r="F56" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="16" t="n">
+        <v>23514.2</v>
+      </c>
+      <c r="H56" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="25" t="inlineStr">
+        <is>
+          <t>Monica Valdes</t>
+        </is>
+      </c>
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C57" s="16" t="n">
+        <v>29755.49</v>
+      </c>
+      <c r="D57" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="16" t="n">
+        <v>17639.95</v>
+      </c>
+      <c r="F57" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="16" t="n">
+        <v>20153.95</v>
+      </c>
+      <c r="H57" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" ht="26" customHeight="1">
+      <c r="A58" s="38" t="inlineStr">
+        <is>
+          <t>4-MONTH TOTAL (all 6 agents)</t>
+        </is>
+      </c>
+      <c r="B58" s="39" t="n"/>
+      <c r="C58" s="39" t="n"/>
+      <c r="D58" s="39" t="n"/>
+      <c r="E58" s="39" t="n"/>
+      <c r="F58" s="39" t="n"/>
+      <c r="G58" s="39" t="n"/>
+      <c r="H58" s="39" t="n"/>
+      <c r="I58" s="39" t="n"/>
+      <c r="J58" s="40" t="n">
+        <v>3875</v>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>SCENARIO 3: 100% FLIP (RWR fully -&gt; REN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="26" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>NB Premium</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>NB Bonus</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>RWR Premium</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>RWR Bonus</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>REN Premium</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>REN Bonus</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>Progress Bar</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL BONUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="25" t="inlineStr">
+        <is>
+          <t>Dialinerys Dieguez</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="C62" s="16" t="n">
+        <v>52434.9</v>
+      </c>
+      <c r="D62" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="E62" s="16" t="n">
+        <v>5962.5</v>
+      </c>
+      <c r="F62" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="16" t="n">
+        <v>96228.35000000001</v>
+      </c>
+      <c r="H62" s="34" t="n">
+        <v>550</v>
+      </c>
+      <c r="I62" s="26" t="n">
+        <v>800</v>
+      </c>
+      <c r="J62" s="36" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="25" t="inlineStr">
+        <is>
+          <t>Monica Valdes</t>
+        </is>
+      </c>
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="C63" s="16" t="n">
+        <v>68546.22</v>
+      </c>
+      <c r="D63" s="34" t="n">
+        <v>375</v>
+      </c>
+      <c r="E63" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="16" t="n">
+        <v>39254.65</v>
+      </c>
+      <c r="H63" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I63" s="26" t="n">
+        <v>625</v>
+      </c>
+      <c r="J63" s="36" t="n">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="25" t="inlineStr">
+        <is>
+          <t>Dialinerys Dieguez</t>
+        </is>
+      </c>
+      <c r="B64" s="14" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C64" s="16" t="n">
+        <v>49689.35</v>
+      </c>
+      <c r="D64" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="E64" s="16" t="n">
+        <v>19575</v>
+      </c>
+      <c r="F64" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="16" t="n">
+        <v>64165.43</v>
+      </c>
+      <c r="H64" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="I64" s="26" t="n">
+        <v>600</v>
+      </c>
+      <c r="J64" s="36" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="25" t="inlineStr">
+        <is>
+          <t>Dialinerys Dieguez</t>
+        </is>
+      </c>
+      <c r="B65" s="14" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="C65" s="16" t="n">
+        <v>30057.89</v>
+      </c>
+      <c r="D65" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="16" t="n">
+        <v>11629.68</v>
+      </c>
+      <c r="F65" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="16" t="n">
+        <v>85544.60000000001</v>
+      </c>
+      <c r="H65" s="34" t="n">
+        <v>550</v>
+      </c>
+      <c r="I65" s="26" t="n">
+        <v>550</v>
+      </c>
+      <c r="J65" s="36" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="25" t="inlineStr">
+        <is>
+          <t>Abel Guaina</t>
+        </is>
+      </c>
+      <c r="B66" s="14" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="C66" s="16" t="n">
+        <v>46523.37</v>
+      </c>
+      <c r="D66" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="E66" s="16" t="n">
+        <v>3901</v>
+      </c>
+      <c r="F66" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="16" t="n">
+        <v>25227.6</v>
+      </c>
+      <c r="H66" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I66" s="26" t="n">
+        <v>500</v>
+      </c>
+      <c r="J66" s="36" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="25" t="inlineStr">
+        <is>
+          <t>Dialinerys Dieguez</t>
+        </is>
+      </c>
+      <c r="B67" s="14" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C67" s="16" t="n">
+        <v>40249.26</v>
+      </c>
+      <c r="D67" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="16" t="n">
+        <v>12530.47</v>
+      </c>
+      <c r="F67" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="16" t="n">
+        <v>65675.38</v>
+      </c>
+      <c r="H67" s="34" t="n">
+        <v>450</v>
+      </c>
+      <c r="I67" s="26" t="n">
+        <v>450</v>
+      </c>
+      <c r="J67" s="36" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="25" t="inlineStr">
+        <is>
+          <t>Melissa Hernandez</t>
+        </is>
+      </c>
+      <c r="B68" s="14" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C68" s="16" t="n">
+        <v>37039</v>
+      </c>
+      <c r="D68" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="16" t="n">
+        <v>63374.5</v>
+      </c>
+      <c r="H68" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="I68" s="26" t="n">
+        <v>350</v>
+      </c>
+      <c r="J68" s="36" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="25" t="inlineStr">
+        <is>
+          <t>Melissa Hernandez</t>
+        </is>
+      </c>
+      <c r="B69" s="14" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="C69" s="16" t="n">
+        <v>7659.5</v>
+      </c>
+      <c r="D69" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="16" t="n">
+        <v>1063</v>
+      </c>
+      <c r="F69" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="16" t="n">
+        <v>49990.7</v>
+      </c>
+      <c r="H69" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="I69" s="26" t="n">
+        <v>350</v>
+      </c>
+      <c r="J69" s="36" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="25" t="inlineStr">
+        <is>
+          <t>Melissa Hernandez</t>
+        </is>
+      </c>
+      <c r="B70" s="14" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="C70" s="16" t="n">
+        <v>39759.7</v>
+      </c>
+      <c r="D70" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="16" t="n">
+        <v>1034</v>
+      </c>
+      <c r="F70" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="16" t="n">
+        <v>56860.6</v>
+      </c>
+      <c r="H70" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="I70" s="26" t="n">
+        <v>350</v>
+      </c>
+      <c r="J70" s="36" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="25" t="inlineStr">
+        <is>
+          <t>Melissa Hernandez</t>
+        </is>
+      </c>
+      <c r="B71" s="14" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C71" s="16" t="n">
+        <v>19288.35</v>
+      </c>
+      <c r="D71" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="16" t="n">
+        <v>43396.2</v>
+      </c>
+      <c r="H71" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="I71" s="26" t="n">
+        <v>350</v>
+      </c>
+      <c r="J71" s="36" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="25" t="inlineStr">
+        <is>
+          <t>Flavia Parra</t>
+        </is>
+      </c>
+      <c r="B72" s="14" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="C72" s="16" t="n">
+        <v>22247.7</v>
+      </c>
+      <c r="D72" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="16" t="n">
+        <v>2099</v>
+      </c>
+      <c r="F72" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="16" t="n">
+        <v>43687.45</v>
+      </c>
+      <c r="H72" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="I72" s="26" t="n">
+        <v>350</v>
+      </c>
+      <c r="J72" s="36" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="25" t="inlineStr">
+        <is>
+          <t>Monica Valdes</t>
+        </is>
+      </c>
+      <c r="B73" s="14" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C73" s="16" t="n">
+        <v>28605.29</v>
+      </c>
+      <c r="D73" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="16" t="n">
+        <v>6502.91</v>
+      </c>
+      <c r="F73" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="16" t="n">
+        <v>48612.96</v>
+      </c>
+      <c r="H73" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="I73" s="26" t="n">
+        <v>350</v>
+      </c>
+      <c r="J73" s="36" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="25" t="inlineStr">
+        <is>
+          <t>Monica Valdes</t>
+        </is>
+      </c>
+      <c r="B74" s="14" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="C74" s="16" t="n">
+        <v>31516.95</v>
+      </c>
+      <c r="D74" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="16" t="n">
+        <v>3092</v>
+      </c>
+      <c r="F74" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="16" t="n">
+        <v>47228.18</v>
+      </c>
+      <c r="H74" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="I74" s="26" t="n">
+        <v>350</v>
+      </c>
+      <c r="J74" s="36" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="25" t="inlineStr">
+        <is>
+          <t>Abel Guaina</t>
+        </is>
+      </c>
+      <c r="B75" s="14" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C75" s="16" t="n">
+        <v>38611.42</v>
+      </c>
+      <c r="D75" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="16" t="n">
         <v>7605</v>
       </c>
-      <c r="H6" s="16" t="n">
-        <v>1734.23</v>
-      </c>
-      <c r="I6" s="34" t="n">
-        <v>0.2280381328073636</v>
-      </c>
-      <c r="J6" s="15" t="n">
-        <v>17</v>
-      </c>
-      <c r="K6" s="16" t="n">
+      <c r="F75" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="16" t="n">
         <v>27518.5</v>
       </c>
-      <c r="L6" s="16" t="n">
-        <v>6186.16</v>
-      </c>
-      <c r="M6" s="34" t="n">
-        <v>0.224800043607028</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="H75" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I75" s="26" t="n">
+        <v>250</v>
+      </c>
+      <c r="J75" s="36" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="25" t="inlineStr">
+        <is>
+          <t>Abel Guaina</t>
+        </is>
+      </c>
+      <c r="B76" s="14" t="inlineStr">
         <is>
           <t>February</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n">
-        <v>13</v>
-      </c>
-      <c r="C7" s="16" t="n">
+      <c r="C76" s="16" t="n">
         <v>25367</v>
       </c>
-      <c r="D7" s="16" t="n">
-        <v>3258.77</v>
-      </c>
-      <c r="E7" s="34" t="n">
-        <v>0.1284649347577561</v>
-      </c>
-      <c r="F7" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="G7" s="16" t="n">
+      <c r="D76" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="16" t="n">
         <v>7517</v>
       </c>
-      <c r="H7" s="16" t="n">
-        <v>1422.16</v>
-      </c>
-      <c r="I7" s="34" t="n">
-        <v>0.1891924970067846</v>
-      </c>
-      <c r="J7" s="15" t="n">
-        <v>19</v>
-      </c>
-      <c r="K7" s="16" t="n">
+      <c r="F76" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="16" t="n">
         <v>30643</v>
       </c>
-      <c r="L7" s="16" t="n">
-        <v>4268.29</v>
-      </c>
-      <c r="M7" s="34" t="n">
-        <v>0.1392908657768495</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="H76" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I76" s="26" t="n">
+        <v>250</v>
+      </c>
+      <c r="J76" s="36" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="25" t="inlineStr">
+        <is>
+          <t>Flavia Parra</t>
+        </is>
+      </c>
+      <c r="B77" s="14" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C77" s="16" t="n">
+        <v>28525.05</v>
+      </c>
+      <c r="D77" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="16" t="n">
+        <v>1464.35</v>
+      </c>
+      <c r="F77" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="16" t="n">
+        <v>39558.05</v>
+      </c>
+      <c r="H77" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I77" s="26" t="n">
+        <v>250</v>
+      </c>
+      <c r="J77" s="36" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="25" t="inlineStr">
+        <is>
+          <t>Flavia Parra</t>
+        </is>
+      </c>
+      <c r="B78" s="14" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C78" s="16" t="n">
+        <v>29581.05</v>
+      </c>
+      <c r="D78" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="16" t="n">
+        <v>885</v>
+      </c>
+      <c r="F78" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="16" t="n">
+        <v>30832.76</v>
+      </c>
+      <c r="H78" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I78" s="26" t="n">
+        <v>250</v>
+      </c>
+      <c r="J78" s="36" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="25" t="inlineStr">
+        <is>
+          <t>Thalia Rojas</t>
+        </is>
+      </c>
+      <c r="B79" s="14" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C79" s="16" t="n">
+        <v>15503.9</v>
+      </c>
+      <c r="D79" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="16" t="n">
+        <v>3690</v>
+      </c>
+      <c r="F79" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="16" t="n">
+        <v>33083.93</v>
+      </c>
+      <c r="H79" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I79" s="26" t="n">
+        <v>250</v>
+      </c>
+      <c r="J79" s="36" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="80" ht="22" customHeight="1">
+      <c r="A80" s="25" t="inlineStr">
+        <is>
+          <t>Thalia Rojas</t>
+        </is>
+      </c>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="C80" s="16" t="n">
+        <v>19414.25</v>
+      </c>
+      <c r="D80" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="16" t="n">
+        <v>7446</v>
+      </c>
+      <c r="F80" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="16" t="n">
+        <v>28298.16</v>
+      </c>
+      <c r="H80" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I80" s="26" t="n">
+        <v>250</v>
+      </c>
+      <c r="J80" s="36" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="81" ht="22" customHeight="1">
+      <c r="A81" s="25" t="inlineStr">
+        <is>
+          <t>Thalia Rojas</t>
+        </is>
+      </c>
+      <c r="B81" s="14" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C81" s="16" t="n">
+        <v>14099</v>
+      </c>
+      <c r="D81" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="16" t="n">
+        <v>3617</v>
+      </c>
+      <c r="F81" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="16" t="n">
+        <v>39794.4</v>
+      </c>
+      <c r="H81" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I81" s="26" t="n">
+        <v>250</v>
+      </c>
+      <c r="J81" s="36" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="82" ht="22" customHeight="1">
+      <c r="A82" s="25" t="inlineStr">
+        <is>
+          <t>Monica Valdes</t>
+        </is>
+      </c>
+      <c r="B82" s="14" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C82" s="16" t="n">
+        <v>29755.49</v>
+      </c>
+      <c r="D82" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="16" t="n">
+        <v>2514</v>
+      </c>
+      <c r="F82" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="16" t="n">
+        <v>35279.9</v>
+      </c>
+      <c r="H82" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I82" s="26" t="n">
+        <v>250</v>
+      </c>
+      <c r="J82" s="36" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="83" ht="22" customHeight="1">
+      <c r="A83" s="25" t="inlineStr">
+        <is>
+          <t>Abel Guaina</t>
+        </is>
+      </c>
+      <c r="B83" s="14" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C83" s="16" t="n">
+        <v>37825.93</v>
+      </c>
+      <c r="D83" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="16" t="n">
+        <v>10935.99</v>
+      </c>
+      <c r="F83" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="16" t="n">
+        <v>15361.95</v>
+      </c>
+      <c r="H83" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" ht="22" customHeight="1">
+      <c r="A84" s="25" t="inlineStr">
+        <is>
+          <t>Flavia Parra</t>
+        </is>
+      </c>
+      <c r="B84" s="14" t="inlineStr">
         <is>
           <t>March</t>
         </is>
       </c>
-      <c r="B8" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="C8" s="16" t="n">
-        <v>46523.37</v>
-      </c>
-      <c r="D8" s="16" t="n">
-        <v>6523.33</v>
-      </c>
-      <c r="E8" s="34" t="n">
-        <v>0.140216196720057</v>
-      </c>
-      <c r="F8" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="G8" s="16" t="n">
-        <v>3901</v>
-      </c>
-      <c r="H8" s="16" t="n">
-        <v>1274.08</v>
-      </c>
-      <c r="I8" s="34" t="n">
-        <v>0.3266034350166624</v>
-      </c>
-      <c r="J8" s="15" t="n">
-        <v>17</v>
-      </c>
-      <c r="K8" s="16" t="n">
-        <v>25227.6</v>
-      </c>
-      <c r="L8" s="16" t="n">
-        <v>5844.85</v>
-      </c>
-      <c r="M8" s="34" t="n">
-        <v>0.2316847421078502</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="n">
-        <v>27</v>
-      </c>
-      <c r="C9" s="16" t="n">
-        <v>37825.93</v>
-      </c>
-      <c r="D9" s="16" t="n">
-        <v>8163.72</v>
-      </c>
-      <c r="E9" s="34" t="n">
-        <v>0.2158233783016042</v>
-      </c>
-      <c r="F9" s="15" t="n">
-        <v>13</v>
-      </c>
-      <c r="G9" s="16" t="n">
-        <v>10935.99</v>
-      </c>
-      <c r="H9" s="16" t="n">
-        <v>5439.19</v>
-      </c>
-      <c r="I9" s="34" t="n">
-        <v>0.4973660363625058</v>
-      </c>
-      <c r="J9" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="K9" s="16" t="n">
-        <v>15361.95</v>
-      </c>
-      <c r="L9" s="16" t="n">
-        <v>3967.81</v>
-      </c>
-      <c r="M9" s="34" t="n">
-        <v>0.2582881730509473</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="35" t="inlineStr">
-        <is>
-          <t>THE BONUS PLAN - bonus calculation under 100% FLIP</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>NB premium</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>NB tier</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>NB bonus</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>RWR premium</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>RWR tier</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>RWR bonus</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>REN premium</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>REN tier</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>REN bonus</t>
-        </is>
-      </c>
-      <c r="K12" s="6" t="inlineStr">
-        <is>
-          <t>Total target</t>
-        </is>
-      </c>
-      <c r="L12" s="6" t="inlineStr">
-        <is>
-          <t>PAID after MIN</t>
-        </is>
-      </c>
-      <c r="M12" s="6" t="inlineStr">
-        <is>
-          <t>Gates</t>
-        </is>
-      </c>
-      <c r="N12" s="6" t="inlineStr">
-        <is>
-          <t>vs Current</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>January</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="n">
-        <v>38611.42</v>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="11" t="n">
-        <v>7605</v>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="G13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="11" t="n">
-        <v>27518.5</v>
-      </c>
-      <c r="I13" s="12" t="inlineStr">
-        <is>
-          <t>T1 $25k</t>
-        </is>
-      </c>
-      <c r="J13" s="11" t="n">
-        <v>250</v>
-      </c>
-      <c r="K13" s="11" t="n">
-        <v>250</v>
-      </c>
-      <c r="L13" s="17" t="n">
-        <v>250</v>
-      </c>
-      <c r="M13" s="36" t="inlineStr">
-        <is>
-          <t>n/Y/n</t>
-        </is>
-      </c>
-      <c r="N13" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>February</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="n">
-        <v>25367</v>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="11" t="n">
-        <v>7517</v>
-      </c>
-      <c r="F14" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="G14" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="11" t="n">
-        <v>30643</v>
-      </c>
-      <c r="I14" s="12" t="inlineStr">
-        <is>
-          <t>T1 $25k</t>
-        </is>
-      </c>
-      <c r="J14" s="11" t="n">
-        <v>250</v>
-      </c>
-      <c r="K14" s="11" t="n">
-        <v>250</v>
-      </c>
-      <c r="L14" s="17" t="n">
-        <v>250</v>
-      </c>
-      <c r="M14" s="36" t="inlineStr">
-        <is>
-          <t>n/Y/n</t>
-        </is>
-      </c>
-      <c r="N14" s="11" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="C84" s="16" t="n">
+        <v>31269</v>
+      </c>
+      <c r="D84" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="16" t="n">
+        <v>23526.7</v>
+      </c>
+      <c r="H84" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" ht="22" customHeight="1">
+      <c r="A85" s="25" t="inlineStr">
+        <is>
+          <t>Thalia Rojas</t>
+        </is>
+      </c>
+      <c r="B85" s="14" t="inlineStr">
         <is>
           <t>March</t>
         </is>
       </c>
-      <c r="B15" s="11" t="n">
-        <v>46523.37</v>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>T1 $45k</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="n">
-        <v>250</v>
-      </c>
-      <c r="E15" s="11" t="n">
-        <v>3901</v>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="11" t="n">
-        <v>25227.6</v>
-      </c>
-      <c r="I15" s="12" t="inlineStr">
-        <is>
-          <t>T1 $25k</t>
-        </is>
-      </c>
-      <c r="J15" s="11" t="n">
-        <v>250</v>
-      </c>
-      <c r="K15" s="11" t="n">
-        <v>500</v>
-      </c>
-      <c r="L15" s="17" t="n">
-        <v>500</v>
-      </c>
-      <c r="M15" s="23" t="inlineStr">
-        <is>
-          <t>Y/Y/Y</t>
-        </is>
-      </c>
-      <c r="N15" s="11" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="n">
-        <v>37825.93</v>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="11" t="n">
-        <v>10935.99</v>
-      </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="G16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="11" t="n">
-        <v>15361.95</v>
-      </c>
-      <c r="I16" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="J16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="36" t="inlineStr">
-        <is>
-          <t>n/Y/n</t>
-        </is>
-      </c>
-      <c r="N16" s="11" t="n">
-        <v>-350</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>4-Month Total</t>
-        </is>
-      </c>
-      <c r="B17" s="37" t="n"/>
-      <c r="C17" s="37" t="n"/>
-      <c r="D17" s="37" t="n"/>
-      <c r="E17" s="37" t="n"/>
-      <c r="F17" s="37" t="n"/>
-      <c r="G17" s="37" t="n"/>
-      <c r="H17" s="37" t="n"/>
-      <c r="I17" s="37" t="n"/>
-      <c r="J17" s="37" t="n"/>
-      <c r="K17" s="37" t="n"/>
-      <c r="L17" s="19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="M17" s="37" t="n"/>
-      <c r="N17" s="19" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Dialinerys Dieguez</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>NB Count</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>NB Premium</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>NB Collected</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>NB Coll %</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>RWR Count</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>RWR Premium</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>RWR Collected</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>RWR Coll %</t>
-        </is>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>REN Count</t>
-        </is>
-      </c>
-      <c r="K20" s="6" t="inlineStr">
-        <is>
-          <t>REN Premium</t>
-        </is>
-      </c>
-      <c r="L20" s="6" t="inlineStr">
-        <is>
-          <t>REN Collected</t>
-        </is>
-      </c>
-      <c r="M20" s="6" t="inlineStr">
-        <is>
-          <t>REN Coll %</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>January</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="n">
-        <v>23</v>
-      </c>
-      <c r="C21" s="16" t="n">
-        <v>40249.26</v>
-      </c>
-      <c r="D21" s="16" t="n">
-        <v>4925</v>
-      </c>
-      <c r="E21" s="34" t="n">
-        <v>0.1223624980931326</v>
-      </c>
-      <c r="F21" s="15" t="n">
-        <v>11</v>
-      </c>
-      <c r="G21" s="16" t="n">
-        <v>12530.47</v>
-      </c>
-      <c r="H21" s="16" t="n">
-        <v>4951.59</v>
-      </c>
-      <c r="I21" s="34" t="n">
-        <v>0.395163948359479</v>
-      </c>
-      <c r="J21" s="15" t="n">
-        <v>48</v>
-      </c>
-      <c r="K21" s="16" t="n">
-        <v>65675.38</v>
-      </c>
-      <c r="L21" s="16" t="n">
-        <v>10936.32</v>
-      </c>
-      <c r="M21" s="34" t="n">
-        <v>0.1665208484518856</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>February</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="n">
-        <v>23</v>
-      </c>
-      <c r="C22" s="16" t="n">
-        <v>30057.89</v>
-      </c>
-      <c r="D22" s="16" t="n">
-        <v>5766.72</v>
-      </c>
-      <c r="E22" s="34" t="n">
-        <v>0.1918537861440041</v>
-      </c>
-      <c r="F22" s="15" t="n">
-        <v>9</v>
-      </c>
-      <c r="G22" s="16" t="n">
-        <v>11629.68</v>
-      </c>
-      <c r="H22" s="16" t="n">
-        <v>1937.6</v>
-      </c>
-      <c r="I22" s="34" t="n">
-        <v>0.1666081955823376</v>
-      </c>
-      <c r="J22" s="15" t="n">
-        <v>56</v>
-      </c>
-      <c r="K22" s="16" t="n">
-        <v>85544.60000000001</v>
-      </c>
-      <c r="L22" s="16" t="n">
-        <v>13931.43</v>
-      </c>
-      <c r="M22" s="34" t="n">
-        <v>0.1628557500999478</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>March</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="n">
-        <v>38</v>
-      </c>
-      <c r="C23" s="16" t="n">
-        <v>52434.9</v>
-      </c>
-      <c r="D23" s="16" t="n">
-        <v>10546.59</v>
-      </c>
-      <c r="E23" s="34" t="n">
-        <v>0.2011368382508596</v>
-      </c>
-      <c r="F23" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="G23" s="16" t="n">
-        <v>5962.5</v>
-      </c>
-      <c r="H23" s="16" t="n">
-        <v>3080</v>
-      </c>
-      <c r="I23" s="34" t="n">
-        <v>0.5165618448637317</v>
-      </c>
-      <c r="J23" s="15" t="n">
-        <v>69</v>
-      </c>
-      <c r="K23" s="16" t="n">
-        <v>96228.35000000001</v>
-      </c>
-      <c r="L23" s="16" t="n">
-        <v>19700.38</v>
-      </c>
-      <c r="M23" s="34" t="n">
-        <v>0.2047253226310126</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-      <c r="B24" s="15" t="n">
-        <v>33</v>
-      </c>
-      <c r="C24" s="16" t="n">
-        <v>49689.35</v>
-      </c>
-      <c r="D24" s="16" t="n">
-        <v>8831.440000000001</v>
-      </c>
-      <c r="E24" s="34" t="n">
-        <v>0.1777330554736579</v>
-      </c>
-      <c r="F24" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G24" s="16" t="n">
-        <v>19575</v>
-      </c>
-      <c r="H24" s="16" t="n">
-        <v>2939.65</v>
-      </c>
-      <c r="I24" s="34" t="n">
-        <v>0.1501736909323116</v>
-      </c>
-      <c r="J24" s="15" t="n">
-        <v>44</v>
-      </c>
-      <c r="K24" s="16" t="n">
-        <v>64165.43</v>
-      </c>
-      <c r="L24" s="16" t="n">
-        <v>16668.05</v>
-      </c>
-      <c r="M24" s="34" t="n">
-        <v>0.2597668245969831</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="35" t="inlineStr">
-        <is>
-          <t>THE BONUS PLAN - bonus calculation under 100% FLIP</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>NB premium</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>NB tier</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>NB bonus</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>RWR premium</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>RWR tier</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>RWR bonus</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>REN premium</t>
-        </is>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>REN tier</t>
-        </is>
-      </c>
-      <c r="J27" s="6" t="inlineStr">
-        <is>
-          <t>REN bonus</t>
-        </is>
-      </c>
-      <c r="K27" s="6" t="inlineStr">
-        <is>
-          <t>Total target</t>
-        </is>
-      </c>
-      <c r="L27" s="6" t="inlineStr">
-        <is>
-          <t>PAID after MIN</t>
-        </is>
-      </c>
-      <c r="M27" s="6" t="inlineStr">
-        <is>
-          <t>Gates</t>
-        </is>
-      </c>
-      <c r="N27" s="6" t="inlineStr">
-        <is>
-          <t>vs Current</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>January</t>
-        </is>
-      </c>
-      <c r="B28" s="11" t="n">
-        <v>40249.26</v>
-      </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="11" t="n">
-        <v>12530.47</v>
-      </c>
-      <c r="F28" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="G28" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="11" t="n">
-        <v>65675.38</v>
-      </c>
-      <c r="I28" s="12" t="inlineStr">
-        <is>
-          <t>T3 $65k</t>
-        </is>
-      </c>
-      <c r="J28" s="11" t="n">
-        <v>450</v>
-      </c>
-      <c r="K28" s="11" t="n">
-        <v>450</v>
-      </c>
-      <c r="L28" s="17" t="n">
-        <v>450</v>
-      </c>
-      <c r="M28" s="36" t="inlineStr">
-        <is>
-          <t>n/Y/n</t>
-        </is>
-      </c>
-      <c r="N28" s="11" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>February</t>
-        </is>
-      </c>
-      <c r="B29" s="11" t="n">
-        <v>30057.89</v>
-      </c>
-      <c r="C29" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>11629.68</v>
-      </c>
-      <c r="F29" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="G29" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="11" t="n">
-        <v>85544.60000000001</v>
-      </c>
-      <c r="I29" s="12" t="inlineStr">
-        <is>
-          <t>T4 $80k</t>
-        </is>
-      </c>
-      <c r="J29" s="11" t="n">
-        <v>550</v>
-      </c>
-      <c r="K29" s="11" t="n">
-        <v>550</v>
-      </c>
-      <c r="L29" s="17" t="n">
-        <v>550</v>
-      </c>
-      <c r="M29" s="36" t="inlineStr">
-        <is>
-          <t>n/Y/n</t>
-        </is>
-      </c>
-      <c r="N29" s="11" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>March</t>
-        </is>
-      </c>
-      <c r="B30" s="11" t="n">
-        <v>52434.9</v>
-      </c>
-      <c r="C30" s="12" t="inlineStr">
-        <is>
-          <t>T1 $45k</t>
-        </is>
-      </c>
-      <c r="D30" s="11" t="n">
-        <v>250</v>
-      </c>
-      <c r="E30" s="11" t="n">
-        <v>5962.5</v>
-      </c>
-      <c r="F30" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="G30" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="11" t="n">
-        <v>96228.35000000001</v>
-      </c>
-      <c r="I30" s="12" t="inlineStr">
-        <is>
-          <t>T4 $80k</t>
-        </is>
-      </c>
-      <c r="J30" s="11" t="n">
-        <v>550</v>
-      </c>
-      <c r="K30" s="11" t="n">
-        <v>800</v>
-      </c>
-      <c r="L30" s="17" t="n">
-        <v>800</v>
-      </c>
-      <c r="M30" s="23" t="inlineStr">
-        <is>
-          <t>Y/Y/Y</t>
-        </is>
-      </c>
-      <c r="N30" s="11" t="n">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="n">
-        <v>49689.35</v>
-      </c>
-      <c r="C31" s="12" t="inlineStr">
-        <is>
-          <t>T1 $45k</t>
-        </is>
-      </c>
-      <c r="D31" s="11" t="n">
-        <v>250</v>
-      </c>
-      <c r="E31" s="11" t="n">
-        <v>19575</v>
-      </c>
-      <c r="F31" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="G31" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="11" t="n">
-        <v>64165.43</v>
-      </c>
-      <c r="I31" s="12" t="inlineStr">
-        <is>
-          <t>T2 $40k</t>
-        </is>
-      </c>
-      <c r="J31" s="11" t="n">
-        <v>350</v>
-      </c>
-      <c r="K31" s="11" t="n">
-        <v>600</v>
-      </c>
-      <c r="L31" s="17" t="n">
-        <v>600</v>
-      </c>
-      <c r="M31" s="23" t="inlineStr">
-        <is>
-          <t>Y/Y/Y</t>
-        </is>
-      </c>
-      <c r="N31" s="11" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="18" t="inlineStr">
-        <is>
-          <t>4-Month Total</t>
-        </is>
-      </c>
-      <c r="B32" s="37" t="n"/>
-      <c r="C32" s="37" t="n"/>
-      <c r="D32" s="37" t="n"/>
-      <c r="E32" s="37" t="n"/>
-      <c r="F32" s="37" t="n"/>
-      <c r="G32" s="37" t="n"/>
-      <c r="H32" s="37" t="n"/>
-      <c r="I32" s="37" t="n"/>
-      <c r="J32" s="37" t="n"/>
-      <c r="K32" s="37" t="n"/>
-      <c r="L32" s="19" t="n">
-        <v>2400</v>
-      </c>
-      <c r="M32" s="37" t="n"/>
-      <c r="N32" s="19" t="n">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>Melissa Hernandez</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>NB Count</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>NB Premium</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>NB Collected</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>NB Coll %</t>
-        </is>
-      </c>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>RWR Count</t>
-        </is>
-      </c>
-      <c r="G35" s="6" t="inlineStr">
-        <is>
-          <t>RWR Premium</t>
-        </is>
-      </c>
-      <c r="H35" s="6" t="inlineStr">
-        <is>
-          <t>RWR Collected</t>
-        </is>
-      </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>RWR Coll %</t>
-        </is>
-      </c>
-      <c r="J35" s="6" t="inlineStr">
-        <is>
-          <t>REN Count</t>
-        </is>
-      </c>
-      <c r="K35" s="6" t="inlineStr">
-        <is>
-          <t>REN Premium</t>
-        </is>
-      </c>
-      <c r="L35" s="6" t="inlineStr">
-        <is>
-          <t>REN Collected</t>
-        </is>
-      </c>
-      <c r="M35" s="6" t="inlineStr">
-        <is>
-          <t>REN Coll %</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="14" t="inlineStr">
-        <is>
-          <t>January</t>
-        </is>
-      </c>
-      <c r="B36" s="15" t="n">
-        <v>31</v>
-      </c>
-      <c r="C36" s="16" t="n">
-        <v>37039</v>
-      </c>
-      <c r="D36" s="16" t="n">
-        <v>7651.14</v>
-      </c>
-      <c r="E36" s="34" t="n">
-        <v>0.2065698317989147</v>
-      </c>
-      <c r="F36" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="15" t="n">
-        <v>48</v>
-      </c>
-      <c r="K36" s="16" t="n">
-        <v>63374.5</v>
-      </c>
-      <c r="L36" s="16" t="n">
-        <v>11897.57</v>
-      </c>
-      <c r="M36" s="34" t="n">
-        <v>0.1877343410993381</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="14" t="inlineStr">
-        <is>
-          <t>February</t>
-        </is>
-      </c>
-      <c r="B37" s="15" t="n">
-        <v>13</v>
-      </c>
-      <c r="C37" s="16" t="n">
-        <v>7659.5</v>
-      </c>
-      <c r="D37" s="16" t="n">
-        <v>2095.02</v>
-      </c>
-      <c r="E37" s="34" t="n">
-        <v>0.2735191592140479</v>
-      </c>
-      <c r="F37" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="16" t="n">
-        <v>1063</v>
-      </c>
-      <c r="H37" s="16" t="n">
-        <v>91.75</v>
-      </c>
-      <c r="I37" s="34" t="n">
-        <v>0.08631232361241768</v>
-      </c>
-      <c r="J37" s="15" t="n">
-        <v>37</v>
-      </c>
-      <c r="K37" s="16" t="n">
-        <v>49990.7</v>
-      </c>
-      <c r="L37" s="16" t="n">
-        <v>6802.73</v>
-      </c>
-      <c r="M37" s="34" t="n">
-        <v>0.1360799108634206</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="14" t="inlineStr">
-        <is>
-          <t>March</t>
-        </is>
-      </c>
-      <c r="B38" s="15" t="n">
-        <v>28</v>
-      </c>
-      <c r="C38" s="16" t="n">
-        <v>39759.7</v>
-      </c>
-      <c r="D38" s="16" t="n">
-        <v>5669.41</v>
-      </c>
-      <c r="E38" s="34" t="n">
-        <v>0.142591870663008</v>
-      </c>
-      <c r="F38" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="16" t="n">
-        <v>1034</v>
-      </c>
-      <c r="H38" s="16" t="n">
-        <v>180.45</v>
-      </c>
-      <c r="I38" s="34" t="n">
-        <v>0.1745164410058027</v>
-      </c>
-      <c r="J38" s="15" t="n">
-        <v>48</v>
-      </c>
-      <c r="K38" s="16" t="n">
-        <v>56860.6</v>
-      </c>
-      <c r="L38" s="16" t="n">
-        <v>8620.469999999999</v>
-      </c>
-      <c r="M38" s="34" t="n">
-        <v>0.1516070882122243</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="14" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-      <c r="B39" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="C39" s="16" t="n">
-        <v>19288.35</v>
-      </c>
-      <c r="D39" s="16" t="n">
-        <v>4344.3</v>
-      </c>
-      <c r="E39" s="34" t="n">
-        <v>0.225229218673448</v>
-      </c>
-      <c r="F39" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="15" t="n">
-        <v>37</v>
-      </c>
-      <c r="K39" s="16" t="n">
-        <v>43396.2</v>
-      </c>
-      <c r="L39" s="16" t="n">
-        <v>7660.7</v>
-      </c>
-      <c r="M39" s="34" t="n">
-        <v>0.1765292813656495</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="35" t="inlineStr">
-        <is>
-          <t>THE BONUS PLAN - bonus calculation under 100% FLIP</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>NB premium</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>NB tier</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>NB bonus</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>RWR premium</t>
-        </is>
-      </c>
-      <c r="F42" s="6" t="inlineStr">
-        <is>
-          <t>RWR tier</t>
-        </is>
-      </c>
-      <c r="G42" s="6" t="inlineStr">
-        <is>
-          <t>RWR bonus</t>
-        </is>
-      </c>
-      <c r="H42" s="6" t="inlineStr">
-        <is>
-          <t>REN premium</t>
-        </is>
-      </c>
-      <c r="I42" s="6" t="inlineStr">
-        <is>
-          <t>REN tier</t>
-        </is>
-      </c>
-      <c r="J42" s="6" t="inlineStr">
-        <is>
-          <t>REN bonus</t>
-        </is>
-      </c>
-      <c r="K42" s="6" t="inlineStr">
-        <is>
-          <t>Total target</t>
-        </is>
-      </c>
-      <c r="L42" s="6" t="inlineStr">
-        <is>
-          <t>PAID after MIN</t>
-        </is>
-      </c>
-      <c r="M42" s="6" t="inlineStr">
-        <is>
-          <t>Gates</t>
-        </is>
-      </c>
-      <c r="N42" s="6" t="inlineStr">
-        <is>
-          <t>vs Current</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="12" t="inlineStr">
-        <is>
-          <t>January</t>
-        </is>
-      </c>
-      <c r="B43" s="11" t="n">
-        <v>37039</v>
-      </c>
-      <c r="C43" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="D43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="G43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="11" t="n">
-        <v>63374.5</v>
-      </c>
-      <c r="I43" s="12" t="inlineStr">
-        <is>
-          <t>T2 $40k</t>
-        </is>
-      </c>
-      <c r="J43" s="11" t="n">
-        <v>350</v>
-      </c>
-      <c r="K43" s="11" t="n">
-        <v>350</v>
-      </c>
-      <c r="L43" s="17" t="n">
-        <v>350</v>
-      </c>
-      <c r="M43" s="36" t="inlineStr">
-        <is>
-          <t>n/Y/n</t>
-        </is>
-      </c>
-      <c r="N43" s="11" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="12" t="inlineStr">
-        <is>
-          <t>February</t>
-        </is>
-      </c>
-      <c r="B44" s="11" t="n">
-        <v>7659.5</v>
-      </c>
-      <c r="C44" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="D44" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="11" t="n">
-        <v>1063</v>
-      </c>
-      <c r="F44" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="G44" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="11" t="n">
-        <v>49990.7</v>
-      </c>
-      <c r="I44" s="12" t="inlineStr">
-        <is>
-          <t>T2 $40k</t>
-        </is>
-      </c>
-      <c r="J44" s="11" t="n">
-        <v>350</v>
-      </c>
-      <c r="K44" s="11" t="n">
-        <v>350</v>
-      </c>
-      <c r="L44" s="17" t="n">
-        <v>350</v>
-      </c>
-      <c r="M44" s="36" t="inlineStr">
-        <is>
-          <t>n/Y/n</t>
-        </is>
-      </c>
-      <c r="N44" s="11" t="n">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="12" t="inlineStr">
-        <is>
-          <t>March</t>
-        </is>
-      </c>
-      <c r="B45" s="11" t="n">
-        <v>39759.7</v>
-      </c>
-      <c r="C45" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="D45" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="11" t="n">
-        <v>1034</v>
-      </c>
-      <c r="F45" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="G45" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="11" t="n">
-        <v>56860.6</v>
-      </c>
-      <c r="I45" s="12" t="inlineStr">
-        <is>
-          <t>T2 $40k</t>
-        </is>
-      </c>
-      <c r="J45" s="11" t="n">
-        <v>350</v>
-      </c>
-      <c r="K45" s="11" t="n">
-        <v>350</v>
-      </c>
-      <c r="L45" s="17" t="n">
-        <v>350</v>
-      </c>
-      <c r="M45" s="36" t="inlineStr">
-        <is>
-          <t>n/Y/n</t>
-        </is>
-      </c>
-      <c r="N45" s="11" t="n">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="12" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-      <c r="B46" s="11" t="n">
-        <v>19288.35</v>
-      </c>
-      <c r="C46" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="D46" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="G46" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="11" t="n">
-        <v>43396.2</v>
-      </c>
-      <c r="I46" s="12" t="inlineStr">
-        <is>
-          <t>T2 $40k</t>
-        </is>
-      </c>
-      <c r="J46" s="11" t="n">
-        <v>350</v>
-      </c>
-      <c r="K46" s="11" t="n">
-        <v>350</v>
-      </c>
-      <c r="L46" s="17" t="n">
-        <v>350</v>
-      </c>
-      <c r="M46" s="36" t="inlineStr">
-        <is>
-          <t>n/Y/n</t>
-        </is>
-      </c>
-      <c r="N46" s="11" t="n">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="18" t="inlineStr">
-        <is>
-          <t>4-Month Total</t>
-        </is>
-      </c>
-      <c r="B47" s="37" t="n"/>
-      <c r="C47" s="37" t="n"/>
-      <c r="D47" s="37" t="n"/>
-      <c r="E47" s="37" t="n"/>
-      <c r="F47" s="37" t="n"/>
-      <c r="G47" s="37" t="n"/>
-      <c r="H47" s="37" t="n"/>
-      <c r="I47" s="37" t="n"/>
-      <c r="J47" s="37" t="n"/>
-      <c r="K47" s="37" t="n"/>
-      <c r="L47" s="19" t="n">
-        <v>1400</v>
-      </c>
-      <c r="M47" s="37" t="n"/>
-      <c r="N47" s="19" t="n">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>Flavia Parra</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>NB Count</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>NB Premium</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>NB Collected</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>NB Coll %</t>
-        </is>
-      </c>
-      <c r="F50" s="6" t="inlineStr">
-        <is>
-          <t>RWR Count</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>RWR Premium</t>
-        </is>
-      </c>
-      <c r="H50" s="6" t="inlineStr">
-        <is>
-          <t>RWR Collected</t>
-        </is>
-      </c>
-      <c r="I50" s="6" t="inlineStr">
-        <is>
-          <t>RWR Coll %</t>
-        </is>
-      </c>
-      <c r="J50" s="6" t="inlineStr">
-        <is>
-          <t>REN Count</t>
-        </is>
-      </c>
-      <c r="K50" s="6" t="inlineStr">
-        <is>
-          <t>REN Premium</t>
-        </is>
-      </c>
-      <c r="L50" s="6" t="inlineStr">
-        <is>
-          <t>REN Collected</t>
-        </is>
-      </c>
-      <c r="M50" s="6" t="inlineStr">
-        <is>
-          <t>REN Coll %</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="14" t="inlineStr">
-        <is>
-          <t>January</t>
-        </is>
-      </c>
-      <c r="B51" s="15" t="n">
-        <v>19</v>
-      </c>
-      <c r="C51" s="16" t="n">
-        <v>28525.05</v>
-      </c>
-      <c r="D51" s="16" t="n">
-        <v>5657.4</v>
-      </c>
-      <c r="E51" s="34" t="n">
-        <v>0.1983309406994904</v>
-      </c>
-      <c r="F51" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" s="16" t="n">
-        <v>1464.35</v>
-      </c>
-      <c r="H51" s="16" t="n">
-        <v>302.12</v>
-      </c>
-      <c r="I51" s="34" t="n">
-        <v>0.2063167958479872</v>
-      </c>
-      <c r="J51" s="15" t="n">
-        <v>35</v>
-      </c>
-      <c r="K51" s="16" t="n">
-        <v>39558.05</v>
-      </c>
-      <c r="L51" s="16" t="n">
-        <v>8795.290000000001</v>
-      </c>
-      <c r="M51" s="34" t="n">
-        <v>0.2223388159932049</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="14" t="inlineStr">
-        <is>
-          <t>February</t>
-        </is>
-      </c>
-      <c r="B52" s="15" t="n">
-        <v>23</v>
-      </c>
-      <c r="C52" s="16" t="n">
-        <v>22247.7</v>
-      </c>
-      <c r="D52" s="16" t="n">
-        <v>3832.59</v>
-      </c>
-      <c r="E52" s="34" t="n">
-        <v>0.1722690435415796</v>
-      </c>
-      <c r="F52" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G52" s="16" t="n">
-        <v>2099</v>
-      </c>
-      <c r="H52" s="16" t="n">
-        <v>321.01</v>
-      </c>
-      <c r="I52" s="34" t="n">
-        <v>0.152934730824202</v>
-      </c>
-      <c r="J52" s="15" t="n">
-        <v>42</v>
-      </c>
-      <c r="K52" s="16" t="n">
-        <v>43687.45</v>
-      </c>
-      <c r="L52" s="16" t="n">
-        <v>13820.09</v>
-      </c>
-      <c r="M52" s="34" t="n">
-        <v>0.3163400473133589</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="14" t="inlineStr">
-        <is>
-          <t>March</t>
-        </is>
-      </c>
-      <c r="B53" s="15" t="n">
-        <v>27</v>
-      </c>
-      <c r="C53" s="16" t="n">
-        <v>31269</v>
-      </c>
-      <c r="D53" s="16" t="n">
-        <v>8642.02</v>
-      </c>
-      <c r="E53" s="34" t="n">
-        <v>0.2763766030253606</v>
-      </c>
-      <c r="F53" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="15" t="n">
-        <v>27</v>
-      </c>
-      <c r="K53" s="16" t="n">
-        <v>23526.7</v>
-      </c>
-      <c r="L53" s="16" t="n">
-        <v>9060.629999999999</v>
-      </c>
-      <c r="M53" s="34" t="n">
-        <v>0.3851211602137146</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="14" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-      <c r="B54" s="15" t="n">
-        <v>23</v>
-      </c>
-      <c r="C54" s="16" t="n">
-        <v>29581.05</v>
-      </c>
-      <c r="D54" s="16" t="n">
-        <v>6600.51</v>
-      </c>
-      <c r="E54" s="34" t="n">
-        <v>0.2231330530863509</v>
-      </c>
-      <c r="F54" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="16" t="n">
-        <v>885</v>
-      </c>
-      <c r="H54" s="16" t="n">
-        <v>885</v>
-      </c>
-      <c r="I54" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" s="15" t="n">
-        <v>31</v>
-      </c>
-      <c r="K54" s="16" t="n">
-        <v>30832.76</v>
-      </c>
-      <c r="L54" s="16" t="n">
-        <v>7710.62</v>
-      </c>
-      <c r="M54" s="34" t="n">
-        <v>0.2500788122762931</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="35" t="inlineStr">
-        <is>
-          <t>THE BONUS PLAN - bonus calculation under 100% FLIP</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>NB premium</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>NB tier</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>NB bonus</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>RWR premium</t>
-        </is>
-      </c>
-      <c r="F57" s="6" t="inlineStr">
-        <is>
-          <t>RWR tier</t>
-        </is>
-      </c>
-      <c r="G57" s="6" t="inlineStr">
-        <is>
-          <t>RWR bonus</t>
-        </is>
-      </c>
-      <c r="H57" s="6" t="inlineStr">
-        <is>
-          <t>REN premium</t>
-        </is>
-      </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>REN tier</t>
-        </is>
-      </c>
-      <c r="J57" s="6" t="inlineStr">
-        <is>
-          <t>REN bonus</t>
-        </is>
-      </c>
-      <c r="K57" s="6" t="inlineStr">
-        <is>
-          <t>Total target</t>
-        </is>
-      </c>
-      <c r="L57" s="6" t="inlineStr">
-        <is>
-          <t>PAID after MIN</t>
-        </is>
-      </c>
-      <c r="M57" s="6" t="inlineStr">
-        <is>
-          <t>Gates</t>
-        </is>
-      </c>
-      <c r="N57" s="6" t="inlineStr">
-        <is>
-          <t>vs Current</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="12" t="inlineStr">
-        <is>
-          <t>January</t>
-        </is>
-      </c>
-      <c r="B58" s="11" t="n">
-        <v>28525.05</v>
-      </c>
-      <c r="C58" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="D58" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" s="11" t="n">
-        <v>1464.35</v>
-      </c>
-      <c r="F58" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="G58" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="11" t="n">
-        <v>39558.05</v>
-      </c>
-      <c r="I58" s="12" t="inlineStr">
-        <is>
-          <t>T1 $25k</t>
-        </is>
-      </c>
-      <c r="J58" s="11" t="n">
-        <v>250</v>
-      </c>
-      <c r="K58" s="11" t="n">
-        <v>250</v>
-      </c>
-      <c r="L58" s="17" t="n">
-        <v>250</v>
-      </c>
-      <c r="M58" s="36" t="inlineStr">
-        <is>
-          <t>n/Y/n</t>
-        </is>
-      </c>
-      <c r="N58" s="11" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t>February</t>
-        </is>
-      </c>
-      <c r="B59" s="11" t="n">
-        <v>22247.7</v>
-      </c>
-      <c r="C59" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="D59" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="11" t="n">
-        <v>2099</v>
-      </c>
-      <c r="F59" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="G59" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" s="11" t="n">
-        <v>43687.45</v>
-      </c>
-      <c r="I59" s="12" t="inlineStr">
-        <is>
-          <t>T2 $40k</t>
-        </is>
-      </c>
-      <c r="J59" s="11" t="n">
-        <v>350</v>
-      </c>
-      <c r="K59" s="11" t="n">
-        <v>350</v>
-      </c>
-      <c r="L59" s="17" t="n">
-        <v>350</v>
-      </c>
-      <c r="M59" s="36" t="inlineStr">
-        <is>
-          <t>n/Y/n</t>
-        </is>
-      </c>
-      <c r="N59" s="11" t="n">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="12" t="inlineStr">
-        <is>
-          <t>March</t>
-        </is>
-      </c>
-      <c r="B60" s="11" t="n">
-        <v>31269</v>
-      </c>
-      <c r="C60" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="D60" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="G60" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" s="11" t="n">
-        <v>23526.7</v>
-      </c>
-      <c r="I60" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="J60" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" s="36" t="inlineStr">
-        <is>
-          <t>n/Y/n</t>
-        </is>
-      </c>
-      <c r="N60" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="12" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-      <c r="B61" s="11" t="n">
-        <v>29581.05</v>
-      </c>
-      <c r="C61" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="D61" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="11" t="n">
-        <v>885</v>
-      </c>
-      <c r="F61" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="G61" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" s="11" t="n">
-        <v>30832.76</v>
-      </c>
-      <c r="I61" s="12" t="inlineStr">
-        <is>
-          <t>T1 $25k</t>
-        </is>
-      </c>
-      <c r="J61" s="11" t="n">
-        <v>250</v>
-      </c>
-      <c r="K61" s="11" t="n">
-        <v>250</v>
-      </c>
-      <c r="L61" s="17" t="n">
-        <v>250</v>
-      </c>
-      <c r="M61" s="36" t="inlineStr">
-        <is>
-          <t>n/Y/n</t>
-        </is>
-      </c>
-      <c r="N61" s="11" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="18" t="inlineStr">
-        <is>
-          <t>4-Month Total</t>
-        </is>
-      </c>
-      <c r="B62" s="37" t="n"/>
-      <c r="C62" s="37" t="n"/>
-      <c r="D62" s="37" t="n"/>
-      <c r="E62" s="37" t="n"/>
-      <c r="F62" s="37" t="n"/>
-      <c r="G62" s="37" t="n"/>
-      <c r="H62" s="37" t="n"/>
-      <c r="I62" s="37" t="n"/>
-      <c r="J62" s="37" t="n"/>
-      <c r="K62" s="37" t="n"/>
-      <c r="L62" s="19" t="n">
-        <v>850</v>
-      </c>
-      <c r="M62" s="37" t="n"/>
-      <c r="N62" s="19" t="n">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>Thalia Rojas</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>NB Count</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>NB Premium</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>NB Collected</t>
-        </is>
-      </c>
-      <c r="E65" s="6" t="inlineStr">
-        <is>
-          <t>NB Coll %</t>
-        </is>
-      </c>
-      <c r="F65" s="6" t="inlineStr">
-        <is>
-          <t>RWR Count</t>
-        </is>
-      </c>
-      <c r="G65" s="6" t="inlineStr">
-        <is>
-          <t>RWR Premium</t>
-        </is>
-      </c>
-      <c r="H65" s="6" t="inlineStr">
-        <is>
-          <t>RWR Collected</t>
-        </is>
-      </c>
-      <c r="I65" s="6" t="inlineStr">
-        <is>
-          <t>RWR Coll %</t>
-        </is>
-      </c>
-      <c r="J65" s="6" t="inlineStr">
-        <is>
-          <t>REN Count</t>
-        </is>
-      </c>
-      <c r="K65" s="6" t="inlineStr">
-        <is>
-          <t>REN Premium</t>
-        </is>
-      </c>
-      <c r="L65" s="6" t="inlineStr">
-        <is>
-          <t>REN Collected</t>
-        </is>
-      </c>
-      <c r="M65" s="6" t="inlineStr">
-        <is>
-          <t>REN Coll %</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="14" t="inlineStr">
-        <is>
-          <t>January</t>
-        </is>
-      </c>
-      <c r="B66" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="C66" s="16" t="n">
-        <v>15503.9</v>
-      </c>
-      <c r="D66" s="16" t="n">
-        <v>2238.28</v>
-      </c>
-      <c r="E66" s="34" t="n">
-        <v>0.1443688362283039</v>
-      </c>
-      <c r="F66" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="G66" s="16" t="n">
-        <v>3690</v>
-      </c>
-      <c r="H66" s="16" t="n">
-        <v>642.04</v>
-      </c>
-      <c r="I66" s="34" t="n">
-        <v>0.1739945799457994</v>
-      </c>
-      <c r="J66" s="15" t="n">
-        <v>28</v>
-      </c>
-      <c r="K66" s="16" t="n">
-        <v>33083.93</v>
-      </c>
-      <c r="L66" s="16" t="n">
-        <v>6461.48</v>
-      </c>
-      <c r="M66" s="34" t="n">
-        <v>0.1953056967536807</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="14" t="inlineStr">
-        <is>
-          <t>February</t>
-        </is>
-      </c>
-      <c r="B67" s="15" t="n">
-        <v>14</v>
-      </c>
-      <c r="C67" s="16" t="n">
-        <v>19414.25</v>
-      </c>
-      <c r="D67" s="16" t="n">
-        <v>3640.91</v>
-      </c>
-      <c r="E67" s="34" t="n">
-        <v>0.1875380197535315</v>
-      </c>
-      <c r="F67" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="G67" s="16" t="n">
-        <v>7446</v>
-      </c>
-      <c r="H67" s="16" t="n">
-        <v>3293.14</v>
-      </c>
-      <c r="I67" s="34" t="n">
-        <v>0.442269674993285</v>
-      </c>
-      <c r="J67" s="15" t="n">
-        <v>24</v>
-      </c>
-      <c r="K67" s="16" t="n">
-        <v>28298.16</v>
-      </c>
-      <c r="L67" s="16" t="n">
-        <v>5276.12</v>
-      </c>
-      <c r="M67" s="34" t="n">
-        <v>0.186447458067945</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="14" t="inlineStr">
-        <is>
-          <t>March</t>
-        </is>
-      </c>
-      <c r="B68" s="15" t="n">
-        <v>19</v>
-      </c>
-      <c r="C68" s="16" t="n">
+      <c r="C85" s="16" t="n">
         <v>17843.69</v>
       </c>
-      <c r="D68" s="16" t="n">
-        <v>4965.76</v>
-      </c>
-      <c r="E68" s="34" t="n">
-        <v>0.2782922142225067</v>
-      </c>
-      <c r="F68" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="G68" s="16" t="n">
+      <c r="D85" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="16" t="n">
         <v>5643.9</v>
       </c>
-      <c r="H68" s="16" t="n">
-        <v>1575.86</v>
-      </c>
-      <c r="I68" s="34" t="n">
-        <v>0.2792147274048087</v>
-      </c>
-      <c r="J68" s="15" t="n">
-        <v>19</v>
-      </c>
-      <c r="K68" s="16" t="n">
+      <c r="F85" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="16" t="n">
         <v>19840.85</v>
       </c>
-      <c r="L68" s="16" t="n">
-        <v>3981.64</v>
-      </c>
-      <c r="M68" s="34" t="n">
-        <v>0.2006789023655741</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="14" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-      <c r="B69" s="15" t="n">
-        <v>9</v>
-      </c>
-      <c r="C69" s="16" t="n">
-        <v>14099</v>
-      </c>
-      <c r="D69" s="16" t="n">
-        <v>3941.94</v>
-      </c>
-      <c r="E69" s="34" t="n">
-        <v>0.2795900418469395</v>
-      </c>
-      <c r="F69" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="G69" s="16" t="n">
-        <v>3617</v>
-      </c>
-      <c r="H69" s="16" t="n">
-        <v>3096.58</v>
-      </c>
-      <c r="I69" s="34" t="n">
-        <v>0.8561183301078241</v>
-      </c>
-      <c r="J69" s="15" t="n">
-        <v>29</v>
-      </c>
-      <c r="K69" s="16" t="n">
-        <v>39794.4</v>
-      </c>
-      <c r="L69" s="16" t="n">
-        <v>7674.9</v>
-      </c>
-      <c r="M69" s="34" t="n">
-        <v>0.1928638200349798</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="35" t="inlineStr">
-        <is>
-          <t>THE BONUS PLAN - bonus calculation under 100% FLIP</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>NB premium</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>NB tier</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>NB bonus</t>
-        </is>
-      </c>
-      <c r="E72" s="6" t="inlineStr">
-        <is>
-          <t>RWR premium</t>
-        </is>
-      </c>
-      <c r="F72" s="6" t="inlineStr">
-        <is>
-          <t>RWR tier</t>
-        </is>
-      </c>
-      <c r="G72" s="6" t="inlineStr">
-        <is>
-          <t>RWR bonus</t>
-        </is>
-      </c>
-      <c r="H72" s="6" t="inlineStr">
-        <is>
-          <t>REN premium</t>
-        </is>
-      </c>
-      <c r="I72" s="6" t="inlineStr">
-        <is>
-          <t>REN tier</t>
-        </is>
-      </c>
-      <c r="J72" s="6" t="inlineStr">
-        <is>
-          <t>REN bonus</t>
-        </is>
-      </c>
-      <c r="K72" s="6" t="inlineStr">
-        <is>
-          <t>Total target</t>
-        </is>
-      </c>
-      <c r="L72" s="6" t="inlineStr">
-        <is>
-          <t>PAID after MIN</t>
-        </is>
-      </c>
-      <c r="M72" s="6" t="inlineStr">
-        <is>
-          <t>Gates</t>
-        </is>
-      </c>
-      <c r="N72" s="6" t="inlineStr">
-        <is>
-          <t>vs Current</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="12" t="inlineStr">
-        <is>
-          <t>January</t>
-        </is>
-      </c>
-      <c r="B73" s="11" t="n">
-        <v>15503.9</v>
-      </c>
-      <c r="C73" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="D73" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" s="11" t="n">
-        <v>3690</v>
-      </c>
-      <c r="F73" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="G73" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" s="11" t="n">
-        <v>33083.93</v>
-      </c>
-      <c r="I73" s="12" t="inlineStr">
-        <is>
-          <t>T1 $25k</t>
-        </is>
-      </c>
-      <c r="J73" s="11" t="n">
-        <v>250</v>
-      </c>
-      <c r="K73" s="11" t="n">
-        <v>250</v>
-      </c>
-      <c r="L73" s="17" t="n">
-        <v>250</v>
-      </c>
-      <c r="M73" s="36" t="inlineStr">
-        <is>
-          <t>n/Y/n</t>
-        </is>
-      </c>
-      <c r="N73" s="11" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="12" t="inlineStr">
-        <is>
-          <t>February</t>
-        </is>
-      </c>
-      <c r="B74" s="11" t="n">
-        <v>19414.25</v>
-      </c>
-      <c r="C74" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="D74" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" s="11" t="n">
-        <v>7446</v>
-      </c>
-      <c r="F74" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="G74" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" s="11" t="n">
-        <v>28298.16</v>
-      </c>
-      <c r="I74" s="12" t="inlineStr">
-        <is>
-          <t>T1 $25k</t>
-        </is>
-      </c>
-      <c r="J74" s="11" t="n">
-        <v>250</v>
-      </c>
-      <c r="K74" s="11" t="n">
-        <v>250</v>
-      </c>
-      <c r="L74" s="17" t="n">
-        <v>250</v>
-      </c>
-      <c r="M74" s="36" t="inlineStr">
-        <is>
-          <t>n/Y/n</t>
-        </is>
-      </c>
-      <c r="N74" s="11" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="12" t="inlineStr">
-        <is>
-          <t>March</t>
-        </is>
-      </c>
-      <c r="B75" s="11" t="n">
-        <v>17843.69</v>
-      </c>
-      <c r="C75" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="D75" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" s="11" t="n">
-        <v>5643.9</v>
-      </c>
-      <c r="F75" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="G75" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="11" t="n">
-        <v>19840.85</v>
-      </c>
-      <c r="I75" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="J75" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" s="36" t="inlineStr">
-        <is>
-          <t>n/Y/n</t>
-        </is>
-      </c>
-      <c r="N75" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="12" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-      <c r="B76" s="11" t="n">
-        <v>14099</v>
-      </c>
-      <c r="C76" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="D76" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" s="11" t="n">
-        <v>3617</v>
-      </c>
-      <c r="F76" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="G76" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" s="11" t="n">
-        <v>39794.4</v>
-      </c>
-      <c r="I76" s="12" t="inlineStr">
-        <is>
-          <t>T1 $25k</t>
-        </is>
-      </c>
-      <c r="J76" s="11" t="n">
-        <v>250</v>
-      </c>
-      <c r="K76" s="11" t="n">
-        <v>250</v>
-      </c>
-      <c r="L76" s="17" t="n">
-        <v>250</v>
-      </c>
-      <c r="M76" s="36" t="inlineStr">
-        <is>
-          <t>n/Y/n</t>
-        </is>
-      </c>
-      <c r="N76" s="11" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="18" t="inlineStr">
-        <is>
-          <t>4-Month Total</t>
-        </is>
-      </c>
-      <c r="B77" s="37" t="n"/>
-      <c r="C77" s="37" t="n"/>
-      <c r="D77" s="37" t="n"/>
-      <c r="E77" s="37" t="n"/>
-      <c r="F77" s="37" t="n"/>
-      <c r="G77" s="37" t="n"/>
-      <c r="H77" s="37" t="n"/>
-      <c r="I77" s="37" t="n"/>
-      <c r="J77" s="37" t="n"/>
-      <c r="K77" s="37" t="n"/>
-      <c r="L77" s="19" t="n">
-        <v>750</v>
-      </c>
-      <c r="M77" s="37" t="n"/>
-      <c r="N77" s="19" t="n">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>Monica Valdes</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
-        <is>
-          <t>NB Count</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>NB Premium</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>NB Collected</t>
-        </is>
-      </c>
-      <c r="E80" s="6" t="inlineStr">
-        <is>
-          <t>NB Coll %</t>
-        </is>
-      </c>
-      <c r="F80" s="6" t="inlineStr">
-        <is>
-          <t>RWR Count</t>
-        </is>
-      </c>
-      <c r="G80" s="6" t="inlineStr">
-        <is>
-          <t>RWR Premium</t>
-        </is>
-      </c>
-      <c r="H80" s="6" t="inlineStr">
-        <is>
-          <t>RWR Collected</t>
-        </is>
-      </c>
-      <c r="I80" s="6" t="inlineStr">
-        <is>
-          <t>RWR Coll %</t>
-        </is>
-      </c>
-      <c r="J80" s="6" t="inlineStr">
-        <is>
-          <t>REN Count</t>
-        </is>
-      </c>
-      <c r="K80" s="6" t="inlineStr">
-        <is>
-          <t>REN Premium</t>
-        </is>
-      </c>
-      <c r="L80" s="6" t="inlineStr">
-        <is>
-          <t>REN Collected</t>
-        </is>
-      </c>
-      <c r="M80" s="6" t="inlineStr">
-        <is>
-          <t>REN Coll %</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="14" t="inlineStr">
-        <is>
-          <t>January</t>
-        </is>
-      </c>
-      <c r="B81" s="15" t="n">
-        <v>23</v>
-      </c>
-      <c r="C81" s="16" t="n">
-        <v>28605.29</v>
-      </c>
-      <c r="D81" s="16" t="n">
-        <v>6551.7</v>
-      </c>
-      <c r="E81" s="34" t="n">
-        <v>0.2290380555484667</v>
-      </c>
-      <c r="F81" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="G81" s="16" t="n">
-        <v>6502.91</v>
-      </c>
-      <c r="H81" s="16" t="n">
-        <v>1439.3</v>
-      </c>
-      <c r="I81" s="34" t="n">
-        <v>0.2213316807398534</v>
-      </c>
-      <c r="J81" s="15" t="n">
-        <v>37</v>
-      </c>
-      <c r="K81" s="16" t="n">
-        <v>48612.96</v>
-      </c>
-      <c r="L81" s="16" t="n">
-        <v>8203.879999999999</v>
-      </c>
-      <c r="M81" s="34" t="n">
-        <v>0.1687591127962584</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="14" t="inlineStr">
-        <is>
-          <t>February</t>
-        </is>
-      </c>
-      <c r="B82" s="15" t="n">
-        <v>21</v>
-      </c>
-      <c r="C82" s="16" t="n">
-        <v>31516.95</v>
-      </c>
-      <c r="D82" s="16" t="n">
-        <v>6512.87</v>
-      </c>
-      <c r="E82" s="34" t="n">
-        <v>0.206646582235908</v>
-      </c>
-      <c r="F82" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G82" s="16" t="n">
-        <v>3092</v>
-      </c>
-      <c r="H82" s="16" t="n">
-        <v>272.87</v>
-      </c>
-      <c r="I82" s="34" t="n">
-        <v>0.0882503234152652</v>
-      </c>
-      <c r="J82" s="15" t="n">
-        <v>29</v>
-      </c>
-      <c r="K82" s="16" t="n">
-        <v>47228.18</v>
-      </c>
-      <c r="L82" s="16" t="n">
-        <v>7155.23</v>
-      </c>
-      <c r="M82" s="34" t="n">
-        <v>0.1515034032647457</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="14" t="inlineStr">
-        <is>
-          <t>March</t>
-        </is>
-      </c>
-      <c r="B83" s="15" t="n">
-        <v>36</v>
-      </c>
-      <c r="C83" s="16" t="n">
-        <v>68546.22</v>
-      </c>
-      <c r="D83" s="16" t="n">
-        <v>17019.79</v>
-      </c>
-      <c r="E83" s="34" t="n">
-        <v>0.2482965508528406</v>
-      </c>
-      <c r="F83" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="15" t="n">
-        <v>28</v>
-      </c>
-      <c r="K83" s="16" t="n">
-        <v>39254.65</v>
-      </c>
-      <c r="L83" s="16" t="n">
-        <v>5300.53</v>
-      </c>
-      <c r="M83" s="34" t="n">
-        <v>0.135029353210384</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="14" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-      <c r="B84" s="15" t="n">
-        <v>22</v>
-      </c>
-      <c r="C84" s="16" t="n">
-        <v>29755.49</v>
-      </c>
-      <c r="D84" s="16" t="n">
-        <v>6197.26</v>
-      </c>
-      <c r="E84" s="34" t="n">
-        <v>0.2082728262918876</v>
-      </c>
-      <c r="F84" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G84" s="16" t="n">
-        <v>2514</v>
-      </c>
-      <c r="H84" s="16" t="n">
-        <v>291.12</v>
-      </c>
-      <c r="I84" s="34" t="n">
-        <v>0.115799522673031</v>
-      </c>
-      <c r="J84" s="15" t="n">
-        <v>22</v>
-      </c>
-      <c r="K84" s="16" t="n">
-        <v>35279.9</v>
-      </c>
-      <c r="L84" s="16" t="n">
-        <v>7305.79</v>
-      </c>
-      <c r="M84" s="34" t="n">
-        <v>0.2070808023832267</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="35" t="inlineStr">
-        <is>
-          <t>THE BONUS PLAN - bonus calculation under 100% FLIP</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t>NB premium</t>
-        </is>
-      </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>NB tier</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>NB bonus</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t>RWR premium</t>
-        </is>
-      </c>
-      <c r="F87" s="6" t="inlineStr">
-        <is>
-          <t>RWR tier</t>
-        </is>
-      </c>
-      <c r="G87" s="6" t="inlineStr">
-        <is>
-          <t>RWR bonus</t>
-        </is>
-      </c>
-      <c r="H87" s="6" t="inlineStr">
-        <is>
-          <t>REN premium</t>
-        </is>
-      </c>
-      <c r="I87" s="6" t="inlineStr">
-        <is>
-          <t>REN tier</t>
-        </is>
-      </c>
-      <c r="J87" s="6" t="inlineStr">
-        <is>
-          <t>REN bonus</t>
-        </is>
-      </c>
-      <c r="K87" s="6" t="inlineStr">
-        <is>
-          <t>Total target</t>
-        </is>
-      </c>
-      <c r="L87" s="6" t="inlineStr">
-        <is>
-          <t>PAID after MIN</t>
-        </is>
-      </c>
-      <c r="M87" s="6" t="inlineStr">
-        <is>
-          <t>Gates</t>
-        </is>
-      </c>
-      <c r="N87" s="6" t="inlineStr">
-        <is>
-          <t>vs Current</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="12" t="inlineStr">
-        <is>
-          <t>January</t>
-        </is>
-      </c>
-      <c r="B88" s="11" t="n">
-        <v>28605.29</v>
-      </c>
-      <c r="C88" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="D88" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" s="11" t="n">
-        <v>6502.91</v>
-      </c>
-      <c r="F88" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="G88" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H88" s="11" t="n">
-        <v>48612.96</v>
-      </c>
-      <c r="I88" s="12" t="inlineStr">
-        <is>
-          <t>T2 $40k</t>
-        </is>
-      </c>
-      <c r="J88" s="11" t="n">
-        <v>350</v>
-      </c>
-      <c r="K88" s="11" t="n">
-        <v>350</v>
-      </c>
-      <c r="L88" s="17" t="n">
-        <v>350</v>
-      </c>
-      <c r="M88" s="36" t="inlineStr">
-        <is>
-          <t>n/Y/n</t>
-        </is>
-      </c>
-      <c r="N88" s="11" t="n">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="12" t="inlineStr">
-        <is>
-          <t>February</t>
-        </is>
-      </c>
-      <c r="B89" s="11" t="n">
-        <v>31516.95</v>
-      </c>
-      <c r="C89" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="D89" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E89" s="11" t="n">
-        <v>3092</v>
-      </c>
-      <c r="F89" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="G89" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H89" s="11" t="n">
-        <v>47228.18</v>
-      </c>
-      <c r="I89" s="12" t="inlineStr">
-        <is>
-          <t>T2 $40k</t>
-        </is>
-      </c>
-      <c r="J89" s="11" t="n">
-        <v>350</v>
-      </c>
-      <c r="K89" s="11" t="n">
-        <v>350</v>
-      </c>
-      <c r="L89" s="17" t="n">
-        <v>350</v>
-      </c>
-      <c r="M89" s="36" t="inlineStr">
-        <is>
-          <t>n/Y/n</t>
-        </is>
-      </c>
-      <c r="N89" s="11" t="n">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="12" t="inlineStr">
-        <is>
-          <t>March</t>
-        </is>
-      </c>
-      <c r="B90" s="11" t="n">
-        <v>68546.22</v>
-      </c>
-      <c r="C90" s="12" t="inlineStr">
-        <is>
-          <t>T2 $55k</t>
-        </is>
-      </c>
-      <c r="D90" s="11" t="n">
-        <v>375</v>
-      </c>
-      <c r="E90" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="G90" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H90" s="11" t="n">
-        <v>39254.65</v>
-      </c>
-      <c r="I90" s="12" t="inlineStr">
-        <is>
-          <t>T1 $25k</t>
-        </is>
-      </c>
-      <c r="J90" s="11" t="n">
-        <v>250</v>
-      </c>
-      <c r="K90" s="11" t="n">
-        <v>625</v>
-      </c>
-      <c r="L90" s="17" t="n">
-        <v>625</v>
-      </c>
-      <c r="M90" s="23" t="inlineStr">
-        <is>
-          <t>Y/Y/Y</t>
-        </is>
-      </c>
-      <c r="N90" s="11" t="n">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="12" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-      <c r="B91" s="11" t="n">
-        <v>29755.49</v>
-      </c>
-      <c r="C91" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="D91" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" s="11" t="n">
-        <v>2514</v>
-      </c>
-      <c r="F91" s="12" t="inlineStr">
-        <is>
-          <t>Below T1</t>
-        </is>
-      </c>
-      <c r="G91" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" s="11" t="n">
-        <v>35279.9</v>
-      </c>
-      <c r="I91" s="12" t="inlineStr">
-        <is>
-          <t>T1 $25k</t>
-        </is>
-      </c>
-      <c r="J91" s="11" t="n">
-        <v>250</v>
-      </c>
-      <c r="K91" s="11" t="n">
-        <v>250</v>
-      </c>
-      <c r="L91" s="17" t="n">
-        <v>250</v>
-      </c>
-      <c r="M91" s="36" t="inlineStr">
-        <is>
-          <t>n/Y/n</t>
-        </is>
-      </c>
-      <c r="N91" s="11" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="18" t="inlineStr">
-        <is>
-          <t>4-Month Total</t>
-        </is>
-      </c>
-      <c r="B92" s="37" t="n"/>
-      <c r="C92" s="37" t="n"/>
-      <c r="D92" s="37" t="n"/>
-      <c r="E92" s="37" t="n"/>
-      <c r="F92" s="37" t="n"/>
-      <c r="G92" s="37" t="n"/>
-      <c r="H92" s="37" t="n"/>
-      <c r="I92" s="37" t="n"/>
-      <c r="J92" s="37" t="n"/>
-      <c r="K92" s="37" t="n"/>
-      <c r="L92" s="19" t="n">
-        <v>1575</v>
-      </c>
-      <c r="M92" s="37" t="n"/>
-      <c r="N92" s="19" t="n">
-        <v>1225</v>
+      <c r="H85" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" ht="26" customHeight="1">
+      <c r="A86" s="38" t="inlineStr">
+        <is>
+          <t>4-MONTH TOTAL (all 6 agents)</t>
+        </is>
+      </c>
+      <c r="B86" s="39" t="n"/>
+      <c r="C86" s="39" t="n"/>
+      <c r="D86" s="39" t="n"/>
+      <c r="E86" s="39" t="n"/>
+      <c r="F86" s="39" t="n"/>
+      <c r="G86" s="39" t="n"/>
+      <c r="H86" s="39" t="n"/>
+      <c r="I86" s="39" t="n"/>
+      <c r="J86" s="40" t="n">
+        <v>7975</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A19:M19"/>
-    <mergeCell ref="A79:M79"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A34:M34"/>
-    <mergeCell ref="A56:M56"/>
-    <mergeCell ref="A4:M4"/>
-    <mergeCell ref="A26:M26"/>
-    <mergeCell ref="A86:M86"/>
-    <mergeCell ref="A49:M49"/>
-    <mergeCell ref="A64:M64"/>
-    <mergeCell ref="A41:M41"/>
-    <mergeCell ref="A71:M71"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="A1:N1"/>
+  <mergeCells count="5">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A60:J60"/>
   </mergeCells>
+  <conditionalFormatting sqref="I6:I29">
+    <cfRule type="dataBar" priority="1">
+      <dataBar showValue="0">
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2500"/>
+        <color rgb="0063BE7B"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I34:I57">
+    <cfRule type="dataBar" priority="2">
+      <dataBar showValue="0">
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2500"/>
+        <color rgb="0063BE7B"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I62:I85">
+    <cfRule type="dataBar" priority="3">
+      <dataBar showValue="0">
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2500"/>
+        <color rgb="0063BE7B"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15775,37 +15241,37 @@
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="38" t="inlineStr">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="38" t="inlineStr">
+      <c r="B6" s="41" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="C6" s="38" t="inlineStr">
+      <c r="C6" s="41" t="inlineStr">
         <is>
           <t>Verify premium, collected, PIF, coverages</t>
         </is>
       </c>
-      <c r="D6" s="38" t="inlineStr">
+      <c r="D6" s="41" t="inlineStr">
         <is>
           <t>Before payroll</t>
         </is>
       </c>
-      <c r="E6" s="38" t="inlineStr">
+      <c r="E6" s="41" t="inlineStr">
         <is>
           <t>Receipts, dec page, MVR, carrier proof</t>
         </is>
       </c>
-      <c r="F6" s="38" t="inlineStr">
+      <c r="F6" s="41" t="inlineStr">
         <is>
           <t>Approved or denied</t>
         </is>
       </c>
-      <c r="G6" s="38" t="inlineStr">
+      <c r="G6" s="41" t="inlineStr">
         <is>
           <t>BI/UM proof attached</t>
         </is>
@@ -15849,37 +15315,37 @@
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="38" t="inlineStr">
+      <c r="A8" s="41" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="38" t="inlineStr">
+      <c r="B8" s="41" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="C8" s="38" t="inlineStr">
+      <c r="C8" s="41" t="inlineStr">
         <is>
           <t>Review policy 90 days after effective</t>
         </is>
       </c>
-      <c r="D8" s="38" t="inlineStr">
+      <c r="D8" s="41" t="inlineStr">
         <is>
           <t>Month 3</t>
         </is>
       </c>
-      <c r="E8" s="38" t="inlineStr">
+      <c r="E8" s="41" t="inlineStr">
         <is>
           <t>Carrier status, cancel/rewrite report</t>
         </is>
       </c>
-      <c r="F8" s="38" t="inlineStr">
+      <c r="F8" s="41" t="inlineStr">
         <is>
           <t>Keep or chargeback</t>
         </is>
       </c>
-      <c r="G8" s="38" t="inlineStr">
+      <c r="G8" s="41" t="inlineStr">
         <is>
           <t>Jan 12 reviewed Apr 12</t>
         </is>
@@ -15923,37 +15389,37 @@
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="38" t="inlineStr">
+      <c r="A10" s="41" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B10" s="38" t="inlineStr">
+      <c r="B10" s="41" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="C10" s="38" t="inlineStr">
+      <c r="C10" s="41" t="inlineStr">
         <is>
           <t>Document exception if ownership approves</t>
         </is>
       </c>
-      <c r="D10" s="38" t="inlineStr">
+      <c r="D10" s="41" t="inlineStr">
         <is>
           <t>As needed</t>
         </is>
       </c>
-      <c r="E10" s="38" t="inlineStr">
+      <c r="E10" s="41" t="inlineStr">
         <is>
           <t>Written approval</t>
         </is>
       </c>
-      <c r="F10" s="38" t="inlineStr">
+      <c r="F10" s="41" t="inlineStr">
         <is>
           <t>Exception logged</t>
         </is>
       </c>
-      <c r="G10" s="38" t="inlineStr">
+      <c r="G10" s="41" t="inlineStr">
         <is>
           <t>Carrier error fix</t>
         </is>
@@ -16053,129 +15519,129 @@
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="39" t="inlineStr">
+      <c r="A4" s="42" t="inlineStr">
         <is>
           <t>NB tiered bonus</t>
         </is>
       </c>
-      <c r="B4" s="39" t="inlineStr">
+      <c r="B4" s="42" t="inlineStr">
         <is>
           <t>Monthly NB written premium: T1 $45k=$250 | T2 $55k=$375 | T3 $70k=$525 | T4 $85k=$725 | T5 $100k=$1,000. Above $100k: +$50 per $5k.</t>
         </is>
       </c>
-      <c r="C4" s="40" t="n"/>
-      <c r="D4" s="40" t="n"/>
-      <c r="E4" s="40" t="n"/>
-      <c r="F4" s="40" t="n"/>
-      <c r="G4" s="40" t="n"/>
-      <c r="H4" s="40" t="n"/>
-      <c r="I4" s="40" t="n"/>
-      <c r="J4" s="40" t="n"/>
-      <c r="K4" s="40" t="n"/>
-      <c r="L4" s="40" t="n"/>
-      <c r="M4" s="40" t="n"/>
-      <c r="N4" s="40" t="n"/>
-      <c r="O4" s="41" t="n"/>
+      <c r="C4" s="43" t="n"/>
+      <c r="D4" s="43" t="n"/>
+      <c r="E4" s="43" t="n"/>
+      <c r="F4" s="43" t="n"/>
+      <c r="G4" s="43" t="n"/>
+      <c r="H4" s="43" t="n"/>
+      <c r="I4" s="43" t="n"/>
+      <c r="J4" s="43" t="n"/>
+      <c r="K4" s="43" t="n"/>
+      <c r="L4" s="43" t="n"/>
+      <c r="M4" s="43" t="n"/>
+      <c r="N4" s="43" t="n"/>
+      <c r="O4" s="44" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="39" t="inlineStr">
+      <c r="A5" s="42" t="inlineStr">
         <is>
           <t>RWR tiered bonus</t>
         </is>
       </c>
-      <c r="B5" s="39" t="inlineStr">
+      <c r="B5" s="42" t="inlineStr">
         <is>
           <t>Same breakpoints as NB, pays ~half: T1=$100 | T2=$200 | T3=$275 | T4=$350 | T5=$500. Above $100k: +$25 per $5k.</t>
         </is>
       </c>
-      <c r="C5" s="40" t="n"/>
-      <c r="D5" s="40" t="n"/>
-      <c r="E5" s="40" t="n"/>
-      <c r="F5" s="40" t="n"/>
-      <c r="G5" s="40" t="n"/>
-      <c r="H5" s="40" t="n"/>
-      <c r="I5" s="40" t="n"/>
-      <c r="J5" s="40" t="n"/>
-      <c r="K5" s="40" t="n"/>
-      <c r="L5" s="40" t="n"/>
-      <c r="M5" s="40" t="n"/>
-      <c r="N5" s="40" t="n"/>
-      <c r="O5" s="41" t="n"/>
+      <c r="C5" s="43" t="n"/>
+      <c r="D5" s="43" t="n"/>
+      <c r="E5" s="43" t="n"/>
+      <c r="F5" s="43" t="n"/>
+      <c r="G5" s="43" t="n"/>
+      <c r="H5" s="43" t="n"/>
+      <c r="I5" s="43" t="n"/>
+      <c r="J5" s="43" t="n"/>
+      <c r="K5" s="43" t="n"/>
+      <c r="L5" s="43" t="n"/>
+      <c r="M5" s="43" t="n"/>
+      <c r="N5" s="43" t="n"/>
+      <c r="O5" s="44" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="39" t="inlineStr">
+      <c r="A6" s="42" t="inlineStr">
         <is>
           <t>REN tiered bonus</t>
         </is>
       </c>
-      <c r="B6" s="39" t="inlineStr">
+      <c r="B6" s="42" t="inlineStr">
         <is>
           <t>Own breakpoints: T1 $25k=$250 | T2 $40k=$350 | T3 $65k=$450 | T4 $80k=$550 | T5 $100k=$800. Above $100k: +$40 per $5k.</t>
         </is>
       </c>
-      <c r="C6" s="40" t="n"/>
-      <c r="D6" s="40" t="n"/>
-      <c r="E6" s="40" t="n"/>
-      <c r="F6" s="40" t="n"/>
-      <c r="G6" s="40" t="n"/>
-      <c r="H6" s="40" t="n"/>
-      <c r="I6" s="40" t="n"/>
-      <c r="J6" s="40" t="n"/>
-      <c r="K6" s="40" t="n"/>
-      <c r="L6" s="40" t="n"/>
-      <c r="M6" s="40" t="n"/>
-      <c r="N6" s="40" t="n"/>
-      <c r="O6" s="41" t="n"/>
+      <c r="C6" s="43" t="n"/>
+      <c r="D6" s="43" t="n"/>
+      <c r="E6" s="43" t="n"/>
+      <c r="F6" s="43" t="n"/>
+      <c r="G6" s="43" t="n"/>
+      <c r="H6" s="43" t="n"/>
+      <c r="I6" s="43" t="n"/>
+      <c r="J6" s="43" t="n"/>
+      <c r="K6" s="43" t="n"/>
+      <c r="L6" s="43" t="n"/>
+      <c r="M6" s="43" t="n"/>
+      <c r="N6" s="43" t="n"/>
+      <c r="O6" s="44" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="39" t="inlineStr">
+      <c r="A7" s="42" t="inlineStr">
         <is>
           <t>Minimums (monthly)</t>
         </is>
       </c>
-      <c r="B7" s="39" t="inlineStr">
+      <c r="B7" s="42" t="inlineStr">
         <is>
           <t>NB written premium &gt;= $45,000 | REN retention rate &gt;= 30% of book | RWR follows NB gate (no separate RWR floor)</t>
         </is>
       </c>
-      <c r="C7" s="40" t="n"/>
-      <c r="D7" s="40" t="n"/>
-      <c r="E7" s="40" t="n"/>
-      <c r="F7" s="40" t="n"/>
-      <c r="G7" s="40" t="n"/>
-      <c r="H7" s="40" t="n"/>
-      <c r="I7" s="40" t="n"/>
-      <c r="J7" s="40" t="n"/>
-      <c r="K7" s="40" t="n"/>
-      <c r="L7" s="40" t="n"/>
-      <c r="M7" s="40" t="n"/>
-      <c r="N7" s="40" t="n"/>
-      <c r="O7" s="41" t="n"/>
+      <c r="C7" s="43" t="n"/>
+      <c r="D7" s="43" t="n"/>
+      <c r="E7" s="43" t="n"/>
+      <c r="F7" s="43" t="n"/>
+      <c r="G7" s="43" t="n"/>
+      <c r="H7" s="43" t="n"/>
+      <c r="I7" s="43" t="n"/>
+      <c r="J7" s="43" t="n"/>
+      <c r="K7" s="43" t="n"/>
+      <c r="L7" s="43" t="n"/>
+      <c r="M7" s="43" t="n"/>
+      <c r="N7" s="43" t="n"/>
+      <c r="O7" s="44" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="39" t="inlineStr">
+      <c r="A8" s="42" t="inlineStr">
         <is>
           <t>Chargeback</t>
         </is>
       </c>
-      <c r="B8" s="39" t="inlineStr">
+      <c r="B8" s="42" t="inlineStr">
         <is>
           <t>3 months (90 days) - bonus reversed if policy cancels/rewrites within 90 days</t>
         </is>
       </c>
-      <c r="C8" s="40" t="n"/>
-      <c r="D8" s="40" t="n"/>
-      <c r="E8" s="40" t="n"/>
-      <c r="F8" s="40" t="n"/>
-      <c r="G8" s="40" t="n"/>
-      <c r="H8" s="40" t="n"/>
-      <c r="I8" s="40" t="n"/>
-      <c r="J8" s="40" t="n"/>
-      <c r="K8" s="40" t="n"/>
-      <c r="L8" s="40" t="n"/>
-      <c r="M8" s="40" t="n"/>
-      <c r="N8" s="40" t="n"/>
-      <c r="O8" s="41" t="n"/>
+      <c r="C8" s="43" t="n"/>
+      <c r="D8" s="43" t="n"/>
+      <c r="E8" s="43" t="n"/>
+      <c r="F8" s="43" t="n"/>
+      <c r="G8" s="43" t="n"/>
+      <c r="H8" s="43" t="n"/>
+      <c r="I8" s="43" t="n"/>
+      <c r="J8" s="43" t="n"/>
+      <c r="K8" s="43" t="n"/>
+      <c r="L8" s="43" t="n"/>
+      <c r="M8" s="43" t="n"/>
+      <c r="N8" s="43" t="n"/>
+      <c r="O8" s="44" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">

--- a/output/Bonus_Plan_SIMPLE.xlsx
+++ b/output/Bonus_Plan_SIMPLE.xlsx
@@ -14,9 +14,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWR Bonus Examples" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REN Bonus Examples" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Combined Bonus Examples" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chargeback Process" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manual Tracker Template" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Data" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Current vs New Comparison" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chargeback Process" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manual Tracker Template" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Data" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29,7 +30,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -107,8 +108,12 @@
       <color rgb="00FFFFFF"/>
       <sz val="13"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -168,6 +173,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0000B050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -246,7 +256,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -350,10 +360,28 @@
     <xf numFmtId="164" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -732,7 +760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1069,34 +1097,46 @@
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7. Chargeback Process</t>
+          <t xml:space="preserve">  7. Current vs New Comparison</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Step-by-step 90-day reversal procedure.</t>
+          <t>Today's plan vs the new plan per agent-month, with the DELTA (who wins / who loses).</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8. Manual Tracker Template</t>
+          <t xml:space="preserve">  8. Chargeback Process</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Monthly template for verified bonus tracking.</t>
+          <t>Step-by-step 90-day reversal procedure.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9. Source Data</t>
+          <t xml:space="preserve">  9. Manual Tracker Template</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Monthly template for verified bonus tracking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  10. Source Data</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>Raw NB/RWR/REN volumes from Jan-Apr 2026.</t>
         </is>
@@ -1111,6 +1151,788 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Monthly Manual Bonus Tracker - The Bonus Plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>Agents enter ONE ROW PER POLICY. Without an entry the policy does NOT get bonused. Manager verifies fields. Per-policy bonus columns auto-calculate from the formulas below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>THE BONUS PLAN FORMULAS (for reference)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="48" t="inlineStr">
+        <is>
+          <t>NB tiered bonus</t>
+        </is>
+      </c>
+      <c r="B4" s="48" t="inlineStr">
+        <is>
+          <t>Monthly NB written premium: T1 $45k=$250 | T2 $55k=$375 | T3 $70k=$525 | T4 $85k=$725 | T5 $100k=$1,000. Above $100k: +$50 per $5k.</t>
+        </is>
+      </c>
+      <c r="C4" s="49" t="n"/>
+      <c r="D4" s="49" t="n"/>
+      <c r="E4" s="49" t="n"/>
+      <c r="F4" s="49" t="n"/>
+      <c r="G4" s="49" t="n"/>
+      <c r="H4" s="49" t="n"/>
+      <c r="I4" s="49" t="n"/>
+      <c r="J4" s="49" t="n"/>
+      <c r="K4" s="49" t="n"/>
+      <c r="L4" s="49" t="n"/>
+      <c r="M4" s="49" t="n"/>
+      <c r="N4" s="49" t="n"/>
+      <c r="O4" s="50" t="n"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="48" t="inlineStr">
+        <is>
+          <t>RWR tiered bonus</t>
+        </is>
+      </c>
+      <c r="B5" s="48" t="inlineStr">
+        <is>
+          <t>Same breakpoints as NB, pays ~half: T1=$100 | T2=$200 | T3=$275 | T4=$350 | T5=$500. Above $100k: +$25 per $5k.</t>
+        </is>
+      </c>
+      <c r="C5" s="49" t="n"/>
+      <c r="D5" s="49" t="n"/>
+      <c r="E5" s="49" t="n"/>
+      <c r="F5" s="49" t="n"/>
+      <c r="G5" s="49" t="n"/>
+      <c r="H5" s="49" t="n"/>
+      <c r="I5" s="49" t="n"/>
+      <c r="J5" s="49" t="n"/>
+      <c r="K5" s="49" t="n"/>
+      <c r="L5" s="49" t="n"/>
+      <c r="M5" s="49" t="n"/>
+      <c r="N5" s="49" t="n"/>
+      <c r="O5" s="50" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="48" t="inlineStr">
+        <is>
+          <t>REN tiered bonus</t>
+        </is>
+      </c>
+      <c r="B6" s="48" t="inlineStr">
+        <is>
+          <t>Own breakpoints: T1 $25k=$250 | T2 $40k=$350 | T3 $65k=$450 | T4 $80k=$550 | T5 $100k=$800. Above $100k: +$40 per $5k.</t>
+        </is>
+      </c>
+      <c r="C6" s="49" t="n"/>
+      <c r="D6" s="49" t="n"/>
+      <c r="E6" s="49" t="n"/>
+      <c r="F6" s="49" t="n"/>
+      <c r="G6" s="49" t="n"/>
+      <c r="H6" s="49" t="n"/>
+      <c r="I6" s="49" t="n"/>
+      <c r="J6" s="49" t="n"/>
+      <c r="K6" s="49" t="n"/>
+      <c r="L6" s="49" t="n"/>
+      <c r="M6" s="49" t="n"/>
+      <c r="N6" s="49" t="n"/>
+      <c r="O6" s="50" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="48" t="inlineStr">
+        <is>
+          <t>Minimums (monthly)</t>
+        </is>
+      </c>
+      <c r="B7" s="48" t="inlineStr">
+        <is>
+          <t>NB written premium &gt;= $45,000 | REN retention rate &gt;= 30% of book | RWR follows NB gate (no separate RWR floor)</t>
+        </is>
+      </c>
+      <c r="C7" s="49" t="n"/>
+      <c r="D7" s="49" t="n"/>
+      <c r="E7" s="49" t="n"/>
+      <c r="F7" s="49" t="n"/>
+      <c r="G7" s="49" t="n"/>
+      <c r="H7" s="49" t="n"/>
+      <c r="I7" s="49" t="n"/>
+      <c r="J7" s="49" t="n"/>
+      <c r="K7" s="49" t="n"/>
+      <c r="L7" s="49" t="n"/>
+      <c r="M7" s="49" t="n"/>
+      <c r="N7" s="49" t="n"/>
+      <c r="O7" s="50" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="48" t="inlineStr">
+        <is>
+          <t>Chargeback</t>
+        </is>
+      </c>
+      <c r="B8" s="48" t="inlineStr">
+        <is>
+          <t>3 months (90 days) - bonus reversed if policy cancels/rewrites within 90 days</t>
+        </is>
+      </c>
+      <c r="C8" s="49" t="n"/>
+      <c r="D8" s="49" t="n"/>
+      <c r="E8" s="49" t="n"/>
+      <c r="F8" s="49" t="n"/>
+      <c r="G8" s="49" t="n"/>
+      <c r="H8" s="49" t="n"/>
+      <c r="I8" s="49" t="n"/>
+      <c r="J8" s="49" t="n"/>
+      <c r="K8" s="49" t="n"/>
+      <c r="L8" s="49" t="n"/>
+      <c r="M8" s="49" t="n"/>
+      <c r="N8" s="49" t="n"/>
+      <c r="O8" s="50" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>ONE ROW PER POLICY</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Policy #</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Carrier</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Type (NB/RWR/REN)</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Eff Date</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Exp Date</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>90-Day Review Date</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>Written Premium</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>Down Payment $</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>Collected % (calc)</t>
+        </is>
+      </c>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>PIF?</t>
+        </is>
+      </c>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>Per-Policy Base $</t>
+        </is>
+      </c>
+      <c r="N11" s="6" t="inlineStr">
+        <is>
+          <t>Collected Incentive $</t>
+        </is>
+      </c>
+      <c r="O11" s="6" t="inlineStr">
+        <is>
+          <t>Total Bonus $</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr"/>
+      <c r="B12" s="14" t="inlineStr"/>
+      <c r="C12" s="14" t="inlineStr"/>
+      <c r="D12" s="14" t="inlineStr"/>
+      <c r="E12" s="14" t="inlineStr"/>
+      <c r="F12" s="14" t="inlineStr"/>
+      <c r="G12" s="14" t="inlineStr"/>
+      <c r="H12" s="14" t="inlineStr"/>
+      <c r="I12" s="14" t="inlineStr"/>
+      <c r="J12" s="14" t="inlineStr"/>
+      <c r="K12" s="14" t="inlineStr"/>
+      <c r="L12" s="14" t="inlineStr"/>
+      <c r="M12" s="14" t="inlineStr"/>
+      <c r="N12" s="14" t="inlineStr"/>
+      <c r="O12" s="14" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr"/>
+      <c r="B13" s="14" t="inlineStr"/>
+      <c r="C13" s="14" t="inlineStr"/>
+      <c r="D13" s="14" t="inlineStr"/>
+      <c r="E13" s="14" t="inlineStr"/>
+      <c r="F13" s="14" t="inlineStr"/>
+      <c r="G13" s="14" t="inlineStr"/>
+      <c r="H13" s="14" t="inlineStr"/>
+      <c r="I13" s="14" t="inlineStr"/>
+      <c r="J13" s="14" t="inlineStr"/>
+      <c r="K13" s="14" t="inlineStr"/>
+      <c r="L13" s="14" t="inlineStr"/>
+      <c r="M13" s="14" t="inlineStr"/>
+      <c r="N13" s="14" t="inlineStr"/>
+      <c r="O13" s="14" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr"/>
+      <c r="B14" s="14" t="inlineStr"/>
+      <c r="C14" s="14" t="inlineStr"/>
+      <c r="D14" s="14" t="inlineStr"/>
+      <c r="E14" s="14" t="inlineStr"/>
+      <c r="F14" s="14" t="inlineStr"/>
+      <c r="G14" s="14" t="inlineStr"/>
+      <c r="H14" s="14" t="inlineStr"/>
+      <c r="I14" s="14" t="inlineStr"/>
+      <c r="J14" s="14" t="inlineStr"/>
+      <c r="K14" s="14" t="inlineStr"/>
+      <c r="L14" s="14" t="inlineStr"/>
+      <c r="M14" s="14" t="inlineStr"/>
+      <c r="N14" s="14" t="inlineStr"/>
+      <c r="O14" s="14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr"/>
+      <c r="B15" s="14" t="inlineStr"/>
+      <c r="C15" s="14" t="inlineStr"/>
+      <c r="D15" s="14" t="inlineStr"/>
+      <c r="E15" s="14" t="inlineStr"/>
+      <c r="F15" s="14" t="inlineStr"/>
+      <c r="G15" s="14" t="inlineStr"/>
+      <c r="H15" s="14" t="inlineStr"/>
+      <c r="I15" s="14" t="inlineStr"/>
+      <c r="J15" s="14" t="inlineStr"/>
+      <c r="K15" s="14" t="inlineStr"/>
+      <c r="L15" s="14" t="inlineStr"/>
+      <c r="M15" s="14" t="inlineStr"/>
+      <c r="N15" s="14" t="inlineStr"/>
+      <c r="O15" s="14" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr"/>
+      <c r="B16" s="14" t="inlineStr"/>
+      <c r="C16" s="14" t="inlineStr"/>
+      <c r="D16" s="14" t="inlineStr"/>
+      <c r="E16" s="14" t="inlineStr"/>
+      <c r="F16" s="14" t="inlineStr"/>
+      <c r="G16" s="14" t="inlineStr"/>
+      <c r="H16" s="14" t="inlineStr"/>
+      <c r="I16" s="14" t="inlineStr"/>
+      <c r="J16" s="14" t="inlineStr"/>
+      <c r="K16" s="14" t="inlineStr"/>
+      <c r="L16" s="14" t="inlineStr"/>
+      <c r="M16" s="14" t="inlineStr"/>
+      <c r="N16" s="14" t="inlineStr"/>
+      <c r="O16" s="14" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr"/>
+      <c r="B17" s="14" t="inlineStr"/>
+      <c r="C17" s="14" t="inlineStr"/>
+      <c r="D17" s="14" t="inlineStr"/>
+      <c r="E17" s="14" t="inlineStr"/>
+      <c r="F17" s="14" t="inlineStr"/>
+      <c r="G17" s="14" t="inlineStr"/>
+      <c r="H17" s="14" t="inlineStr"/>
+      <c r="I17" s="14" t="inlineStr"/>
+      <c r="J17" s="14" t="inlineStr"/>
+      <c r="K17" s="14" t="inlineStr"/>
+      <c r="L17" s="14" t="inlineStr"/>
+      <c r="M17" s="14" t="inlineStr"/>
+      <c r="N17" s="14" t="inlineStr"/>
+      <c r="O17" s="14" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr"/>
+      <c r="B18" s="14" t="inlineStr"/>
+      <c r="C18" s="14" t="inlineStr"/>
+      <c r="D18" s="14" t="inlineStr"/>
+      <c r="E18" s="14" t="inlineStr"/>
+      <c r="F18" s="14" t="inlineStr"/>
+      <c r="G18" s="14" t="inlineStr"/>
+      <c r="H18" s="14" t="inlineStr"/>
+      <c r="I18" s="14" t="inlineStr"/>
+      <c r="J18" s="14" t="inlineStr"/>
+      <c r="K18" s="14" t="inlineStr"/>
+      <c r="L18" s="14" t="inlineStr"/>
+      <c r="M18" s="14" t="inlineStr"/>
+      <c r="N18" s="14" t="inlineStr"/>
+      <c r="O18" s="14" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr"/>
+      <c r="B19" s="14" t="inlineStr"/>
+      <c r="C19" s="14" t="inlineStr"/>
+      <c r="D19" s="14" t="inlineStr"/>
+      <c r="E19" s="14" t="inlineStr"/>
+      <c r="F19" s="14" t="inlineStr"/>
+      <c r="G19" s="14" t="inlineStr"/>
+      <c r="H19" s="14" t="inlineStr"/>
+      <c r="I19" s="14" t="inlineStr"/>
+      <c r="J19" s="14" t="inlineStr"/>
+      <c r="K19" s="14" t="inlineStr"/>
+      <c r="L19" s="14" t="inlineStr"/>
+      <c r="M19" s="14" t="inlineStr"/>
+      <c r="N19" s="14" t="inlineStr"/>
+      <c r="O19" s="14" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr"/>
+      <c r="B20" s="14" t="inlineStr"/>
+      <c r="C20" s="14" t="inlineStr"/>
+      <c r="D20" s="14" t="inlineStr"/>
+      <c r="E20" s="14" t="inlineStr"/>
+      <c r="F20" s="14" t="inlineStr"/>
+      <c r="G20" s="14" t="inlineStr"/>
+      <c r="H20" s="14" t="inlineStr"/>
+      <c r="I20" s="14" t="inlineStr"/>
+      <c r="J20" s="14" t="inlineStr"/>
+      <c r="K20" s="14" t="inlineStr"/>
+      <c r="L20" s="14" t="inlineStr"/>
+      <c r="M20" s="14" t="inlineStr"/>
+      <c r="N20" s="14" t="inlineStr"/>
+      <c r="O20" s="14" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr"/>
+      <c r="B21" s="14" t="inlineStr"/>
+      <c r="C21" s="14" t="inlineStr"/>
+      <c r="D21" s="14" t="inlineStr"/>
+      <c r="E21" s="14" t="inlineStr"/>
+      <c r="F21" s="14" t="inlineStr"/>
+      <c r="G21" s="14" t="inlineStr"/>
+      <c r="H21" s="14" t="inlineStr"/>
+      <c r="I21" s="14" t="inlineStr"/>
+      <c r="J21" s="14" t="inlineStr"/>
+      <c r="K21" s="14" t="inlineStr"/>
+      <c r="L21" s="14" t="inlineStr"/>
+      <c r="M21" s="14" t="inlineStr"/>
+      <c r="N21" s="14" t="inlineStr"/>
+      <c r="O21" s="14" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr"/>
+      <c r="B22" s="14" t="inlineStr"/>
+      <c r="C22" s="14" t="inlineStr"/>
+      <c r="D22" s="14" t="inlineStr"/>
+      <c r="E22" s="14" t="inlineStr"/>
+      <c r="F22" s="14" t="inlineStr"/>
+      <c r="G22" s="14" t="inlineStr"/>
+      <c r="H22" s="14" t="inlineStr"/>
+      <c r="I22" s="14" t="inlineStr"/>
+      <c r="J22" s="14" t="inlineStr"/>
+      <c r="K22" s="14" t="inlineStr"/>
+      <c r="L22" s="14" t="inlineStr"/>
+      <c r="M22" s="14" t="inlineStr"/>
+      <c r="N22" s="14" t="inlineStr"/>
+      <c r="O22" s="14" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr"/>
+      <c r="B23" s="14" t="inlineStr"/>
+      <c r="C23" s="14" t="inlineStr"/>
+      <c r="D23" s="14" t="inlineStr"/>
+      <c r="E23" s="14" t="inlineStr"/>
+      <c r="F23" s="14" t="inlineStr"/>
+      <c r="G23" s="14" t="inlineStr"/>
+      <c r="H23" s="14" t="inlineStr"/>
+      <c r="I23" s="14" t="inlineStr"/>
+      <c r="J23" s="14" t="inlineStr"/>
+      <c r="K23" s="14" t="inlineStr"/>
+      <c r="L23" s="14" t="inlineStr"/>
+      <c r="M23" s="14" t="inlineStr"/>
+      <c r="N23" s="14" t="inlineStr"/>
+      <c r="O23" s="14" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr"/>
+      <c r="B24" s="14" t="inlineStr"/>
+      <c r="C24" s="14" t="inlineStr"/>
+      <c r="D24" s="14" t="inlineStr"/>
+      <c r="E24" s="14" t="inlineStr"/>
+      <c r="F24" s="14" t="inlineStr"/>
+      <c r="G24" s="14" t="inlineStr"/>
+      <c r="H24" s="14" t="inlineStr"/>
+      <c r="I24" s="14" t="inlineStr"/>
+      <c r="J24" s="14" t="inlineStr"/>
+      <c r="K24" s="14" t="inlineStr"/>
+      <c r="L24" s="14" t="inlineStr"/>
+      <c r="M24" s="14" t="inlineStr"/>
+      <c r="N24" s="14" t="inlineStr"/>
+      <c r="O24" s="14" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr"/>
+      <c r="B25" s="14" t="inlineStr"/>
+      <c r="C25" s="14" t="inlineStr"/>
+      <c r="D25" s="14" t="inlineStr"/>
+      <c r="E25" s="14" t="inlineStr"/>
+      <c r="F25" s="14" t="inlineStr"/>
+      <c r="G25" s="14" t="inlineStr"/>
+      <c r="H25" s="14" t="inlineStr"/>
+      <c r="I25" s="14" t="inlineStr"/>
+      <c r="J25" s="14" t="inlineStr"/>
+      <c r="K25" s="14" t="inlineStr"/>
+      <c r="L25" s="14" t="inlineStr"/>
+      <c r="M25" s="14" t="inlineStr"/>
+      <c r="N25" s="14" t="inlineStr"/>
+      <c r="O25" s="14" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr"/>
+      <c r="B26" s="14" t="inlineStr"/>
+      <c r="C26" s="14" t="inlineStr"/>
+      <c r="D26" s="14" t="inlineStr"/>
+      <c r="E26" s="14" t="inlineStr"/>
+      <c r="F26" s="14" t="inlineStr"/>
+      <c r="G26" s="14" t="inlineStr"/>
+      <c r="H26" s="14" t="inlineStr"/>
+      <c r="I26" s="14" t="inlineStr"/>
+      <c r="J26" s="14" t="inlineStr"/>
+      <c r="K26" s="14" t="inlineStr"/>
+      <c r="L26" s="14" t="inlineStr"/>
+      <c r="M26" s="14" t="inlineStr"/>
+      <c r="N26" s="14" t="inlineStr"/>
+      <c r="O26" s="14" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr"/>
+      <c r="B27" s="14" t="inlineStr"/>
+      <c r="C27" s="14" t="inlineStr"/>
+      <c r="D27" s="14" t="inlineStr"/>
+      <c r="E27" s="14" t="inlineStr"/>
+      <c r="F27" s="14" t="inlineStr"/>
+      <c r="G27" s="14" t="inlineStr"/>
+      <c r="H27" s="14" t="inlineStr"/>
+      <c r="I27" s="14" t="inlineStr"/>
+      <c r="J27" s="14" t="inlineStr"/>
+      <c r="K27" s="14" t="inlineStr"/>
+      <c r="L27" s="14" t="inlineStr"/>
+      <c r="M27" s="14" t="inlineStr"/>
+      <c r="N27" s="14" t="inlineStr"/>
+      <c r="O27" s="14" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr"/>
+      <c r="B28" s="14" t="inlineStr"/>
+      <c r="C28" s="14" t="inlineStr"/>
+      <c r="D28" s="14" t="inlineStr"/>
+      <c r="E28" s="14" t="inlineStr"/>
+      <c r="F28" s="14" t="inlineStr"/>
+      <c r="G28" s="14" t="inlineStr"/>
+      <c r="H28" s="14" t="inlineStr"/>
+      <c r="I28" s="14" t="inlineStr"/>
+      <c r="J28" s="14" t="inlineStr"/>
+      <c r="K28" s="14" t="inlineStr"/>
+      <c r="L28" s="14" t="inlineStr"/>
+      <c r="M28" s="14" t="inlineStr"/>
+      <c r="N28" s="14" t="inlineStr"/>
+      <c r="O28" s="14" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr"/>
+      <c r="B29" s="14" t="inlineStr"/>
+      <c r="C29" s="14" t="inlineStr"/>
+      <c r="D29" s="14" t="inlineStr"/>
+      <c r="E29" s="14" t="inlineStr"/>
+      <c r="F29" s="14" t="inlineStr"/>
+      <c r="G29" s="14" t="inlineStr"/>
+      <c r="H29" s="14" t="inlineStr"/>
+      <c r="I29" s="14" t="inlineStr"/>
+      <c r="J29" s="14" t="inlineStr"/>
+      <c r="K29" s="14" t="inlineStr"/>
+      <c r="L29" s="14" t="inlineStr"/>
+      <c r="M29" s="14" t="inlineStr"/>
+      <c r="N29" s="14" t="inlineStr"/>
+      <c r="O29" s="14" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr"/>
+      <c r="B30" s="14" t="inlineStr"/>
+      <c r="C30" s="14" t="inlineStr"/>
+      <c r="D30" s="14" t="inlineStr"/>
+      <c r="E30" s="14" t="inlineStr"/>
+      <c r="F30" s="14" t="inlineStr"/>
+      <c r="G30" s="14" t="inlineStr"/>
+      <c r="H30" s="14" t="inlineStr"/>
+      <c r="I30" s="14" t="inlineStr"/>
+      <c r="J30" s="14" t="inlineStr"/>
+      <c r="K30" s="14" t="inlineStr"/>
+      <c r="L30" s="14" t="inlineStr"/>
+      <c r="M30" s="14" t="inlineStr"/>
+      <c r="N30" s="14" t="inlineStr"/>
+      <c r="O30" s="14" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr"/>
+      <c r="B31" s="14" t="inlineStr"/>
+      <c r="C31" s="14" t="inlineStr"/>
+      <c r="D31" s="14" t="inlineStr"/>
+      <c r="E31" s="14" t="inlineStr"/>
+      <c r="F31" s="14" t="inlineStr"/>
+      <c r="G31" s="14" t="inlineStr"/>
+      <c r="H31" s="14" t="inlineStr"/>
+      <c r="I31" s="14" t="inlineStr"/>
+      <c r="J31" s="14" t="inlineStr"/>
+      <c r="K31" s="14" t="inlineStr"/>
+      <c r="L31" s="14" t="inlineStr"/>
+      <c r="M31" s="14" t="inlineStr"/>
+      <c r="N31" s="14" t="inlineStr"/>
+      <c r="O31" s="14" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr"/>
+      <c r="B32" s="14" t="inlineStr"/>
+      <c r="C32" s="14" t="inlineStr"/>
+      <c r="D32" s="14" t="inlineStr"/>
+      <c r="E32" s="14" t="inlineStr"/>
+      <c r="F32" s="14" t="inlineStr"/>
+      <c r="G32" s="14" t="inlineStr"/>
+      <c r="H32" s="14" t="inlineStr"/>
+      <c r="I32" s="14" t="inlineStr"/>
+      <c r="J32" s="14" t="inlineStr"/>
+      <c r="K32" s="14" t="inlineStr"/>
+      <c r="L32" s="14" t="inlineStr"/>
+      <c r="M32" s="14" t="inlineStr"/>
+      <c r="N32" s="14" t="inlineStr"/>
+      <c r="O32" s="14" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr"/>
+      <c r="B33" s="14" t="inlineStr"/>
+      <c r="C33" s="14" t="inlineStr"/>
+      <c r="D33" s="14" t="inlineStr"/>
+      <c r="E33" s="14" t="inlineStr"/>
+      <c r="F33" s="14" t="inlineStr"/>
+      <c r="G33" s="14" t="inlineStr"/>
+      <c r="H33" s="14" t="inlineStr"/>
+      <c r="I33" s="14" t="inlineStr"/>
+      <c r="J33" s="14" t="inlineStr"/>
+      <c r="K33" s="14" t="inlineStr"/>
+      <c r="L33" s="14" t="inlineStr"/>
+      <c r="M33" s="14" t="inlineStr"/>
+      <c r="N33" s="14" t="inlineStr"/>
+      <c r="O33" s="14" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr"/>
+      <c r="B34" s="14" t="inlineStr"/>
+      <c r="C34" s="14" t="inlineStr"/>
+      <c r="D34" s="14" t="inlineStr"/>
+      <c r="E34" s="14" t="inlineStr"/>
+      <c r="F34" s="14" t="inlineStr"/>
+      <c r="G34" s="14" t="inlineStr"/>
+      <c r="H34" s="14" t="inlineStr"/>
+      <c r="I34" s="14" t="inlineStr"/>
+      <c r="J34" s="14" t="inlineStr"/>
+      <c r="K34" s="14" t="inlineStr"/>
+      <c r="L34" s="14" t="inlineStr"/>
+      <c r="M34" s="14" t="inlineStr"/>
+      <c r="N34" s="14" t="inlineStr"/>
+      <c r="O34" s="14" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr"/>
+      <c r="B35" s="14" t="inlineStr"/>
+      <c r="C35" s="14" t="inlineStr"/>
+      <c r="D35" s="14" t="inlineStr"/>
+      <c r="E35" s="14" t="inlineStr"/>
+      <c r="F35" s="14" t="inlineStr"/>
+      <c r="G35" s="14" t="inlineStr"/>
+      <c r="H35" s="14" t="inlineStr"/>
+      <c r="I35" s="14" t="inlineStr"/>
+      <c r="J35" s="14" t="inlineStr"/>
+      <c r="K35" s="14" t="inlineStr"/>
+      <c r="L35" s="14" t="inlineStr"/>
+      <c r="M35" s="14" t="inlineStr"/>
+      <c r="N35" s="14" t="inlineStr"/>
+      <c r="O35" s="14" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr"/>
+      <c r="B36" s="14" t="inlineStr"/>
+      <c r="C36" s="14" t="inlineStr"/>
+      <c r="D36" s="14" t="inlineStr"/>
+      <c r="E36" s="14" t="inlineStr"/>
+      <c r="F36" s="14" t="inlineStr"/>
+      <c r="G36" s="14" t="inlineStr"/>
+      <c r="H36" s="14" t="inlineStr"/>
+      <c r="I36" s="14" t="inlineStr"/>
+      <c r="J36" s="14" t="inlineStr"/>
+      <c r="K36" s="14" t="inlineStr"/>
+      <c r="L36" s="14" t="inlineStr"/>
+      <c r="M36" s="14" t="inlineStr"/>
+      <c r="N36" s="14" t="inlineStr"/>
+      <c r="O36" s="14" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr"/>
+      <c r="B37" s="14" t="inlineStr"/>
+      <c r="C37" s="14" t="inlineStr"/>
+      <c r="D37" s="14" t="inlineStr"/>
+      <c r="E37" s="14" t="inlineStr"/>
+      <c r="F37" s="14" t="inlineStr"/>
+      <c r="G37" s="14" t="inlineStr"/>
+      <c r="H37" s="14" t="inlineStr"/>
+      <c r="I37" s="14" t="inlineStr"/>
+      <c r="J37" s="14" t="inlineStr"/>
+      <c r="K37" s="14" t="inlineStr"/>
+      <c r="L37" s="14" t="inlineStr"/>
+      <c r="M37" s="14" t="inlineStr"/>
+      <c r="N37" s="14" t="inlineStr"/>
+      <c r="O37" s="14" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr"/>
+      <c r="B38" s="14" t="inlineStr"/>
+      <c r="C38" s="14" t="inlineStr"/>
+      <c r="D38" s="14" t="inlineStr"/>
+      <c r="E38" s="14" t="inlineStr"/>
+      <c r="F38" s="14" t="inlineStr"/>
+      <c r="G38" s="14" t="inlineStr"/>
+      <c r="H38" s="14" t="inlineStr"/>
+      <c r="I38" s="14" t="inlineStr"/>
+      <c r="J38" s="14" t="inlineStr"/>
+      <c r="K38" s="14" t="inlineStr"/>
+      <c r="L38" s="14" t="inlineStr"/>
+      <c r="M38" s="14" t="inlineStr"/>
+      <c r="N38" s="14" t="inlineStr"/>
+      <c r="O38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr"/>
+      <c r="B39" s="14" t="inlineStr"/>
+      <c r="C39" s="14" t="inlineStr"/>
+      <c r="D39" s="14" t="inlineStr"/>
+      <c r="E39" s="14" t="inlineStr"/>
+      <c r="F39" s="14" t="inlineStr"/>
+      <c r="G39" s="14" t="inlineStr"/>
+      <c r="H39" s="14" t="inlineStr"/>
+      <c r="I39" s="14" t="inlineStr"/>
+      <c r="J39" s="14" t="inlineStr"/>
+      <c r="K39" s="14" t="inlineStr"/>
+      <c r="L39" s="14" t="inlineStr"/>
+      <c r="M39" s="14" t="inlineStr"/>
+      <c r="N39" s="14" t="inlineStr"/>
+      <c r="O39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr"/>
+      <c r="B40" s="14" t="inlineStr"/>
+      <c r="C40" s="14" t="inlineStr"/>
+      <c r="D40" s="14" t="inlineStr"/>
+      <c r="E40" s="14" t="inlineStr"/>
+      <c r="F40" s="14" t="inlineStr"/>
+      <c r="G40" s="14" t="inlineStr"/>
+      <c r="H40" s="14" t="inlineStr"/>
+      <c r="I40" s="14" t="inlineStr"/>
+      <c r="J40" s="14" t="inlineStr"/>
+      <c r="K40" s="14" t="inlineStr"/>
+      <c r="L40" s="14" t="inlineStr"/>
+      <c r="M40" s="14" t="inlineStr"/>
+      <c r="N40" s="14" t="inlineStr"/>
+      <c r="O40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr"/>
+      <c r="B41" s="14" t="inlineStr"/>
+      <c r="C41" s="14" t="inlineStr"/>
+      <c r="D41" s="14" t="inlineStr"/>
+      <c r="E41" s="14" t="inlineStr"/>
+      <c r="F41" s="14" t="inlineStr"/>
+      <c r="G41" s="14" t="inlineStr"/>
+      <c r="H41" s="14" t="inlineStr"/>
+      <c r="I41" s="14" t="inlineStr"/>
+      <c r="J41" s="14" t="inlineStr"/>
+      <c r="K41" s="14" t="inlineStr"/>
+      <c r="L41" s="14" t="inlineStr"/>
+      <c r="M41" s="14" t="inlineStr"/>
+      <c r="N41" s="14" t="inlineStr"/>
+      <c r="O41" s="14" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="B8:O8"/>
+    <mergeCell ref="B4:O4"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="B6:O6"/>
+    <mergeCell ref="B7:O7"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="B5:O5"/>
+    <mergeCell ref="A3:O3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1241,7 +2063,7 @@
       <c r="E5" s="16" t="n">
         <v>4938.26</v>
       </c>
-      <c r="F5" s="45" t="n">
+      <c r="F5" s="51" t="n">
         <v>0.1278963581240991</v>
       </c>
       <c r="G5" s="15" t="n">
@@ -1253,7 +2075,7 @@
       <c r="I5" s="16" t="n">
         <v>6186.16</v>
       </c>
-      <c r="J5" s="45" t="n">
+      <c r="J5" s="51" t="n">
         <v>0.224800043607028</v>
       </c>
       <c r="K5" s="15" t="n">
@@ -1265,7 +2087,7 @@
       <c r="M5" s="16" t="n">
         <v>1734.23</v>
       </c>
-      <c r="N5" s="45" t="n">
+      <c r="N5" s="51" t="n">
         <v>0.2280381328073636</v>
       </c>
     </row>
@@ -1289,7 +2111,7 @@
       <c r="E6" s="16" t="n">
         <v>3258.77</v>
       </c>
-      <c r="F6" s="45" t="n">
+      <c r="F6" s="51" t="n">
         <v>0.1284649347577561</v>
       </c>
       <c r="G6" s="15" t="n">
@@ -1301,7 +2123,7 @@
       <c r="I6" s="16" t="n">
         <v>4268.29</v>
       </c>
-      <c r="J6" s="45" t="n">
+      <c r="J6" s="51" t="n">
         <v>0.1392908657768495</v>
       </c>
       <c r="K6" s="15" t="n">
@@ -1313,7 +2135,7 @@
       <c r="M6" s="16" t="n">
         <v>1422.16</v>
       </c>
-      <c r="N6" s="45" t="n">
+      <c r="N6" s="51" t="n">
         <v>0.1891924970067846</v>
       </c>
     </row>
@@ -1337,7 +2159,7 @@
       <c r="E7" s="16" t="n">
         <v>6523.33</v>
       </c>
-      <c r="F7" s="45" t="n">
+      <c r="F7" s="51" t="n">
         <v>0.140216196720057</v>
       </c>
       <c r="G7" s="15" t="n">
@@ -1349,7 +2171,7 @@
       <c r="I7" s="16" t="n">
         <v>5844.85</v>
       </c>
-      <c r="J7" s="45" t="n">
+      <c r="J7" s="51" t="n">
         <v>0.2316847421078502</v>
       </c>
       <c r="K7" s="15" t="n">
@@ -1361,7 +2183,7 @@
       <c r="M7" s="16" t="n">
         <v>1274.08</v>
       </c>
-      <c r="N7" s="45" t="n">
+      <c r="N7" s="51" t="n">
         <v>0.3266034350166624</v>
       </c>
     </row>
@@ -1385,7 +2207,7 @@
       <c r="E8" s="16" t="n">
         <v>8163.72</v>
       </c>
-      <c r="F8" s="45" t="n">
+      <c r="F8" s="51" t="n">
         <v>0.2158233783016042</v>
       </c>
       <c r="G8" s="15" t="n">
@@ -1397,7 +2219,7 @@
       <c r="I8" s="16" t="n">
         <v>3967.81</v>
       </c>
-      <c r="J8" s="45" t="n">
+      <c r="J8" s="51" t="n">
         <v>0.2582881730509473</v>
       </c>
       <c r="K8" s="15" t="n">
@@ -1409,7 +2231,7 @@
       <c r="M8" s="16" t="n">
         <v>5439.19</v>
       </c>
-      <c r="N8" s="45" t="n">
+      <c r="N8" s="51" t="n">
         <v>0.4973660363625058</v>
       </c>
     </row>
@@ -1420,7 +2242,7 @@
           <t>4-mo TOTAL</t>
         </is>
       </c>
-      <c r="C9" s="46" t="n">
+      <c r="C9" s="52" t="n">
         <v>95</v>
       </c>
       <c r="D9" s="19" t="n">
@@ -1429,10 +2251,10 @@
       <c r="E9" s="19" t="n">
         <v>22884.08</v>
       </c>
-      <c r="F9" s="47" t="n">
+      <c r="F9" s="53" t="n">
         <v>0.1542805350206961</v>
       </c>
-      <c r="G9" s="46" t="n">
+      <c r="G9" s="52" t="n">
         <v>68</v>
       </c>
       <c r="H9" s="19" t="n">
@@ -1441,10 +2263,10 @@
       <c r="I9" s="19" t="n">
         <v>20267.11</v>
       </c>
-      <c r="J9" s="47" t="n">
+      <c r="J9" s="53" t="n">
         <v>0.2052343747231042</v>
       </c>
-      <c r="K9" s="46" t="n">
+      <c r="K9" s="52" t="n">
         <v>34</v>
       </c>
       <c r="L9" s="19" t="n">
@@ -1453,7 +2275,7 @@
       <c r="M9" s="19" t="n">
         <v>9869.66</v>
       </c>
-      <c r="N9" s="47" t="n">
+      <c r="N9" s="53" t="n">
         <v>0.3294390097930538</v>
       </c>
     </row>
@@ -1477,7 +2299,7 @@
       <c r="E11" s="16" t="n">
         <v>4925</v>
       </c>
-      <c r="F11" s="45" t="n">
+      <c r="F11" s="51" t="n">
         <v>0.1223624980931326</v>
       </c>
       <c r="G11" s="15" t="n">
@@ -1489,7 +2311,7 @@
       <c r="I11" s="16" t="n">
         <v>10936.32</v>
       </c>
-      <c r="J11" s="45" t="n">
+      <c r="J11" s="51" t="n">
         <v>0.1665208484518856</v>
       </c>
       <c r="K11" s="15" t="n">
@@ -1501,7 +2323,7 @@
       <c r="M11" s="16" t="n">
         <v>4951.59</v>
       </c>
-      <c r="N11" s="45" t="n">
+      <c r="N11" s="51" t="n">
         <v>0.395163948359479</v>
       </c>
     </row>
@@ -1525,7 +2347,7 @@
       <c r="E12" s="16" t="n">
         <v>5766.72</v>
       </c>
-      <c r="F12" s="45" t="n">
+      <c r="F12" s="51" t="n">
         <v>0.1918537861440041</v>
       </c>
       <c r="G12" s="15" t="n">
@@ -1537,7 +2359,7 @@
       <c r="I12" s="16" t="n">
         <v>13931.43</v>
       </c>
-      <c r="J12" s="45" t="n">
+      <c r="J12" s="51" t="n">
         <v>0.1628557500999478</v>
       </c>
       <c r="K12" s="15" t="n">
@@ -1549,7 +2371,7 @@
       <c r="M12" s="16" t="n">
         <v>1937.6</v>
       </c>
-      <c r="N12" s="45" t="n">
+      <c r="N12" s="51" t="n">
         <v>0.1666081955823376</v>
       </c>
     </row>
@@ -1573,7 +2395,7 @@
       <c r="E13" s="16" t="n">
         <v>10546.59</v>
       </c>
-      <c r="F13" s="45" t="n">
+      <c r="F13" s="51" t="n">
         <v>0.2011368382508596</v>
       </c>
       <c r="G13" s="15" t="n">
@@ -1585,7 +2407,7 @@
       <c r="I13" s="16" t="n">
         <v>19700.38</v>
       </c>
-      <c r="J13" s="45" t="n">
+      <c r="J13" s="51" t="n">
         <v>0.2047253226310126</v>
       </c>
       <c r="K13" s="15" t="n">
@@ -1597,7 +2419,7 @@
       <c r="M13" s="16" t="n">
         <v>3080</v>
       </c>
-      <c r="N13" s="45" t="n">
+      <c r="N13" s="51" t="n">
         <v>0.5165618448637317</v>
       </c>
     </row>
@@ -1621,7 +2443,7 @@
       <c r="E14" s="16" t="n">
         <v>8831.440000000001</v>
       </c>
-      <c r="F14" s="45" t="n">
+      <c r="F14" s="51" t="n">
         <v>0.1777330554736579</v>
       </c>
       <c r="G14" s="15" t="n">
@@ -1633,7 +2455,7 @@
       <c r="I14" s="16" t="n">
         <v>16668.05</v>
       </c>
-      <c r="J14" s="45" t="n">
+      <c r="J14" s="51" t="n">
         <v>0.2597668245969831</v>
       </c>
       <c r="K14" s="15" t="n">
@@ -1645,7 +2467,7 @@
       <c r="M14" s="16" t="n">
         <v>2939.65</v>
       </c>
-      <c r="N14" s="45" t="n">
+      <c r="N14" s="51" t="n">
         <v>0.1501736909323116</v>
       </c>
     </row>
@@ -1656,7 +2478,7 @@
           <t>4-mo TOTAL</t>
         </is>
       </c>
-      <c r="C15" s="46" t="n">
+      <c r="C15" s="52" t="n">
         <v>117</v>
       </c>
       <c r="D15" s="19" t="n">
@@ -1665,10 +2487,10 @@
       <c r="E15" s="19" t="n">
         <v>30069.75</v>
       </c>
-      <c r="F15" s="47" t="n">
+      <c r="F15" s="53" t="n">
         <v>0.1743867416259452</v>
       </c>
-      <c r="G15" s="46" t="n">
+      <c r="G15" s="52" t="n">
         <v>217</v>
       </c>
       <c r="H15" s="19" t="n">
@@ -1677,10 +2499,10 @@
       <c r="I15" s="19" t="n">
         <v>61236.18000000001</v>
       </c>
-      <c r="J15" s="47" t="n">
+      <c r="J15" s="53" t="n">
         <v>0.1965130808087551</v>
       </c>
-      <c r="K15" s="46" t="n">
+      <c r="K15" s="52" t="n">
         <v>29</v>
       </c>
       <c r="L15" s="19" t="n">
@@ -1689,7 +2511,7 @@
       <c r="M15" s="19" t="n">
         <v>12908.84</v>
       </c>
-      <c r="N15" s="47" t="n">
+      <c r="N15" s="53" t="n">
         <v>0.2597474930907196</v>
       </c>
     </row>
@@ -1713,7 +2535,7 @@
       <c r="E17" s="16" t="n">
         <v>7651.14</v>
       </c>
-      <c r="F17" s="45" t="n">
+      <c r="F17" s="51" t="n">
         <v>0.2065698317989147</v>
       </c>
       <c r="G17" s="15" t="n">
@@ -1725,7 +2547,7 @@
       <c r="I17" s="16" t="n">
         <v>11897.57</v>
       </c>
-      <c r="J17" s="45" t="n">
+      <c r="J17" s="51" t="n">
         <v>0.1877343410993381</v>
       </c>
       <c r="K17" s="15" t="n">
@@ -1737,7 +2559,7 @@
       <c r="M17" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="N17" s="45" t="n">
+      <c r="N17" s="51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1761,7 +2583,7 @@
       <c r="E18" s="16" t="n">
         <v>2095.02</v>
       </c>
-      <c r="F18" s="45" t="n">
+      <c r="F18" s="51" t="n">
         <v>0.2735191592140479</v>
       </c>
       <c r="G18" s="15" t="n">
@@ -1773,7 +2595,7 @@
       <c r="I18" s="16" t="n">
         <v>6802.73</v>
       </c>
-      <c r="J18" s="45" t="n">
+      <c r="J18" s="51" t="n">
         <v>0.1360799108634206</v>
       </c>
       <c r="K18" s="15" t="n">
@@ -1785,7 +2607,7 @@
       <c r="M18" s="16" t="n">
         <v>91.75</v>
       </c>
-      <c r="N18" s="45" t="n">
+      <c r="N18" s="51" t="n">
         <v>0.08631232361241768</v>
       </c>
     </row>
@@ -1809,7 +2631,7 @@
       <c r="E19" s="16" t="n">
         <v>5669.41</v>
       </c>
-      <c r="F19" s="45" t="n">
+      <c r="F19" s="51" t="n">
         <v>0.142591870663008</v>
       </c>
       <c r="G19" s="15" t="n">
@@ -1821,7 +2643,7 @@
       <c r="I19" s="16" t="n">
         <v>8620.469999999999</v>
       </c>
-      <c r="J19" s="45" t="n">
+      <c r="J19" s="51" t="n">
         <v>0.1516070882122243</v>
       </c>
       <c r="K19" s="15" t="n">
@@ -1833,7 +2655,7 @@
       <c r="M19" s="16" t="n">
         <v>180.45</v>
       </c>
-      <c r="N19" s="45" t="n">
+      <c r="N19" s="51" t="n">
         <v>0.1745164410058027</v>
       </c>
     </row>
@@ -1857,7 +2679,7 @@
       <c r="E20" s="16" t="n">
         <v>4344.3</v>
       </c>
-      <c r="F20" s="45" t="n">
+      <c r="F20" s="51" t="n">
         <v>0.225229218673448</v>
       </c>
       <c r="G20" s="15" t="n">
@@ -1869,7 +2691,7 @@
       <c r="I20" s="16" t="n">
         <v>7660.7</v>
       </c>
-      <c r="J20" s="45" t="n">
+      <c r="J20" s="51" t="n">
         <v>0.1765292813656495</v>
       </c>
       <c r="K20" s="15" t="n">
@@ -1881,7 +2703,7 @@
       <c r="M20" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="N20" s="45" t="n">
+      <c r="N20" s="51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1892,7 +2714,7 @@
           <t>4-mo TOTAL</t>
         </is>
       </c>
-      <c r="C21" s="46" t="n">
+      <c r="C21" s="52" t="n">
         <v>87</v>
       </c>
       <c r="D21" s="19" t="n">
@@ -1901,10 +2723,10 @@
       <c r="E21" s="19" t="n">
         <v>19759.87</v>
       </c>
-      <c r="F21" s="47" t="n">
+      <c r="F21" s="53" t="n">
         <v>0.1904629117787531</v>
       </c>
-      <c r="G21" s="46" t="n">
+      <c r="G21" s="52" t="n">
         <v>170</v>
       </c>
       <c r="H21" s="19" t="n">
@@ -1913,10 +2735,10 @@
       <c r="I21" s="19" t="n">
         <v>34981.46999999999</v>
       </c>
-      <c r="J21" s="47" t="n">
+      <c r="J21" s="53" t="n">
         <v>0.1637540609113293</v>
       </c>
-      <c r="K21" s="46" t="n">
+      <c r="K21" s="52" t="n">
         <v>2</v>
       </c>
       <c r="L21" s="19" t="n">
@@ -1925,7 +2747,7 @@
       <c r="M21" s="19" t="n">
         <v>272.2</v>
       </c>
-      <c r="N21" s="47" t="n">
+      <c r="N21" s="53" t="n">
         <v>0.1298044825941821</v>
       </c>
     </row>
@@ -1949,7 +2771,7 @@
       <c r="E23" s="16" t="n">
         <v>5657.4</v>
       </c>
-      <c r="F23" s="45" t="n">
+      <c r="F23" s="51" t="n">
         <v>0.1983309406994904</v>
       </c>
       <c r="G23" s="15" t="n">
@@ -1961,7 +2783,7 @@
       <c r="I23" s="16" t="n">
         <v>8795.290000000001</v>
       </c>
-      <c r="J23" s="45" t="n">
+      <c r="J23" s="51" t="n">
         <v>0.2223388159932049</v>
       </c>
       <c r="K23" s="15" t="n">
@@ -1973,7 +2795,7 @@
       <c r="M23" s="16" t="n">
         <v>302.12</v>
       </c>
-      <c r="N23" s="45" t="n">
+      <c r="N23" s="51" t="n">
         <v>0.2063167958479872</v>
       </c>
     </row>
@@ -1997,7 +2819,7 @@
       <c r="E24" s="16" t="n">
         <v>3832.59</v>
       </c>
-      <c r="F24" s="45" t="n">
+      <c r="F24" s="51" t="n">
         <v>0.1722690435415796</v>
       </c>
       <c r="G24" s="15" t="n">
@@ -2009,7 +2831,7 @@
       <c r="I24" s="16" t="n">
         <v>13820.09</v>
       </c>
-      <c r="J24" s="45" t="n">
+      <c r="J24" s="51" t="n">
         <v>0.3163400473133589</v>
       </c>
       <c r="K24" s="15" t="n">
@@ -2021,7 +2843,7 @@
       <c r="M24" s="16" t="n">
         <v>321.01</v>
       </c>
-      <c r="N24" s="45" t="n">
+      <c r="N24" s="51" t="n">
         <v>0.152934730824202</v>
       </c>
     </row>
@@ -2045,7 +2867,7 @@
       <c r="E25" s="16" t="n">
         <v>8642.02</v>
       </c>
-      <c r="F25" s="45" t="n">
+      <c r="F25" s="51" t="n">
         <v>0.2763766030253606</v>
       </c>
       <c r="G25" s="15" t="n">
@@ -2057,7 +2879,7 @@
       <c r="I25" s="16" t="n">
         <v>9060.629999999999</v>
       </c>
-      <c r="J25" s="45" t="n">
+      <c r="J25" s="51" t="n">
         <v>0.3851211602137146</v>
       </c>
       <c r="K25" s="15" t="n">
@@ -2069,7 +2891,7 @@
       <c r="M25" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="N25" s="45" t="n">
+      <c r="N25" s="51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2093,7 +2915,7 @@
       <c r="E26" s="16" t="n">
         <v>6600.51</v>
       </c>
-      <c r="F26" s="45" t="n">
+      <c r="F26" s="51" t="n">
         <v>0.2231330530863509</v>
       </c>
       <c r="G26" s="15" t="n">
@@ -2105,7 +2927,7 @@
       <c r="I26" s="16" t="n">
         <v>7710.62</v>
       </c>
-      <c r="J26" s="45" t="n">
+      <c r="J26" s="51" t="n">
         <v>0.2500788122762931</v>
       </c>
       <c r="K26" s="15" t="n">
@@ -2117,7 +2939,7 @@
       <c r="M26" s="16" t="n">
         <v>885</v>
       </c>
-      <c r="N26" s="45" t="n">
+      <c r="N26" s="51" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2128,7 +2950,7 @@
           <t>4-mo TOTAL</t>
         </is>
       </c>
-      <c r="C27" s="46" t="n">
+      <c r="C27" s="52" t="n">
         <v>92</v>
       </c>
       <c r="D27" s="19" t="n">
@@ -2137,10 +2959,10 @@
       <c r="E27" s="19" t="n">
         <v>24732.52</v>
       </c>
-      <c r="F27" s="47" t="n">
+      <c r="F27" s="53" t="n">
         <v>0.2215722952658418</v>
       </c>
-      <c r="G27" s="46" t="n">
+      <c r="G27" s="52" t="n">
         <v>135</v>
       </c>
       <c r="H27" s="19" t="n">
@@ -2149,10 +2971,10 @@
       <c r="I27" s="19" t="n">
         <v>39386.63</v>
       </c>
-      <c r="J27" s="47" t="n">
+      <c r="J27" s="53" t="n">
         <v>0.2862297260215039</v>
       </c>
-      <c r="K27" s="46" t="n">
+      <c r="K27" s="52" t="n">
         <v>4</v>
       </c>
       <c r="L27" s="19" t="n">
@@ -2161,7 +2983,7 @@
       <c r="M27" s="19" t="n">
         <v>1508.13</v>
       </c>
-      <c r="N27" s="47" t="n">
+      <c r="N27" s="53" t="n">
         <v>0.3390313262220823</v>
       </c>
     </row>
@@ -2185,7 +3007,7 @@
       <c r="E29" s="16" t="n">
         <v>2238.28</v>
       </c>
-      <c r="F29" s="45" t="n">
+      <c r="F29" s="51" t="n">
         <v>0.1443688362283039</v>
       </c>
       <c r="G29" s="15" t="n">
@@ -2197,7 +3019,7 @@
       <c r="I29" s="16" t="n">
         <v>6461.48</v>
       </c>
-      <c r="J29" s="45" t="n">
+      <c r="J29" s="51" t="n">
         <v>0.1953056967536807</v>
       </c>
       <c r="K29" s="15" t="n">
@@ -2209,7 +3031,7 @@
       <c r="M29" s="16" t="n">
         <v>642.04</v>
       </c>
-      <c r="N29" s="45" t="n">
+      <c r="N29" s="51" t="n">
         <v>0.1739945799457994</v>
       </c>
     </row>
@@ -2233,7 +3055,7 @@
       <c r="E30" s="16" t="n">
         <v>3640.91</v>
       </c>
-      <c r="F30" s="45" t="n">
+      <c r="F30" s="51" t="n">
         <v>0.1875380197535315</v>
       </c>
       <c r="G30" s="15" t="n">
@@ -2245,7 +3067,7 @@
       <c r="I30" s="16" t="n">
         <v>5276.12</v>
       </c>
-      <c r="J30" s="45" t="n">
+      <c r="J30" s="51" t="n">
         <v>0.186447458067945</v>
       </c>
       <c r="K30" s="15" t="n">
@@ -2257,7 +3079,7 @@
       <c r="M30" s="16" t="n">
         <v>3293.14</v>
       </c>
-      <c r="N30" s="45" t="n">
+      <c r="N30" s="51" t="n">
         <v>0.442269674993285</v>
       </c>
     </row>
@@ -2281,7 +3103,7 @@
       <c r="E31" s="16" t="n">
         <v>4965.76</v>
       </c>
-      <c r="F31" s="45" t="n">
+      <c r="F31" s="51" t="n">
         <v>0.2782922142225067</v>
       </c>
       <c r="G31" s="15" t="n">
@@ -2293,7 +3115,7 @@
       <c r="I31" s="16" t="n">
         <v>3981.64</v>
       </c>
-      <c r="J31" s="45" t="n">
+      <c r="J31" s="51" t="n">
         <v>0.2006789023655741</v>
       </c>
       <c r="K31" s="15" t="n">
@@ -2305,7 +3127,7 @@
       <c r="M31" s="16" t="n">
         <v>1575.86</v>
       </c>
-      <c r="N31" s="45" t="n">
+      <c r="N31" s="51" t="n">
         <v>0.2792147274048087</v>
       </c>
     </row>
@@ -2329,7 +3151,7 @@
       <c r="E32" s="16" t="n">
         <v>3941.94</v>
       </c>
-      <c r="F32" s="45" t="n">
+      <c r="F32" s="51" t="n">
         <v>0.2795900418469395</v>
       </c>
       <c r="G32" s="15" t="n">
@@ -2341,7 +3163,7 @@
       <c r="I32" s="16" t="n">
         <v>7674.9</v>
       </c>
-      <c r="J32" s="45" t="n">
+      <c r="J32" s="51" t="n">
         <v>0.1928638200349798</v>
       </c>
       <c r="K32" s="15" t="n">
@@ -2353,7 +3175,7 @@
       <c r="M32" s="16" t="n">
         <v>3096.58</v>
       </c>
-      <c r="N32" s="45" t="n">
+      <c r="N32" s="51" t="n">
         <v>0.8561183301078241</v>
       </c>
     </row>
@@ -2364,7 +3186,7 @@
           <t>4-mo TOTAL</t>
         </is>
       </c>
-      <c r="C33" s="46" t="n">
+      <c r="C33" s="52" t="n">
         <v>52</v>
       </c>
       <c r="D33" s="19" t="n">
@@ -2373,10 +3195,10 @@
       <c r="E33" s="19" t="n">
         <v>14786.89</v>
       </c>
-      <c r="F33" s="47" t="n">
+      <c r="F33" s="53" t="n">
         <v>0.2211592017091021</v>
       </c>
-      <c r="G33" s="46" t="n">
+      <c r="G33" s="52" t="n">
         <v>100</v>
       </c>
       <c r="H33" s="19" t="n">
@@ -2385,10 +3207,10 @@
       <c r="I33" s="19" t="n">
         <v>23394.14</v>
       </c>
-      <c r="J33" s="47" t="n">
+      <c r="J33" s="53" t="n">
         <v>0.1933122972294714</v>
       </c>
-      <c r="K33" s="46" t="n">
+      <c r="K33" s="52" t="n">
         <v>18</v>
       </c>
       <c r="L33" s="19" t="n">
@@ -2397,7 +3219,7 @@
       <c r="M33" s="19" t="n">
         <v>8607.619999999999</v>
       </c>
-      <c r="N33" s="47" t="n">
+      <c r="N33" s="53" t="n">
         <v>0.4220062852688398</v>
       </c>
     </row>
@@ -2421,7 +3243,7 @@
       <c r="E35" s="16" t="n">
         <v>6551.7</v>
       </c>
-      <c r="F35" s="45" t="n">
+      <c r="F35" s="51" t="n">
         <v>0.2290380555484667</v>
       </c>
       <c r="G35" s="15" t="n">
@@ -2433,7 +3255,7 @@
       <c r="I35" s="16" t="n">
         <v>8203.879999999999</v>
       </c>
-      <c r="J35" s="45" t="n">
+      <c r="J35" s="51" t="n">
         <v>0.1687591127962584</v>
       </c>
       <c r="K35" s="15" t="n">
@@ -2445,7 +3267,7 @@
       <c r="M35" s="16" t="n">
         <v>1439.3</v>
       </c>
-      <c r="N35" s="45" t="n">
+      <c r="N35" s="51" t="n">
         <v>0.2213316807398534</v>
       </c>
     </row>
@@ -2469,7 +3291,7 @@
       <c r="E36" s="16" t="n">
         <v>6512.87</v>
       </c>
-      <c r="F36" s="45" t="n">
+      <c r="F36" s="51" t="n">
         <v>0.206646582235908</v>
       </c>
       <c r="G36" s="15" t="n">
@@ -2481,7 +3303,7 @@
       <c r="I36" s="16" t="n">
         <v>7155.23</v>
       </c>
-      <c r="J36" s="45" t="n">
+      <c r="J36" s="51" t="n">
         <v>0.1515034032647457</v>
       </c>
       <c r="K36" s="15" t="n">
@@ -2493,7 +3315,7 @@
       <c r="M36" s="16" t="n">
         <v>272.87</v>
       </c>
-      <c r="N36" s="45" t="n">
+      <c r="N36" s="51" t="n">
         <v>0.0882503234152652</v>
       </c>
     </row>
@@ -2517,7 +3339,7 @@
       <c r="E37" s="16" t="n">
         <v>17019.79</v>
       </c>
-      <c r="F37" s="45" t="n">
+      <c r="F37" s="51" t="n">
         <v>0.2482965508528406</v>
       </c>
       <c r="G37" s="15" t="n">
@@ -2529,7 +3351,7 @@
       <c r="I37" s="16" t="n">
         <v>5300.53</v>
       </c>
-      <c r="J37" s="45" t="n">
+      <c r="J37" s="51" t="n">
         <v>0.135029353210384</v>
       </c>
       <c r="K37" s="15" t="n">
@@ -2541,7 +3363,7 @@
       <c r="M37" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="N37" s="45" t="n">
+      <c r="N37" s="51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2565,7 +3387,7 @@
       <c r="E38" s="16" t="n">
         <v>6197.26</v>
       </c>
-      <c r="F38" s="45" t="n">
+      <c r="F38" s="51" t="n">
         <v>0.2082728262918876</v>
       </c>
       <c r="G38" s="15" t="n">
@@ -2577,7 +3399,7 @@
       <c r="I38" s="16" t="n">
         <v>7305.79</v>
       </c>
-      <c r="J38" s="45" t="n">
+      <c r="J38" s="51" t="n">
         <v>0.2070808023832267</v>
       </c>
       <c r="K38" s="15" t="n">
@@ -2589,7 +3411,7 @@
       <c r="M38" s="16" t="n">
         <v>291.12</v>
       </c>
-      <c r="N38" s="45" t="n">
+      <c r="N38" s="51" t="n">
         <v>0.115799522673031</v>
       </c>
     </row>
@@ -2600,7 +3422,7 @@
           <t>4-mo TOTAL</t>
         </is>
       </c>
-      <c r="C39" s="46" t="n">
+      <c r="C39" s="52" t="n">
         <v>102</v>
       </c>
       <c r="D39" s="19" t="n">
@@ -2609,10 +3431,10 @@
       <c r="E39" s="19" t="n">
         <v>36281.62</v>
       </c>
-      <c r="F39" s="47" t="n">
+      <c r="F39" s="53" t="n">
         <v>0.2290160042089596</v>
       </c>
-      <c r="G39" s="46" t="n">
+      <c r="G39" s="52" t="n">
         <v>116</v>
       </c>
       <c r="H39" s="19" t="n">
@@ -2621,10 +3443,10 @@
       <c r="I39" s="19" t="n">
         <v>27965.43</v>
       </c>
-      <c r="J39" s="47" t="n">
+      <c r="J39" s="53" t="n">
         <v>0.1641397901308573</v>
       </c>
-      <c r="K39" s="46" t="n">
+      <c r="K39" s="52" t="n">
         <v>10</v>
       </c>
       <c r="L39" s="19" t="n">
@@ -2633,7 +3455,7 @@
       <c r="M39" s="19" t="n">
         <v>2003.29</v>
       </c>
-      <c r="N39" s="47" t="n">
+      <c r="N39" s="53" t="n">
         <v>0.1654393335155683</v>
       </c>
     </row>
@@ -15140,6 +15962,2888 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J86"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CURRENT vs NEW PLAN - per agent-month comparison</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>CURRENT = today's plan: count NB+RWR policies, 30/38/50 tier -&gt; $250/$350/$450 + $10/policy above 50. NEW = the new tier-based plan (NB + RWR + REN combined). Sorted by DELTA descending: biggest winners on top, biggest losses at the bottom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>SCENARIO 1: REAL DATA (Jan-Apr 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>NB #</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>RWR #</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT bonus (today)</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>NB Bonus</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>RWR Bonus</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>REN Bonus</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>NEW TOTAL</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>DELTA (new - current)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>Abel Guaina</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="D6" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="E6" s="41" t="n">
+        <v>350</v>
+      </c>
+      <c r="F6" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="G6" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="42" t="n">
+        <v>250</v>
+      </c>
+      <c r="J6" s="43" t="n">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>Monica Valdes</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="E7" s="41" t="n">
+        <v>590</v>
+      </c>
+      <c r="F7" s="34" t="n">
+        <v>375</v>
+      </c>
+      <c r="G7" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="42" t="n">
+        <v>375</v>
+      </c>
+      <c r="J7" s="43" t="n">
+        <v>-215</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>Abel Guaina</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="E8" s="41" t="n">
+        <v>250</v>
+      </c>
+      <c r="F8" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="43" t="n">
+        <v>-250</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>Dialinerys Dieguez</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="n">
+        <v>33</v>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>44</v>
+      </c>
+      <c r="E9" s="41" t="n">
+        <v>720</v>
+      </c>
+      <c r="F9" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="G9" s="34" t="n">
+        <v>200</v>
+      </c>
+      <c r="H9" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="42" t="n">
+        <v>450</v>
+      </c>
+      <c r="J9" s="43" t="n">
+        <v>-270</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>Abel Guaina</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="D10" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="E10" s="41" t="n">
+        <v>350</v>
+      </c>
+      <c r="F10" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="43" t="n">
+        <v>-350</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>Abel Guaina</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="n">
+        <v>27</v>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="E11" s="41" t="n">
+        <v>350</v>
+      </c>
+      <c r="F11" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="43" t="n">
+        <v>-350</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t>Thalia Rojas</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="E12" s="41" t="n">
+        <v>350</v>
+      </c>
+      <c r="F12" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="43" t="n">
+        <v>-350</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>Thalia Rojas</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="D13" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="E13" s="41" t="n">
+        <v>350</v>
+      </c>
+      <c r="F13" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="43" t="n">
+        <v>-350</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>Thalia Rojas</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="D14" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="E14" s="41" t="n">
+        <v>350</v>
+      </c>
+      <c r="F14" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="43" t="n">
+        <v>-350</v>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>Thalia Rojas</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="D15" s="15" t="n">
+        <v>29</v>
+      </c>
+      <c r="E15" s="41" t="n">
+        <v>350</v>
+      </c>
+      <c r="F15" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="43" t="n">
+        <v>-350</v>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t>Monica Valdes</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="D16" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="E16" s="41" t="n">
+        <v>350</v>
+      </c>
+      <c r="F16" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="43" t="n">
+        <v>-350</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>Dialinerys Dieguez</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="D17" s="15" t="n">
+        <v>69</v>
+      </c>
+      <c r="E17" s="41" t="n">
+        <v>1020</v>
+      </c>
+      <c r="F17" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="G17" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="H17" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="42" t="n">
+        <v>600</v>
+      </c>
+      <c r="J17" s="43" t="n">
+        <v>-420</v>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="25" t="inlineStr">
+        <is>
+          <t>Melissa Hernandez</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D18" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="E18" s="41" t="n">
+        <v>450</v>
+      </c>
+      <c r="F18" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="43" t="n">
+        <v>-450</v>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t>Monica Valdes</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="D19" s="15" t="n">
+        <v>29</v>
+      </c>
+      <c r="E19" s="41" t="n">
+        <v>450</v>
+      </c>
+      <c r="F19" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="43" t="n">
+        <v>-450</v>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="25" t="inlineStr">
+        <is>
+          <t>Melissa Hernandez</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="D20" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="E20" s="41" t="n">
+        <v>470</v>
+      </c>
+      <c r="F20" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="43" t="n">
+        <v>-470</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>Flavia Parra</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="D21" s="15" t="n">
+        <v>35</v>
+      </c>
+      <c r="E21" s="41" t="n">
+        <v>490</v>
+      </c>
+      <c r="F21" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="43" t="n">
+        <v>-490</v>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="25" t="inlineStr">
+        <is>
+          <t>Flavia Parra</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="n">
+        <v>27</v>
+      </c>
+      <c r="D22" s="15" t="n">
+        <v>27</v>
+      </c>
+      <c r="E22" s="41" t="n">
+        <v>490</v>
+      </c>
+      <c r="F22" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="43" t="n">
+        <v>-490</v>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="25" t="inlineStr">
+        <is>
+          <t>Flavia Parra</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="D23" s="15" t="n">
+        <v>31</v>
+      </c>
+      <c r="E23" s="41" t="n">
+        <v>490</v>
+      </c>
+      <c r="F23" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="43" t="n">
+        <v>-490</v>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="25" t="inlineStr">
+        <is>
+          <t>Monica Valdes</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="D24" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="E24" s="41" t="n">
+        <v>550</v>
+      </c>
+      <c r="F24" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="43" t="n">
+        <v>-550</v>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>Flavia Parra</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="D25" s="15" t="n">
+        <v>42</v>
+      </c>
+      <c r="E25" s="41" t="n">
+        <v>600</v>
+      </c>
+      <c r="F25" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="43" t="n">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>Dialinerys Dieguez</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="D26" s="15" t="n">
+        <v>48</v>
+      </c>
+      <c r="E26" s="41" t="n">
+        <v>660</v>
+      </c>
+      <c r="F26" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="43" t="n">
+        <v>-660</v>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>Melissa Hernandez</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="D27" s="15" t="n">
+        <v>48</v>
+      </c>
+      <c r="E27" s="41" t="n">
+        <v>710</v>
+      </c>
+      <c r="F27" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="43" t="n">
+        <v>-710</v>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>Dialinerys Dieguez</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="D28" s="15" t="n">
+        <v>56</v>
+      </c>
+      <c r="E28" s="41" t="n">
+        <v>740</v>
+      </c>
+      <c r="F28" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="43" t="n">
+        <v>-740</v>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Melissa Hernandez</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="n">
+        <v>31</v>
+      </c>
+      <c r="D29" s="15" t="n">
+        <v>48</v>
+      </c>
+      <c r="E29" s="41" t="n">
+        <v>740</v>
+      </c>
+      <c r="F29" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="43" t="n">
+        <v>-740</v>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>4-MONTH TOTAL (all 6 agents)</t>
+        </is>
+      </c>
+      <c r="B30" s="39" t="n"/>
+      <c r="C30" s="39" t="n"/>
+      <c r="D30" s="39" t="n"/>
+      <c r="E30" s="44" t="n">
+        <v>12220</v>
+      </c>
+      <c r="F30" s="39" t="n"/>
+      <c r="G30" s="39" t="n"/>
+      <c r="H30" s="39" t="n"/>
+      <c r="I30" s="45" t="n">
+        <v>1675</v>
+      </c>
+      <c r="J30" s="43" t="n">
+        <v>-10545</v>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>SCENARIO 2: 50% SWAP (half of RWR -&gt; REN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>NB #</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>RWR #</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT bonus (today)</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>NB Bonus</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>RWR Bonus</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>REN Bonus</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>NEW TOTAL</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>DELTA (new - current)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Dialinerys Dieguez</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="n">
+        <v>33</v>
+      </c>
+      <c r="D34" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="E34" s="41" t="n">
+        <v>500</v>
+      </c>
+      <c r="F34" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="G34" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="I34" s="42" t="n">
+        <v>600</v>
+      </c>
+      <c r="J34" s="42" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>Dialinerys Dieguez</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="D35" s="15" t="n">
+        <v>35</v>
+      </c>
+      <c r="E35" s="41" t="n">
+        <v>680</v>
+      </c>
+      <c r="F35" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="G35" s="34" t="n">
+        <v>100</v>
+      </c>
+      <c r="H35" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="I35" s="42" t="n">
+        <v>700</v>
+      </c>
+      <c r="J35" s="42" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>Abel Guaina</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D36" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="E36" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>Dialinerys Dieguez</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="D37" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="E37" s="41" t="n">
+        <v>350</v>
+      </c>
+      <c r="F37" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="I37" s="42" t="n">
+        <v>350</v>
+      </c>
+      <c r="J37" s="46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>Melissa Hernandez</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D38" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="E38" s="41" t="n">
+        <v>250</v>
+      </c>
+      <c r="F38" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I38" s="42" t="n">
+        <v>250</v>
+      </c>
+      <c r="J38" s="46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="25" t="inlineStr">
+        <is>
+          <t>Thalia Rojas</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="D39" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="E39" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>Thalia Rojas</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="D40" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="E40" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="25" t="inlineStr">
+        <is>
+          <t>Thalia Rojas</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="D41" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="E41" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="25" t="inlineStr">
+        <is>
+          <t>Thalia Rojas</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="D42" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="E42" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="25" t="inlineStr">
+        <is>
+          <t>Monica Valdes</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="D43" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="E43" s="41" t="n">
+        <v>450</v>
+      </c>
+      <c r="F43" s="34" t="n">
+        <v>375</v>
+      </c>
+      <c r="G43" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="42" t="n">
+        <v>375</v>
+      </c>
+      <c r="J43" s="43" t="n">
+        <v>-75</v>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="25" t="inlineStr">
+        <is>
+          <t>Abel Guaina</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="D44" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="E44" s="41" t="n">
+        <v>350</v>
+      </c>
+      <c r="F44" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="G44" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="42" t="n">
+        <v>250</v>
+      </c>
+      <c r="J44" s="43" t="n">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="25" t="inlineStr">
+        <is>
+          <t>Monica Valdes</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C45" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="D45" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="E45" s="41" t="n">
+        <v>350</v>
+      </c>
+      <c r="F45" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I45" s="42" t="n">
+        <v>250</v>
+      </c>
+      <c r="J45" s="43" t="n">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="25" t="inlineStr">
+        <is>
+          <t>Monica Valdes</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="C46" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="D46" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="E46" s="41" t="n">
+        <v>350</v>
+      </c>
+      <c r="F46" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I46" s="42" t="n">
+        <v>250</v>
+      </c>
+      <c r="J46" s="43" t="n">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="25" t="inlineStr">
+        <is>
+          <t>Dialinerys Dieguez</t>
+        </is>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="C47" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="D47" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="E47" s="41" t="n">
+        <v>460</v>
+      </c>
+      <c r="F47" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="I47" s="42" t="n">
+        <v>350</v>
+      </c>
+      <c r="J47" s="43" t="n">
+        <v>-110</v>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="25" t="inlineStr">
+        <is>
+          <t>Melissa Hernandez</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="D48" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="E48" s="41" t="n">
+        <v>470</v>
+      </c>
+      <c r="F48" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I48" s="42" t="n">
+        <v>250</v>
+      </c>
+      <c r="J48" s="43" t="n">
+        <v>-220</v>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="25" t="inlineStr">
+        <is>
+          <t>Abel Guaina</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C49" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="D49" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="E49" s="41" t="n">
+        <v>250</v>
+      </c>
+      <c r="F49" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="43" t="n">
+        <v>-250</v>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="25" t="inlineStr">
+        <is>
+          <t>Abel Guaina</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="n">
+        <v>27</v>
+      </c>
+      <c r="D50" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E50" s="41" t="n">
+        <v>250</v>
+      </c>
+      <c r="F50" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="43" t="n">
+        <v>-250</v>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="25" t="inlineStr">
+        <is>
+          <t>Melissa Hernandez</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C51" s="15" t="n">
+        <v>31</v>
+      </c>
+      <c r="D51" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="E51" s="41" t="n">
+        <v>500</v>
+      </c>
+      <c r="F51" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I51" s="42" t="n">
+        <v>250</v>
+      </c>
+      <c r="J51" s="43" t="n">
+        <v>-250</v>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="25" t="inlineStr">
+        <is>
+          <t>Melissa Hernandez</t>
+        </is>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C52" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="D52" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="E52" s="41" t="n">
+        <v>250</v>
+      </c>
+      <c r="F52" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="43" t="n">
+        <v>-250</v>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="25" t="inlineStr">
+        <is>
+          <t>Monica Valdes</t>
+        </is>
+      </c>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C53" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="D53" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="E53" s="41" t="n">
+        <v>250</v>
+      </c>
+      <c r="F53" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="43" t="n">
+        <v>-250</v>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="25" t="inlineStr">
+        <is>
+          <t>Flavia Parra</t>
+        </is>
+      </c>
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C54" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="D54" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="E54" s="41" t="n">
+        <v>350</v>
+      </c>
+      <c r="F54" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="43" t="n">
+        <v>-350</v>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="25" t="inlineStr">
+        <is>
+          <t>Flavia Parra</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="C55" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="D55" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="E55" s="41" t="n">
+        <v>350</v>
+      </c>
+      <c r="F55" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="43" t="n">
+        <v>-350</v>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="25" t="inlineStr">
+        <is>
+          <t>Flavia Parra</t>
+        </is>
+      </c>
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="C56" s="15" t="n">
+        <v>27</v>
+      </c>
+      <c r="D56" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="E56" s="41" t="n">
+        <v>350</v>
+      </c>
+      <c r="F56" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="43" t="n">
+        <v>-350</v>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="25" t="inlineStr">
+        <is>
+          <t>Flavia Parra</t>
+        </is>
+      </c>
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C57" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="D57" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="E57" s="41" t="n">
+        <v>350</v>
+      </c>
+      <c r="F57" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="43" t="n">
+        <v>-350</v>
+      </c>
+    </row>
+    <row r="58" ht="28" customHeight="1">
+      <c r="A58" s="18" t="inlineStr">
+        <is>
+          <t>4-MONTH TOTAL (all 6 agents)</t>
+        </is>
+      </c>
+      <c r="B58" s="39" t="n"/>
+      <c r="C58" s="39" t="n"/>
+      <c r="D58" s="39" t="n"/>
+      <c r="E58" s="44" t="n">
+        <v>7110</v>
+      </c>
+      <c r="F58" s="39" t="n"/>
+      <c r="G58" s="39" t="n"/>
+      <c r="H58" s="39" t="n"/>
+      <c r="I58" s="45" t="n">
+        <v>3875</v>
+      </c>
+      <c r="J58" s="43" t="n">
+        <v>-3235</v>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>SCENARIO 3: 100% FLIP (RWR fully -&gt; REN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="26" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>NB #</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>RWR #</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT bonus (today)</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>NB Bonus</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>RWR Bonus</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>REN Bonus</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>NEW TOTAL</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>DELTA (new - current)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="25" t="inlineStr">
+        <is>
+          <t>Dialinerys Dieguez</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="C62" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="D62" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E62" s="41" t="n">
+        <v>350</v>
+      </c>
+      <c r="F62" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="G62" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="34" t="n">
+        <v>550</v>
+      </c>
+      <c r="I62" s="42" t="n">
+        <v>800</v>
+      </c>
+      <c r="J62" s="42" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="25" t="inlineStr">
+        <is>
+          <t>Melissa Hernandez</t>
+        </is>
+      </c>
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="C63" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D63" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="I63" s="42" t="n">
+        <v>350</v>
+      </c>
+      <c r="J63" s="42" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="25" t="inlineStr">
+        <is>
+          <t>Melissa Hernandez</t>
+        </is>
+      </c>
+      <c r="B64" s="14" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="C64" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="D64" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="I64" s="42" t="n">
+        <v>350</v>
+      </c>
+      <c r="J64" s="42" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="25" t="inlineStr">
+        <is>
+          <t>Melissa Hernandez</t>
+        </is>
+      </c>
+      <c r="B65" s="14" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C65" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="D65" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="I65" s="42" t="n">
+        <v>350</v>
+      </c>
+      <c r="J65" s="42" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="25" t="inlineStr">
+        <is>
+          <t>Flavia Parra</t>
+        </is>
+      </c>
+      <c r="B66" s="14" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="C66" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="D66" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E66" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="I66" s="42" t="n">
+        <v>350</v>
+      </c>
+      <c r="J66" s="42" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="25" t="inlineStr">
+        <is>
+          <t>Monica Valdes</t>
+        </is>
+      </c>
+      <c r="B67" s="14" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C67" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="D67" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E67" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="I67" s="42" t="n">
+        <v>350</v>
+      </c>
+      <c r="J67" s="42" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="25" t="inlineStr">
+        <is>
+          <t>Monica Valdes</t>
+        </is>
+      </c>
+      <c r="B68" s="14" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="C68" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="D68" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E68" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="I68" s="42" t="n">
+        <v>350</v>
+      </c>
+      <c r="J68" s="42" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="25" t="inlineStr">
+        <is>
+          <t>Dialinerys Dieguez</t>
+        </is>
+      </c>
+      <c r="B69" s="14" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="C69" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="D69" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="E69" s="41" t="n">
+        <v>250</v>
+      </c>
+      <c r="F69" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="34" t="n">
+        <v>550</v>
+      </c>
+      <c r="I69" s="42" t="n">
+        <v>550</v>
+      </c>
+      <c r="J69" s="42" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="25" t="inlineStr">
+        <is>
+          <t>Monica Valdes</t>
+        </is>
+      </c>
+      <c r="B70" s="14" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="C70" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="D70" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="41" t="n">
+        <v>350</v>
+      </c>
+      <c r="F70" s="34" t="n">
+        <v>375</v>
+      </c>
+      <c r="G70" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I70" s="42" t="n">
+        <v>625</v>
+      </c>
+      <c r="J70" s="42" t="n">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="25" t="inlineStr">
+        <is>
+          <t>Abel Guaina</t>
+        </is>
+      </c>
+      <c r="B71" s="14" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="C71" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D71" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E71" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I71" s="42" t="n">
+        <v>250</v>
+      </c>
+      <c r="J71" s="42" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="25" t="inlineStr">
+        <is>
+          <t>Dialinerys Dieguez</t>
+        </is>
+      </c>
+      <c r="B72" s="14" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C72" s="15" t="n">
+        <v>33</v>
+      </c>
+      <c r="D72" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E72" s="41" t="n">
+        <v>350</v>
+      </c>
+      <c r="F72" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="G72" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="I72" s="42" t="n">
+        <v>600</v>
+      </c>
+      <c r="J72" s="42" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="25" t="inlineStr">
+        <is>
+          <t>Flavia Parra</t>
+        </is>
+      </c>
+      <c r="B73" s="14" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C73" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="D73" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I73" s="42" t="n">
+        <v>250</v>
+      </c>
+      <c r="J73" s="42" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="25" t="inlineStr">
+        <is>
+          <t>Flavia Parra</t>
+        </is>
+      </c>
+      <c r="B74" s="14" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C74" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="D74" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I74" s="42" t="n">
+        <v>250</v>
+      </c>
+      <c r="J74" s="42" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="25" t="inlineStr">
+        <is>
+          <t>Thalia Rojas</t>
+        </is>
+      </c>
+      <c r="B75" s="14" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C75" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="D75" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E75" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I75" s="42" t="n">
+        <v>250</v>
+      </c>
+      <c r="J75" s="42" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="25" t="inlineStr">
+        <is>
+          <t>Thalia Rojas</t>
+        </is>
+      </c>
+      <c r="B76" s="14" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="C76" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="D76" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E76" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I76" s="42" t="n">
+        <v>250</v>
+      </c>
+      <c r="J76" s="42" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="25" t="inlineStr">
+        <is>
+          <t>Thalia Rojas</t>
+        </is>
+      </c>
+      <c r="B77" s="14" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C77" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="D77" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E77" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I77" s="42" t="n">
+        <v>250</v>
+      </c>
+      <c r="J77" s="42" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="25" t="inlineStr">
+        <is>
+          <t>Monica Valdes</t>
+        </is>
+      </c>
+      <c r="B78" s="14" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C78" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="D78" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E78" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I78" s="42" t="n">
+        <v>250</v>
+      </c>
+      <c r="J78" s="42" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="25" t="inlineStr">
+        <is>
+          <t>Dialinerys Dieguez</t>
+        </is>
+      </c>
+      <c r="B79" s="14" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C79" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="D79" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="E79" s="41" t="n">
+        <v>250</v>
+      </c>
+      <c r="F79" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="34" t="n">
+        <v>450</v>
+      </c>
+      <c r="I79" s="42" t="n">
+        <v>450</v>
+      </c>
+      <c r="J79" s="42" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="80" ht="22" customHeight="1">
+      <c r="A80" s="25" t="inlineStr">
+        <is>
+          <t>Abel Guaina</t>
+        </is>
+      </c>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="C80" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="D80" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E80" s="41" t="n">
+        <v>350</v>
+      </c>
+      <c r="F80" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="G80" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I80" s="42" t="n">
+        <v>500</v>
+      </c>
+      <c r="J80" s="42" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="81" ht="22" customHeight="1">
+      <c r="A81" s="25" t="inlineStr">
+        <is>
+          <t>Melissa Hernandez</t>
+        </is>
+      </c>
+      <c r="B81" s="14" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C81" s="15" t="n">
+        <v>31</v>
+      </c>
+      <c r="D81" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="41" t="n">
+        <v>250</v>
+      </c>
+      <c r="F81" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="I81" s="42" t="n">
+        <v>350</v>
+      </c>
+      <c r="J81" s="42" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82" ht="22" customHeight="1">
+      <c r="A82" s="25" t="inlineStr">
+        <is>
+          <t>Abel Guaina</t>
+        </is>
+      </c>
+      <c r="B82" s="14" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C82" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="D82" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="E82" s="41" t="n">
+        <v>250</v>
+      </c>
+      <c r="F82" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I82" s="42" t="n">
+        <v>250</v>
+      </c>
+      <c r="J82" s="46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" ht="22" customHeight="1">
+      <c r="A83" s="25" t="inlineStr">
+        <is>
+          <t>Flavia Parra</t>
+        </is>
+      </c>
+      <c r="B83" s="14" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="C83" s="15" t="n">
+        <v>27</v>
+      </c>
+      <c r="D83" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" ht="22" customHeight="1">
+      <c r="A84" s="25" t="inlineStr">
+        <is>
+          <t>Thalia Rojas</t>
+        </is>
+      </c>
+      <c r="B84" s="14" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="C84" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="D84" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E84" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" ht="22" customHeight="1">
+      <c r="A85" s="25" t="inlineStr">
+        <is>
+          <t>Abel Guaina</t>
+        </is>
+      </c>
+      <c r="B85" s="14" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C85" s="15" t="n">
+        <v>27</v>
+      </c>
+      <c r="D85" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="E85" s="41" t="n">
+        <v>350</v>
+      </c>
+      <c r="F85" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="43" t="n">
+        <v>-350</v>
+      </c>
+    </row>
+    <row r="86" ht="28" customHeight="1">
+      <c r="A86" s="18" t="inlineStr">
+        <is>
+          <t>4-MONTH TOTAL (all 6 agents)</t>
+        </is>
+      </c>
+      <c r="B86" s="39" t="n"/>
+      <c r="C86" s="39" t="n"/>
+      <c r="D86" s="39" t="n"/>
+      <c r="E86" s="44" t="n">
+        <v>2750</v>
+      </c>
+      <c r="F86" s="39" t="n"/>
+      <c r="G86" s="39" t="n"/>
+      <c r="H86" s="39" t="n"/>
+      <c r="I86" s="45" t="n">
+        <v>7975</v>
+      </c>
+      <c r="J86" s="42" t="n">
+        <v>5225</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A60:J60"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -15241,37 +18945,37 @@
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="41" t="inlineStr">
+      <c r="A6" s="47" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="41" t="inlineStr">
+      <c r="B6" s="47" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="C6" s="41" t="inlineStr">
+      <c r="C6" s="47" t="inlineStr">
         <is>
           <t>Verify premium, collected, PIF, coverages</t>
         </is>
       </c>
-      <c r="D6" s="41" t="inlineStr">
+      <c r="D6" s="47" t="inlineStr">
         <is>
           <t>Before payroll</t>
         </is>
       </c>
-      <c r="E6" s="41" t="inlineStr">
+      <c r="E6" s="47" t="inlineStr">
         <is>
           <t>Receipts, dec page, MVR, carrier proof</t>
         </is>
       </c>
-      <c r="F6" s="41" t="inlineStr">
+      <c r="F6" s="47" t="inlineStr">
         <is>
           <t>Approved or denied</t>
         </is>
       </c>
-      <c r="G6" s="41" t="inlineStr">
+      <c r="G6" s="47" t="inlineStr">
         <is>
           <t>BI/UM proof attached</t>
         </is>
@@ -15315,37 +19019,37 @@
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="41" t="inlineStr">
+      <c r="A8" s="47" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="41" t="inlineStr">
+      <c r="B8" s="47" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="C8" s="41" t="inlineStr">
+      <c r="C8" s="47" t="inlineStr">
         <is>
           <t>Review policy 90 days after effective</t>
         </is>
       </c>
-      <c r="D8" s="41" t="inlineStr">
+      <c r="D8" s="47" t="inlineStr">
         <is>
           <t>Month 3</t>
         </is>
       </c>
-      <c r="E8" s="41" t="inlineStr">
+      <c r="E8" s="47" t="inlineStr">
         <is>
           <t>Carrier status, cancel/rewrite report</t>
         </is>
       </c>
-      <c r="F8" s="41" t="inlineStr">
+      <c r="F8" s="47" t="inlineStr">
         <is>
           <t>Keep or chargeback</t>
         </is>
       </c>
-      <c r="G8" s="41" t="inlineStr">
+      <c r="G8" s="47" t="inlineStr">
         <is>
           <t>Jan 12 reviewed Apr 12</t>
         </is>
@@ -15389,37 +19093,37 @@
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="41" t="inlineStr">
+      <c r="A10" s="47" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B10" s="41" t="inlineStr">
+      <c r="B10" s="47" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="C10" s="41" t="inlineStr">
+      <c r="C10" s="47" t="inlineStr">
         <is>
           <t>Document exception if ownership approves</t>
         </is>
       </c>
-      <c r="D10" s="41" t="inlineStr">
+      <c r="D10" s="47" t="inlineStr">
         <is>
           <t>As needed</t>
         </is>
       </c>
-      <c r="E10" s="41" t="inlineStr">
+      <c r="E10" s="47" t="inlineStr">
         <is>
           <t>Written approval</t>
         </is>
       </c>
-      <c r="F10" s="41" t="inlineStr">
+      <c r="F10" s="47" t="inlineStr">
         <is>
           <t>Exception logged</t>
         </is>
       </c>
-      <c r="G10" s="41" t="inlineStr">
+      <c r="G10" s="47" t="inlineStr">
         <is>
           <t>Carrier error fix</t>
         </is>
@@ -15469,786 +19173,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:O41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="7" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Monthly Manual Bonus Tracker - The Bonus Plan</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="22" t="inlineStr">
-        <is>
-          <t>Agents enter ONE ROW PER POLICY. Without an entry the policy does NOT get bonused. Manager verifies fields. Per-policy bonus columns auto-calculate from the formulas below.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>THE BONUS PLAN FORMULAS (for reference)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="42" t="inlineStr">
-        <is>
-          <t>NB tiered bonus</t>
-        </is>
-      </c>
-      <c r="B4" s="42" t="inlineStr">
-        <is>
-          <t>Monthly NB written premium: T1 $45k=$250 | T2 $55k=$375 | T3 $70k=$525 | T4 $85k=$725 | T5 $100k=$1,000. Above $100k: +$50 per $5k.</t>
-        </is>
-      </c>
-      <c r="C4" s="43" t="n"/>
-      <c r="D4" s="43" t="n"/>
-      <c r="E4" s="43" t="n"/>
-      <c r="F4" s="43" t="n"/>
-      <c r="G4" s="43" t="n"/>
-      <c r="H4" s="43" t="n"/>
-      <c r="I4" s="43" t="n"/>
-      <c r="J4" s="43" t="n"/>
-      <c r="K4" s="43" t="n"/>
-      <c r="L4" s="43" t="n"/>
-      <c r="M4" s="43" t="n"/>
-      <c r="N4" s="43" t="n"/>
-      <c r="O4" s="44" t="n"/>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="42" t="inlineStr">
-        <is>
-          <t>RWR tiered bonus</t>
-        </is>
-      </c>
-      <c r="B5" s="42" t="inlineStr">
-        <is>
-          <t>Same breakpoints as NB, pays ~half: T1=$100 | T2=$200 | T3=$275 | T4=$350 | T5=$500. Above $100k: +$25 per $5k.</t>
-        </is>
-      </c>
-      <c r="C5" s="43" t="n"/>
-      <c r="D5" s="43" t="n"/>
-      <c r="E5" s="43" t="n"/>
-      <c r="F5" s="43" t="n"/>
-      <c r="G5" s="43" t="n"/>
-      <c r="H5" s="43" t="n"/>
-      <c r="I5" s="43" t="n"/>
-      <c r="J5" s="43" t="n"/>
-      <c r="K5" s="43" t="n"/>
-      <c r="L5" s="43" t="n"/>
-      <c r="M5" s="43" t="n"/>
-      <c r="N5" s="43" t="n"/>
-      <c r="O5" s="44" t="n"/>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="42" t="inlineStr">
-        <is>
-          <t>REN tiered bonus</t>
-        </is>
-      </c>
-      <c r="B6" s="42" t="inlineStr">
-        <is>
-          <t>Own breakpoints: T1 $25k=$250 | T2 $40k=$350 | T3 $65k=$450 | T4 $80k=$550 | T5 $100k=$800. Above $100k: +$40 per $5k.</t>
-        </is>
-      </c>
-      <c r="C6" s="43" t="n"/>
-      <c r="D6" s="43" t="n"/>
-      <c r="E6" s="43" t="n"/>
-      <c r="F6" s="43" t="n"/>
-      <c r="G6" s="43" t="n"/>
-      <c r="H6" s="43" t="n"/>
-      <c r="I6" s="43" t="n"/>
-      <c r="J6" s="43" t="n"/>
-      <c r="K6" s="43" t="n"/>
-      <c r="L6" s="43" t="n"/>
-      <c r="M6" s="43" t="n"/>
-      <c r="N6" s="43" t="n"/>
-      <c r="O6" s="44" t="n"/>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="42" t="inlineStr">
-        <is>
-          <t>Minimums (monthly)</t>
-        </is>
-      </c>
-      <c r="B7" s="42" t="inlineStr">
-        <is>
-          <t>NB written premium &gt;= $45,000 | REN retention rate &gt;= 30% of book | RWR follows NB gate (no separate RWR floor)</t>
-        </is>
-      </c>
-      <c r="C7" s="43" t="n"/>
-      <c r="D7" s="43" t="n"/>
-      <c r="E7" s="43" t="n"/>
-      <c r="F7" s="43" t="n"/>
-      <c r="G7" s="43" t="n"/>
-      <c r="H7" s="43" t="n"/>
-      <c r="I7" s="43" t="n"/>
-      <c r="J7" s="43" t="n"/>
-      <c r="K7" s="43" t="n"/>
-      <c r="L7" s="43" t="n"/>
-      <c r="M7" s="43" t="n"/>
-      <c r="N7" s="43" t="n"/>
-      <c r="O7" s="44" t="n"/>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="42" t="inlineStr">
-        <is>
-          <t>Chargeback</t>
-        </is>
-      </c>
-      <c r="B8" s="42" t="inlineStr">
-        <is>
-          <t>3 months (90 days) - bonus reversed if policy cancels/rewrites within 90 days</t>
-        </is>
-      </c>
-      <c r="C8" s="43" t="n"/>
-      <c r="D8" s="43" t="n"/>
-      <c r="E8" s="43" t="n"/>
-      <c r="F8" s="43" t="n"/>
-      <c r="G8" s="43" t="n"/>
-      <c r="H8" s="43" t="n"/>
-      <c r="I8" s="43" t="n"/>
-      <c r="J8" s="43" t="n"/>
-      <c r="K8" s="43" t="n"/>
-      <c r="L8" s="43" t="n"/>
-      <c r="M8" s="43" t="n"/>
-      <c r="N8" s="43" t="n"/>
-      <c r="O8" s="44" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>ONE ROW PER POLICY</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Agent</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Customer</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Policy #</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Carrier</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>Type (NB/RWR/REN)</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Eff Date</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Exp Date</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>90-Day Review Date</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>Written Premium</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>Down Payment $</t>
-        </is>
-      </c>
-      <c r="K11" s="6" t="inlineStr">
-        <is>
-          <t>Collected % (calc)</t>
-        </is>
-      </c>
-      <c r="L11" s="6" t="inlineStr">
-        <is>
-          <t>PIF?</t>
-        </is>
-      </c>
-      <c r="M11" s="6" t="inlineStr">
-        <is>
-          <t>Per-Policy Base $</t>
-        </is>
-      </c>
-      <c r="N11" s="6" t="inlineStr">
-        <is>
-          <t>Collected Incentive $</t>
-        </is>
-      </c>
-      <c r="O11" s="6" t="inlineStr">
-        <is>
-          <t>Total Bonus $</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr"/>
-      <c r="B12" s="14" t="inlineStr"/>
-      <c r="C12" s="14" t="inlineStr"/>
-      <c r="D12" s="14" t="inlineStr"/>
-      <c r="E12" s="14" t="inlineStr"/>
-      <c r="F12" s="14" t="inlineStr"/>
-      <c r="G12" s="14" t="inlineStr"/>
-      <c r="H12" s="14" t="inlineStr"/>
-      <c r="I12" s="14" t="inlineStr"/>
-      <c r="J12" s="14" t="inlineStr"/>
-      <c r="K12" s="14" t="inlineStr"/>
-      <c r="L12" s="14" t="inlineStr"/>
-      <c r="M12" s="14" t="inlineStr"/>
-      <c r="N12" s="14" t="inlineStr"/>
-      <c r="O12" s="14" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr"/>
-      <c r="B13" s="14" t="inlineStr"/>
-      <c r="C13" s="14" t="inlineStr"/>
-      <c r="D13" s="14" t="inlineStr"/>
-      <c r="E13" s="14" t="inlineStr"/>
-      <c r="F13" s="14" t="inlineStr"/>
-      <c r="G13" s="14" t="inlineStr"/>
-      <c r="H13" s="14" t="inlineStr"/>
-      <c r="I13" s="14" t="inlineStr"/>
-      <c r="J13" s="14" t="inlineStr"/>
-      <c r="K13" s="14" t="inlineStr"/>
-      <c r="L13" s="14" t="inlineStr"/>
-      <c r="M13" s="14" t="inlineStr"/>
-      <c r="N13" s="14" t="inlineStr"/>
-      <c r="O13" s="14" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr"/>
-      <c r="B14" s="14" t="inlineStr"/>
-      <c r="C14" s="14" t="inlineStr"/>
-      <c r="D14" s="14" t="inlineStr"/>
-      <c r="E14" s="14" t="inlineStr"/>
-      <c r="F14" s="14" t="inlineStr"/>
-      <c r="G14" s="14" t="inlineStr"/>
-      <c r="H14" s="14" t="inlineStr"/>
-      <c r="I14" s="14" t="inlineStr"/>
-      <c r="J14" s="14" t="inlineStr"/>
-      <c r="K14" s="14" t="inlineStr"/>
-      <c r="L14" s="14" t="inlineStr"/>
-      <c r="M14" s="14" t="inlineStr"/>
-      <c r="N14" s="14" t="inlineStr"/>
-      <c r="O14" s="14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr"/>
-      <c r="B15" s="14" t="inlineStr"/>
-      <c r="C15" s="14" t="inlineStr"/>
-      <c r="D15" s="14" t="inlineStr"/>
-      <c r="E15" s="14" t="inlineStr"/>
-      <c r="F15" s="14" t="inlineStr"/>
-      <c r="G15" s="14" t="inlineStr"/>
-      <c r="H15" s="14" t="inlineStr"/>
-      <c r="I15" s="14" t="inlineStr"/>
-      <c r="J15" s="14" t="inlineStr"/>
-      <c r="K15" s="14" t="inlineStr"/>
-      <c r="L15" s="14" t="inlineStr"/>
-      <c r="M15" s="14" t="inlineStr"/>
-      <c r="N15" s="14" t="inlineStr"/>
-      <c r="O15" s="14" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="inlineStr"/>
-      <c r="B16" s="14" t="inlineStr"/>
-      <c r="C16" s="14" t="inlineStr"/>
-      <c r="D16" s="14" t="inlineStr"/>
-      <c r="E16" s="14" t="inlineStr"/>
-      <c r="F16" s="14" t="inlineStr"/>
-      <c r="G16" s="14" t="inlineStr"/>
-      <c r="H16" s="14" t="inlineStr"/>
-      <c r="I16" s="14" t="inlineStr"/>
-      <c r="J16" s="14" t="inlineStr"/>
-      <c r="K16" s="14" t="inlineStr"/>
-      <c r="L16" s="14" t="inlineStr"/>
-      <c r="M16" s="14" t="inlineStr"/>
-      <c r="N16" s="14" t="inlineStr"/>
-      <c r="O16" s="14" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr"/>
-      <c r="B17" s="14" t="inlineStr"/>
-      <c r="C17" s="14" t="inlineStr"/>
-      <c r="D17" s="14" t="inlineStr"/>
-      <c r="E17" s="14" t="inlineStr"/>
-      <c r="F17" s="14" t="inlineStr"/>
-      <c r="G17" s="14" t="inlineStr"/>
-      <c r="H17" s="14" t="inlineStr"/>
-      <c r="I17" s="14" t="inlineStr"/>
-      <c r="J17" s="14" t="inlineStr"/>
-      <c r="K17" s="14" t="inlineStr"/>
-      <c r="L17" s="14" t="inlineStr"/>
-      <c r="M17" s="14" t="inlineStr"/>
-      <c r="N17" s="14" t="inlineStr"/>
-      <c r="O17" s="14" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr"/>
-      <c r="B18" s="14" t="inlineStr"/>
-      <c r="C18" s="14" t="inlineStr"/>
-      <c r="D18" s="14" t="inlineStr"/>
-      <c r="E18" s="14" t="inlineStr"/>
-      <c r="F18" s="14" t="inlineStr"/>
-      <c r="G18" s="14" t="inlineStr"/>
-      <c r="H18" s="14" t="inlineStr"/>
-      <c r="I18" s="14" t="inlineStr"/>
-      <c r="J18" s="14" t="inlineStr"/>
-      <c r="K18" s="14" t="inlineStr"/>
-      <c r="L18" s="14" t="inlineStr"/>
-      <c r="M18" s="14" t="inlineStr"/>
-      <c r="N18" s="14" t="inlineStr"/>
-      <c r="O18" s="14" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr"/>
-      <c r="B19" s="14" t="inlineStr"/>
-      <c r="C19" s="14" t="inlineStr"/>
-      <c r="D19" s="14" t="inlineStr"/>
-      <c r="E19" s="14" t="inlineStr"/>
-      <c r="F19" s="14" t="inlineStr"/>
-      <c r="G19" s="14" t="inlineStr"/>
-      <c r="H19" s="14" t="inlineStr"/>
-      <c r="I19" s="14" t="inlineStr"/>
-      <c r="J19" s="14" t="inlineStr"/>
-      <c r="K19" s="14" t="inlineStr"/>
-      <c r="L19" s="14" t="inlineStr"/>
-      <c r="M19" s="14" t="inlineStr"/>
-      <c r="N19" s="14" t="inlineStr"/>
-      <c r="O19" s="14" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr"/>
-      <c r="B20" s="14" t="inlineStr"/>
-      <c r="C20" s="14" t="inlineStr"/>
-      <c r="D20" s="14" t="inlineStr"/>
-      <c r="E20" s="14" t="inlineStr"/>
-      <c r="F20" s="14" t="inlineStr"/>
-      <c r="G20" s="14" t="inlineStr"/>
-      <c r="H20" s="14" t="inlineStr"/>
-      <c r="I20" s="14" t="inlineStr"/>
-      <c r="J20" s="14" t="inlineStr"/>
-      <c r="K20" s="14" t="inlineStr"/>
-      <c r="L20" s="14" t="inlineStr"/>
-      <c r="M20" s="14" t="inlineStr"/>
-      <c r="N20" s="14" t="inlineStr"/>
-      <c r="O20" s="14" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr"/>
-      <c r="B21" s="14" t="inlineStr"/>
-      <c r="C21" s="14" t="inlineStr"/>
-      <c r="D21" s="14" t="inlineStr"/>
-      <c r="E21" s="14" t="inlineStr"/>
-      <c r="F21" s="14" t="inlineStr"/>
-      <c r="G21" s="14" t="inlineStr"/>
-      <c r="H21" s="14" t="inlineStr"/>
-      <c r="I21" s="14" t="inlineStr"/>
-      <c r="J21" s="14" t="inlineStr"/>
-      <c r="K21" s="14" t="inlineStr"/>
-      <c r="L21" s="14" t="inlineStr"/>
-      <c r="M21" s="14" t="inlineStr"/>
-      <c r="N21" s="14" t="inlineStr"/>
-      <c r="O21" s="14" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr"/>
-      <c r="B22" s="14" t="inlineStr"/>
-      <c r="C22" s="14" t="inlineStr"/>
-      <c r="D22" s="14" t="inlineStr"/>
-      <c r="E22" s="14" t="inlineStr"/>
-      <c r="F22" s="14" t="inlineStr"/>
-      <c r="G22" s="14" t="inlineStr"/>
-      <c r="H22" s="14" t="inlineStr"/>
-      <c r="I22" s="14" t="inlineStr"/>
-      <c r="J22" s="14" t="inlineStr"/>
-      <c r="K22" s="14" t="inlineStr"/>
-      <c r="L22" s="14" t="inlineStr"/>
-      <c r="M22" s="14" t="inlineStr"/>
-      <c r="N22" s="14" t="inlineStr"/>
-      <c r="O22" s="14" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr"/>
-      <c r="B23" s="14" t="inlineStr"/>
-      <c r="C23" s="14" t="inlineStr"/>
-      <c r="D23" s="14" t="inlineStr"/>
-      <c r="E23" s="14" t="inlineStr"/>
-      <c r="F23" s="14" t="inlineStr"/>
-      <c r="G23" s="14" t="inlineStr"/>
-      <c r="H23" s="14" t="inlineStr"/>
-      <c r="I23" s="14" t="inlineStr"/>
-      <c r="J23" s="14" t="inlineStr"/>
-      <c r="K23" s="14" t="inlineStr"/>
-      <c r="L23" s="14" t="inlineStr"/>
-      <c r="M23" s="14" t="inlineStr"/>
-      <c r="N23" s="14" t="inlineStr"/>
-      <c r="O23" s="14" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr"/>
-      <c r="B24" s="14" t="inlineStr"/>
-      <c r="C24" s="14" t="inlineStr"/>
-      <c r="D24" s="14" t="inlineStr"/>
-      <c r="E24" s="14" t="inlineStr"/>
-      <c r="F24" s="14" t="inlineStr"/>
-      <c r="G24" s="14" t="inlineStr"/>
-      <c r="H24" s="14" t="inlineStr"/>
-      <c r="I24" s="14" t="inlineStr"/>
-      <c r="J24" s="14" t="inlineStr"/>
-      <c r="K24" s="14" t="inlineStr"/>
-      <c r="L24" s="14" t="inlineStr"/>
-      <c r="M24" s="14" t="inlineStr"/>
-      <c r="N24" s="14" t="inlineStr"/>
-      <c r="O24" s="14" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="inlineStr"/>
-      <c r="B25" s="14" t="inlineStr"/>
-      <c r="C25" s="14" t="inlineStr"/>
-      <c r="D25" s="14" t="inlineStr"/>
-      <c r="E25" s="14" t="inlineStr"/>
-      <c r="F25" s="14" t="inlineStr"/>
-      <c r="G25" s="14" t="inlineStr"/>
-      <c r="H25" s="14" t="inlineStr"/>
-      <c r="I25" s="14" t="inlineStr"/>
-      <c r="J25" s="14" t="inlineStr"/>
-      <c r="K25" s="14" t="inlineStr"/>
-      <c r="L25" s="14" t="inlineStr"/>
-      <c r="M25" s="14" t="inlineStr"/>
-      <c r="N25" s="14" t="inlineStr"/>
-      <c r="O25" s="14" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr"/>
-      <c r="B26" s="14" t="inlineStr"/>
-      <c r="C26" s="14" t="inlineStr"/>
-      <c r="D26" s="14" t="inlineStr"/>
-      <c r="E26" s="14" t="inlineStr"/>
-      <c r="F26" s="14" t="inlineStr"/>
-      <c r="G26" s="14" t="inlineStr"/>
-      <c r="H26" s="14" t="inlineStr"/>
-      <c r="I26" s="14" t="inlineStr"/>
-      <c r="J26" s="14" t="inlineStr"/>
-      <c r="K26" s="14" t="inlineStr"/>
-      <c r="L26" s="14" t="inlineStr"/>
-      <c r="M26" s="14" t="inlineStr"/>
-      <c r="N26" s="14" t="inlineStr"/>
-      <c r="O26" s="14" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="14" t="inlineStr"/>
-      <c r="B27" s="14" t="inlineStr"/>
-      <c r="C27" s="14" t="inlineStr"/>
-      <c r="D27" s="14" t="inlineStr"/>
-      <c r="E27" s="14" t="inlineStr"/>
-      <c r="F27" s="14" t="inlineStr"/>
-      <c r="G27" s="14" t="inlineStr"/>
-      <c r="H27" s="14" t="inlineStr"/>
-      <c r="I27" s="14" t="inlineStr"/>
-      <c r="J27" s="14" t="inlineStr"/>
-      <c r="K27" s="14" t="inlineStr"/>
-      <c r="L27" s="14" t="inlineStr"/>
-      <c r="M27" s="14" t="inlineStr"/>
-      <c r="N27" s="14" t="inlineStr"/>
-      <c r="O27" s="14" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="14" t="inlineStr"/>
-      <c r="B28" s="14" t="inlineStr"/>
-      <c r="C28" s="14" t="inlineStr"/>
-      <c r="D28" s="14" t="inlineStr"/>
-      <c r="E28" s="14" t="inlineStr"/>
-      <c r="F28" s="14" t="inlineStr"/>
-      <c r="G28" s="14" t="inlineStr"/>
-      <c r="H28" s="14" t="inlineStr"/>
-      <c r="I28" s="14" t="inlineStr"/>
-      <c r="J28" s="14" t="inlineStr"/>
-      <c r="K28" s="14" t="inlineStr"/>
-      <c r="L28" s="14" t="inlineStr"/>
-      <c r="M28" s="14" t="inlineStr"/>
-      <c r="N28" s="14" t="inlineStr"/>
-      <c r="O28" s="14" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="14" t="inlineStr"/>
-      <c r="B29" s="14" t="inlineStr"/>
-      <c r="C29" s="14" t="inlineStr"/>
-      <c r="D29" s="14" t="inlineStr"/>
-      <c r="E29" s="14" t="inlineStr"/>
-      <c r="F29" s="14" t="inlineStr"/>
-      <c r="G29" s="14" t="inlineStr"/>
-      <c r="H29" s="14" t="inlineStr"/>
-      <c r="I29" s="14" t="inlineStr"/>
-      <c r="J29" s="14" t="inlineStr"/>
-      <c r="K29" s="14" t="inlineStr"/>
-      <c r="L29" s="14" t="inlineStr"/>
-      <c r="M29" s="14" t="inlineStr"/>
-      <c r="N29" s="14" t="inlineStr"/>
-      <c r="O29" s="14" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="14" t="inlineStr"/>
-      <c r="B30" s="14" t="inlineStr"/>
-      <c r="C30" s="14" t="inlineStr"/>
-      <c r="D30" s="14" t="inlineStr"/>
-      <c r="E30" s="14" t="inlineStr"/>
-      <c r="F30" s="14" t="inlineStr"/>
-      <c r="G30" s="14" t="inlineStr"/>
-      <c r="H30" s="14" t="inlineStr"/>
-      <c r="I30" s="14" t="inlineStr"/>
-      <c r="J30" s="14" t="inlineStr"/>
-      <c r="K30" s="14" t="inlineStr"/>
-      <c r="L30" s="14" t="inlineStr"/>
-      <c r="M30" s="14" t="inlineStr"/>
-      <c r="N30" s="14" t="inlineStr"/>
-      <c r="O30" s="14" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="14" t="inlineStr"/>
-      <c r="B31" s="14" t="inlineStr"/>
-      <c r="C31" s="14" t="inlineStr"/>
-      <c r="D31" s="14" t="inlineStr"/>
-      <c r="E31" s="14" t="inlineStr"/>
-      <c r="F31" s="14" t="inlineStr"/>
-      <c r="G31" s="14" t="inlineStr"/>
-      <c r="H31" s="14" t="inlineStr"/>
-      <c r="I31" s="14" t="inlineStr"/>
-      <c r="J31" s="14" t="inlineStr"/>
-      <c r="K31" s="14" t="inlineStr"/>
-      <c r="L31" s="14" t="inlineStr"/>
-      <c r="M31" s="14" t="inlineStr"/>
-      <c r="N31" s="14" t="inlineStr"/>
-      <c r="O31" s="14" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="14" t="inlineStr"/>
-      <c r="B32" s="14" t="inlineStr"/>
-      <c r="C32" s="14" t="inlineStr"/>
-      <c r="D32" s="14" t="inlineStr"/>
-      <c r="E32" s="14" t="inlineStr"/>
-      <c r="F32" s="14" t="inlineStr"/>
-      <c r="G32" s="14" t="inlineStr"/>
-      <c r="H32" s="14" t="inlineStr"/>
-      <c r="I32" s="14" t="inlineStr"/>
-      <c r="J32" s="14" t="inlineStr"/>
-      <c r="K32" s="14" t="inlineStr"/>
-      <c r="L32" s="14" t="inlineStr"/>
-      <c r="M32" s="14" t="inlineStr"/>
-      <c r="N32" s="14" t="inlineStr"/>
-      <c r="O32" s="14" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="14" t="inlineStr"/>
-      <c r="B33" s="14" t="inlineStr"/>
-      <c r="C33" s="14" t="inlineStr"/>
-      <c r="D33" s="14" t="inlineStr"/>
-      <c r="E33" s="14" t="inlineStr"/>
-      <c r="F33" s="14" t="inlineStr"/>
-      <c r="G33" s="14" t="inlineStr"/>
-      <c r="H33" s="14" t="inlineStr"/>
-      <c r="I33" s="14" t="inlineStr"/>
-      <c r="J33" s="14" t="inlineStr"/>
-      <c r="K33" s="14" t="inlineStr"/>
-      <c r="L33" s="14" t="inlineStr"/>
-      <c r="M33" s="14" t="inlineStr"/>
-      <c r="N33" s="14" t="inlineStr"/>
-      <c r="O33" s="14" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="14" t="inlineStr"/>
-      <c r="B34" s="14" t="inlineStr"/>
-      <c r="C34" s="14" t="inlineStr"/>
-      <c r="D34" s="14" t="inlineStr"/>
-      <c r="E34" s="14" t="inlineStr"/>
-      <c r="F34" s="14" t="inlineStr"/>
-      <c r="G34" s="14" t="inlineStr"/>
-      <c r="H34" s="14" t="inlineStr"/>
-      <c r="I34" s="14" t="inlineStr"/>
-      <c r="J34" s="14" t="inlineStr"/>
-      <c r="K34" s="14" t="inlineStr"/>
-      <c r="L34" s="14" t="inlineStr"/>
-      <c r="M34" s="14" t="inlineStr"/>
-      <c r="N34" s="14" t="inlineStr"/>
-      <c r="O34" s="14" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="14" t="inlineStr"/>
-      <c r="B35" s="14" t="inlineStr"/>
-      <c r="C35" s="14" t="inlineStr"/>
-      <c r="D35" s="14" t="inlineStr"/>
-      <c r="E35" s="14" t="inlineStr"/>
-      <c r="F35" s="14" t="inlineStr"/>
-      <c r="G35" s="14" t="inlineStr"/>
-      <c r="H35" s="14" t="inlineStr"/>
-      <c r="I35" s="14" t="inlineStr"/>
-      <c r="J35" s="14" t="inlineStr"/>
-      <c r="K35" s="14" t="inlineStr"/>
-      <c r="L35" s="14" t="inlineStr"/>
-      <c r="M35" s="14" t="inlineStr"/>
-      <c r="N35" s="14" t="inlineStr"/>
-      <c r="O35" s="14" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="14" t="inlineStr"/>
-      <c r="B36" s="14" t="inlineStr"/>
-      <c r="C36" s="14" t="inlineStr"/>
-      <c r="D36" s="14" t="inlineStr"/>
-      <c r="E36" s="14" t="inlineStr"/>
-      <c r="F36" s="14" t="inlineStr"/>
-      <c r="G36" s="14" t="inlineStr"/>
-      <c r="H36" s="14" t="inlineStr"/>
-      <c r="I36" s="14" t="inlineStr"/>
-      <c r="J36" s="14" t="inlineStr"/>
-      <c r="K36" s="14" t="inlineStr"/>
-      <c r="L36" s="14" t="inlineStr"/>
-      <c r="M36" s="14" t="inlineStr"/>
-      <c r="N36" s="14" t="inlineStr"/>
-      <c r="O36" s="14" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="14" t="inlineStr"/>
-      <c r="B37" s="14" t="inlineStr"/>
-      <c r="C37" s="14" t="inlineStr"/>
-      <c r="D37" s="14" t="inlineStr"/>
-      <c r="E37" s="14" t="inlineStr"/>
-      <c r="F37" s="14" t="inlineStr"/>
-      <c r="G37" s="14" t="inlineStr"/>
-      <c r="H37" s="14" t="inlineStr"/>
-      <c r="I37" s="14" t="inlineStr"/>
-      <c r="J37" s="14" t="inlineStr"/>
-      <c r="K37" s="14" t="inlineStr"/>
-      <c r="L37" s="14" t="inlineStr"/>
-      <c r="M37" s="14" t="inlineStr"/>
-      <c r="N37" s="14" t="inlineStr"/>
-      <c r="O37" s="14" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="14" t="inlineStr"/>
-      <c r="B38" s="14" t="inlineStr"/>
-      <c r="C38" s="14" t="inlineStr"/>
-      <c r="D38" s="14" t="inlineStr"/>
-      <c r="E38" s="14" t="inlineStr"/>
-      <c r="F38" s="14" t="inlineStr"/>
-      <c r="G38" s="14" t="inlineStr"/>
-      <c r="H38" s="14" t="inlineStr"/>
-      <c r="I38" s="14" t="inlineStr"/>
-      <c r="J38" s="14" t="inlineStr"/>
-      <c r="K38" s="14" t="inlineStr"/>
-      <c r="L38" s="14" t="inlineStr"/>
-      <c r="M38" s="14" t="inlineStr"/>
-      <c r="N38" s="14" t="inlineStr"/>
-      <c r="O38" s="14" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="14" t="inlineStr"/>
-      <c r="B39" s="14" t="inlineStr"/>
-      <c r="C39" s="14" t="inlineStr"/>
-      <c r="D39" s="14" t="inlineStr"/>
-      <c r="E39" s="14" t="inlineStr"/>
-      <c r="F39" s="14" t="inlineStr"/>
-      <c r="G39" s="14" t="inlineStr"/>
-      <c r="H39" s="14" t="inlineStr"/>
-      <c r="I39" s="14" t="inlineStr"/>
-      <c r="J39" s="14" t="inlineStr"/>
-      <c r="K39" s="14" t="inlineStr"/>
-      <c r="L39" s="14" t="inlineStr"/>
-      <c r="M39" s="14" t="inlineStr"/>
-      <c r="N39" s="14" t="inlineStr"/>
-      <c r="O39" s="14" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="14" t="inlineStr"/>
-      <c r="B40" s="14" t="inlineStr"/>
-      <c r="C40" s="14" t="inlineStr"/>
-      <c r="D40" s="14" t="inlineStr"/>
-      <c r="E40" s="14" t="inlineStr"/>
-      <c r="F40" s="14" t="inlineStr"/>
-      <c r="G40" s="14" t="inlineStr"/>
-      <c r="H40" s="14" t="inlineStr"/>
-      <c r="I40" s="14" t="inlineStr"/>
-      <c r="J40" s="14" t="inlineStr"/>
-      <c r="K40" s="14" t="inlineStr"/>
-      <c r="L40" s="14" t="inlineStr"/>
-      <c r="M40" s="14" t="inlineStr"/>
-      <c r="N40" s="14" t="inlineStr"/>
-      <c r="O40" s="14" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="14" t="inlineStr"/>
-      <c r="B41" s="14" t="inlineStr"/>
-      <c r="C41" s="14" t="inlineStr"/>
-      <c r="D41" s="14" t="inlineStr"/>
-      <c r="E41" s="14" t="inlineStr"/>
-      <c r="F41" s="14" t="inlineStr"/>
-      <c r="G41" s="14" t="inlineStr"/>
-      <c r="H41" s="14" t="inlineStr"/>
-      <c r="I41" s="14" t="inlineStr"/>
-      <c r="J41" s="14" t="inlineStr"/>
-      <c r="K41" s="14" t="inlineStr"/>
-      <c r="L41" s="14" t="inlineStr"/>
-      <c r="M41" s="14" t="inlineStr"/>
-      <c r="N41" s="14" t="inlineStr"/>
-      <c r="O41" s="14" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="B8:O8"/>
-    <mergeCell ref="B4:O4"/>
-    <mergeCell ref="A2:O2"/>
-    <mergeCell ref="A10:O10"/>
-    <mergeCell ref="B6:O6"/>
-    <mergeCell ref="B7:O7"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="B5:O5"/>
-    <mergeCell ref="A3:O3"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/output/Bonus_Plan_SIMPLE.xlsx
+++ b/output/Bonus_Plan_SIMPLE.xlsx
@@ -30,7 +30,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -95,9 +95,6 @@
       <b val="1"/>
       <color rgb="009C0006"/>
       <sz val="12"/>
-    </font>
-    <font>
-      <color rgb="009C9C9C"/>
     </font>
     <font>
       <b val="1"/>
@@ -259,7 +256,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -343,30 +340,24 @@
     <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="16" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="16" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -378,13 +369,13 @@
     <xf numFmtId="164" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="17" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -826,7 +817,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>TODAY: $12,220. NEW PLAN: $1,675 if behavior stays the same, $8,375 with 50% renewal shift, $18,475 if all rewrites had been renewals. New plan pays LESS for the wrong behavior and significantly MORE for the right behavior - including the retention kicker that rewards agents who actually retain the book.</t>
+          <t>TODAY: $12,220. NEW PLAN: $1,675 if behavior stays the same, $3,875 with 50% renewal shift, $7,975 if all rewrites had been renewals. New plan costs LESS while paying for the right behavior.</t>
         </is>
       </c>
     </row>
@@ -885,7 +876,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>T1 $25k=$250 | T2 $40k=$350 | T3 $65k=$450 | T4 $80k=$550 | T5 $100k=$800. Above $100k: +$40 per $5k. PLUS retention kicker: 50-74% retained = +$250, 75-99% = +$500, 100% = +$1,000.</t>
+          <t>T1 $25k=$250 | T2 $40k=$350 | T3 $65k=$450 | T4 $80k=$550 | T5 $100k=$800. Above $100k: +$40 per $5k. Gate: 30% retention rate.</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1207,238 +1198,230 @@
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="50" t="inlineStr">
+      <c r="A4" s="48" t="inlineStr">
         <is>
           <t>NB tiered bonus</t>
         </is>
       </c>
-      <c r="B4" s="50" t="inlineStr">
+      <c r="B4" s="48" t="inlineStr">
         <is>
           <t>Monthly NB written premium: T1 $45k=$250 | T2 $55k=$375 | T3 $70k=$525 | T4 $85k=$725 | T5 $100k=$1,000. Above $100k: +$50 per $5k.</t>
         </is>
       </c>
-      <c r="C4" s="51" t="n"/>
-      <c r="D4" s="51" t="n"/>
-      <c r="E4" s="51" t="n"/>
-      <c r="F4" s="51" t="n"/>
-      <c r="G4" s="51" t="n"/>
-      <c r="H4" s="51" t="n"/>
-      <c r="I4" s="51" t="n"/>
-      <c r="J4" s="51" t="n"/>
-      <c r="K4" s="51" t="n"/>
-      <c r="L4" s="51" t="n"/>
-      <c r="M4" s="51" t="n"/>
-      <c r="N4" s="51" t="n"/>
-      <c r="O4" s="52" t="n"/>
+      <c r="C4" s="49" t="n"/>
+      <c r="D4" s="49" t="n"/>
+      <c r="E4" s="49" t="n"/>
+      <c r="F4" s="49" t="n"/>
+      <c r="G4" s="49" t="n"/>
+      <c r="H4" s="49" t="n"/>
+      <c r="I4" s="49" t="n"/>
+      <c r="J4" s="49" t="n"/>
+      <c r="K4" s="49" t="n"/>
+      <c r="L4" s="49" t="n"/>
+      <c r="M4" s="49" t="n"/>
+      <c r="N4" s="49" t="n"/>
+      <c r="O4" s="50" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="50" t="inlineStr">
+      <c r="A5" s="48" t="inlineStr">
         <is>
           <t>RWR tiered bonus</t>
         </is>
       </c>
-      <c r="B5" s="50" t="inlineStr">
+      <c r="B5" s="48" t="inlineStr">
         <is>
           <t>Same breakpoints as NB, pays ~half: T1=$100 | T2=$200 | T3=$275 | T4=$350 | T5=$500. Above $100k: +$25 per $5k.</t>
         </is>
       </c>
-      <c r="C5" s="51" t="n"/>
-      <c r="D5" s="51" t="n"/>
-      <c r="E5" s="51" t="n"/>
-      <c r="F5" s="51" t="n"/>
-      <c r="G5" s="51" t="n"/>
-      <c r="H5" s="51" t="n"/>
-      <c r="I5" s="51" t="n"/>
-      <c r="J5" s="51" t="n"/>
-      <c r="K5" s="51" t="n"/>
-      <c r="L5" s="51" t="n"/>
-      <c r="M5" s="51" t="n"/>
-      <c r="N5" s="51" t="n"/>
-      <c r="O5" s="52" t="n"/>
+      <c r="C5" s="49" t="n"/>
+      <c r="D5" s="49" t="n"/>
+      <c r="E5" s="49" t="n"/>
+      <c r="F5" s="49" t="n"/>
+      <c r="G5" s="49" t="n"/>
+      <c r="H5" s="49" t="n"/>
+      <c r="I5" s="49" t="n"/>
+      <c r="J5" s="49" t="n"/>
+      <c r="K5" s="49" t="n"/>
+      <c r="L5" s="49" t="n"/>
+      <c r="M5" s="49" t="n"/>
+      <c r="N5" s="49" t="n"/>
+      <c r="O5" s="50" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="50" t="inlineStr">
+      <c r="A6" s="48" t="inlineStr">
         <is>
           <t>REN tiered bonus</t>
         </is>
       </c>
-      <c r="B6" s="50" t="inlineStr">
+      <c r="B6" s="48" t="inlineStr">
         <is>
           <t>Own breakpoints: T1 $25k=$250 | T2 $40k=$350 | T3 $65k=$450 | T4 $80k=$550 | T5 $100k=$800. Above $100k: +$40 per $5k.</t>
         </is>
       </c>
-      <c r="C6" s="51" t="n"/>
-      <c r="D6" s="51" t="n"/>
-      <c r="E6" s="51" t="n"/>
-      <c r="F6" s="51" t="n"/>
-      <c r="G6" s="51" t="n"/>
-      <c r="H6" s="51" t="n"/>
-      <c r="I6" s="51" t="n"/>
-      <c r="J6" s="51" t="n"/>
-      <c r="K6" s="51" t="n"/>
-      <c r="L6" s="51" t="n"/>
-      <c r="M6" s="51" t="n"/>
-      <c r="N6" s="51" t="n"/>
-      <c r="O6" s="52" t="n"/>
+      <c r="C6" s="49" t="n"/>
+      <c r="D6" s="49" t="n"/>
+      <c r="E6" s="49" t="n"/>
+      <c r="F6" s="49" t="n"/>
+      <c r="G6" s="49" t="n"/>
+      <c r="H6" s="49" t="n"/>
+      <c r="I6" s="49" t="n"/>
+      <c r="J6" s="49" t="n"/>
+      <c r="K6" s="49" t="n"/>
+      <c r="L6" s="49" t="n"/>
+      <c r="M6" s="49" t="n"/>
+      <c r="N6" s="49" t="n"/>
+      <c r="O6" s="50" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="50" t="inlineStr">
-        <is>
-          <t>REN retention kicker</t>
-        </is>
-      </c>
-      <c r="B7" s="50" t="inlineStr">
-        <is>
-          <t>On top of REN tier bonus. 30-49% = $0 | 50-74% = +$250 | 75-99% = +$500 | 100% = +$1,000.</t>
-        </is>
-      </c>
-      <c r="C7" s="51" t="n"/>
-      <c r="D7" s="51" t="n"/>
-      <c r="E7" s="51" t="n"/>
-      <c r="F7" s="51" t="n"/>
-      <c r="G7" s="51" t="n"/>
-      <c r="H7" s="51" t="n"/>
-      <c r="I7" s="51" t="n"/>
-      <c r="J7" s="51" t="n"/>
-      <c r="K7" s="51" t="n"/>
-      <c r="L7" s="51" t="n"/>
-      <c r="M7" s="51" t="n"/>
-      <c r="N7" s="51" t="n"/>
-      <c r="O7" s="52" t="n"/>
+      <c r="A7" s="48" t="inlineStr">
+        <is>
+          <t>Minimums (monthly)</t>
+        </is>
+      </c>
+      <c r="B7" s="48" t="inlineStr">
+        <is>
+          <t>NB written premium &gt;= $45,000 | REN retention rate &gt;= 30% of book | RWR follows NB gate (no separate RWR floor)</t>
+        </is>
+      </c>
+      <c r="C7" s="49" t="n"/>
+      <c r="D7" s="49" t="n"/>
+      <c r="E7" s="49" t="n"/>
+      <c r="F7" s="49" t="n"/>
+      <c r="G7" s="49" t="n"/>
+      <c r="H7" s="49" t="n"/>
+      <c r="I7" s="49" t="n"/>
+      <c r="J7" s="49" t="n"/>
+      <c r="K7" s="49" t="n"/>
+      <c r="L7" s="49" t="n"/>
+      <c r="M7" s="49" t="n"/>
+      <c r="N7" s="49" t="n"/>
+      <c r="O7" s="50" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="50" t="inlineStr">
-        <is>
-          <t>Minimums (monthly)</t>
-        </is>
-      </c>
-      <c r="B8" s="50" t="inlineStr">
-        <is>
-          <t>NB written premium &gt;= $45,000 | REN retention rate &gt;= 30% of book | RWR follows NB gate (no separate RWR floor)</t>
-        </is>
-      </c>
-      <c r="C8" s="51" t="n"/>
-      <c r="D8" s="51" t="n"/>
-      <c r="E8" s="51" t="n"/>
-      <c r="F8" s="51" t="n"/>
-      <c r="G8" s="51" t="n"/>
-      <c r="H8" s="51" t="n"/>
-      <c r="I8" s="51" t="n"/>
-      <c r="J8" s="51" t="n"/>
-      <c r="K8" s="51" t="n"/>
-      <c r="L8" s="51" t="n"/>
-      <c r="M8" s="51" t="n"/>
-      <c r="N8" s="51" t="n"/>
-      <c r="O8" s="52" t="n"/>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="50" t="inlineStr">
+      <c r="A8" s="48" t="inlineStr">
         <is>
           <t>Chargeback</t>
         </is>
       </c>
-      <c r="B9" s="50" t="inlineStr">
+      <c r="B8" s="48" t="inlineStr">
         <is>
           <t>3 months (90 days) - bonus reversed if policy cancels/rewrites within 90 days</t>
         </is>
       </c>
-      <c r="C9" s="51" t="n"/>
-      <c r="D9" s="51" t="n"/>
-      <c r="E9" s="51" t="n"/>
-      <c r="F9" s="51" t="n"/>
-      <c r="G9" s="51" t="n"/>
-      <c r="H9" s="51" t="n"/>
-      <c r="I9" s="51" t="n"/>
-      <c r="J9" s="51" t="n"/>
-      <c r="K9" s="51" t="n"/>
-      <c r="L9" s="51" t="n"/>
-      <c r="M9" s="51" t="n"/>
-      <c r="N9" s="51" t="n"/>
-      <c r="O9" s="52" t="n"/>
+      <c r="C8" s="49" t="n"/>
+      <c r="D8" s="49" t="n"/>
+      <c r="E8" s="49" t="n"/>
+      <c r="F8" s="49" t="n"/>
+      <c r="G8" s="49" t="n"/>
+      <c r="H8" s="49" t="n"/>
+      <c r="I8" s="49" t="n"/>
+      <c r="J8" s="49" t="n"/>
+      <c r="K8" s="49" t="n"/>
+      <c r="L8" s="49" t="n"/>
+      <c r="M8" s="49" t="n"/>
+      <c r="N8" s="49" t="n"/>
+      <c r="O8" s="50" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>ONE ROW PER POLICY</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>ONE ROW PER POLICY</t>
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Policy #</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Carrier</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Type (NB/RWR/REN)</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Eff Date</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Exp Date</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>90-Day Review Date</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>Written Premium</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>Down Payment $</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>Collected % (calc)</t>
+        </is>
+      </c>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>PIF?</t>
+        </is>
+      </c>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>Per-Policy Base $</t>
+        </is>
+      </c>
+      <c r="N11" s="6" t="inlineStr">
+        <is>
+          <t>Collected Incentive $</t>
+        </is>
+      </c>
+      <c r="O11" s="6" t="inlineStr">
+        <is>
+          <t>Total Bonus $</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Agent</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Customer</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Policy #</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Carrier</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>Type (NB/RWR/REN)</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>Eff Date</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Exp Date</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>90-Day Review Date</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>Written Premium</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>Down Payment $</t>
-        </is>
-      </c>
-      <c r="K12" s="6" t="inlineStr">
-        <is>
-          <t>Collected % (calc)</t>
-        </is>
-      </c>
-      <c r="L12" s="6" t="inlineStr">
-        <is>
-          <t>PIF?</t>
-        </is>
-      </c>
-      <c r="M12" s="6" t="inlineStr">
-        <is>
-          <t>Per-Policy Base $</t>
-        </is>
-      </c>
-      <c r="N12" s="6" t="inlineStr">
-        <is>
-          <t>Collected Incentive $</t>
-        </is>
-      </c>
-      <c r="O12" s="6" t="inlineStr">
-        <is>
-          <t>Total Bonus $</t>
-        </is>
-      </c>
+      <c r="A12" s="14" t="inlineStr"/>
+      <c r="B12" s="14" t="inlineStr"/>
+      <c r="C12" s="14" t="inlineStr"/>
+      <c r="D12" s="14" t="inlineStr"/>
+      <c r="E12" s="14" t="inlineStr"/>
+      <c r="F12" s="14" t="inlineStr"/>
+      <c r="G12" s="14" t="inlineStr"/>
+      <c r="H12" s="14" t="inlineStr"/>
+      <c r="I12" s="14" t="inlineStr"/>
+      <c r="J12" s="14" t="inlineStr"/>
+      <c r="K12" s="14" t="inlineStr"/>
+      <c r="L12" s="14" t="inlineStr"/>
+      <c r="M12" s="14" t="inlineStr"/>
+      <c r="N12" s="14" t="inlineStr"/>
+      <c r="O12" s="14" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr"/>
@@ -1933,31 +1916,13 @@
       <c r="N41" s="14" t="inlineStr"/>
       <c r="O41" s="14" t="inlineStr"/>
     </row>
-    <row r="42">
-      <c r="A42" s="14" t="inlineStr"/>
-      <c r="B42" s="14" t="inlineStr"/>
-      <c r="C42" s="14" t="inlineStr"/>
-      <c r="D42" s="14" t="inlineStr"/>
-      <c r="E42" s="14" t="inlineStr"/>
-      <c r="F42" s="14" t="inlineStr"/>
-      <c r="G42" s="14" t="inlineStr"/>
-      <c r="H42" s="14" t="inlineStr"/>
-      <c r="I42" s="14" t="inlineStr"/>
-      <c r="J42" s="14" t="inlineStr"/>
-      <c r="K42" s="14" t="inlineStr"/>
-      <c r="L42" s="14" t="inlineStr"/>
-      <c r="M42" s="14" t="inlineStr"/>
-      <c r="N42" s="14" t="inlineStr"/>
-      <c r="O42" s="14" t="inlineStr"/>
-    </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="B9:O9"/>
+  <mergeCells count="9">
     <mergeCell ref="B8:O8"/>
     <mergeCell ref="B4:O4"/>
     <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A10:O10"/>
     <mergeCell ref="B6:O6"/>
-    <mergeCell ref="A11:O11"/>
     <mergeCell ref="B7:O7"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="B5:O5"/>
@@ -2098,7 +2063,7 @@
       <c r="E5" s="16" t="n">
         <v>4938.26</v>
       </c>
-      <c r="F5" s="53" t="n">
+      <c r="F5" s="51" t="n">
         <v>0.1278963581240991</v>
       </c>
       <c r="G5" s="15" t="n">
@@ -2110,7 +2075,7 @@
       <c r="I5" s="16" t="n">
         <v>6186.16</v>
       </c>
-      <c r="J5" s="53" t="n">
+      <c r="J5" s="51" t="n">
         <v>0.224800043607028</v>
       </c>
       <c r="K5" s="15" t="n">
@@ -2122,7 +2087,7 @@
       <c r="M5" s="16" t="n">
         <v>1734.23</v>
       </c>
-      <c r="N5" s="53" t="n">
+      <c r="N5" s="51" t="n">
         <v>0.2280381328073636</v>
       </c>
     </row>
@@ -2146,7 +2111,7 @@
       <c r="E6" s="16" t="n">
         <v>3258.77</v>
       </c>
-      <c r="F6" s="53" t="n">
+      <c r="F6" s="51" t="n">
         <v>0.1284649347577561</v>
       </c>
       <c r="G6" s="15" t="n">
@@ -2158,7 +2123,7 @@
       <c r="I6" s="16" t="n">
         <v>4268.29</v>
       </c>
-      <c r="J6" s="53" t="n">
+      <c r="J6" s="51" t="n">
         <v>0.1392908657768495</v>
       </c>
       <c r="K6" s="15" t="n">
@@ -2170,7 +2135,7 @@
       <c r="M6" s="16" t="n">
         <v>1422.16</v>
       </c>
-      <c r="N6" s="53" t="n">
+      <c r="N6" s="51" t="n">
         <v>0.1891924970067846</v>
       </c>
     </row>
@@ -2194,7 +2159,7 @@
       <c r="E7" s="16" t="n">
         <v>6523.33</v>
       </c>
-      <c r="F7" s="53" t="n">
+      <c r="F7" s="51" t="n">
         <v>0.140216196720057</v>
       </c>
       <c r="G7" s="15" t="n">
@@ -2206,7 +2171,7 @@
       <c r="I7" s="16" t="n">
         <v>5844.85</v>
       </c>
-      <c r="J7" s="53" t="n">
+      <c r="J7" s="51" t="n">
         <v>0.2316847421078502</v>
       </c>
       <c r="K7" s="15" t="n">
@@ -2218,7 +2183,7 @@
       <c r="M7" s="16" t="n">
         <v>1274.08</v>
       </c>
-      <c r="N7" s="53" t="n">
+      <c r="N7" s="51" t="n">
         <v>0.3266034350166624</v>
       </c>
     </row>
@@ -2242,7 +2207,7 @@
       <c r="E8" s="16" t="n">
         <v>8163.72</v>
       </c>
-      <c r="F8" s="53" t="n">
+      <c r="F8" s="51" t="n">
         <v>0.2158233783016042</v>
       </c>
       <c r="G8" s="15" t="n">
@@ -2254,7 +2219,7 @@
       <c r="I8" s="16" t="n">
         <v>3967.81</v>
       </c>
-      <c r="J8" s="53" t="n">
+      <c r="J8" s="51" t="n">
         <v>0.2582881730509473</v>
       </c>
       <c r="K8" s="15" t="n">
@@ -2266,7 +2231,7 @@
       <c r="M8" s="16" t="n">
         <v>5439.19</v>
       </c>
-      <c r="N8" s="53" t="n">
+      <c r="N8" s="51" t="n">
         <v>0.4973660363625058</v>
       </c>
     </row>
@@ -2277,7 +2242,7 @@
           <t>4-mo TOTAL</t>
         </is>
       </c>
-      <c r="C9" s="54" t="n">
+      <c r="C9" s="52" t="n">
         <v>95</v>
       </c>
       <c r="D9" s="19" t="n">
@@ -2286,10 +2251,10 @@
       <c r="E9" s="19" t="n">
         <v>22884.08</v>
       </c>
-      <c r="F9" s="55" t="n">
+      <c r="F9" s="53" t="n">
         <v>0.1542805350206961</v>
       </c>
-      <c r="G9" s="54" t="n">
+      <c r="G9" s="52" t="n">
         <v>68</v>
       </c>
       <c r="H9" s="19" t="n">
@@ -2298,10 +2263,10 @@
       <c r="I9" s="19" t="n">
         <v>20267.11</v>
       </c>
-      <c r="J9" s="55" t="n">
+      <c r="J9" s="53" t="n">
         <v>0.2052343747231042</v>
       </c>
-      <c r="K9" s="54" t="n">
+      <c r="K9" s="52" t="n">
         <v>34</v>
       </c>
       <c r="L9" s="19" t="n">
@@ -2310,7 +2275,7 @@
       <c r="M9" s="19" t="n">
         <v>9869.66</v>
       </c>
-      <c r="N9" s="55" t="n">
+      <c r="N9" s="53" t="n">
         <v>0.3294390097930538</v>
       </c>
     </row>
@@ -2334,7 +2299,7 @@
       <c r="E11" s="16" t="n">
         <v>4925</v>
       </c>
-      <c r="F11" s="53" t="n">
+      <c r="F11" s="51" t="n">
         <v>0.1223624980931326</v>
       </c>
       <c r="G11" s="15" t="n">
@@ -2346,7 +2311,7 @@
       <c r="I11" s="16" t="n">
         <v>10936.32</v>
       </c>
-      <c r="J11" s="53" t="n">
+      <c r="J11" s="51" t="n">
         <v>0.1665208484518856</v>
       </c>
       <c r="K11" s="15" t="n">
@@ -2358,7 +2323,7 @@
       <c r="M11" s="16" t="n">
         <v>4951.59</v>
       </c>
-      <c r="N11" s="53" t="n">
+      <c r="N11" s="51" t="n">
         <v>0.395163948359479</v>
       </c>
     </row>
@@ -2382,7 +2347,7 @@
       <c r="E12" s="16" t="n">
         <v>5766.72</v>
       </c>
-      <c r="F12" s="53" t="n">
+      <c r="F12" s="51" t="n">
         <v>0.1918537861440041</v>
       </c>
       <c r="G12" s="15" t="n">
@@ -2394,7 +2359,7 @@
       <c r="I12" s="16" t="n">
         <v>13931.43</v>
       </c>
-      <c r="J12" s="53" t="n">
+      <c r="J12" s="51" t="n">
         <v>0.1628557500999478</v>
       </c>
       <c r="K12" s="15" t="n">
@@ -2406,7 +2371,7 @@
       <c r="M12" s="16" t="n">
         <v>1937.6</v>
       </c>
-      <c r="N12" s="53" t="n">
+      <c r="N12" s="51" t="n">
         <v>0.1666081955823376</v>
       </c>
     </row>
@@ -2430,7 +2395,7 @@
       <c r="E13" s="16" t="n">
         <v>10546.59</v>
       </c>
-      <c r="F13" s="53" t="n">
+      <c r="F13" s="51" t="n">
         <v>0.2011368382508596</v>
       </c>
       <c r="G13" s="15" t="n">
@@ -2442,7 +2407,7 @@
       <c r="I13" s="16" t="n">
         <v>19700.38</v>
       </c>
-      <c r="J13" s="53" t="n">
+      <c r="J13" s="51" t="n">
         <v>0.2047253226310126</v>
       </c>
       <c r="K13" s="15" t="n">
@@ -2454,7 +2419,7 @@
       <c r="M13" s="16" t="n">
         <v>3080</v>
       </c>
-      <c r="N13" s="53" t="n">
+      <c r="N13" s="51" t="n">
         <v>0.5165618448637317</v>
       </c>
     </row>
@@ -2478,7 +2443,7 @@
       <c r="E14" s="16" t="n">
         <v>8831.440000000001</v>
       </c>
-      <c r="F14" s="53" t="n">
+      <c r="F14" s="51" t="n">
         <v>0.1777330554736579</v>
       </c>
       <c r="G14" s="15" t="n">
@@ -2490,7 +2455,7 @@
       <c r="I14" s="16" t="n">
         <v>16668.05</v>
       </c>
-      <c r="J14" s="53" t="n">
+      <c r="J14" s="51" t="n">
         <v>0.2597668245969831</v>
       </c>
       <c r="K14" s="15" t="n">
@@ -2502,7 +2467,7 @@
       <c r="M14" s="16" t="n">
         <v>2939.65</v>
       </c>
-      <c r="N14" s="53" t="n">
+      <c r="N14" s="51" t="n">
         <v>0.1501736909323116</v>
       </c>
     </row>
@@ -2513,7 +2478,7 @@
           <t>4-mo TOTAL</t>
         </is>
       </c>
-      <c r="C15" s="54" t="n">
+      <c r="C15" s="52" t="n">
         <v>117</v>
       </c>
       <c r="D15" s="19" t="n">
@@ -2522,10 +2487,10 @@
       <c r="E15" s="19" t="n">
         <v>30069.75</v>
       </c>
-      <c r="F15" s="55" t="n">
+      <c r="F15" s="53" t="n">
         <v>0.1743867416259452</v>
       </c>
-      <c r="G15" s="54" t="n">
+      <c r="G15" s="52" t="n">
         <v>217</v>
       </c>
       <c r="H15" s="19" t="n">
@@ -2534,10 +2499,10 @@
       <c r="I15" s="19" t="n">
         <v>61236.18000000001</v>
       </c>
-      <c r="J15" s="55" t="n">
+      <c r="J15" s="53" t="n">
         <v>0.1965130808087551</v>
       </c>
-      <c r="K15" s="54" t="n">
+      <c r="K15" s="52" t="n">
         <v>29</v>
       </c>
       <c r="L15" s="19" t="n">
@@ -2546,7 +2511,7 @@
       <c r="M15" s="19" t="n">
         <v>12908.84</v>
       </c>
-      <c r="N15" s="55" t="n">
+      <c r="N15" s="53" t="n">
         <v>0.2597474930907196</v>
       </c>
     </row>
@@ -2570,7 +2535,7 @@
       <c r="E17" s="16" t="n">
         <v>7651.14</v>
       </c>
-      <c r="F17" s="53" t="n">
+      <c r="F17" s="51" t="n">
         <v>0.2065698317989147</v>
       </c>
       <c r="G17" s="15" t="n">
@@ -2582,7 +2547,7 @@
       <c r="I17" s="16" t="n">
         <v>11897.57</v>
       </c>
-      <c r="J17" s="53" t="n">
+      <c r="J17" s="51" t="n">
         <v>0.1877343410993381</v>
       </c>
       <c r="K17" s="15" t="n">
@@ -2594,7 +2559,7 @@
       <c r="M17" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="N17" s="53" t="n">
+      <c r="N17" s="51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2618,7 +2583,7 @@
       <c r="E18" s="16" t="n">
         <v>2095.02</v>
       </c>
-      <c r="F18" s="53" t="n">
+      <c r="F18" s="51" t="n">
         <v>0.2735191592140479</v>
       </c>
       <c r="G18" s="15" t="n">
@@ -2630,7 +2595,7 @@
       <c r="I18" s="16" t="n">
         <v>6802.73</v>
       </c>
-      <c r="J18" s="53" t="n">
+      <c r="J18" s="51" t="n">
         <v>0.1360799108634206</v>
       </c>
       <c r="K18" s="15" t="n">
@@ -2642,7 +2607,7 @@
       <c r="M18" s="16" t="n">
         <v>91.75</v>
       </c>
-      <c r="N18" s="53" t="n">
+      <c r="N18" s="51" t="n">
         <v>0.08631232361241768</v>
       </c>
     </row>
@@ -2666,7 +2631,7 @@
       <c r="E19" s="16" t="n">
         <v>5669.41</v>
       </c>
-      <c r="F19" s="53" t="n">
+      <c r="F19" s="51" t="n">
         <v>0.142591870663008</v>
       </c>
       <c r="G19" s="15" t="n">
@@ -2678,7 +2643,7 @@
       <c r="I19" s="16" t="n">
         <v>8620.469999999999</v>
       </c>
-      <c r="J19" s="53" t="n">
+      <c r="J19" s="51" t="n">
         <v>0.1516070882122243</v>
       </c>
       <c r="K19" s="15" t="n">
@@ -2690,7 +2655,7 @@
       <c r="M19" s="16" t="n">
         <v>180.45</v>
       </c>
-      <c r="N19" s="53" t="n">
+      <c r="N19" s="51" t="n">
         <v>0.1745164410058027</v>
       </c>
     </row>
@@ -2714,7 +2679,7 @@
       <c r="E20" s="16" t="n">
         <v>4344.3</v>
       </c>
-      <c r="F20" s="53" t="n">
+      <c r="F20" s="51" t="n">
         <v>0.225229218673448</v>
       </c>
       <c r="G20" s="15" t="n">
@@ -2726,7 +2691,7 @@
       <c r="I20" s="16" t="n">
         <v>7660.7</v>
       </c>
-      <c r="J20" s="53" t="n">
+      <c r="J20" s="51" t="n">
         <v>0.1765292813656495</v>
       </c>
       <c r="K20" s="15" t="n">
@@ -2738,7 +2703,7 @@
       <c r="M20" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="N20" s="53" t="n">
+      <c r="N20" s="51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2749,7 +2714,7 @@
           <t>4-mo TOTAL</t>
         </is>
       </c>
-      <c r="C21" s="54" t="n">
+      <c r="C21" s="52" t="n">
         <v>87</v>
       </c>
       <c r="D21" s="19" t="n">
@@ -2758,10 +2723,10 @@
       <c r="E21" s="19" t="n">
         <v>19759.87</v>
       </c>
-      <c r="F21" s="55" t="n">
+      <c r="F21" s="53" t="n">
         <v>0.1904629117787531</v>
       </c>
-      <c r="G21" s="54" t="n">
+      <c r="G21" s="52" t="n">
         <v>170</v>
       </c>
       <c r="H21" s="19" t="n">
@@ -2770,10 +2735,10 @@
       <c r="I21" s="19" t="n">
         <v>34981.46999999999</v>
       </c>
-      <c r="J21" s="55" t="n">
+      <c r="J21" s="53" t="n">
         <v>0.1637540609113293</v>
       </c>
-      <c r="K21" s="54" t="n">
+      <c r="K21" s="52" t="n">
         <v>2</v>
       </c>
       <c r="L21" s="19" t="n">
@@ -2782,7 +2747,7 @@
       <c r="M21" s="19" t="n">
         <v>272.2</v>
       </c>
-      <c r="N21" s="55" t="n">
+      <c r="N21" s="53" t="n">
         <v>0.1298044825941821</v>
       </c>
     </row>
@@ -2806,7 +2771,7 @@
       <c r="E23" s="16" t="n">
         <v>5657.4</v>
       </c>
-      <c r="F23" s="53" t="n">
+      <c r="F23" s="51" t="n">
         <v>0.1983309406994904</v>
       </c>
       <c r="G23" s="15" t="n">
@@ -2818,7 +2783,7 @@
       <c r="I23" s="16" t="n">
         <v>8795.290000000001</v>
       </c>
-      <c r="J23" s="53" t="n">
+      <c r="J23" s="51" t="n">
         <v>0.2223388159932049</v>
       </c>
       <c r="K23" s="15" t="n">
@@ -2830,7 +2795,7 @@
       <c r="M23" s="16" t="n">
         <v>302.12</v>
       </c>
-      <c r="N23" s="53" t="n">
+      <c r="N23" s="51" t="n">
         <v>0.2063167958479872</v>
       </c>
     </row>
@@ -2854,7 +2819,7 @@
       <c r="E24" s="16" t="n">
         <v>3832.59</v>
       </c>
-      <c r="F24" s="53" t="n">
+      <c r="F24" s="51" t="n">
         <v>0.1722690435415796</v>
       </c>
       <c r="G24" s="15" t="n">
@@ -2866,7 +2831,7 @@
       <c r="I24" s="16" t="n">
         <v>13820.09</v>
       </c>
-      <c r="J24" s="53" t="n">
+      <c r="J24" s="51" t="n">
         <v>0.3163400473133589</v>
       </c>
       <c r="K24" s="15" t="n">
@@ -2878,7 +2843,7 @@
       <c r="M24" s="16" t="n">
         <v>321.01</v>
       </c>
-      <c r="N24" s="53" t="n">
+      <c r="N24" s="51" t="n">
         <v>0.152934730824202</v>
       </c>
     </row>
@@ -2902,7 +2867,7 @@
       <c r="E25" s="16" t="n">
         <v>8642.02</v>
       </c>
-      <c r="F25" s="53" t="n">
+      <c r="F25" s="51" t="n">
         <v>0.2763766030253606</v>
       </c>
       <c r="G25" s="15" t="n">
@@ -2914,7 +2879,7 @@
       <c r="I25" s="16" t="n">
         <v>9060.629999999999</v>
       </c>
-      <c r="J25" s="53" t="n">
+      <c r="J25" s="51" t="n">
         <v>0.3851211602137146</v>
       </c>
       <c r="K25" s="15" t="n">
@@ -2926,7 +2891,7 @@
       <c r="M25" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="N25" s="53" t="n">
+      <c r="N25" s="51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2950,7 +2915,7 @@
       <c r="E26" s="16" t="n">
         <v>6600.51</v>
       </c>
-      <c r="F26" s="53" t="n">
+      <c r="F26" s="51" t="n">
         <v>0.2231330530863509</v>
       </c>
       <c r="G26" s="15" t="n">
@@ -2962,7 +2927,7 @@
       <c r="I26" s="16" t="n">
         <v>7710.62</v>
       </c>
-      <c r="J26" s="53" t="n">
+      <c r="J26" s="51" t="n">
         <v>0.2500788122762931</v>
       </c>
       <c r="K26" s="15" t="n">
@@ -2974,7 +2939,7 @@
       <c r="M26" s="16" t="n">
         <v>885</v>
       </c>
-      <c r="N26" s="53" t="n">
+      <c r="N26" s="51" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2985,7 +2950,7 @@
           <t>4-mo TOTAL</t>
         </is>
       </c>
-      <c r="C27" s="54" t="n">
+      <c r="C27" s="52" t="n">
         <v>92</v>
       </c>
       <c r="D27" s="19" t="n">
@@ -2994,10 +2959,10 @@
       <c r="E27" s="19" t="n">
         <v>24732.52</v>
       </c>
-      <c r="F27" s="55" t="n">
+      <c r="F27" s="53" t="n">
         <v>0.2215722952658418</v>
       </c>
-      <c r="G27" s="54" t="n">
+      <c r="G27" s="52" t="n">
         <v>135</v>
       </c>
       <c r="H27" s="19" t="n">
@@ -3006,10 +2971,10 @@
       <c r="I27" s="19" t="n">
         <v>39386.63</v>
       </c>
-      <c r="J27" s="55" t="n">
+      <c r="J27" s="53" t="n">
         <v>0.2862297260215039</v>
       </c>
-      <c r="K27" s="54" t="n">
+      <c r="K27" s="52" t="n">
         <v>4</v>
       </c>
       <c r="L27" s="19" t="n">
@@ -3018,7 +2983,7 @@
       <c r="M27" s="19" t="n">
         <v>1508.13</v>
       </c>
-      <c r="N27" s="55" t="n">
+      <c r="N27" s="53" t="n">
         <v>0.3390313262220823</v>
       </c>
     </row>
@@ -3042,7 +3007,7 @@
       <c r="E29" s="16" t="n">
         <v>2238.28</v>
       </c>
-      <c r="F29" s="53" t="n">
+      <c r="F29" s="51" t="n">
         <v>0.1443688362283039</v>
       </c>
       <c r="G29" s="15" t="n">
@@ -3054,7 +3019,7 @@
       <c r="I29" s="16" t="n">
         <v>6461.48</v>
       </c>
-      <c r="J29" s="53" t="n">
+      <c r="J29" s="51" t="n">
         <v>0.1953056967536807</v>
       </c>
       <c r="K29" s="15" t="n">
@@ -3066,7 +3031,7 @@
       <c r="M29" s="16" t="n">
         <v>642.04</v>
       </c>
-      <c r="N29" s="53" t="n">
+      <c r="N29" s="51" t="n">
         <v>0.1739945799457994</v>
       </c>
     </row>
@@ -3090,7 +3055,7 @@
       <c r="E30" s="16" t="n">
         <v>3640.91</v>
       </c>
-      <c r="F30" s="53" t="n">
+      <c r="F30" s="51" t="n">
         <v>0.1875380197535315</v>
       </c>
       <c r="G30" s="15" t="n">
@@ -3102,7 +3067,7 @@
       <c r="I30" s="16" t="n">
         <v>5276.12</v>
       </c>
-      <c r="J30" s="53" t="n">
+      <c r="J30" s="51" t="n">
         <v>0.186447458067945</v>
       </c>
       <c r="K30" s="15" t="n">
@@ -3114,7 +3079,7 @@
       <c r="M30" s="16" t="n">
         <v>3293.14</v>
       </c>
-      <c r="N30" s="53" t="n">
+      <c r="N30" s="51" t="n">
         <v>0.442269674993285</v>
       </c>
     </row>
@@ -3138,7 +3103,7 @@
       <c r="E31" s="16" t="n">
         <v>4965.76</v>
       </c>
-      <c r="F31" s="53" t="n">
+      <c r="F31" s="51" t="n">
         <v>0.2782922142225067</v>
       </c>
       <c r="G31" s="15" t="n">
@@ -3150,7 +3115,7 @@
       <c r="I31" s="16" t="n">
         <v>3981.64</v>
       </c>
-      <c r="J31" s="53" t="n">
+      <c r="J31" s="51" t="n">
         <v>0.2006789023655741</v>
       </c>
       <c r="K31" s="15" t="n">
@@ -3162,7 +3127,7 @@
       <c r="M31" s="16" t="n">
         <v>1575.86</v>
       </c>
-      <c r="N31" s="53" t="n">
+      <c r="N31" s="51" t="n">
         <v>0.2792147274048087</v>
       </c>
     </row>
@@ -3186,7 +3151,7 @@
       <c r="E32" s="16" t="n">
         <v>3941.94</v>
       </c>
-      <c r="F32" s="53" t="n">
+      <c r="F32" s="51" t="n">
         <v>0.2795900418469395</v>
       </c>
       <c r="G32" s="15" t="n">
@@ -3198,7 +3163,7 @@
       <c r="I32" s="16" t="n">
         <v>7674.9</v>
       </c>
-      <c r="J32" s="53" t="n">
+      <c r="J32" s="51" t="n">
         <v>0.1928638200349798</v>
       </c>
       <c r="K32" s="15" t="n">
@@ -3210,7 +3175,7 @@
       <c r="M32" s="16" t="n">
         <v>3096.58</v>
       </c>
-      <c r="N32" s="53" t="n">
+      <c r="N32" s="51" t="n">
         <v>0.8561183301078241</v>
       </c>
     </row>
@@ -3221,7 +3186,7 @@
           <t>4-mo TOTAL</t>
         </is>
       </c>
-      <c r="C33" s="54" t="n">
+      <c r="C33" s="52" t="n">
         <v>52</v>
       </c>
       <c r="D33" s="19" t="n">
@@ -3230,10 +3195,10 @@
       <c r="E33" s="19" t="n">
         <v>14786.89</v>
       </c>
-      <c r="F33" s="55" t="n">
+      <c r="F33" s="53" t="n">
         <v>0.2211592017091021</v>
       </c>
-      <c r="G33" s="54" t="n">
+      <c r="G33" s="52" t="n">
         <v>100</v>
       </c>
       <c r="H33" s="19" t="n">
@@ -3242,10 +3207,10 @@
       <c r="I33" s="19" t="n">
         <v>23394.14</v>
       </c>
-      <c r="J33" s="55" t="n">
+      <c r="J33" s="53" t="n">
         <v>0.1933122972294714</v>
       </c>
-      <c r="K33" s="54" t="n">
+      <c r="K33" s="52" t="n">
         <v>18</v>
       </c>
       <c r="L33" s="19" t="n">
@@ -3254,7 +3219,7 @@
       <c r="M33" s="19" t="n">
         <v>8607.619999999999</v>
       </c>
-      <c r="N33" s="55" t="n">
+      <c r="N33" s="53" t="n">
         <v>0.4220062852688398</v>
       </c>
     </row>
@@ -3278,7 +3243,7 @@
       <c r="E35" s="16" t="n">
         <v>6551.7</v>
       </c>
-      <c r="F35" s="53" t="n">
+      <c r="F35" s="51" t="n">
         <v>0.2290380555484667</v>
       </c>
       <c r="G35" s="15" t="n">
@@ -3290,7 +3255,7 @@
       <c r="I35" s="16" t="n">
         <v>8203.879999999999</v>
       </c>
-      <c r="J35" s="53" t="n">
+      <c r="J35" s="51" t="n">
         <v>0.1687591127962584</v>
       </c>
       <c r="K35" s="15" t="n">
@@ -3302,7 +3267,7 @@
       <c r="M35" s="16" t="n">
         <v>1439.3</v>
       </c>
-      <c r="N35" s="53" t="n">
+      <c r="N35" s="51" t="n">
         <v>0.2213316807398534</v>
       </c>
     </row>
@@ -3326,7 +3291,7 @@
       <c r="E36" s="16" t="n">
         <v>6512.87</v>
       </c>
-      <c r="F36" s="53" t="n">
+      <c r="F36" s="51" t="n">
         <v>0.206646582235908</v>
       </c>
       <c r="G36" s="15" t="n">
@@ -3338,7 +3303,7 @@
       <c r="I36" s="16" t="n">
         <v>7155.23</v>
       </c>
-      <c r="J36" s="53" t="n">
+      <c r="J36" s="51" t="n">
         <v>0.1515034032647457</v>
       </c>
       <c r="K36" s="15" t="n">
@@ -3350,7 +3315,7 @@
       <c r="M36" s="16" t="n">
         <v>272.87</v>
       </c>
-      <c r="N36" s="53" t="n">
+      <c r="N36" s="51" t="n">
         <v>0.0882503234152652</v>
       </c>
     </row>
@@ -3374,7 +3339,7 @@
       <c r="E37" s="16" t="n">
         <v>17019.79</v>
       </c>
-      <c r="F37" s="53" t="n">
+      <c r="F37" s="51" t="n">
         <v>0.2482965508528406</v>
       </c>
       <c r="G37" s="15" t="n">
@@ -3386,7 +3351,7 @@
       <c r="I37" s="16" t="n">
         <v>5300.53</v>
       </c>
-      <c r="J37" s="53" t="n">
+      <c r="J37" s="51" t="n">
         <v>0.135029353210384</v>
       </c>
       <c r="K37" s="15" t="n">
@@ -3398,7 +3363,7 @@
       <c r="M37" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="N37" s="53" t="n">
+      <c r="N37" s="51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3422,7 +3387,7 @@
       <c r="E38" s="16" t="n">
         <v>6197.26</v>
       </c>
-      <c r="F38" s="53" t="n">
+      <c r="F38" s="51" t="n">
         <v>0.2082728262918876</v>
       </c>
       <c r="G38" s="15" t="n">
@@ -3434,7 +3399,7 @@
       <c r="I38" s="16" t="n">
         <v>7305.79</v>
       </c>
-      <c r="J38" s="53" t="n">
+      <c r="J38" s="51" t="n">
         <v>0.2070808023832267</v>
       </c>
       <c r="K38" s="15" t="n">
@@ -3446,7 +3411,7 @@
       <c r="M38" s="16" t="n">
         <v>291.12</v>
       </c>
-      <c r="N38" s="53" t="n">
+      <c r="N38" s="51" t="n">
         <v>0.115799522673031</v>
       </c>
     </row>
@@ -3457,7 +3422,7 @@
           <t>4-mo TOTAL</t>
         </is>
       </c>
-      <c r="C39" s="54" t="n">
+      <c r="C39" s="52" t="n">
         <v>102</v>
       </c>
       <c r="D39" s="19" t="n">
@@ -3466,10 +3431,10 @@
       <c r="E39" s="19" t="n">
         <v>36281.62</v>
       </c>
-      <c r="F39" s="55" t="n">
+      <c r="F39" s="53" t="n">
         <v>0.2290160042089596</v>
       </c>
-      <c r="G39" s="54" t="n">
+      <c r="G39" s="52" t="n">
         <v>116</v>
       </c>
       <c r="H39" s="19" t="n">
@@ -3478,10 +3443,10 @@
       <c r="I39" s="19" t="n">
         <v>27965.43</v>
       </c>
-      <c r="J39" s="55" t="n">
+      <c r="J39" s="53" t="n">
         <v>0.1641397901308573</v>
       </c>
-      <c r="K39" s="54" t="n">
+      <c r="K39" s="52" t="n">
         <v>10</v>
       </c>
       <c r="L39" s="19" t="n">
@@ -3490,7 +3455,7 @@
       <c r="M39" s="19" t="n">
         <v>2003.29</v>
       </c>
-      <c r="N39" s="55" t="n">
+      <c r="N39" s="53" t="n">
         <v>0.1654393335155683</v>
       </c>
     </row>
@@ -3605,10 +3570,10 @@
         <v>2925</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>8375</v>
+        <v>3875</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>18475</v>
+        <v>7975</v>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
@@ -3626,10 +3591,10 @@
         <v>1675</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>8375</v>
+        <v>3875</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>18475</v>
+        <v>7975</v>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
@@ -4884,13 +4849,13 @@
         <v>350</v>
       </c>
       <c r="J43" s="11" t="n">
-        <v>850</v>
+        <v>350</v>
       </c>
       <c r="K43" s="17" t="n">
-        <v>850</v>
+        <v>350</v>
       </c>
       <c r="L43" s="16" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -4926,13 +4891,13 @@
         <v>500</v>
       </c>
       <c r="J44" s="11" t="n">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="K44" s="17" t="n">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="L44" s="16" t="n">
-        <v>250</v>
+        <v>-250</v>
       </c>
     </row>
     <row r="45">
@@ -5052,13 +5017,13 @@
         <v>350</v>
       </c>
       <c r="J47" s="11" t="n">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="K47" s="17" t="n">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="L47" s="16" t="n">
-        <v>400</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="48">
@@ -5136,13 +5101,13 @@
         <v>460</v>
       </c>
       <c r="J49" s="11" t="n">
-        <v>850</v>
+        <v>350</v>
       </c>
       <c r="K49" s="17" t="n">
-        <v>850</v>
+        <v>350</v>
       </c>
       <c r="L49" s="16" t="n">
-        <v>390</v>
+        <v>-110</v>
       </c>
     </row>
     <row r="50">
@@ -5178,13 +5143,13 @@
         <v>250</v>
       </c>
       <c r="J50" s="11" t="n">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="K50" s="17" t="n">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="L50" s="16" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -5304,13 +5269,13 @@
         <v>350</v>
       </c>
       <c r="J53" s="11" t="n">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="K53" s="17" t="n">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="L53" s="16" t="n">
-        <v>400</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="54">
@@ -5388,13 +5353,13 @@
         <v>680</v>
       </c>
       <c r="J55" s="11" t="n">
-        <v>1200</v>
+        <v>700</v>
       </c>
       <c r="K55" s="17" t="n">
-        <v>1200</v>
+        <v>700</v>
       </c>
       <c r="L55" s="16" t="n">
-        <v>520</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56">
@@ -5430,13 +5395,13 @@
         <v>470</v>
       </c>
       <c r="J56" s="11" t="n">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="K56" s="17" t="n">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="L56" s="16" t="n">
-        <v>280</v>
+        <v>-220</v>
       </c>
     </row>
     <row r="57">
@@ -5640,13 +5605,13 @@
         <v>500</v>
       </c>
       <c r="J61" s="11" t="n">
-        <v>1100</v>
+        <v>600</v>
       </c>
       <c r="K61" s="17" t="n">
-        <v>1100</v>
+        <v>600</v>
       </c>
       <c r="L61" s="16" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="62">
@@ -5827,13 +5792,13 @@
         <v>7110</v>
       </c>
       <c r="J66" s="19" t="n">
-        <v>8375</v>
+        <v>3875</v>
       </c>
       <c r="K66" s="19" t="n">
-        <v>8375</v>
+        <v>3875</v>
       </c>
       <c r="L66" s="19" t="n">
-        <v>1265</v>
+        <v>-3235</v>
       </c>
     </row>
     <row r="69">
@@ -5853,7 +5818,7 @@
     <row r="71" ht="44" customHeight="1">
       <c r="A71" s="20" t="inlineStr">
         <is>
-          <t>100% FLIP - 'if you had been renewing instead of rewriting': The Bonus Plan WITH MIN pays $18,475 (151% of today's $12,220 current). Agent earns close to today for doing the RIGHT behavior.</t>
+          <t>100% FLIP - 'if you had been renewing instead of rewriting': The Bonus Plan WITH MIN pays $7,975 (65% of today's $12,220 current). Agent earns close to today for doing the RIGHT behavior.</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6506,398 +6471,326 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="14" t="inlineStr">
-        <is>
-          <t>Kicker 30-49%</t>
-        </is>
-      </c>
-      <c r="B35" s="14" t="inlineStr">
-        <is>
-          <t>+$0</t>
-        </is>
-      </c>
-      <c r="C35" s="14" t="inlineStr"/>
-      <c r="D35" s="14" t="inlineStr">
-        <is>
-          <t>Qualifies for tier bonus, no kicker.</t>
-        </is>
-      </c>
-    </row>
     <row r="36">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>Kicker 50-74%</t>
-        </is>
-      </c>
-      <c r="B36" s="12" t="inlineStr">
-        <is>
-          <t>+$250</t>
-        </is>
-      </c>
-      <c r="C36" s="12" t="inlineStr"/>
-      <c r="D36" s="12" t="inlineStr">
-        <is>
-          <t>Solid retention - on top of the tier bonus.</t>
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>4. RULES THAT APPLY ON TOP</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="14" t="inlineStr">
-        <is>
-          <t>Kicker 75-99%</t>
-        </is>
-      </c>
-      <c r="B37" s="14" t="inlineStr">
-        <is>
-          <t>+$500</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="inlineStr"/>
-      <c r="D37" s="14" t="inlineStr">
-        <is>
-          <t>Strong retention - bigger kicker.</t>
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>How it works</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>Kicker 100%</t>
+          <t>NB minimum</t>
         </is>
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>+$1,000</t>
-        </is>
-      </c>
-      <c r="C38" s="12" t="inlineStr"/>
-      <c r="D38" s="12" t="inlineStr">
-        <is>
-          <t>Perfect retention - top kicker.</t>
+          <t>$45,000 monthly written premium</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>NB premium below $45k -&gt; NB bonus = $0 (also blocks RWR).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>REN minimum</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>&gt;= 30% retention rate of book</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>Retention &lt; 30% -&gt; REN bonus = $0.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>4. RULES THAT APPLY ON TOP</t>
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>RWR gate</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>NB minimum met</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>No separate RWR floor.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>Rule</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>How it works</t>
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>90-day chargeback</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>100% reversal</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>Bonus on a policy is REVERSED if it cancels/rewrites within 90 days of effective date.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>NB minimum</t>
+          <t>Manual tracker</t>
         </is>
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>$45,000 monthly written premium</t>
+          <t>Required per policy</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>NB premium below $45k -&gt; NB bonus = $0 (also blocks RWR).</t>
+          <t>No entry = no bonus on that policy.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
-          <t>REN minimum</t>
+          <t>Renewal book</t>
         </is>
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>&gt;= 30% retention rate of book</t>
+          <t>Assigned per agent</t>
         </is>
       </c>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>Retention &lt; 30% -&gt; REN bonus = $0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="12" t="inlineStr">
-        <is>
-          <t>RWR gate</t>
-        </is>
-      </c>
-      <c r="B44" s="12" t="inlineStr">
-        <is>
-          <t>NB minimum met</t>
-        </is>
-      </c>
-      <c r="C44" s="12" t="inlineStr">
-        <is>
-          <t>No separate RWR floor.</t>
+          <t>Newer agents inherit a book from former employees.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="14" t="inlineStr">
-        <is>
-          <t>90-day chargeback</t>
-        </is>
-      </c>
-      <c r="B45" s="14" t="inlineStr">
-        <is>
-          <t>100% reversal</t>
-        </is>
-      </c>
-      <c r="C45" s="14" t="inlineStr">
-        <is>
-          <t>Bonus on a policy is REVERSED if it cancels/rewrites within 90 days of effective date.</t>
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>5. WORKED EXAMPLE - Dialinerys Dieguez, March 2026</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="12" t="inlineStr">
-        <is>
-          <t>Manual tracker</t>
-        </is>
-      </c>
-      <c r="B46" s="12" t="inlineStr">
-        <is>
-          <t>Required per policy</t>
-        </is>
-      </c>
-      <c r="C46" s="12" t="inlineStr">
-        <is>
-          <t>No entry = no bonus on that policy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="24" customHeight="1">
       <c r="A47" s="14" t="inlineStr">
         <is>
-          <t>Renewal book</t>
+          <t>Volumes</t>
         </is>
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>Assigned per agent</t>
-        </is>
-      </c>
-      <c r="C47" s="14" t="inlineStr">
-        <is>
-          <t>Newer agents inherit a book from former employees.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>5. WORKED EXAMPLE - Dialinerys Dieguez, March 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>Math</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>Result</t>
+          <t>NB 38 policies = $52,435 written premium (20.1% collected)</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="inlineStr"/>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>Volumes</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>RWR 69 policies = $96,228 written premium (20.5% collected)</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="inlineStr"/>
+    </row>
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>Volumes</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>REN 7 policies = $5,962 written premium</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="inlineStr"/>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>NB tier</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>$52k NB written premium lands in T1 $45k</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>$250</t>
         </is>
       </c>
     </row>
     <row r="51" ht="24" customHeight="1">
       <c r="A51" s="14" t="inlineStr">
         <is>
-          <t>Volumes</t>
+          <t>RWR tier</t>
         </is>
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>NB 38 policies = $52,435 written premium (20.1% collected)</t>
-        </is>
-      </c>
-      <c r="C51" s="14" t="inlineStr"/>
+          <t>$96k RWR written premium lands in T4 $85k</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>$350</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="24" customHeight="1">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>Volumes</t>
+          <t>REN tier</t>
         </is>
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>RWR 69 policies = $96,228 written premium (20.5% collected)</t>
-        </is>
-      </c>
-      <c r="C52" s="12" t="inlineStr"/>
+          <t>$6k REN written premium lands in Below T1</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="24" customHeight="1">
       <c r="A53" s="14" t="inlineStr">
         <is>
-          <t>Volumes</t>
+          <t>Subtotal target</t>
         </is>
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>REN 7 policies = $5,962 written premium</t>
-        </is>
-      </c>
-      <c r="C53" s="14" t="inlineStr"/>
+          <t>(NB + RWR + REN, before gates)</t>
+        </is>
+      </c>
+      <c r="C53" s="14" t="inlineStr">
+        <is>
+          <t>$600</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="24" customHeight="1">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>NB tier</t>
+          <t>NB gate ($45,000)</t>
         </is>
       </c>
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t>$52k NB written premium lands in T1 $45k</t>
-        </is>
-      </c>
-      <c r="C54" s="12" t="inlineStr">
-        <is>
-          <t>$250</t>
+          <t>NB written $52,435 vs $45,000</t>
+        </is>
+      </c>
+      <c r="C54" s="23" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1">
       <c r="A55" s="14" t="inlineStr">
         <is>
-          <t>RWR tier</t>
+          <t>REN gate (&gt;= 30% retention)</t>
         </is>
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>$96k RWR written premium lands in T4 $85k</t>
-        </is>
-      </c>
-      <c r="C55" s="14" t="inlineStr">
-        <is>
-          <t>$350</t>
+          <t>Assumed retention 75% vs 30%</t>
+        </is>
+      </c>
+      <c r="C55" s="23" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="56" ht="24" customHeight="1">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>REN tier</t>
+          <t>RWR gate (NB met)</t>
         </is>
       </c>
       <c r="B56" s="12" t="inlineStr">
         <is>
-          <t>$6k REN written premium lands in Below T1</t>
-        </is>
-      </c>
-      <c r="C56" s="12" t="inlineStr">
-        <is>
-          <t>$0</t>
+          <t>RWR pays only if NB gate passed?</t>
+        </is>
+      </c>
+      <c r="C56" s="23" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="57" ht="24" customHeight="1">
-      <c r="A57" s="14" t="inlineStr">
-        <is>
-          <t>Subtotal target</t>
-        </is>
-      </c>
-      <c r="B57" s="14" t="inlineStr">
-        <is>
-          <t>(NB + RWR + REN, before gates)</t>
-        </is>
-      </c>
-      <c r="C57" s="14" t="inlineStr">
-        <is>
-          <t>$600</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="12" t="inlineStr">
-        <is>
-          <t>NB gate ($45,000)</t>
-        </is>
-      </c>
-      <c r="B58" s="12" t="inlineStr">
-        <is>
-          <t>NB written $52,435 vs $45,000</t>
-        </is>
-      </c>
-      <c r="C58" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="24" customHeight="1">
-      <c r="A59" s="14" t="inlineStr">
-        <is>
-          <t>REN gate (&gt;= 30% retention)</t>
-        </is>
-      </c>
-      <c r="B59" s="14" t="inlineStr">
-        <is>
-          <t>Assumed retention 75% vs 30%</t>
-        </is>
-      </c>
-      <c r="C59" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="24" customHeight="1">
-      <c r="A60" s="12" t="inlineStr">
-        <is>
-          <t>RWR gate (NB met)</t>
-        </is>
-      </c>
-      <c r="B60" s="12" t="inlineStr">
-        <is>
-          <t>RWR pays only if NB gate passed?</t>
-        </is>
-      </c>
-      <c r="C60" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="24" customHeight="1">
-      <c r="A61" s="24" t="inlineStr">
+      <c r="A57" s="24" t="inlineStr">
         <is>
           <t>FINAL PAID</t>
         </is>
       </c>
-      <c r="B61" s="24" t="inlineStr">
+      <c r="B57" s="24" t="inlineStr">
         <is>
           <t>Pay only the lines whose gates passed</t>
         </is>
       </c>
-      <c r="C61" s="24" t="inlineStr">
+      <c r="C57" s="24" t="inlineStr">
         <is>
           <t>$600.00</t>
         </is>
@@ -6905,13 +6798,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A36:G36"/>
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A40:G40"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A49:G49"/>
+    <mergeCell ref="A45:G45"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11089,16 +10982,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11150,11 +11042,6 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Retention Kicker (75% assumed)</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
           <t>Total Bonus $</t>
         </is>
       </c>
@@ -11181,10 +11068,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F6" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="31" t="n">
+      <c r="F6" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11210,10 +11094,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F7" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="31" t="n">
+      <c r="F7" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11239,10 +11120,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F8" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="31" t="n">
+      <c r="F8" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11268,10 +11146,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F9" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="31" t="n">
+      <c r="F9" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11297,10 +11172,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F10" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="31" t="n">
+      <c r="F10" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11326,10 +11198,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F11" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="31" t="n">
+      <c r="F11" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11355,10 +11224,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F12" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="31" t="n">
+      <c r="F12" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11384,10 +11250,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F13" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="31" t="n">
+      <c r="F13" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11413,10 +11276,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F14" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="31" t="n">
+      <c r="F14" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11442,10 +11302,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F15" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="31" t="n">
+      <c r="F15" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11471,10 +11328,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F16" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="31" t="n">
+      <c r="F16" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11500,10 +11354,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F17" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="31" t="n">
+      <c r="F17" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11529,10 +11380,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F18" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="31" t="n">
+      <c r="F18" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11558,10 +11406,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F19" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="31" t="n">
+      <c r="F19" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11587,10 +11432,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F20" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="31" t="n">
+      <c r="F20" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11616,10 +11458,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F21" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="31" t="n">
+      <c r="F21" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11645,10 +11484,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F22" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="31" t="n">
+      <c r="F22" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11674,10 +11510,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F23" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="31" t="n">
+      <c r="F23" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11703,10 +11536,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F24" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="31" t="n">
+      <c r="F24" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11732,10 +11562,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F25" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="31" t="n">
+      <c r="F25" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11761,10 +11588,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F26" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="31" t="n">
+      <c r="F26" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11790,10 +11614,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F27" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="31" t="n">
+      <c r="F27" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11819,10 +11640,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F28" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="31" t="n">
+      <c r="F28" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11848,17 +11666,14 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F29" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="31" t="n">
+      <c r="F29" s="31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>REN tiers: T1 $25k=$250 | T2 $40k=$350 | T3 $65k=$450 | T4 $80k=$550 | T5 $100k=$800 (above $100k: +$40/$5k). Retention KICKER on top: 30-49%=$0, 50-74%=+$250, 75-99%=+$500, 100%=+$1,000. Model assumes 75% retention -&gt; +$500 kicker per eligible row.</t>
+          <t>REN tiers: T1 $25k=$250 | T2 $40k=$350 | T3 $65k=$450 | T4 $80k=$550 | T5 $100k=$800 | Above $100k: +$40 per $5k. REN gated by 30% retention rate.</t>
         </is>
       </c>
     </row>
@@ -11897,11 +11712,6 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>Retention Kicker (75% assumed)</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="inlineStr">
-        <is>
           <t>Total Bonus $</t>
         </is>
       </c>
@@ -11928,11 +11738,8 @@
           <t>Tier 2 (T2 $40k) - $350</t>
         </is>
       </c>
-      <c r="F34" s="34" t="n">
-        <v>500</v>
-      </c>
-      <c r="G34" s="28" t="n">
-        <v>850</v>
+      <c r="F34" s="28" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
@@ -11957,11 +11764,8 @@
           <t>Tier 2 (T2 $40k) - $350</t>
         </is>
       </c>
-      <c r="F35" s="34" t="n">
-        <v>500</v>
-      </c>
-      <c r="G35" s="28" t="n">
-        <v>850</v>
+      <c r="F35" s="28" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
@@ -11986,11 +11790,8 @@
           <t>Tier 2 (T2 $40k) - $350</t>
         </is>
       </c>
-      <c r="F36" s="34" t="n">
-        <v>500</v>
-      </c>
-      <c r="G36" s="28" t="n">
-        <v>850</v>
+      <c r="F36" s="28" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
@@ -12015,11 +11816,8 @@
           <t>Tier 2 (T2 $40k) - $350</t>
         </is>
       </c>
-      <c r="F37" s="34" t="n">
-        <v>500</v>
-      </c>
-      <c r="G37" s="28" t="n">
-        <v>850</v>
+      <c r="F37" s="28" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
@@ -12044,11 +11842,8 @@
           <t>Tier 1 (T1 $25k) - $250</t>
         </is>
       </c>
-      <c r="F38" s="34" t="n">
-        <v>500</v>
-      </c>
-      <c r="G38" s="28" t="n">
-        <v>750</v>
+      <c r="F38" s="28" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
@@ -12073,11 +11868,8 @@
           <t>Tier 1 (T1 $25k) - $250</t>
         </is>
       </c>
-      <c r="F39" s="34" t="n">
-        <v>500</v>
-      </c>
-      <c r="G39" s="28" t="n">
-        <v>750</v>
+      <c r="F39" s="28" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
@@ -12102,11 +11894,8 @@
           <t>Tier 1 (T1 $25k) - $250</t>
         </is>
       </c>
-      <c r="F40" s="34" t="n">
-        <v>500</v>
-      </c>
-      <c r="G40" s="28" t="n">
-        <v>750</v>
+      <c r="F40" s="28" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
@@ -12131,11 +11920,8 @@
           <t>Tier 1 (T1 $25k) - $250</t>
         </is>
       </c>
-      <c r="F41" s="34" t="n">
-        <v>500</v>
-      </c>
-      <c r="G41" s="28" t="n">
-        <v>750</v>
+      <c r="F41" s="28" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
@@ -12160,11 +11946,8 @@
           <t>Tier 1 (T1 $25k) - $250</t>
         </is>
       </c>
-      <c r="F42" s="34" t="n">
-        <v>500</v>
-      </c>
-      <c r="G42" s="28" t="n">
-        <v>750</v>
+      <c r="F42" s="28" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
@@ -12189,10 +11972,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F43" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="31" t="n">
+      <c r="F43" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12218,10 +11998,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F44" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="31" t="n">
+      <c r="F44" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12247,10 +12024,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F45" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="31" t="n">
+      <c r="F45" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12276,10 +12050,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F46" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="31" t="n">
+      <c r="F46" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12305,10 +12076,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F47" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="31" t="n">
+      <c r="F47" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12334,10 +12102,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F48" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="31" t="n">
+      <c r="F48" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12363,10 +12128,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F49" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="31" t="n">
+      <c r="F49" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12392,10 +12154,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F50" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="31" t="n">
+      <c r="F50" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12421,10 +12180,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F51" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="31" t="n">
+      <c r="F51" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12450,10 +12206,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F52" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="31" t="n">
+      <c r="F52" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12479,10 +12232,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F53" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="31" t="n">
+      <c r="F53" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12508,10 +12258,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F54" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="31" t="n">
+      <c r="F54" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12537,10 +12284,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F55" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" s="31" t="n">
+      <c r="F55" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12566,10 +12310,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F56" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" s="31" t="n">
+      <c r="F56" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12595,17 +12336,14 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F57" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" s="31" t="n">
+      <c r="F57" s="31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>REN tiers: T1 $25k=$250 | T2 $40k=$350 | T3 $65k=$450 | T4 $80k=$550 | T5 $100k=$800 (above $100k: +$40/$5k). Retention KICKER on top: 30-49%=$0, 50-74%=+$250, 75-99%=+$500, 100%=+$1,000. Model assumes 75% retention -&gt; +$500 kicker per eligible row.</t>
+          <t>REN tiers: T1 $25k=$250 | T2 $40k=$350 | T3 $65k=$450 | T4 $80k=$550 | T5 $100k=$800 | Above $100k: +$40 per $5k. REN gated by 30% retention rate.</t>
         </is>
       </c>
     </row>
@@ -12644,11 +12382,6 @@
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>Retention Kicker (75% assumed)</t>
-        </is>
-      </c>
-      <c r="G61" s="6" t="inlineStr">
-        <is>
           <t>Total Bonus $</t>
         </is>
       </c>
@@ -12675,11 +12408,8 @@
           <t>Tier 4 (T4 $80k) - $550</t>
         </is>
       </c>
-      <c r="F62" s="34" t="n">
-        <v>500</v>
-      </c>
-      <c r="G62" s="28" t="n">
-        <v>1050</v>
+      <c r="F62" s="28" t="n">
+        <v>550</v>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1">
@@ -12704,11 +12434,8 @@
           <t>Tier 4 (T4 $80k) - $550</t>
         </is>
       </c>
-      <c r="F63" s="34" t="n">
-        <v>500</v>
-      </c>
-      <c r="G63" s="28" t="n">
-        <v>1050</v>
+      <c r="F63" s="28" t="n">
+        <v>550</v>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
@@ -12728,16 +12455,13 @@
       <c r="D64" s="26" t="n">
         <v>65675.38</v>
       </c>
-      <c r="E64" s="35" t="inlineStr">
+      <c r="E64" s="33" t="inlineStr">
         <is>
           <t>Tier 3 (T3 $65k) - $450</t>
         </is>
       </c>
-      <c r="F64" s="34" t="n">
-        <v>500</v>
-      </c>
-      <c r="G64" s="28" t="n">
-        <v>950</v>
+      <c r="F64" s="28" t="n">
+        <v>450</v>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1">
@@ -12762,11 +12486,8 @@
           <t>Tier 2 (T2 $40k) - $350</t>
         </is>
       </c>
-      <c r="F65" s="34" t="n">
-        <v>500</v>
-      </c>
-      <c r="G65" s="28" t="n">
-        <v>850</v>
+      <c r="F65" s="28" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
@@ -12791,11 +12512,8 @@
           <t>Tier 2 (T2 $40k) - $350</t>
         </is>
       </c>
-      <c r="F66" s="34" t="n">
-        <v>500</v>
-      </c>
-      <c r="G66" s="28" t="n">
-        <v>850</v>
+      <c r="F66" s="28" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1">
@@ -12820,11 +12538,8 @@
           <t>Tier 2 (T2 $40k) - $350</t>
         </is>
       </c>
-      <c r="F67" s="34" t="n">
-        <v>500</v>
-      </c>
-      <c r="G67" s="28" t="n">
-        <v>850</v>
+      <c r="F67" s="28" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1">
@@ -12849,11 +12564,8 @@
           <t>Tier 2 (T2 $40k) - $350</t>
         </is>
       </c>
-      <c r="F68" s="34" t="n">
-        <v>500</v>
-      </c>
-      <c r="G68" s="28" t="n">
-        <v>850</v>
+      <c r="F68" s="28" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1">
@@ -12878,11 +12590,8 @@
           <t>Tier 2 (T2 $40k) - $350</t>
         </is>
       </c>
-      <c r="F69" s="34" t="n">
-        <v>500</v>
-      </c>
-      <c r="G69" s="28" t="n">
-        <v>850</v>
+      <c r="F69" s="28" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1">
@@ -12907,11 +12616,8 @@
           <t>Tier 2 (T2 $40k) - $350</t>
         </is>
       </c>
-      <c r="F70" s="34" t="n">
-        <v>500</v>
-      </c>
-      <c r="G70" s="28" t="n">
-        <v>850</v>
+      <c r="F70" s="28" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1">
@@ -12936,11 +12642,8 @@
           <t>Tier 2 (T2 $40k) - $350</t>
         </is>
       </c>
-      <c r="F71" s="34" t="n">
-        <v>500</v>
-      </c>
-      <c r="G71" s="28" t="n">
-        <v>850</v>
+      <c r="F71" s="28" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1">
@@ -12965,11 +12668,8 @@
           <t>Tier 2 (T2 $40k) - $350</t>
         </is>
       </c>
-      <c r="F72" s="34" t="n">
-        <v>500</v>
-      </c>
-      <c r="G72" s="28" t="n">
-        <v>850</v>
+      <c r="F72" s="28" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1">
@@ -12994,11 +12694,8 @@
           <t>Tier 1 (T1 $25k) - $250</t>
         </is>
       </c>
-      <c r="F73" s="34" t="n">
-        <v>500</v>
-      </c>
-      <c r="G73" s="28" t="n">
-        <v>750</v>
+      <c r="F73" s="28" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1">
@@ -13023,11 +12720,8 @@
           <t>Tier 1 (T1 $25k) - $250</t>
         </is>
       </c>
-      <c r="F74" s="34" t="n">
-        <v>500</v>
-      </c>
-      <c r="G74" s="28" t="n">
-        <v>750</v>
+      <c r="F74" s="28" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1">
@@ -13052,11 +12746,8 @@
           <t>Tier 1 (T1 $25k) - $250</t>
         </is>
       </c>
-      <c r="F75" s="34" t="n">
-        <v>500</v>
-      </c>
-      <c r="G75" s="28" t="n">
-        <v>750</v>
+      <c r="F75" s="28" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1">
@@ -13081,11 +12772,8 @@
           <t>Tier 1 (T1 $25k) - $250</t>
         </is>
       </c>
-      <c r="F76" s="34" t="n">
-        <v>500</v>
-      </c>
-      <c r="G76" s="28" t="n">
-        <v>750</v>
+      <c r="F76" s="28" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1">
@@ -13110,11 +12798,8 @@
           <t>Tier 1 (T1 $25k) - $250</t>
         </is>
       </c>
-      <c r="F77" s="34" t="n">
-        <v>500</v>
-      </c>
-      <c r="G77" s="28" t="n">
-        <v>750</v>
+      <c r="F77" s="28" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1">
@@ -13139,11 +12824,8 @@
           <t>Tier 1 (T1 $25k) - $250</t>
         </is>
       </c>
-      <c r="F78" s="34" t="n">
-        <v>500</v>
-      </c>
-      <c r="G78" s="28" t="n">
-        <v>750</v>
+      <c r="F78" s="28" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="79" ht="22" customHeight="1">
@@ -13168,11 +12850,8 @@
           <t>Tier 1 (T1 $25k) - $250</t>
         </is>
       </c>
-      <c r="F79" s="34" t="n">
-        <v>500</v>
-      </c>
-      <c r="G79" s="28" t="n">
-        <v>750</v>
+      <c r="F79" s="28" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1">
@@ -13197,11 +12876,8 @@
           <t>Tier 1 (T1 $25k) - $250</t>
         </is>
       </c>
-      <c r="F80" s="34" t="n">
-        <v>500</v>
-      </c>
-      <c r="G80" s="28" t="n">
-        <v>750</v>
+      <c r="F80" s="28" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1">
@@ -13226,11 +12902,8 @@
           <t>Tier 1 (T1 $25k) - $250</t>
         </is>
       </c>
-      <c r="F81" s="34" t="n">
-        <v>500</v>
-      </c>
-      <c r="G81" s="28" t="n">
-        <v>750</v>
+      <c r="F81" s="28" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1">
@@ -13255,11 +12928,8 @@
           <t>Tier 1 (T1 $25k) - $250</t>
         </is>
       </c>
-      <c r="F82" s="34" t="n">
-        <v>500</v>
-      </c>
-      <c r="G82" s="28" t="n">
-        <v>750</v>
+      <c r="F82" s="28" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="83" ht="22" customHeight="1">
@@ -13284,10 +12954,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F83" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" s="31" t="n">
+      <c r="F83" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13313,10 +12980,7 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F84" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" s="31" t="n">
+      <c r="F84" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13342,30 +13006,27 @@
           <t>Below T1 (need $25k REN premium)</t>
         </is>
       </c>
-      <c r="F85" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" s="31" t="n">
+      <c r="F85" s="31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>REN tiers: T1 $25k=$250 | T2 $40k=$350 | T3 $65k=$450 | T4 $80k=$550 | T5 $100k=$800 (above $100k: +$40/$5k). Retention KICKER on top: 30-49%=$0, 50-74%=+$250, 75-99%=+$500, 100%=+$1,000. Model assumes 75% retention -&gt; +$500 kicker per eligible row.</t>
+          <t>REN tiers: T1 $25k=$250 | T2 $40k=$350 | T3 $65k=$450 | T4 $80k=$550 | T5 $100k=$800 | Above $100k: +$40 per $5k. REN gated by 30% retention rate.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A32:G32"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A58:G58"/>
+    <mergeCell ref="A60:F60"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A86:G86"/>
-    <mergeCell ref="A60:G60"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A86:F86"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D29">
     <cfRule type="dataBar" priority="1">
@@ -13429,7 +13090,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Each row = one agent-month. Shows the NB, RWR, and REN bonus side by side and the TOTAL BONUS for the month. REN bonus already includes the assumed +$500 retention kicker (75% rate). Sorted by total bonus descending. Bonus cells that paid are shaded green; red total = nothing paid (NB minimum not met).</t>
+          <t>Each row = one agent-month. Shows the NB, RWR, and REN bonus side by side and the TOTAL BONUS for the month. Sorted by total bonus descending. Bonus cells that paid are shaded green; red total = nothing paid (NB minimum not met).</t>
         </is>
       </c>
     </row>
@@ -13506,25 +13167,25 @@
       <c r="C6" s="16" t="n">
         <v>52434.9</v>
       </c>
-      <c r="D6" s="36" t="n">
+      <c r="D6" s="34" t="n">
         <v>250</v>
       </c>
       <c r="E6" s="16" t="n">
         <v>96228.35000000001</v>
       </c>
-      <c r="F6" s="36" t="n">
+      <c r="F6" s="34" t="n">
         <v>350</v>
       </c>
       <c r="G6" s="16" t="n">
         <v>5962.5</v>
       </c>
-      <c r="H6" s="37" t="n">
+      <c r="H6" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="26" t="n">
         <v>600</v>
       </c>
-      <c r="J6" s="38" t="n">
+      <c r="J6" s="36" t="n">
         <v>600</v>
       </c>
     </row>
@@ -13542,25 +13203,25 @@
       <c r="C7" s="16" t="n">
         <v>49689.35</v>
       </c>
-      <c r="D7" s="36" t="n">
+      <c r="D7" s="34" t="n">
         <v>250</v>
       </c>
       <c r="E7" s="16" t="n">
         <v>64165.43</v>
       </c>
-      <c r="F7" s="36" t="n">
+      <c r="F7" s="34" t="n">
         <v>200</v>
       </c>
       <c r="G7" s="16" t="n">
         <v>19575</v>
       </c>
-      <c r="H7" s="37" t="n">
+      <c r="H7" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="26" t="n">
         <v>450</v>
       </c>
-      <c r="J7" s="38" t="n">
+      <c r="J7" s="36" t="n">
         <v>450</v>
       </c>
     </row>
@@ -13578,25 +13239,25 @@
       <c r="C8" s="16" t="n">
         <v>68546.22</v>
       </c>
-      <c r="D8" s="36" t="n">
+      <c r="D8" s="34" t="n">
         <v>375</v>
       </c>
       <c r="E8" s="16" t="n">
         <v>39254.65</v>
       </c>
-      <c r="F8" s="37" t="n">
+      <c r="F8" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="37" t="n">
+      <c r="H8" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="26" t="n">
         <v>375</v>
       </c>
-      <c r="J8" s="38" t="n">
+      <c r="J8" s="36" t="n">
         <v>375</v>
       </c>
     </row>
@@ -13614,25 +13275,25 @@
       <c r="C9" s="16" t="n">
         <v>46523.37</v>
       </c>
-      <c r="D9" s="36" t="n">
+      <c r="D9" s="34" t="n">
         <v>250</v>
       </c>
       <c r="E9" s="16" t="n">
         <v>25227.6</v>
       </c>
-      <c r="F9" s="37" t="n">
+      <c r="F9" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="16" t="n">
         <v>3901</v>
       </c>
-      <c r="H9" s="37" t="n">
+      <c r="H9" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="26" t="n">
         <v>250</v>
       </c>
-      <c r="J9" s="38" t="n">
+      <c r="J9" s="36" t="n">
         <v>250</v>
       </c>
     </row>
@@ -13650,25 +13311,25 @@
       <c r="C10" s="16" t="n">
         <v>38611.42</v>
       </c>
-      <c r="D10" s="37" t="n">
+      <c r="D10" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="16" t="n">
         <v>27518.5</v>
       </c>
-      <c r="F10" s="37" t="n">
+      <c r="F10" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="16" t="n">
         <v>7605</v>
       </c>
-      <c r="H10" s="37" t="n">
+      <c r="H10" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="39" t="n">
+      <c r="J10" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13686,25 +13347,25 @@
       <c r="C11" s="16" t="n">
         <v>25367</v>
       </c>
-      <c r="D11" s="37" t="n">
+      <c r="D11" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="16" t="n">
         <v>30643</v>
       </c>
-      <c r="F11" s="37" t="n">
+      <c r="F11" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="16" t="n">
         <v>7517</v>
       </c>
-      <c r="H11" s="37" t="n">
+      <c r="H11" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="39" t="n">
+      <c r="J11" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13722,25 +13383,25 @@
       <c r="C12" s="16" t="n">
         <v>37825.93</v>
       </c>
-      <c r="D12" s="37" t="n">
+      <c r="D12" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="16" t="n">
         <v>15361.95</v>
       </c>
-      <c r="F12" s="37" t="n">
+      <c r="F12" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="16" t="n">
         <v>10935.99</v>
       </c>
-      <c r="H12" s="37" t="n">
+      <c r="H12" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="39" t="n">
+      <c r="J12" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13758,25 +13419,25 @@
       <c r="C13" s="16" t="n">
         <v>40249.26</v>
       </c>
-      <c r="D13" s="37" t="n">
+      <c r="D13" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="16" t="n">
         <v>65675.38</v>
       </c>
-      <c r="F13" s="37" t="n">
+      <c r="F13" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="16" t="n">
         <v>12530.47</v>
       </c>
-      <c r="H13" s="37" t="n">
+      <c r="H13" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="39" t="n">
+      <c r="J13" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13794,25 +13455,25 @@
       <c r="C14" s="16" t="n">
         <v>30057.89</v>
       </c>
-      <c r="D14" s="37" t="n">
+      <c r="D14" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="16" t="n">
         <v>85544.60000000001</v>
       </c>
-      <c r="F14" s="37" t="n">
+      <c r="F14" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="16" t="n">
         <v>11629.68</v>
       </c>
-      <c r="H14" s="37" t="n">
+      <c r="H14" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="39" t="n">
+      <c r="J14" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13830,25 +13491,25 @@
       <c r="C15" s="16" t="n">
         <v>37039</v>
       </c>
-      <c r="D15" s="37" t="n">
+      <c r="D15" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="16" t="n">
         <v>63374.5</v>
       </c>
-      <c r="F15" s="37" t="n">
+      <c r="F15" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="37" t="n">
+      <c r="H15" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="39" t="n">
+      <c r="J15" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13866,25 +13527,25 @@
       <c r="C16" s="16" t="n">
         <v>7659.5</v>
       </c>
-      <c r="D16" s="37" t="n">
+      <c r="D16" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="16" t="n">
         <v>49990.7</v>
       </c>
-      <c r="F16" s="37" t="n">
+      <c r="F16" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="16" t="n">
         <v>1063</v>
       </c>
-      <c r="H16" s="37" t="n">
+      <c r="H16" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="39" t="n">
+      <c r="J16" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13902,25 +13563,25 @@
       <c r="C17" s="16" t="n">
         <v>39759.7</v>
       </c>
-      <c r="D17" s="37" t="n">
+      <c r="D17" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="16" t="n">
         <v>56860.6</v>
       </c>
-      <c r="F17" s="37" t="n">
+      <c r="F17" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="16" t="n">
         <v>1034</v>
       </c>
-      <c r="H17" s="37" t="n">
+      <c r="H17" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="39" t="n">
+      <c r="J17" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13938,25 +13599,25 @@
       <c r="C18" s="16" t="n">
         <v>19288.35</v>
       </c>
-      <c r="D18" s="37" t="n">
+      <c r="D18" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="16" t="n">
         <v>43396.2</v>
       </c>
-      <c r="F18" s="37" t="n">
+      <c r="F18" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="37" t="n">
+      <c r="H18" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="39" t="n">
+      <c r="J18" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13974,25 +13635,25 @@
       <c r="C19" s="16" t="n">
         <v>28525.05</v>
       </c>
-      <c r="D19" s="37" t="n">
+      <c r="D19" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="16" t="n">
         <v>39558.05</v>
       </c>
-      <c r="F19" s="37" t="n">
+      <c r="F19" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="16" t="n">
         <v>1464.35</v>
       </c>
-      <c r="H19" s="37" t="n">
+      <c r="H19" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="39" t="n">
+      <c r="J19" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14010,25 +13671,25 @@
       <c r="C20" s="16" t="n">
         <v>22247.7</v>
       </c>
-      <c r="D20" s="37" t="n">
+      <c r="D20" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="16" t="n">
         <v>43687.45</v>
       </c>
-      <c r="F20" s="37" t="n">
+      <c r="F20" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="16" t="n">
         <v>2099</v>
       </c>
-      <c r="H20" s="37" t="n">
+      <c r="H20" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="39" t="n">
+      <c r="J20" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14046,25 +13707,25 @@
       <c r="C21" s="16" t="n">
         <v>31269</v>
       </c>
-      <c r="D21" s="37" t="n">
+      <c r="D21" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="16" t="n">
         <v>23526.7</v>
       </c>
-      <c r="F21" s="37" t="n">
+      <c r="F21" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="37" t="n">
+      <c r="H21" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="39" t="n">
+      <c r="J21" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14082,25 +13743,25 @@
       <c r="C22" s="16" t="n">
         <v>29581.05</v>
       </c>
-      <c r="D22" s="37" t="n">
+      <c r="D22" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="16" t="n">
         <v>30832.76</v>
       </c>
-      <c r="F22" s="37" t="n">
+      <c r="F22" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="16" t="n">
         <v>885</v>
       </c>
-      <c r="H22" s="37" t="n">
+      <c r="H22" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="39" t="n">
+      <c r="J22" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14118,25 +13779,25 @@
       <c r="C23" s="16" t="n">
         <v>15503.9</v>
       </c>
-      <c r="D23" s="37" t="n">
+      <c r="D23" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="16" t="n">
         <v>33083.93</v>
       </c>
-      <c r="F23" s="37" t="n">
+      <c r="F23" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="16" t="n">
         <v>3690</v>
       </c>
-      <c r="H23" s="37" t="n">
+      <c r="H23" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J23" s="39" t="n">
+      <c r="J23" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14154,25 +13815,25 @@
       <c r="C24" s="16" t="n">
         <v>19414.25</v>
       </c>
-      <c r="D24" s="37" t="n">
+      <c r="D24" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="16" t="n">
         <v>28298.16</v>
       </c>
-      <c r="F24" s="37" t="n">
+      <c r="F24" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="16" t="n">
         <v>7446</v>
       </c>
-      <c r="H24" s="37" t="n">
+      <c r="H24" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J24" s="39" t="n">
+      <c r="J24" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14190,25 +13851,25 @@
       <c r="C25" s="16" t="n">
         <v>17843.69</v>
       </c>
-      <c r="D25" s="37" t="n">
+      <c r="D25" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="16" t="n">
         <v>19840.85</v>
       </c>
-      <c r="F25" s="37" t="n">
+      <c r="F25" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="16" t="n">
         <v>5643.9</v>
       </c>
-      <c r="H25" s="37" t="n">
+      <c r="H25" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I25" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="39" t="n">
+      <c r="J25" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14226,25 +13887,25 @@
       <c r="C26" s="16" t="n">
         <v>14099</v>
       </c>
-      <c r="D26" s="37" t="n">
+      <c r="D26" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="16" t="n">
         <v>39794.4</v>
       </c>
-      <c r="F26" s="37" t="n">
+      <c r="F26" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="16" t="n">
         <v>3617</v>
       </c>
-      <c r="H26" s="37" t="n">
+      <c r="H26" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="39" t="n">
+      <c r="J26" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14262,25 +13923,25 @@
       <c r="C27" s="16" t="n">
         <v>28605.29</v>
       </c>
-      <c r="D27" s="37" t="n">
+      <c r="D27" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="16" t="n">
         <v>48612.96</v>
       </c>
-      <c r="F27" s="37" t="n">
+      <c r="F27" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="16" t="n">
         <v>6502.91</v>
       </c>
-      <c r="H27" s="37" t="n">
+      <c r="H27" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="39" t="n">
+      <c r="J27" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14298,25 +13959,25 @@
       <c r="C28" s="16" t="n">
         <v>31516.95</v>
       </c>
-      <c r="D28" s="37" t="n">
+      <c r="D28" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="16" t="n">
         <v>47228.18</v>
       </c>
-      <c r="F28" s="37" t="n">
+      <c r="F28" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="16" t="n">
         <v>3092</v>
       </c>
-      <c r="H28" s="37" t="n">
+      <c r="H28" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="39" t="n">
+      <c r="J28" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14334,43 +13995,43 @@
       <c r="C29" s="16" t="n">
         <v>29755.49</v>
       </c>
-      <c r="D29" s="37" t="n">
+      <c r="D29" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E29" s="16" t="n">
         <v>35279.9</v>
       </c>
-      <c r="F29" s="37" t="n">
+      <c r="F29" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="16" t="n">
         <v>2514</v>
       </c>
-      <c r="H29" s="37" t="n">
+      <c r="H29" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="39" t="n">
+      <c r="J29" s="37" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="40" t="inlineStr">
+      <c r="A30" s="38" t="inlineStr">
         <is>
           <t>4-MONTH TOTAL (all 6 agents)</t>
         </is>
       </c>
-      <c r="B30" s="41" t="n"/>
-      <c r="C30" s="41" t="n"/>
-      <c r="D30" s="41" t="n"/>
-      <c r="E30" s="41" t="n"/>
-      <c r="F30" s="41" t="n"/>
-      <c r="G30" s="41" t="n"/>
-      <c r="H30" s="41" t="n"/>
-      <c r="I30" s="41" t="n"/>
-      <c r="J30" s="42" t="n">
+      <c r="B30" s="39" t="n"/>
+      <c r="C30" s="39" t="n"/>
+      <c r="D30" s="39" t="n"/>
+      <c r="E30" s="39" t="n"/>
+      <c r="F30" s="39" t="n"/>
+      <c r="G30" s="39" t="n"/>
+      <c r="H30" s="39" t="n"/>
+      <c r="I30" s="39" t="n"/>
+      <c r="J30" s="40" t="n">
         <v>1675</v>
       </c>
     </row>
@@ -14447,26 +14108,26 @@
       <c r="C34" s="16" t="n">
         <v>52434.9</v>
       </c>
-      <c r="D34" s="36" t="n">
+      <c r="D34" s="34" t="n">
         <v>250</v>
       </c>
       <c r="E34" s="16" t="n">
         <v>48114.175</v>
       </c>
-      <c r="F34" s="36" t="n">
+      <c r="F34" s="34" t="n">
         <v>100</v>
       </c>
       <c r="G34" s="16" t="n">
         <v>54076.675</v>
       </c>
-      <c r="H34" s="36" t="n">
-        <v>850</v>
+      <c r="H34" s="34" t="n">
+        <v>350</v>
       </c>
       <c r="I34" s="26" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J34" s="38" t="n">
-        <v>1200</v>
+        <v>700</v>
+      </c>
+      <c r="J34" s="36" t="n">
+        <v>700</v>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
@@ -14483,62 +14144,62 @@
       <c r="C35" s="16" t="n">
         <v>49689.35</v>
       </c>
-      <c r="D35" s="36" t="n">
+      <c r="D35" s="34" t="n">
         <v>250</v>
       </c>
       <c r="E35" s="16" t="n">
         <v>32082.715</v>
       </c>
-      <c r="F35" s="37" t="n">
+      <c r="F35" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G35" s="16" t="n">
         <v>51657.715</v>
       </c>
-      <c r="H35" s="36" t="n">
-        <v>850</v>
+      <c r="H35" s="34" t="n">
+        <v>350</v>
       </c>
       <c r="I35" s="26" t="n">
-        <v>1100</v>
-      </c>
-      <c r="J35" s="38" t="n">
-        <v>1100</v>
+        <v>600</v>
+      </c>
+      <c r="J35" s="36" t="n">
+        <v>600</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="25" t="inlineStr">
         <is>
-          <t>Dialinerys Dieguez</t>
+          <t>Monica Valdes</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>January</t>
+          <t>March</t>
         </is>
       </c>
       <c r="C36" s="16" t="n">
-        <v>40249.26</v>
-      </c>
-      <c r="D36" s="37" t="n">
-        <v>0</v>
+        <v>68546.22</v>
+      </c>
+      <c r="D36" s="34" t="n">
+        <v>375</v>
       </c>
       <c r="E36" s="16" t="n">
-        <v>32837.69</v>
-      </c>
-      <c r="F36" s="37" t="n">
+        <v>19627.325</v>
+      </c>
+      <c r="F36" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="16" t="n">
-        <v>45368.16</v>
-      </c>
-      <c r="H36" s="36" t="n">
-        <v>850</v>
+        <v>19627.325</v>
+      </c>
+      <c r="H36" s="35" t="n">
+        <v>0</v>
       </c>
       <c r="I36" s="26" t="n">
-        <v>850</v>
-      </c>
-      <c r="J36" s="38" t="n">
-        <v>850</v>
+        <v>375</v>
+      </c>
+      <c r="J36" s="36" t="n">
+        <v>375</v>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
@@ -14549,104 +14210,104 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>January</t>
         </is>
       </c>
       <c r="C37" s="16" t="n">
-        <v>30057.89</v>
-      </c>
-      <c r="D37" s="37" t="n">
+        <v>40249.26</v>
+      </c>
+      <c r="D37" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E37" s="16" t="n">
-        <v>42772.3</v>
-      </c>
-      <c r="F37" s="37" t="n">
+        <v>32837.69</v>
+      </c>
+      <c r="F37" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="16" t="n">
-        <v>54401.98</v>
-      </c>
-      <c r="H37" s="36" t="n">
-        <v>850</v>
+        <v>45368.16</v>
+      </c>
+      <c r="H37" s="34" t="n">
+        <v>350</v>
       </c>
       <c r="I37" s="26" t="n">
-        <v>850</v>
-      </c>
-      <c r="J37" s="38" t="n">
-        <v>850</v>
+        <v>350</v>
+      </c>
+      <c r="J37" s="36" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="25" t="inlineStr">
         <is>
-          <t>Melissa Hernandez</t>
+          <t>Dialinerys Dieguez</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>January</t>
+          <t>February</t>
         </is>
       </c>
       <c r="C38" s="16" t="n">
-        <v>37039</v>
-      </c>
-      <c r="D38" s="37" t="n">
+        <v>30057.89</v>
+      </c>
+      <c r="D38" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E38" s="16" t="n">
-        <v>31687.25</v>
-      </c>
-      <c r="F38" s="37" t="n">
+        <v>42772.3</v>
+      </c>
+      <c r="F38" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="16" t="n">
-        <v>31687.25</v>
-      </c>
-      <c r="H38" s="36" t="n">
-        <v>750</v>
+        <v>54401.98</v>
+      </c>
+      <c r="H38" s="34" t="n">
+        <v>350</v>
       </c>
       <c r="I38" s="26" t="n">
-        <v>750</v>
-      </c>
-      <c r="J38" s="38" t="n">
-        <v>750</v>
+        <v>350</v>
+      </c>
+      <c r="J38" s="36" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="25" t="inlineStr">
         <is>
-          <t>Melissa Hernandez</t>
+          <t>Abel Guaina</t>
         </is>
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>March</t>
         </is>
       </c>
       <c r="C39" s="16" t="n">
-        <v>7659.5</v>
-      </c>
-      <c r="D39" s="37" t="n">
-        <v>0</v>
+        <v>46523.37</v>
+      </c>
+      <c r="D39" s="34" t="n">
+        <v>250</v>
       </c>
       <c r="E39" s="16" t="n">
-        <v>24995.35</v>
-      </c>
-      <c r="F39" s="37" t="n">
+        <v>12613.8</v>
+      </c>
+      <c r="F39" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G39" s="16" t="n">
-        <v>26058.35</v>
-      </c>
-      <c r="H39" s="36" t="n">
-        <v>750</v>
+        <v>16514.8</v>
+      </c>
+      <c r="H39" s="35" t="n">
+        <v>0</v>
       </c>
       <c r="I39" s="26" t="n">
-        <v>750</v>
-      </c>
-      <c r="J39" s="38" t="n">
-        <v>750</v>
+        <v>250</v>
+      </c>
+      <c r="J39" s="36" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
@@ -14657,104 +14318,104 @@
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>March</t>
+          <t>January</t>
         </is>
       </c>
       <c r="C40" s="16" t="n">
-        <v>39759.7</v>
-      </c>
-      <c r="D40" s="37" t="n">
+        <v>37039</v>
+      </c>
+      <c r="D40" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E40" s="16" t="n">
-        <v>28430.3</v>
-      </c>
-      <c r="F40" s="37" t="n">
+        <v>31687.25</v>
+      </c>
+      <c r="F40" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="16" t="n">
-        <v>29464.3</v>
-      </c>
-      <c r="H40" s="36" t="n">
-        <v>750</v>
+        <v>31687.25</v>
+      </c>
+      <c r="H40" s="34" t="n">
+        <v>250</v>
       </c>
       <c r="I40" s="26" t="n">
-        <v>750</v>
-      </c>
-      <c r="J40" s="38" t="n">
-        <v>750</v>
+        <v>250</v>
+      </c>
+      <c r="J40" s="36" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="25" t="inlineStr">
         <is>
-          <t>Monica Valdes</t>
+          <t>Melissa Hernandez</t>
         </is>
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>January</t>
+          <t>February</t>
         </is>
       </c>
       <c r="C41" s="16" t="n">
-        <v>28605.29</v>
-      </c>
-      <c r="D41" s="37" t="n">
+        <v>7659.5</v>
+      </c>
+      <c r="D41" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E41" s="16" t="n">
-        <v>24306.48</v>
-      </c>
-      <c r="F41" s="37" t="n">
+        <v>24995.35</v>
+      </c>
+      <c r="F41" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G41" s="16" t="n">
-        <v>30809.39</v>
-      </c>
-      <c r="H41" s="36" t="n">
-        <v>750</v>
+        <v>26058.35</v>
+      </c>
+      <c r="H41" s="34" t="n">
+        <v>250</v>
       </c>
       <c r="I41" s="26" t="n">
-        <v>750</v>
-      </c>
-      <c r="J41" s="38" t="n">
-        <v>750</v>
+        <v>250</v>
+      </c>
+      <c r="J41" s="36" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="25" t="inlineStr">
         <is>
-          <t>Monica Valdes</t>
+          <t>Melissa Hernandez</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>March</t>
         </is>
       </c>
       <c r="C42" s="16" t="n">
-        <v>31516.95</v>
-      </c>
-      <c r="D42" s="37" t="n">
+        <v>39759.7</v>
+      </c>
+      <c r="D42" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E42" s="16" t="n">
-        <v>23614.09</v>
-      </c>
-      <c r="F42" s="37" t="n">
+        <v>28430.3</v>
+      </c>
+      <c r="F42" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G42" s="16" t="n">
-        <v>26706.09</v>
-      </c>
-      <c r="H42" s="36" t="n">
-        <v>750</v>
+        <v>29464.3</v>
+      </c>
+      <c r="H42" s="34" t="n">
+        <v>250</v>
       </c>
       <c r="I42" s="26" t="n">
-        <v>750</v>
-      </c>
-      <c r="J42" s="38" t="n">
-        <v>750</v>
+        <v>250</v>
+      </c>
+      <c r="J42" s="36" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
@@ -14765,67 +14426,67 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>March</t>
+          <t>January</t>
         </is>
       </c>
       <c r="C43" s="16" t="n">
-        <v>68546.22</v>
-      </c>
-      <c r="D43" s="36" t="n">
-        <v>375</v>
+        <v>28605.29</v>
+      </c>
+      <c r="D43" s="35" t="n">
+        <v>0</v>
       </c>
       <c r="E43" s="16" t="n">
-        <v>19627.325</v>
-      </c>
-      <c r="F43" s="37" t="n">
+        <v>24306.48</v>
+      </c>
+      <c r="F43" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G43" s="16" t="n">
-        <v>19627.325</v>
-      </c>
-      <c r="H43" s="37" t="n">
-        <v>0</v>
+        <v>30809.39</v>
+      </c>
+      <c r="H43" s="34" t="n">
+        <v>250</v>
       </c>
       <c r="I43" s="26" t="n">
-        <v>375</v>
-      </c>
-      <c r="J43" s="38" t="n">
-        <v>375</v>
+        <v>250</v>
+      </c>
+      <c r="J43" s="36" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="25" t="inlineStr">
         <is>
-          <t>Abel Guaina</t>
+          <t>Monica Valdes</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>March</t>
+          <t>February</t>
         </is>
       </c>
       <c r="C44" s="16" t="n">
-        <v>46523.37</v>
-      </c>
-      <c r="D44" s="36" t="n">
+        <v>31516.95</v>
+      </c>
+      <c r="D44" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="16" t="n">
+        <v>23614.09</v>
+      </c>
+      <c r="F44" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="16" t="n">
+        <v>26706.09</v>
+      </c>
+      <c r="H44" s="34" t="n">
         <v>250</v>
-      </c>
-      <c r="E44" s="16" t="n">
-        <v>12613.8</v>
-      </c>
-      <c r="F44" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="16" t="n">
-        <v>16514.8</v>
-      </c>
-      <c r="H44" s="37" t="n">
-        <v>0</v>
       </c>
       <c r="I44" s="26" t="n">
         <v>250</v>
       </c>
-      <c r="J44" s="38" t="n">
+      <c r="J44" s="36" t="n">
         <v>250</v>
       </c>
     </row>
@@ -14843,25 +14504,25 @@
       <c r="C45" s="16" t="n">
         <v>38611.42</v>
       </c>
-      <c r="D45" s="37" t="n">
+      <c r="D45" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E45" s="16" t="n">
         <v>13759.25</v>
       </c>
-      <c r="F45" s="37" t="n">
+      <c r="F45" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G45" s="16" t="n">
         <v>21364.25</v>
       </c>
-      <c r="H45" s="37" t="n">
+      <c r="H45" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I45" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J45" s="39" t="n">
+      <c r="J45" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14879,25 +14540,25 @@
       <c r="C46" s="16" t="n">
         <v>25367</v>
       </c>
-      <c r="D46" s="37" t="n">
+      <c r="D46" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E46" s="16" t="n">
         <v>15321.5</v>
       </c>
-      <c r="F46" s="37" t="n">
+      <c r="F46" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G46" s="16" t="n">
         <v>22838.5</v>
       </c>
-      <c r="H46" s="37" t="n">
+      <c r="H46" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I46" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J46" s="39" t="n">
+      <c r="J46" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14915,25 +14576,25 @@
       <c r="C47" s="16" t="n">
         <v>37825.93</v>
       </c>
-      <c r="D47" s="37" t="n">
+      <c r="D47" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E47" s="16" t="n">
         <v>7680.975</v>
       </c>
-      <c r="F47" s="37" t="n">
+      <c r="F47" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G47" s="16" t="n">
         <v>18616.965</v>
       </c>
-      <c r="H47" s="37" t="n">
+      <c r="H47" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I47" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J47" s="39" t="n">
+      <c r="J47" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14951,25 +14612,25 @@
       <c r="C48" s="16" t="n">
         <v>19288.35</v>
       </c>
-      <c r="D48" s="37" t="n">
+      <c r="D48" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E48" s="16" t="n">
         <v>21698.1</v>
       </c>
-      <c r="F48" s="37" t="n">
+      <c r="F48" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G48" s="16" t="n">
         <v>21698.1</v>
       </c>
-      <c r="H48" s="37" t="n">
+      <c r="H48" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J48" s="39" t="n">
+      <c r="J48" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14987,25 +14648,25 @@
       <c r="C49" s="16" t="n">
         <v>28525.05</v>
       </c>
-      <c r="D49" s="37" t="n">
+      <c r="D49" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E49" s="16" t="n">
         <v>19779.025</v>
       </c>
-      <c r="F49" s="37" t="n">
+      <c r="F49" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G49" s="16" t="n">
         <v>21243.375</v>
       </c>
-      <c r="H49" s="37" t="n">
+      <c r="H49" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I49" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J49" s="39" t="n">
+      <c r="J49" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15023,25 +14684,25 @@
       <c r="C50" s="16" t="n">
         <v>22247.7</v>
       </c>
-      <c r="D50" s="37" t="n">
+      <c r="D50" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E50" s="16" t="n">
         <v>21843.725</v>
       </c>
-      <c r="F50" s="37" t="n">
+      <c r="F50" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G50" s="16" t="n">
         <v>23942.725</v>
       </c>
-      <c r="H50" s="37" t="n">
+      <c r="H50" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I50" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J50" s="39" t="n">
+      <c r="J50" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15059,25 +14720,25 @@
       <c r="C51" s="16" t="n">
         <v>31269</v>
       </c>
-      <c r="D51" s="37" t="n">
+      <c r="D51" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E51" s="16" t="n">
         <v>11763.35</v>
       </c>
-      <c r="F51" s="37" t="n">
+      <c r="F51" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G51" s="16" t="n">
         <v>11763.35</v>
       </c>
-      <c r="H51" s="37" t="n">
+      <c r="H51" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I51" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J51" s="39" t="n">
+      <c r="J51" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15095,25 +14756,25 @@
       <c r="C52" s="16" t="n">
         <v>29581.05</v>
       </c>
-      <c r="D52" s="37" t="n">
+      <c r="D52" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E52" s="16" t="n">
         <v>15416.38</v>
       </c>
-      <c r="F52" s="37" t="n">
+      <c r="F52" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G52" s="16" t="n">
         <v>16301.38</v>
       </c>
-      <c r="H52" s="37" t="n">
+      <c r="H52" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I52" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J52" s="39" t="n">
+      <c r="J52" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15131,25 +14792,25 @@
       <c r="C53" s="16" t="n">
         <v>15503.9</v>
       </c>
-      <c r="D53" s="37" t="n">
+      <c r="D53" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E53" s="16" t="n">
         <v>16541.965</v>
       </c>
-      <c r="F53" s="37" t="n">
+      <c r="F53" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G53" s="16" t="n">
         <v>20231.965</v>
       </c>
-      <c r="H53" s="37" t="n">
+      <c r="H53" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J53" s="39" t="n">
+      <c r="J53" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15167,25 +14828,25 @@
       <c r="C54" s="16" t="n">
         <v>19414.25</v>
       </c>
-      <c r="D54" s="37" t="n">
+      <c r="D54" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E54" s="16" t="n">
         <v>14149.08</v>
       </c>
-      <c r="F54" s="37" t="n">
+      <c r="F54" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G54" s="16" t="n">
         <v>21595.08</v>
       </c>
-      <c r="H54" s="37" t="n">
+      <c r="H54" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I54" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J54" s="39" t="n">
+      <c r="J54" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15203,25 +14864,25 @@
       <c r="C55" s="16" t="n">
         <v>17843.69</v>
       </c>
-      <c r="D55" s="37" t="n">
+      <c r="D55" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E55" s="16" t="n">
         <v>9920.424999999999</v>
       </c>
-      <c r="F55" s="37" t="n">
+      <c r="F55" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G55" s="16" t="n">
         <v>15564.325</v>
       </c>
-      <c r="H55" s="37" t="n">
+      <c r="H55" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I55" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J55" s="39" t="n">
+      <c r="J55" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15239,25 +14900,25 @@
       <c r="C56" s="16" t="n">
         <v>14099</v>
       </c>
-      <c r="D56" s="37" t="n">
+      <c r="D56" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E56" s="16" t="n">
         <v>19897.2</v>
       </c>
-      <c r="F56" s="37" t="n">
+      <c r="F56" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G56" s="16" t="n">
         <v>23514.2</v>
       </c>
-      <c r="H56" s="37" t="n">
+      <c r="H56" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J56" s="39" t="n">
+      <c r="J56" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15275,44 +14936,44 @@
       <c r="C57" s="16" t="n">
         <v>29755.49</v>
       </c>
-      <c r="D57" s="37" t="n">
+      <c r="D57" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E57" s="16" t="n">
         <v>17639.95</v>
       </c>
-      <c r="F57" s="37" t="n">
+      <c r="F57" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G57" s="16" t="n">
         <v>20153.95</v>
       </c>
-      <c r="H57" s="37" t="n">
+      <c r="H57" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I57" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J57" s="39" t="n">
+      <c r="J57" s="37" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="58" ht="26" customHeight="1">
-      <c r="A58" s="40" t="inlineStr">
+      <c r="A58" s="38" t="inlineStr">
         <is>
           <t>4-MONTH TOTAL (all 6 agents)</t>
         </is>
       </c>
-      <c r="B58" s="41" t="n"/>
-      <c r="C58" s="41" t="n"/>
-      <c r="D58" s="41" t="n"/>
-      <c r="E58" s="41" t="n"/>
-      <c r="F58" s="41" t="n"/>
-      <c r="G58" s="41" t="n"/>
-      <c r="H58" s="41" t="n"/>
-      <c r="I58" s="41" t="n"/>
-      <c r="J58" s="42" t="n">
-        <v>8375</v>
+      <c r="B58" s="39" t="n"/>
+      <c r="C58" s="39" t="n"/>
+      <c r="D58" s="39" t="n"/>
+      <c r="E58" s="39" t="n"/>
+      <c r="F58" s="39" t="n"/>
+      <c r="G58" s="39" t="n"/>
+      <c r="H58" s="39" t="n"/>
+      <c r="I58" s="39" t="n"/>
+      <c r="J58" s="40" t="n">
+        <v>3875</v>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1">
@@ -15388,26 +15049,26 @@
       <c r="C62" s="16" t="n">
         <v>52434.9</v>
       </c>
-      <c r="D62" s="36" t="n">
+      <c r="D62" s="34" t="n">
         <v>250</v>
       </c>
       <c r="E62" s="16" t="n">
         <v>5962.5</v>
       </c>
-      <c r="F62" s="37" t="n">
+      <c r="F62" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G62" s="16" t="n">
         <v>96228.35000000001</v>
       </c>
-      <c r="H62" s="36" t="n">
-        <v>1050</v>
+      <c r="H62" s="34" t="n">
+        <v>550</v>
       </c>
       <c r="I62" s="26" t="n">
-        <v>1300</v>
-      </c>
-      <c r="J62" s="38" t="n">
-        <v>1300</v>
+        <v>800</v>
+      </c>
+      <c r="J62" s="36" t="n">
+        <v>800</v>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1">
@@ -15424,26 +15085,26 @@
       <c r="C63" s="16" t="n">
         <v>68546.22</v>
       </c>
-      <c r="D63" s="36" t="n">
+      <c r="D63" s="34" t="n">
         <v>375</v>
       </c>
       <c r="E63" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="F63" s="37" t="n">
+      <c r="F63" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G63" s="16" t="n">
         <v>39254.65</v>
       </c>
-      <c r="H63" s="36" t="n">
-        <v>750</v>
+      <c r="H63" s="34" t="n">
+        <v>250</v>
       </c>
       <c r="I63" s="26" t="n">
-        <v>1125</v>
-      </c>
-      <c r="J63" s="38" t="n">
-        <v>1125</v>
+        <v>625</v>
+      </c>
+      <c r="J63" s="36" t="n">
+        <v>625</v>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
@@ -15460,26 +15121,26 @@
       <c r="C64" s="16" t="n">
         <v>49689.35</v>
       </c>
-      <c r="D64" s="36" t="n">
+      <c r="D64" s="34" t="n">
         <v>250</v>
       </c>
       <c r="E64" s="16" t="n">
         <v>19575</v>
       </c>
-      <c r="F64" s="37" t="n">
+      <c r="F64" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G64" s="16" t="n">
         <v>64165.43</v>
       </c>
-      <c r="H64" s="36" t="n">
-        <v>850</v>
+      <c r="H64" s="34" t="n">
+        <v>350</v>
       </c>
       <c r="I64" s="26" t="n">
-        <v>1100</v>
-      </c>
-      <c r="J64" s="38" t="n">
-        <v>1100</v>
+        <v>600</v>
+      </c>
+      <c r="J64" s="36" t="n">
+        <v>600</v>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1">
@@ -15496,26 +15157,26 @@
       <c r="C65" s="16" t="n">
         <v>30057.89</v>
       </c>
-      <c r="D65" s="37" t="n">
+      <c r="D65" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E65" s="16" t="n">
         <v>11629.68</v>
       </c>
-      <c r="F65" s="37" t="n">
+      <c r="F65" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G65" s="16" t="n">
         <v>85544.60000000001</v>
       </c>
-      <c r="H65" s="36" t="n">
-        <v>1050</v>
+      <c r="H65" s="34" t="n">
+        <v>550</v>
       </c>
       <c r="I65" s="26" t="n">
-        <v>1050</v>
-      </c>
-      <c r="J65" s="38" t="n">
-        <v>1050</v>
+        <v>550</v>
+      </c>
+      <c r="J65" s="36" t="n">
+        <v>550</v>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
@@ -15532,26 +15193,26 @@
       <c r="C66" s="16" t="n">
         <v>46523.37</v>
       </c>
-      <c r="D66" s="36" t="n">
+      <c r="D66" s="34" t="n">
         <v>250</v>
       </c>
       <c r="E66" s="16" t="n">
         <v>3901</v>
       </c>
-      <c r="F66" s="37" t="n">
+      <c r="F66" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G66" s="16" t="n">
         <v>25227.6</v>
       </c>
-      <c r="H66" s="36" t="n">
-        <v>750</v>
+      <c r="H66" s="34" t="n">
+        <v>250</v>
       </c>
       <c r="I66" s="26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J66" s="38" t="n">
-        <v>1000</v>
+        <v>500</v>
+      </c>
+      <c r="J66" s="36" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1">
@@ -15568,26 +15229,26 @@
       <c r="C67" s="16" t="n">
         <v>40249.26</v>
       </c>
-      <c r="D67" s="37" t="n">
+      <c r="D67" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E67" s="16" t="n">
         <v>12530.47</v>
       </c>
-      <c r="F67" s="37" t="n">
+      <c r="F67" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G67" s="16" t="n">
         <v>65675.38</v>
       </c>
-      <c r="H67" s="36" t="n">
-        <v>950</v>
+      <c r="H67" s="34" t="n">
+        <v>450</v>
       </c>
       <c r="I67" s="26" t="n">
-        <v>950</v>
-      </c>
-      <c r="J67" s="38" t="n">
-        <v>950</v>
+        <v>450</v>
+      </c>
+      <c r="J67" s="36" t="n">
+        <v>450</v>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1">
@@ -15604,26 +15265,26 @@
       <c r="C68" s="16" t="n">
         <v>37039</v>
       </c>
-      <c r="D68" s="37" t="n">
+      <c r="D68" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E68" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="F68" s="37" t="n">
+      <c r="F68" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G68" s="16" t="n">
         <v>63374.5</v>
       </c>
-      <c r="H68" s="36" t="n">
-        <v>850</v>
+      <c r="H68" s="34" t="n">
+        <v>350</v>
       </c>
       <c r="I68" s="26" t="n">
-        <v>850</v>
-      </c>
-      <c r="J68" s="38" t="n">
-        <v>850</v>
+        <v>350</v>
+      </c>
+      <c r="J68" s="36" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1">
@@ -15640,26 +15301,26 @@
       <c r="C69" s="16" t="n">
         <v>7659.5</v>
       </c>
-      <c r="D69" s="37" t="n">
+      <c r="D69" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E69" s="16" t="n">
         <v>1063</v>
       </c>
-      <c r="F69" s="37" t="n">
+      <c r="F69" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G69" s="16" t="n">
         <v>49990.7</v>
       </c>
-      <c r="H69" s="36" t="n">
-        <v>850</v>
+      <c r="H69" s="34" t="n">
+        <v>350</v>
       </c>
       <c r="I69" s="26" t="n">
-        <v>850</v>
-      </c>
-      <c r="J69" s="38" t="n">
-        <v>850</v>
+        <v>350</v>
+      </c>
+      <c r="J69" s="36" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1">
@@ -15676,26 +15337,26 @@
       <c r="C70" s="16" t="n">
         <v>39759.7</v>
       </c>
-      <c r="D70" s="37" t="n">
+      <c r="D70" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E70" s="16" t="n">
         <v>1034</v>
       </c>
-      <c r="F70" s="37" t="n">
+      <c r="F70" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G70" s="16" t="n">
         <v>56860.6</v>
       </c>
-      <c r="H70" s="36" t="n">
-        <v>850</v>
+      <c r="H70" s="34" t="n">
+        <v>350</v>
       </c>
       <c r="I70" s="26" t="n">
-        <v>850</v>
-      </c>
-      <c r="J70" s="38" t="n">
-        <v>850</v>
+        <v>350</v>
+      </c>
+      <c r="J70" s="36" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1">
@@ -15712,26 +15373,26 @@
       <c r="C71" s="16" t="n">
         <v>19288.35</v>
       </c>
-      <c r="D71" s="37" t="n">
+      <c r="D71" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E71" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="F71" s="37" t="n">
+      <c r="F71" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G71" s="16" t="n">
         <v>43396.2</v>
       </c>
-      <c r="H71" s="36" t="n">
-        <v>850</v>
+      <c r="H71" s="34" t="n">
+        <v>350</v>
       </c>
       <c r="I71" s="26" t="n">
-        <v>850</v>
-      </c>
-      <c r="J71" s="38" t="n">
-        <v>850</v>
+        <v>350</v>
+      </c>
+      <c r="J71" s="36" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1">
@@ -15748,26 +15409,26 @@
       <c r="C72" s="16" t="n">
         <v>22247.7</v>
       </c>
-      <c r="D72" s="37" t="n">
+      <c r="D72" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E72" s="16" t="n">
         <v>2099</v>
       </c>
-      <c r="F72" s="37" t="n">
+      <c r="F72" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G72" s="16" t="n">
         <v>43687.45</v>
       </c>
-      <c r="H72" s="36" t="n">
-        <v>850</v>
+      <c r="H72" s="34" t="n">
+        <v>350</v>
       </c>
       <c r="I72" s="26" t="n">
-        <v>850</v>
-      </c>
-      <c r="J72" s="38" t="n">
-        <v>850</v>
+        <v>350</v>
+      </c>
+      <c r="J72" s="36" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1">
@@ -15784,26 +15445,26 @@
       <c r="C73" s="16" t="n">
         <v>28605.29</v>
       </c>
-      <c r="D73" s="37" t="n">
+      <c r="D73" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E73" s="16" t="n">
         <v>6502.91</v>
       </c>
-      <c r="F73" s="37" t="n">
+      <c r="F73" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G73" s="16" t="n">
         <v>48612.96</v>
       </c>
-      <c r="H73" s="36" t="n">
-        <v>850</v>
+      <c r="H73" s="34" t="n">
+        <v>350</v>
       </c>
       <c r="I73" s="26" t="n">
-        <v>850</v>
-      </c>
-      <c r="J73" s="38" t="n">
-        <v>850</v>
+        <v>350</v>
+      </c>
+      <c r="J73" s="36" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1">
@@ -15820,26 +15481,26 @@
       <c r="C74" s="16" t="n">
         <v>31516.95</v>
       </c>
-      <c r="D74" s="37" t="n">
+      <c r="D74" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E74" s="16" t="n">
         <v>3092</v>
       </c>
-      <c r="F74" s="37" t="n">
+      <c r="F74" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G74" s="16" t="n">
         <v>47228.18</v>
       </c>
-      <c r="H74" s="36" t="n">
-        <v>850</v>
+      <c r="H74" s="34" t="n">
+        <v>350</v>
       </c>
       <c r="I74" s="26" t="n">
-        <v>850</v>
-      </c>
-      <c r="J74" s="38" t="n">
-        <v>850</v>
+        <v>350</v>
+      </c>
+      <c r="J74" s="36" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1">
@@ -15856,26 +15517,26 @@
       <c r="C75" s="16" t="n">
         <v>38611.42</v>
       </c>
-      <c r="D75" s="37" t="n">
+      <c r="D75" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E75" s="16" t="n">
         <v>7605</v>
       </c>
-      <c r="F75" s="37" t="n">
+      <c r="F75" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G75" s="16" t="n">
         <v>27518.5</v>
       </c>
-      <c r="H75" s="36" t="n">
-        <v>750</v>
+      <c r="H75" s="34" t="n">
+        <v>250</v>
       </c>
       <c r="I75" s="26" t="n">
-        <v>750</v>
-      </c>
-      <c r="J75" s="38" t="n">
-        <v>750</v>
+        <v>250</v>
+      </c>
+      <c r="J75" s="36" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1">
@@ -15892,26 +15553,26 @@
       <c r="C76" s="16" t="n">
         <v>25367</v>
       </c>
-      <c r="D76" s="37" t="n">
+      <c r="D76" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E76" s="16" t="n">
         <v>7517</v>
       </c>
-      <c r="F76" s="37" t="n">
+      <c r="F76" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G76" s="16" t="n">
         <v>30643</v>
       </c>
-      <c r="H76" s="36" t="n">
-        <v>750</v>
+      <c r="H76" s="34" t="n">
+        <v>250</v>
       </c>
       <c r="I76" s="26" t="n">
-        <v>750</v>
-      </c>
-      <c r="J76" s="38" t="n">
-        <v>750</v>
+        <v>250</v>
+      </c>
+      <c r="J76" s="36" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1">
@@ -15928,26 +15589,26 @@
       <c r="C77" s="16" t="n">
         <v>28525.05</v>
       </c>
-      <c r="D77" s="37" t="n">
+      <c r="D77" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E77" s="16" t="n">
         <v>1464.35</v>
       </c>
-      <c r="F77" s="37" t="n">
+      <c r="F77" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G77" s="16" t="n">
         <v>39558.05</v>
       </c>
-      <c r="H77" s="36" t="n">
-        <v>750</v>
+      <c r="H77" s="34" t="n">
+        <v>250</v>
       </c>
       <c r="I77" s="26" t="n">
-        <v>750</v>
-      </c>
-      <c r="J77" s="38" t="n">
-        <v>750</v>
+        <v>250</v>
+      </c>
+      <c r="J77" s="36" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1">
@@ -15964,26 +15625,26 @@
       <c r="C78" s="16" t="n">
         <v>29581.05</v>
       </c>
-      <c r="D78" s="37" t="n">
+      <c r="D78" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E78" s="16" t="n">
         <v>885</v>
       </c>
-      <c r="F78" s="37" t="n">
+      <c r="F78" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G78" s="16" t="n">
         <v>30832.76</v>
       </c>
-      <c r="H78" s="36" t="n">
-        <v>750</v>
+      <c r="H78" s="34" t="n">
+        <v>250</v>
       </c>
       <c r="I78" s="26" t="n">
-        <v>750</v>
-      </c>
-      <c r="J78" s="38" t="n">
-        <v>750</v>
+        <v>250</v>
+      </c>
+      <c r="J78" s="36" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="79" ht="22" customHeight="1">
@@ -16000,26 +15661,26 @@
       <c r="C79" s="16" t="n">
         <v>15503.9</v>
       </c>
-      <c r="D79" s="37" t="n">
+      <c r="D79" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E79" s="16" t="n">
         <v>3690</v>
       </c>
-      <c r="F79" s="37" t="n">
+      <c r="F79" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G79" s="16" t="n">
         <v>33083.93</v>
       </c>
-      <c r="H79" s="36" t="n">
-        <v>750</v>
+      <c r="H79" s="34" t="n">
+        <v>250</v>
       </c>
       <c r="I79" s="26" t="n">
-        <v>750</v>
-      </c>
-      <c r="J79" s="38" t="n">
-        <v>750</v>
+        <v>250</v>
+      </c>
+      <c r="J79" s="36" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1">
@@ -16036,26 +15697,26 @@
       <c r="C80" s="16" t="n">
         <v>19414.25</v>
       </c>
-      <c r="D80" s="37" t="n">
+      <c r="D80" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E80" s="16" t="n">
         <v>7446</v>
       </c>
-      <c r="F80" s="37" t="n">
+      <c r="F80" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G80" s="16" t="n">
         <v>28298.16</v>
       </c>
-      <c r="H80" s="36" t="n">
-        <v>750</v>
+      <c r="H80" s="34" t="n">
+        <v>250</v>
       </c>
       <c r="I80" s="26" t="n">
-        <v>750</v>
-      </c>
-      <c r="J80" s="38" t="n">
-        <v>750</v>
+        <v>250</v>
+      </c>
+      <c r="J80" s="36" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1">
@@ -16072,26 +15733,26 @@
       <c r="C81" s="16" t="n">
         <v>14099</v>
       </c>
-      <c r="D81" s="37" t="n">
+      <c r="D81" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E81" s="16" t="n">
         <v>3617</v>
       </c>
-      <c r="F81" s="37" t="n">
+      <c r="F81" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G81" s="16" t="n">
         <v>39794.4</v>
       </c>
-      <c r="H81" s="36" t="n">
-        <v>750</v>
+      <c r="H81" s="34" t="n">
+        <v>250</v>
       </c>
       <c r="I81" s="26" t="n">
-        <v>750</v>
-      </c>
-      <c r="J81" s="38" t="n">
-        <v>750</v>
+        <v>250</v>
+      </c>
+      <c r="J81" s="36" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1">
@@ -16108,26 +15769,26 @@
       <c r="C82" s="16" t="n">
         <v>29755.49</v>
       </c>
-      <c r="D82" s="37" t="n">
+      <c r="D82" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E82" s="16" t="n">
         <v>2514</v>
       </c>
-      <c r="F82" s="37" t="n">
+      <c r="F82" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G82" s="16" t="n">
         <v>35279.9</v>
       </c>
-      <c r="H82" s="36" t="n">
-        <v>750</v>
+      <c r="H82" s="34" t="n">
+        <v>250</v>
       </c>
       <c r="I82" s="26" t="n">
-        <v>750</v>
-      </c>
-      <c r="J82" s="38" t="n">
-        <v>750</v>
+        <v>250</v>
+      </c>
+      <c r="J82" s="36" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="83" ht="22" customHeight="1">
@@ -16144,25 +15805,25 @@
       <c r="C83" s="16" t="n">
         <v>37825.93</v>
       </c>
-      <c r="D83" s="37" t="n">
+      <c r="D83" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E83" s="16" t="n">
         <v>10935.99</v>
       </c>
-      <c r="F83" s="37" t="n">
+      <c r="F83" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G83" s="16" t="n">
         <v>15361.95</v>
       </c>
-      <c r="H83" s="37" t="n">
+      <c r="H83" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I83" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J83" s="39" t="n">
+      <c r="J83" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16180,25 +15841,25 @@
       <c r="C84" s="16" t="n">
         <v>31269</v>
       </c>
-      <c r="D84" s="37" t="n">
+      <c r="D84" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E84" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="F84" s="37" t="n">
+      <c r="F84" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G84" s="16" t="n">
         <v>23526.7</v>
       </c>
-      <c r="H84" s="37" t="n">
+      <c r="H84" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I84" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J84" s="39" t="n">
+      <c r="J84" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16216,44 +15877,44 @@
       <c r="C85" s="16" t="n">
         <v>17843.69</v>
       </c>
-      <c r="D85" s="37" t="n">
+      <c r="D85" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E85" s="16" t="n">
         <v>5643.9</v>
       </c>
-      <c r="F85" s="37" t="n">
+      <c r="F85" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G85" s="16" t="n">
         <v>19840.85</v>
       </c>
-      <c r="H85" s="37" t="n">
+      <c r="H85" s="35" t="n">
         <v>0</v>
       </c>
       <c r="I85" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J85" s="39" t="n">
+      <c r="J85" s="37" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="86" ht="26" customHeight="1">
-      <c r="A86" s="40" t="inlineStr">
+      <c r="A86" s="38" t="inlineStr">
         <is>
           <t>4-MONTH TOTAL (all 6 agents)</t>
         </is>
       </c>
-      <c r="B86" s="41" t="n"/>
-      <c r="C86" s="41" t="n"/>
-      <c r="D86" s="41" t="n"/>
-      <c r="E86" s="41" t="n"/>
-      <c r="F86" s="41" t="n"/>
-      <c r="G86" s="41" t="n"/>
-      <c r="H86" s="41" t="n"/>
-      <c r="I86" s="41" t="n"/>
-      <c r="J86" s="42" t="n">
-        <v>18475</v>
+      <c r="B86" s="39" t="n"/>
+      <c r="C86" s="39" t="n"/>
+      <c r="D86" s="39" t="n"/>
+      <c r="E86" s="39" t="n"/>
+      <c r="F86" s="39" t="n"/>
+      <c r="G86" s="39" t="n"/>
+      <c r="H86" s="39" t="n"/>
+      <c r="I86" s="39" t="n"/>
+      <c r="J86" s="40" t="n">
+        <v>7975</v>
       </c>
     </row>
   </sheetData>
@@ -16330,7 +15991,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>CURRENT = today's plan: count NB+RWR policies, 30/38/50 tier -&gt; $250/$350/$450 + $10/policy above 50. NEW = the new tier-based plan (NB + RWR + REN combined, REN bonus already includes the assumed +$500 retention kicker at 75%). Sorted by DELTA descending: biggest winners on top, biggest losses at the bottom.</t>
+          <t>CURRENT = today's plan: count NB+RWR policies, 30/38/50 tier -&gt; $250/$350/$450 + $10/policy above 50. NEW = the new tier-based plan (NB + RWR + REN combined). Sorted by DELTA descending: biggest winners on top, biggest losses at the bottom.</t>
         </is>
       </c>
     </row>
@@ -16442,22 +16103,22 @@
       <c r="H6" s="16" t="n">
         <v>3901</v>
       </c>
-      <c r="I6" s="43" t="n">
+      <c r="I6" s="41" t="n">
         <v>350</v>
       </c>
-      <c r="J6" s="36" t="n">
+      <c r="J6" s="34" t="n">
         <v>250</v>
       </c>
-      <c r="K6" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="44" t="n">
+      <c r="K6" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="42" t="n">
         <v>250</v>
       </c>
-      <c r="N6" s="45" t="n">
+      <c r="N6" s="43" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -16490,22 +16151,22 @@
       <c r="H7" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="43" t="n">
+      <c r="I7" s="41" t="n">
         <v>590</v>
       </c>
-      <c r="J7" s="36" t="n">
+      <c r="J7" s="34" t="n">
         <v>375</v>
       </c>
-      <c r="K7" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="44" t="n">
+      <c r="K7" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="42" t="n">
         <v>375</v>
       </c>
-      <c r="N7" s="45" t="n">
+      <c r="N7" s="43" t="n">
         <v>-215</v>
       </c>
     </row>
@@ -16538,22 +16199,22 @@
       <c r="H8" s="16" t="n">
         <v>7517</v>
       </c>
-      <c r="I8" s="43" t="n">
+      <c r="I8" s="41" t="n">
         <v>250</v>
       </c>
-      <c r="J8" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="45" t="n">
+      <c r="J8" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="43" t="n">
         <v>-250</v>
       </c>
     </row>
@@ -16586,22 +16247,22 @@
       <c r="H9" s="16" t="n">
         <v>19575</v>
       </c>
-      <c r="I9" s="43" t="n">
+      <c r="I9" s="41" t="n">
         <v>720</v>
       </c>
-      <c r="J9" s="36" t="n">
+      <c r="J9" s="34" t="n">
         <v>250</v>
       </c>
-      <c r="K9" s="36" t="n">
+      <c r="K9" s="34" t="n">
         <v>200</v>
       </c>
-      <c r="L9" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="44" t="n">
+      <c r="L9" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="42" t="n">
         <v>450</v>
       </c>
-      <c r="N9" s="45" t="n">
+      <c r="N9" s="43" t="n">
         <v>-270</v>
       </c>
     </row>
@@ -16634,22 +16295,22 @@
       <c r="H10" s="16" t="n">
         <v>7605</v>
       </c>
-      <c r="I10" s="43" t="n">
+      <c r="I10" s="41" t="n">
         <v>350</v>
       </c>
-      <c r="J10" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="45" t="n">
+      <c r="J10" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="43" t="n">
         <v>-350</v>
       </c>
     </row>
@@ -16682,22 +16343,22 @@
       <c r="H11" s="16" t="n">
         <v>10935.99</v>
       </c>
-      <c r="I11" s="43" t="n">
+      <c r="I11" s="41" t="n">
         <v>350</v>
       </c>
-      <c r="J11" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="45" t="n">
+      <c r="J11" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="43" t="n">
         <v>-350</v>
       </c>
     </row>
@@ -16730,22 +16391,22 @@
       <c r="H12" s="16" t="n">
         <v>3690</v>
       </c>
-      <c r="I12" s="43" t="n">
+      <c r="I12" s="41" t="n">
         <v>350</v>
       </c>
-      <c r="J12" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="45" t="n">
+      <c r="J12" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="43" t="n">
         <v>-350</v>
       </c>
     </row>
@@ -16778,22 +16439,22 @@
       <c r="H13" s="16" t="n">
         <v>7446</v>
       </c>
-      <c r="I13" s="43" t="n">
+      <c r="I13" s="41" t="n">
         <v>350</v>
       </c>
-      <c r="J13" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="45" t="n">
+      <c r="J13" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="43" t="n">
         <v>-350</v>
       </c>
     </row>
@@ -16826,22 +16487,22 @@
       <c r="H14" s="16" t="n">
         <v>5643.9</v>
       </c>
-      <c r="I14" s="43" t="n">
+      <c r="I14" s="41" t="n">
         <v>350</v>
       </c>
-      <c r="J14" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="45" t="n">
+      <c r="J14" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="43" t="n">
         <v>-350</v>
       </c>
     </row>
@@ -16874,22 +16535,22 @@
       <c r="H15" s="16" t="n">
         <v>3617</v>
       </c>
-      <c r="I15" s="43" t="n">
+      <c r="I15" s="41" t="n">
         <v>350</v>
       </c>
-      <c r="J15" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="45" t="n">
+      <c r="J15" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="43" t="n">
         <v>-350</v>
       </c>
     </row>
@@ -16922,22 +16583,22 @@
       <c r="H16" s="16" t="n">
         <v>2514</v>
       </c>
-      <c r="I16" s="43" t="n">
+      <c r="I16" s="41" t="n">
         <v>350</v>
       </c>
-      <c r="J16" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="45" t="n">
+      <c r="J16" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="43" t="n">
         <v>-350</v>
       </c>
     </row>
@@ -16970,22 +16631,22 @@
       <c r="H17" s="16" t="n">
         <v>5962.5</v>
       </c>
-      <c r="I17" s="43" t="n">
+      <c r="I17" s="41" t="n">
         <v>1020</v>
       </c>
-      <c r="J17" s="36" t="n">
+      <c r="J17" s="34" t="n">
         <v>250</v>
       </c>
-      <c r="K17" s="36" t="n">
+      <c r="K17" s="34" t="n">
         <v>350</v>
       </c>
-      <c r="L17" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="44" t="n">
+      <c r="L17" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="42" t="n">
         <v>600</v>
       </c>
-      <c r="N17" s="45" t="n">
+      <c r="N17" s="43" t="n">
         <v>-420</v>
       </c>
     </row>
@@ -17018,22 +16679,22 @@
       <c r="H18" s="16" t="n">
         <v>1063</v>
       </c>
-      <c r="I18" s="43" t="n">
+      <c r="I18" s="41" t="n">
         <v>450</v>
       </c>
-      <c r="J18" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="45" t="n">
+      <c r="J18" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="43" t="n">
         <v>-450</v>
       </c>
     </row>
@@ -17066,22 +16727,22 @@
       <c r="H19" s="16" t="n">
         <v>3092</v>
       </c>
-      <c r="I19" s="43" t="n">
+      <c r="I19" s="41" t="n">
         <v>450</v>
       </c>
-      <c r="J19" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="45" t="n">
+      <c r="J19" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="43" t="n">
         <v>-450</v>
       </c>
     </row>
@@ -17114,22 +16775,22 @@
       <c r="H20" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="43" t="n">
+      <c r="I20" s="41" t="n">
         <v>470</v>
       </c>
-      <c r="J20" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="45" t="n">
+      <c r="J20" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="43" t="n">
         <v>-470</v>
       </c>
     </row>
@@ -17162,22 +16823,22 @@
       <c r="H21" s="16" t="n">
         <v>1464.35</v>
       </c>
-      <c r="I21" s="43" t="n">
+      <c r="I21" s="41" t="n">
         <v>490</v>
       </c>
-      <c r="J21" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="45" t="n">
+      <c r="J21" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="43" t="n">
         <v>-490</v>
       </c>
     </row>
@@ -17210,22 +16871,22 @@
       <c r="H22" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="I22" s="43" t="n">
+      <c r="I22" s="41" t="n">
         <v>490</v>
       </c>
-      <c r="J22" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="45" t="n">
+      <c r="J22" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="43" t="n">
         <v>-490</v>
       </c>
     </row>
@@ -17258,22 +16919,22 @@
       <c r="H23" s="16" t="n">
         <v>885</v>
       </c>
-      <c r="I23" s="43" t="n">
+      <c r="I23" s="41" t="n">
         <v>490</v>
       </c>
-      <c r="J23" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="45" t="n">
+      <c r="J23" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="43" t="n">
         <v>-490</v>
       </c>
     </row>
@@ -17306,22 +16967,22 @@
       <c r="H24" s="16" t="n">
         <v>6502.91</v>
       </c>
-      <c r="I24" s="43" t="n">
+      <c r="I24" s="41" t="n">
         <v>550</v>
       </c>
-      <c r="J24" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="45" t="n">
+      <c r="J24" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="43" t="n">
         <v>-550</v>
       </c>
     </row>
@@ -17354,22 +17015,22 @@
       <c r="H25" s="16" t="n">
         <v>2099</v>
       </c>
-      <c r="I25" s="43" t="n">
+      <c r="I25" s="41" t="n">
         <v>600</v>
       </c>
-      <c r="J25" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="45" t="n">
+      <c r="J25" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="43" t="n">
         <v>-600</v>
       </c>
     </row>
@@ -17402,22 +17063,22 @@
       <c r="H26" s="16" t="n">
         <v>12530.47</v>
       </c>
-      <c r="I26" s="43" t="n">
+      <c r="I26" s="41" t="n">
         <v>660</v>
       </c>
-      <c r="J26" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="45" t="n">
+      <c r="J26" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="43" t="n">
         <v>-660</v>
       </c>
     </row>
@@ -17450,22 +17111,22 @@
       <c r="H27" s="16" t="n">
         <v>1034</v>
       </c>
-      <c r="I27" s="43" t="n">
+      <c r="I27" s="41" t="n">
         <v>710</v>
       </c>
-      <c r="J27" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="45" t="n">
+      <c r="J27" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="43" t="n">
         <v>-710</v>
       </c>
     </row>
@@ -17498,22 +17159,22 @@
       <c r="H28" s="16" t="n">
         <v>11629.68</v>
       </c>
-      <c r="I28" s="43" t="n">
+      <c r="I28" s="41" t="n">
         <v>740</v>
       </c>
-      <c r="J28" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" s="45" t="n">
+      <c r="J28" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="43" t="n">
         <v>-740</v>
       </c>
     </row>
@@ -17546,22 +17207,22 @@
       <c r="H29" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="I29" s="43" t="n">
+      <c r="I29" s="41" t="n">
         <v>740</v>
       </c>
-      <c r="J29" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="45" t="n">
+      <c r="J29" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="43" t="n">
         <v>-740</v>
       </c>
     </row>
@@ -17571,23 +17232,23 @@
           <t>4-MONTH TOTAL (all 6 agents)</t>
         </is>
       </c>
-      <c r="B30" s="41" t="n"/>
-      <c r="C30" s="41" t="n"/>
-      <c r="D30" s="41" t="n"/>
-      <c r="E30" s="41" t="n"/>
-      <c r="F30" s="41" t="n"/>
-      <c r="G30" s="41" t="n"/>
-      <c r="H30" s="41" t="n"/>
-      <c r="I30" s="46" t="n">
+      <c r="B30" s="39" t="n"/>
+      <c r="C30" s="39" t="n"/>
+      <c r="D30" s="39" t="n"/>
+      <c r="E30" s="39" t="n"/>
+      <c r="F30" s="39" t="n"/>
+      <c r="G30" s="39" t="n"/>
+      <c r="H30" s="39" t="n"/>
+      <c r="I30" s="44" t="n">
         <v>12220</v>
       </c>
-      <c r="J30" s="41" t="n"/>
-      <c r="K30" s="41" t="n"/>
-      <c r="L30" s="41" t="n"/>
-      <c r="M30" s="47" t="n">
+      <c r="J30" s="39" t="n"/>
+      <c r="K30" s="39" t="n"/>
+      <c r="L30" s="39" t="n"/>
+      <c r="M30" s="45" t="n">
         <v>1675</v>
       </c>
-      <c r="N30" s="45" t="n">
+      <c r="N30" s="43" t="n">
         <v>-10545</v>
       </c>
     </row>
@@ -17699,23 +17360,23 @@
       <c r="H34" s="16" t="n">
         <v>51657.715</v>
       </c>
-      <c r="I34" s="43" t="n">
+      <c r="I34" s="41" t="n">
         <v>500</v>
       </c>
-      <c r="J34" s="36" t="n">
+      <c r="J34" s="34" t="n">
         <v>250</v>
       </c>
-      <c r="K34" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="36" t="n">
-        <v>850</v>
-      </c>
-      <c r="M34" s="44" t="n">
-        <v>1100</v>
-      </c>
-      <c r="N34" s="44" t="n">
+      <c r="K34" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="M34" s="42" t="n">
         <v>600</v>
+      </c>
+      <c r="N34" s="42" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
@@ -17747,221 +17408,221 @@
       <c r="H35" s="16" t="n">
         <v>54076.675</v>
       </c>
-      <c r="I35" s="43" t="n">
+      <c r="I35" s="41" t="n">
         <v>680</v>
       </c>
-      <c r="J35" s="36" t="n">
+      <c r="J35" s="34" t="n">
         <v>250</v>
       </c>
-      <c r="K35" s="36" t="n">
+      <c r="K35" s="34" t="n">
         <v>100</v>
       </c>
-      <c r="L35" s="36" t="n">
-        <v>850</v>
-      </c>
-      <c r="M35" s="44" t="n">
-        <v>1200</v>
-      </c>
-      <c r="N35" s="44" t="n">
-        <v>520</v>
+      <c r="L35" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="M35" s="42" t="n">
+        <v>700</v>
+      </c>
+      <c r="N35" s="42" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="25" t="inlineStr">
         <is>
-          <t>Dialinerys Dieguez</t>
+          <t>Abel Guaina</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>January</t>
+          <t>February</t>
         </is>
       </c>
       <c r="C36" s="15" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D36" s="16" t="n">
-        <v>40249.26</v>
+        <v>25367</v>
       </c>
       <c r="E36" s="15" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="F36" s="16" t="n">
-        <v>32837.69</v>
+        <v>15321.5</v>
       </c>
       <c r="G36" s="15" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H36" s="16" t="n">
-        <v>45368.16</v>
-      </c>
-      <c r="I36" s="43" t="n">
-        <v>350</v>
-      </c>
-      <c r="J36" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="36" t="n">
-        <v>850</v>
-      </c>
-      <c r="M36" s="44" t="n">
-        <v>850</v>
-      </c>
-      <c r="N36" s="44" t="n">
-        <v>500</v>
+        <v>22838.5</v>
+      </c>
+      <c r="I36" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="25" t="inlineStr">
         <is>
-          <t>Melissa Hernandez</t>
+          <t>Dialinerys Dieguez</t>
         </is>
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>January</t>
         </is>
       </c>
       <c r="C37" s="15" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D37" s="16" t="n">
-        <v>7659.5</v>
+        <v>40249.26</v>
       </c>
       <c r="E37" s="15" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F37" s="16" t="n">
-        <v>24995.35</v>
+        <v>32837.69</v>
       </c>
       <c r="G37" s="15" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="H37" s="16" t="n">
-        <v>26058.35</v>
-      </c>
-      <c r="I37" s="43" t="n">
-        <v>250</v>
-      </c>
-      <c r="J37" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="36" t="n">
-        <v>750</v>
-      </c>
-      <c r="M37" s="44" t="n">
-        <v>750</v>
-      </c>
-      <c r="N37" s="44" t="n">
-        <v>500</v>
+        <v>45368.16</v>
+      </c>
+      <c r="I37" s="41" t="n">
+        <v>350</v>
+      </c>
+      <c r="J37" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="M37" s="42" t="n">
+        <v>350</v>
+      </c>
+      <c r="N37" s="46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="25" t="inlineStr">
         <is>
-          <t>Monica Valdes</t>
+          <t>Melissa Hernandez</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>January</t>
+          <t>February</t>
         </is>
       </c>
       <c r="C38" s="15" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D38" s="16" t="n">
-        <v>28605.29</v>
+        <v>7659.5</v>
       </c>
       <c r="E38" s="15" t="n">
         <v>19</v>
       </c>
       <c r="F38" s="16" t="n">
-        <v>24306.48</v>
+        <v>24995.35</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H38" s="16" t="n">
-        <v>30809.39</v>
-      </c>
-      <c r="I38" s="43" t="n">
-        <v>350</v>
-      </c>
-      <c r="J38" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="36" t="n">
-        <v>750</v>
-      </c>
-      <c r="M38" s="44" t="n">
-        <v>750</v>
-      </c>
-      <c r="N38" s="44" t="n">
-        <v>400</v>
+        <v>26058.35</v>
+      </c>
+      <c r="I38" s="41" t="n">
+        <v>250</v>
+      </c>
+      <c r="J38" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="M38" s="42" t="n">
+        <v>250</v>
+      </c>
+      <c r="N38" s="46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="25" t="inlineStr">
         <is>
-          <t>Monica Valdes</t>
+          <t>Thalia Rojas</t>
         </is>
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>January</t>
         </is>
       </c>
       <c r="C39" s="15" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D39" s="16" t="n">
-        <v>31516.95</v>
+        <v>15503.9</v>
       </c>
       <c r="E39" s="15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F39" s="16" t="n">
-        <v>23614.09</v>
+        <v>16541.965</v>
       </c>
       <c r="G39" s="15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H39" s="16" t="n">
-        <v>26706.09</v>
-      </c>
-      <c r="I39" s="43" t="n">
-        <v>350</v>
-      </c>
-      <c r="J39" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="36" t="n">
-        <v>750</v>
-      </c>
-      <c r="M39" s="44" t="n">
-        <v>750</v>
-      </c>
-      <c r="N39" s="44" t="n">
-        <v>400</v>
+        <v>20231.965</v>
+      </c>
+      <c r="I39" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="25" t="inlineStr">
         <is>
-          <t>Dialinerys Dieguez</t>
+          <t>Thalia Rojas</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
@@ -17970,46 +17631,46 @@
         </is>
       </c>
       <c r="C40" s="15" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D40" s="16" t="n">
-        <v>30057.89</v>
+        <v>19414.25</v>
       </c>
       <c r="E40" s="15" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F40" s="16" t="n">
-        <v>42772.3</v>
+        <v>14149.08</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="H40" s="16" t="n">
-        <v>54401.98</v>
-      </c>
-      <c r="I40" s="43" t="n">
-        <v>460</v>
-      </c>
-      <c r="J40" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="36" t="n">
-        <v>850</v>
-      </c>
-      <c r="M40" s="44" t="n">
-        <v>850</v>
-      </c>
-      <c r="N40" s="44" t="n">
-        <v>390</v>
+        <v>21595.08</v>
+      </c>
+      <c r="I40" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="25" t="inlineStr">
         <is>
-          <t>Melissa Hernandez</t>
+          <t>Thalia Rojas</t>
         </is>
       </c>
       <c r="B41" s="14" t="inlineStr">
@@ -18018,334 +17679,334 @@
         </is>
       </c>
       <c r="C41" s="15" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D41" s="16" t="n">
-        <v>39759.7</v>
+        <v>17843.69</v>
       </c>
       <c r="E41" s="15" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="F41" s="16" t="n">
-        <v>28430.3</v>
+        <v>9920.424999999999</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H41" s="16" t="n">
-        <v>29464.3</v>
-      </c>
-      <c r="I41" s="43" t="n">
-        <v>470</v>
-      </c>
-      <c r="J41" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="36" t="n">
-        <v>750</v>
-      </c>
-      <c r="M41" s="44" t="n">
-        <v>750</v>
-      </c>
-      <c r="N41" s="44" t="n">
-        <v>280</v>
+        <v>15564.325</v>
+      </c>
+      <c r="I41" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="25" t="inlineStr">
         <is>
-          <t>Melissa Hernandez</t>
+          <t>Thalia Rojas</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>January</t>
+          <t>April</t>
         </is>
       </c>
       <c r="C42" s="15" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="D42" s="16" t="n">
-        <v>37039</v>
+        <v>14099</v>
       </c>
       <c r="E42" s="15" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F42" s="16" t="n">
-        <v>31687.25</v>
+        <v>19897.2</v>
       </c>
       <c r="G42" s="15" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H42" s="16" t="n">
-        <v>31687.25</v>
-      </c>
-      <c r="I42" s="43" t="n">
-        <v>500</v>
-      </c>
-      <c r="J42" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="36" t="n">
-        <v>750</v>
-      </c>
-      <c r="M42" s="44" t="n">
-        <v>750</v>
-      </c>
-      <c r="N42" s="44" t="n">
-        <v>250</v>
+        <v>23514.2</v>
+      </c>
+      <c r="I42" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="25" t="inlineStr">
         <is>
-          <t>Abel Guaina</t>
+          <t>Monica Valdes</t>
         </is>
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>March</t>
         </is>
       </c>
       <c r="C43" s="15" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="D43" s="16" t="n">
-        <v>25367</v>
+        <v>68546.22</v>
       </c>
       <c r="E43" s="15" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F43" s="16" t="n">
-        <v>15321.5</v>
+        <v>19627.325</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H43" s="16" t="n">
-        <v>22838.5</v>
-      </c>
-      <c r="I43" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" s="48" t="n">
-        <v>0</v>
+        <v>19627.325</v>
+      </c>
+      <c r="I43" s="41" t="n">
+        <v>450</v>
+      </c>
+      <c r="J43" s="34" t="n">
+        <v>375</v>
+      </c>
+      <c r="K43" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="42" t="n">
+        <v>375</v>
+      </c>
+      <c r="N43" s="43" t="n">
+        <v>-75</v>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="25" t="inlineStr">
         <is>
-          <t>Thalia Rojas</t>
+          <t>Abel Guaina</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>January</t>
+          <t>March</t>
         </is>
       </c>
       <c r="C44" s="15" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D44" s="16" t="n">
-        <v>15503.9</v>
+        <v>46523.37</v>
       </c>
       <c r="E44" s="15" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F44" s="16" t="n">
-        <v>16541.965</v>
+        <v>12613.8</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H44" s="16" t="n">
-        <v>20231.965</v>
-      </c>
-      <c r="I44" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="48" t="n">
-        <v>0</v>
+        <v>16514.8</v>
+      </c>
+      <c r="I44" s="41" t="n">
+        <v>350</v>
+      </c>
+      <c r="J44" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="K44" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="42" t="n">
+        <v>250</v>
+      </c>
+      <c r="N44" s="43" t="n">
+        <v>-100</v>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="25" t="inlineStr">
         <is>
-          <t>Thalia Rojas</t>
+          <t>Monica Valdes</t>
         </is>
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>January</t>
         </is>
       </c>
       <c r="C45" s="15" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D45" s="16" t="n">
-        <v>19414.25</v>
+        <v>28605.29</v>
       </c>
       <c r="E45" s="15" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F45" s="16" t="n">
-        <v>14149.08</v>
+        <v>24306.48</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H45" s="16" t="n">
-        <v>21595.08</v>
-      </c>
-      <c r="I45" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" s="48" t="n">
-        <v>0</v>
+        <v>30809.39</v>
+      </c>
+      <c r="I45" s="41" t="n">
+        <v>350</v>
+      </c>
+      <c r="J45" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="M45" s="42" t="n">
+        <v>250</v>
+      </c>
+      <c r="N45" s="43" t="n">
+        <v>-100</v>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="25" t="inlineStr">
         <is>
-          <t>Thalia Rojas</t>
+          <t>Monica Valdes</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>March</t>
+          <t>February</t>
         </is>
       </c>
       <c r="C46" s="15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D46" s="16" t="n">
-        <v>17843.69</v>
+        <v>31516.95</v>
       </c>
       <c r="E46" s="15" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F46" s="16" t="n">
-        <v>9920.424999999999</v>
+        <v>23614.09</v>
       </c>
       <c r="G46" s="15" t="n">
         <v>16</v>
       </c>
       <c r="H46" s="16" t="n">
-        <v>15564.325</v>
-      </c>
-      <c r="I46" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="48" t="n">
-        <v>0</v>
+        <v>26706.09</v>
+      </c>
+      <c r="I46" s="41" t="n">
+        <v>350</v>
+      </c>
+      <c r="J46" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="M46" s="42" t="n">
+        <v>250</v>
+      </c>
+      <c r="N46" s="43" t="n">
+        <v>-100</v>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="25" t="inlineStr">
         <is>
-          <t>Thalia Rojas</t>
+          <t>Dialinerys Dieguez</t>
         </is>
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>February</t>
         </is>
       </c>
       <c r="C47" s="15" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D47" s="16" t="n">
-        <v>14099</v>
+        <v>30057.89</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F47" s="16" t="n">
-        <v>19897.2</v>
+        <v>42772.3</v>
       </c>
       <c r="G47" s="15" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="H47" s="16" t="n">
-        <v>23514.2</v>
-      </c>
-      <c r="I47" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" s="48" t="n">
-        <v>0</v>
+        <v>54401.98</v>
+      </c>
+      <c r="I47" s="41" t="n">
+        <v>460</v>
+      </c>
+      <c r="J47" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="M47" s="42" t="n">
+        <v>350</v>
+      </c>
+      <c r="N47" s="43" t="n">
+        <v>-110</v>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="25" t="inlineStr">
         <is>
-          <t>Monica Valdes</t>
+          <t>Melissa Hernandez</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
@@ -18354,40 +18015,40 @@
         </is>
       </c>
       <c r="C48" s="15" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D48" s="16" t="n">
-        <v>68546.22</v>
+        <v>39759.7</v>
       </c>
       <c r="E48" s="15" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F48" s="16" t="n">
-        <v>19627.325</v>
+        <v>28430.3</v>
       </c>
       <c r="G48" s="15" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H48" s="16" t="n">
-        <v>19627.325</v>
-      </c>
-      <c r="I48" s="43" t="n">
-        <v>450</v>
-      </c>
-      <c r="J48" s="36" t="n">
-        <v>375</v>
-      </c>
-      <c r="K48" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" s="44" t="n">
-        <v>375</v>
-      </c>
-      <c r="N48" s="45" t="n">
-        <v>-75</v>
+        <v>29464.3</v>
+      </c>
+      <c r="I48" s="41" t="n">
+        <v>470</v>
+      </c>
+      <c r="J48" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="M48" s="42" t="n">
+        <v>250</v>
+      </c>
+      <c r="N48" s="43" t="n">
+        <v>-220</v>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
@@ -18398,44 +18059,44 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>March</t>
+          <t>January</t>
         </is>
       </c>
       <c r="C49" s="15" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D49" s="16" t="n">
-        <v>46523.37</v>
+        <v>38611.42</v>
       </c>
       <c r="E49" s="15" t="n">
         <v>9</v>
       </c>
       <c r="F49" s="16" t="n">
-        <v>12613.8</v>
+        <v>13759.25</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H49" s="16" t="n">
-        <v>16514.8</v>
-      </c>
-      <c r="I49" s="43" t="n">
-        <v>350</v>
-      </c>
-      <c r="J49" s="36" t="n">
+        <v>21364.25</v>
+      </c>
+      <c r="I49" s="41" t="n">
         <v>250</v>
       </c>
-      <c r="K49" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" s="44" t="n">
-        <v>250</v>
-      </c>
-      <c r="N49" s="45" t="n">
-        <v>-100</v>
+      <c r="J49" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="43" t="n">
+        <v>-250</v>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
@@ -18446,91 +18107,91 @@
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>January</t>
+          <t>April</t>
         </is>
       </c>
       <c r="C50" s="15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D50" s="16" t="n">
-        <v>38611.42</v>
+        <v>37825.93</v>
       </c>
       <c r="E50" s="15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F50" s="16" t="n">
-        <v>13759.25</v>
+        <v>7680.975</v>
       </c>
       <c r="G50" s="15" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H50" s="16" t="n">
-        <v>21364.25</v>
-      </c>
-      <c r="I50" s="43" t="n">
+        <v>18616.965</v>
+      </c>
+      <c r="I50" s="41" t="n">
         <v>250</v>
       </c>
-      <c r="J50" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="45" t="n">
+      <c r="J50" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="43" t="n">
         <v>-250</v>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="25" t="inlineStr">
         <is>
-          <t>Abel Guaina</t>
+          <t>Melissa Hernandez</t>
         </is>
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>January</t>
         </is>
       </c>
       <c r="C51" s="15" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D51" s="16" t="n">
-        <v>37825.93</v>
+        <v>37039</v>
       </c>
       <c r="E51" s="15" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="F51" s="16" t="n">
-        <v>7680.975</v>
+        <v>31687.25</v>
       </c>
       <c r="G51" s="15" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H51" s="16" t="n">
-        <v>18616.965</v>
-      </c>
-      <c r="I51" s="43" t="n">
+        <v>31687.25</v>
+      </c>
+      <c r="I51" s="41" t="n">
+        <v>500</v>
+      </c>
+      <c r="J51" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="34" t="n">
         <v>250</v>
       </c>
-      <c r="J51" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" s="45" t="n">
+      <c r="M51" s="42" t="n">
+        <v>250</v>
+      </c>
+      <c r="N51" s="43" t="n">
         <v>-250</v>
       </c>
     </row>
@@ -18563,22 +18224,22 @@
       <c r="H52" s="16" t="n">
         <v>21698.1</v>
       </c>
-      <c r="I52" s="43" t="n">
+      <c r="I52" s="41" t="n">
         <v>250</v>
       </c>
-      <c r="J52" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" s="45" t="n">
+      <c r="J52" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="43" t="n">
         <v>-250</v>
       </c>
     </row>
@@ -18611,22 +18272,22 @@
       <c r="H53" s="16" t="n">
         <v>20153.95</v>
       </c>
-      <c r="I53" s="43" t="n">
+      <c r="I53" s="41" t="n">
         <v>250</v>
       </c>
-      <c r="J53" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" s="45" t="n">
+      <c r="J53" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="43" t="n">
         <v>-250</v>
       </c>
     </row>
@@ -18659,22 +18320,22 @@
       <c r="H54" s="16" t="n">
         <v>21243.375</v>
       </c>
-      <c r="I54" s="43" t="n">
+      <c r="I54" s="41" t="n">
         <v>350</v>
       </c>
-      <c r="J54" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="45" t="n">
+      <c r="J54" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="43" t="n">
         <v>-350</v>
       </c>
     </row>
@@ -18707,22 +18368,22 @@
       <c r="H55" s="16" t="n">
         <v>23942.725</v>
       </c>
-      <c r="I55" s="43" t="n">
+      <c r="I55" s="41" t="n">
         <v>350</v>
       </c>
-      <c r="J55" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" s="45" t="n">
+      <c r="J55" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="43" t="n">
         <v>-350</v>
       </c>
     </row>
@@ -18755,22 +18416,22 @@
       <c r="H56" s="16" t="n">
         <v>11763.35</v>
       </c>
-      <c r="I56" s="43" t="n">
+      <c r="I56" s="41" t="n">
         <v>350</v>
       </c>
-      <c r="J56" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" s="45" t="n">
+      <c r="J56" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="43" t="n">
         <v>-350</v>
       </c>
     </row>
@@ -18803,22 +18464,22 @@
       <c r="H57" s="16" t="n">
         <v>16301.38</v>
       </c>
-      <c r="I57" s="43" t="n">
+      <c r="I57" s="41" t="n">
         <v>350</v>
       </c>
-      <c r="J57" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" s="45" t="n">
+      <c r="J57" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="43" t="n">
         <v>-350</v>
       </c>
     </row>
@@ -18828,24 +18489,24 @@
           <t>4-MONTH TOTAL (all 6 agents)</t>
         </is>
       </c>
-      <c r="B58" s="41" t="n"/>
-      <c r="C58" s="41" t="n"/>
-      <c r="D58" s="41" t="n"/>
-      <c r="E58" s="41" t="n"/>
-      <c r="F58" s="41" t="n"/>
-      <c r="G58" s="41" t="n"/>
-      <c r="H58" s="41" t="n"/>
-      <c r="I58" s="46" t="n">
+      <c r="B58" s="39" t="n"/>
+      <c r="C58" s="39" t="n"/>
+      <c r="D58" s="39" t="n"/>
+      <c r="E58" s="39" t="n"/>
+      <c r="F58" s="39" t="n"/>
+      <c r="G58" s="39" t="n"/>
+      <c r="H58" s="39" t="n"/>
+      <c r="I58" s="44" t="n">
         <v>7110</v>
       </c>
-      <c r="J58" s="41" t="n"/>
-      <c r="K58" s="41" t="n"/>
-      <c r="L58" s="41" t="n"/>
-      <c r="M58" s="47" t="n">
-        <v>8375</v>
-      </c>
-      <c r="N58" s="44" t="n">
-        <v>1265</v>
+      <c r="J58" s="39" t="n"/>
+      <c r="K58" s="39" t="n"/>
+      <c r="L58" s="39" t="n"/>
+      <c r="M58" s="45" t="n">
+        <v>3875</v>
+      </c>
+      <c r="N58" s="43" t="n">
+        <v>-3235</v>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1">
@@ -18956,23 +18617,23 @@
       <c r="H62" s="16" t="n">
         <v>96228.35000000001</v>
       </c>
-      <c r="I62" s="43" t="n">
+      <c r="I62" s="41" t="n">
         <v>350</v>
       </c>
-      <c r="J62" s="36" t="n">
+      <c r="J62" s="34" t="n">
         <v>250</v>
       </c>
-      <c r="K62" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" s="36" t="n">
-        <v>1050</v>
-      </c>
-      <c r="M62" s="44" t="n">
-        <v>1300</v>
-      </c>
-      <c r="N62" s="44" t="n">
-        <v>950</v>
+      <c r="K62" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="34" t="n">
+        <v>550</v>
+      </c>
+      <c r="M62" s="42" t="n">
+        <v>800</v>
+      </c>
+      <c r="N62" s="42" t="n">
+        <v>450</v>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1">
@@ -19004,23 +18665,23 @@
       <c r="H63" s="16" t="n">
         <v>49990.7</v>
       </c>
-      <c r="I63" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" s="36" t="n">
-        <v>850</v>
-      </c>
-      <c r="M63" s="44" t="n">
-        <v>850</v>
-      </c>
-      <c r="N63" s="44" t="n">
-        <v>850</v>
+      <c r="I63" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="M63" s="42" t="n">
+        <v>350</v>
+      </c>
+      <c r="N63" s="42" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
@@ -19052,23 +18713,23 @@
       <c r="H64" s="16" t="n">
         <v>56860.6</v>
       </c>
-      <c r="I64" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" s="36" t="n">
-        <v>850</v>
-      </c>
-      <c r="M64" s="44" t="n">
-        <v>850</v>
-      </c>
-      <c r="N64" s="44" t="n">
-        <v>850</v>
+      <c r="I64" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="M64" s="42" t="n">
+        <v>350</v>
+      </c>
+      <c r="N64" s="42" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1">
@@ -19100,23 +18761,23 @@
       <c r="H65" s="16" t="n">
         <v>43396.2</v>
       </c>
-      <c r="I65" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" s="36" t="n">
-        <v>850</v>
-      </c>
-      <c r="M65" s="44" t="n">
-        <v>850</v>
-      </c>
-      <c r="N65" s="44" t="n">
-        <v>850</v>
+      <c r="I65" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="M65" s="42" t="n">
+        <v>350</v>
+      </c>
+      <c r="N65" s="42" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
@@ -19148,23 +18809,23 @@
       <c r="H66" s="16" t="n">
         <v>43687.45</v>
       </c>
-      <c r="I66" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="36" t="n">
-        <v>850</v>
-      </c>
-      <c r="M66" s="44" t="n">
-        <v>850</v>
-      </c>
-      <c r="N66" s="44" t="n">
-        <v>850</v>
+      <c r="I66" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="M66" s="42" t="n">
+        <v>350</v>
+      </c>
+      <c r="N66" s="42" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1">
@@ -19196,23 +18857,23 @@
       <c r="H67" s="16" t="n">
         <v>48612.96</v>
       </c>
-      <c r="I67" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" s="36" t="n">
-        <v>850</v>
-      </c>
-      <c r="M67" s="44" t="n">
-        <v>850</v>
-      </c>
-      <c r="N67" s="44" t="n">
-        <v>850</v>
+      <c r="I67" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="M67" s="42" t="n">
+        <v>350</v>
+      </c>
+      <c r="N67" s="42" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1">
@@ -19244,23 +18905,23 @@
       <c r="H68" s="16" t="n">
         <v>47228.18</v>
       </c>
-      <c r="I68" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" s="36" t="n">
-        <v>850</v>
-      </c>
-      <c r="M68" s="44" t="n">
-        <v>850</v>
-      </c>
-      <c r="N68" s="44" t="n">
-        <v>850</v>
+      <c r="I68" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="M68" s="42" t="n">
+        <v>350</v>
+      </c>
+      <c r="N68" s="42" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1">
@@ -19292,23 +18953,23 @@
       <c r="H69" s="16" t="n">
         <v>85544.60000000001</v>
       </c>
-      <c r="I69" s="43" t="n">
+      <c r="I69" s="41" t="n">
         <v>250</v>
       </c>
-      <c r="J69" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" s="36" t="n">
-        <v>1050</v>
-      </c>
-      <c r="M69" s="44" t="n">
-        <v>1050</v>
-      </c>
-      <c r="N69" s="44" t="n">
-        <v>800</v>
+      <c r="J69" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" s="34" t="n">
+        <v>550</v>
+      </c>
+      <c r="M69" s="42" t="n">
+        <v>550</v>
+      </c>
+      <c r="N69" s="42" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1">
@@ -19340,23 +19001,23 @@
       <c r="H70" s="16" t="n">
         <v>39254.65</v>
       </c>
-      <c r="I70" s="43" t="n">
+      <c r="I70" s="41" t="n">
         <v>350</v>
       </c>
-      <c r="J70" s="36" t="n">
+      <c r="J70" s="34" t="n">
         <v>375</v>
       </c>
-      <c r="K70" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" s="36" t="n">
-        <v>750</v>
-      </c>
-      <c r="M70" s="44" t="n">
-        <v>1125</v>
-      </c>
-      <c r="N70" s="44" t="n">
-        <v>775</v>
+      <c r="K70" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="M70" s="42" t="n">
+        <v>625</v>
+      </c>
+      <c r="N70" s="42" t="n">
+        <v>275</v>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1">
@@ -19388,23 +19049,23 @@
       <c r="H71" s="16" t="n">
         <v>30643</v>
       </c>
-      <c r="I71" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="36" t="n">
-        <v>750</v>
-      </c>
-      <c r="M71" s="44" t="n">
-        <v>750</v>
-      </c>
-      <c r="N71" s="44" t="n">
-        <v>750</v>
+      <c r="I71" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="M71" s="42" t="n">
+        <v>250</v>
+      </c>
+      <c r="N71" s="42" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1">
@@ -19436,23 +19097,23 @@
       <c r="H72" s="16" t="n">
         <v>64165.43</v>
       </c>
-      <c r="I72" s="43" t="n">
+      <c r="I72" s="41" t="n">
         <v>350</v>
       </c>
-      <c r="J72" s="36" t="n">
+      <c r="J72" s="34" t="n">
         <v>250</v>
       </c>
-      <c r="K72" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" s="36" t="n">
-        <v>850</v>
-      </c>
-      <c r="M72" s="44" t="n">
-        <v>1100</v>
-      </c>
-      <c r="N72" s="44" t="n">
-        <v>750</v>
+      <c r="K72" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="M72" s="42" t="n">
+        <v>600</v>
+      </c>
+      <c r="N72" s="42" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1">
@@ -19484,23 +19145,23 @@
       <c r="H73" s="16" t="n">
         <v>39558.05</v>
       </c>
-      <c r="I73" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" s="36" t="n">
-        <v>750</v>
-      </c>
-      <c r="M73" s="44" t="n">
-        <v>750</v>
-      </c>
-      <c r="N73" s="44" t="n">
-        <v>750</v>
+      <c r="I73" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="M73" s="42" t="n">
+        <v>250</v>
+      </c>
+      <c r="N73" s="42" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1">
@@ -19532,23 +19193,23 @@
       <c r="H74" s="16" t="n">
         <v>30832.76</v>
       </c>
-      <c r="I74" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="36" t="n">
-        <v>750</v>
-      </c>
-      <c r="M74" s="44" t="n">
-        <v>750</v>
-      </c>
-      <c r="N74" s="44" t="n">
-        <v>750</v>
+      <c r="I74" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="M74" s="42" t="n">
+        <v>250</v>
+      </c>
+      <c r="N74" s="42" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1">
@@ -19580,23 +19241,23 @@
       <c r="H75" s="16" t="n">
         <v>33083.93</v>
       </c>
-      <c r="I75" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="36" t="n">
-        <v>750</v>
-      </c>
-      <c r="M75" s="44" t="n">
-        <v>750</v>
-      </c>
-      <c r="N75" s="44" t="n">
-        <v>750</v>
+      <c r="I75" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="M75" s="42" t="n">
+        <v>250</v>
+      </c>
+      <c r="N75" s="42" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1">
@@ -19628,23 +19289,23 @@
       <c r="H76" s="16" t="n">
         <v>28298.16</v>
       </c>
-      <c r="I76" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" s="36" t="n">
-        <v>750</v>
-      </c>
-      <c r="M76" s="44" t="n">
-        <v>750</v>
-      </c>
-      <c r="N76" s="44" t="n">
-        <v>750</v>
+      <c r="I76" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="M76" s="42" t="n">
+        <v>250</v>
+      </c>
+      <c r="N76" s="42" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1">
@@ -19676,23 +19337,23 @@
       <c r="H77" s="16" t="n">
         <v>39794.4</v>
       </c>
-      <c r="I77" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" s="36" t="n">
-        <v>750</v>
-      </c>
-      <c r="M77" s="44" t="n">
-        <v>750</v>
-      </c>
-      <c r="N77" s="44" t="n">
-        <v>750</v>
+      <c r="I77" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="M77" s="42" t="n">
+        <v>250</v>
+      </c>
+      <c r="N77" s="42" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1">
@@ -19724,23 +19385,23 @@
       <c r="H78" s="16" t="n">
         <v>35279.9</v>
       </c>
-      <c r="I78" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" s="36" t="n">
-        <v>750</v>
-      </c>
-      <c r="M78" s="44" t="n">
-        <v>750</v>
-      </c>
-      <c r="N78" s="44" t="n">
-        <v>750</v>
+      <c r="I78" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="M78" s="42" t="n">
+        <v>250</v>
+      </c>
+      <c r="N78" s="42" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="79" ht="22" customHeight="1">
@@ -19772,23 +19433,23 @@
       <c r="H79" s="16" t="n">
         <v>65675.38</v>
       </c>
-      <c r="I79" s="43" t="n">
+      <c r="I79" s="41" t="n">
         <v>250</v>
       </c>
-      <c r="J79" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" s="36" t="n">
-        <v>950</v>
-      </c>
-      <c r="M79" s="44" t="n">
-        <v>950</v>
-      </c>
-      <c r="N79" s="44" t="n">
-        <v>700</v>
+      <c r="J79" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="34" t="n">
+        <v>450</v>
+      </c>
+      <c r="M79" s="42" t="n">
+        <v>450</v>
+      </c>
+      <c r="N79" s="42" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1">
@@ -19820,23 +19481,23 @@
       <c r="H80" s="16" t="n">
         <v>25227.6</v>
       </c>
-      <c r="I80" s="43" t="n">
+      <c r="I80" s="41" t="n">
         <v>350</v>
       </c>
-      <c r="J80" s="36" t="n">
+      <c r="J80" s="34" t="n">
         <v>250</v>
       </c>
-      <c r="K80" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" s="36" t="n">
-        <v>750</v>
-      </c>
-      <c r="M80" s="44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="N80" s="44" t="n">
-        <v>650</v>
+      <c r="K80" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="M80" s="42" t="n">
+        <v>500</v>
+      </c>
+      <c r="N80" s="42" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1">
@@ -19868,23 +19529,23 @@
       <c r="H81" s="16" t="n">
         <v>63374.5</v>
       </c>
-      <c r="I81" s="43" t="n">
+      <c r="I81" s="41" t="n">
         <v>250</v>
       </c>
-      <c r="J81" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" s="36" t="n">
-        <v>850</v>
-      </c>
-      <c r="M81" s="44" t="n">
-        <v>850</v>
-      </c>
-      <c r="N81" s="44" t="n">
-        <v>600</v>
+      <c r="J81" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="M81" s="42" t="n">
+        <v>350</v>
+      </c>
+      <c r="N81" s="42" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1">
@@ -19916,23 +19577,23 @@
       <c r="H82" s="16" t="n">
         <v>27518.5</v>
       </c>
-      <c r="I82" s="43" t="n">
+      <c r="I82" s="41" t="n">
         <v>250</v>
       </c>
-      <c r="J82" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="36" t="n">
-        <v>750</v>
-      </c>
-      <c r="M82" s="44" t="n">
-        <v>750</v>
-      </c>
-      <c r="N82" s="44" t="n">
-        <v>500</v>
+      <c r="J82" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="M82" s="42" t="n">
+        <v>250</v>
+      </c>
+      <c r="N82" s="46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83" ht="22" customHeight="1">
@@ -19964,22 +19625,22 @@
       <c r="H83" s="16" t="n">
         <v>23526.7</v>
       </c>
-      <c r="I83" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N83" s="48" t="n">
+      <c r="I83" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" s="46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -20012,22 +19673,22 @@
       <c r="H84" s="16" t="n">
         <v>19840.85</v>
       </c>
-      <c r="I84" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" s="48" t="n">
+      <c r="I84" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -20060,22 +19721,22 @@
       <c r="H85" s="16" t="n">
         <v>15361.95</v>
       </c>
-      <c r="I85" s="43" t="n">
+      <c r="I85" s="41" t="n">
         <v>350</v>
       </c>
-      <c r="J85" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" s="45" t="n">
+      <c r="J85" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" s="43" t="n">
         <v>-350</v>
       </c>
     </row>
@@ -20085,24 +19746,24 @@
           <t>4-MONTH TOTAL (all 6 agents)</t>
         </is>
       </c>
-      <c r="B86" s="41" t="n"/>
-      <c r="C86" s="41" t="n"/>
-      <c r="D86" s="41" t="n"/>
-      <c r="E86" s="41" t="n"/>
-      <c r="F86" s="41" t="n"/>
-      <c r="G86" s="41" t="n"/>
-      <c r="H86" s="41" t="n"/>
-      <c r="I86" s="46" t="n">
+      <c r="B86" s="39" t="n"/>
+      <c r="C86" s="39" t="n"/>
+      <c r="D86" s="39" t="n"/>
+      <c r="E86" s="39" t="n"/>
+      <c r="F86" s="39" t="n"/>
+      <c r="G86" s="39" t="n"/>
+      <c r="H86" s="39" t="n"/>
+      <c r="I86" s="44" t="n">
         <v>2750</v>
       </c>
-      <c r="J86" s="41" t="n"/>
-      <c r="K86" s="41" t="n"/>
-      <c r="L86" s="41" t="n"/>
-      <c r="M86" s="47" t="n">
-        <v>18475</v>
-      </c>
-      <c r="N86" s="44" t="n">
-        <v>15725</v>
+      <c r="J86" s="39" t="n"/>
+      <c r="K86" s="39" t="n"/>
+      <c r="L86" s="39" t="n"/>
+      <c r="M86" s="45" t="n">
+        <v>7975</v>
+      </c>
+      <c r="N86" s="42" t="n">
+        <v>5225</v>
       </c>
     </row>
   </sheetData>
@@ -20224,37 +19885,37 @@
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="49" t="inlineStr">
+      <c r="A6" s="47" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="49" t="inlineStr">
+      <c r="B6" s="47" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="C6" s="49" t="inlineStr">
+      <c r="C6" s="47" t="inlineStr">
         <is>
           <t>Verify premium, collected, PIF, coverages</t>
         </is>
       </c>
-      <c r="D6" s="49" t="inlineStr">
+      <c r="D6" s="47" t="inlineStr">
         <is>
           <t>Before payroll</t>
         </is>
       </c>
-      <c r="E6" s="49" t="inlineStr">
+      <c r="E6" s="47" t="inlineStr">
         <is>
           <t>Receipts, dec page, MVR, carrier proof</t>
         </is>
       </c>
-      <c r="F6" s="49" t="inlineStr">
+      <c r="F6" s="47" t="inlineStr">
         <is>
           <t>Approved or denied</t>
         </is>
       </c>
-      <c r="G6" s="49" t="inlineStr">
+      <c r="G6" s="47" t="inlineStr">
         <is>
           <t>BI/UM proof attached</t>
         </is>
@@ -20298,37 +19959,37 @@
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="49" t="inlineStr">
+      <c r="A8" s="47" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="49" t="inlineStr">
+      <c r="B8" s="47" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="C8" s="49" t="inlineStr">
+      <c r="C8" s="47" t="inlineStr">
         <is>
           <t>Review policy 90 days after effective</t>
         </is>
       </c>
-      <c r="D8" s="49" t="inlineStr">
+      <c r="D8" s="47" t="inlineStr">
         <is>
           <t>Month 3</t>
         </is>
       </c>
-      <c r="E8" s="49" t="inlineStr">
+      <c r="E8" s="47" t="inlineStr">
         <is>
           <t>Carrier status, cancel/rewrite report</t>
         </is>
       </c>
-      <c r="F8" s="49" t="inlineStr">
+      <c r="F8" s="47" t="inlineStr">
         <is>
           <t>Keep or chargeback</t>
         </is>
       </c>
-      <c r="G8" s="49" t="inlineStr">
+      <c r="G8" s="47" t="inlineStr">
         <is>
           <t>Jan 12 reviewed Apr 12</t>
         </is>
@@ -20372,37 +20033,37 @@
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="49" t="inlineStr">
+      <c r="A10" s="47" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B10" s="49" t="inlineStr">
+      <c r="B10" s="47" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="C10" s="49" t="inlineStr">
+      <c r="C10" s="47" t="inlineStr">
         <is>
           <t>Document exception if ownership approves</t>
         </is>
       </c>
-      <c r="D10" s="49" t="inlineStr">
+      <c r="D10" s="47" t="inlineStr">
         <is>
           <t>As needed</t>
         </is>
       </c>
-      <c r="E10" s="49" t="inlineStr">
+      <c r="E10" s="47" t="inlineStr">
         <is>
           <t>Written approval</t>
         </is>
       </c>
-      <c r="F10" s="49" t="inlineStr">
+      <c r="F10" s="47" t="inlineStr">
         <is>
           <t>Exception logged</t>
         </is>
       </c>
-      <c r="G10" s="49" t="inlineStr">
+      <c r="G10" s="47" t="inlineStr">
         <is>
           <t>Carrier error fix</t>
         </is>
